--- a/languages/de/output/import/德语B1.xlsx
+++ b/languages/de/output/import/德语B1.xlsx
@@ -435,7 +435,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>[ɡeːlœst] 溶解物；溶质〈adj.〉</t>
+          <t>[ɡeːlœst] 解决的；轻松自在的；溶解的〈adj.〉</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -445,7 +445,7 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>溶解物；溶质</t>
+          <t>解决的；轻松自在的；溶解的</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>[leːp] 活的；生动的；精力充沛的〈n.〉</t>
+          <t>[leːp] 活；生活（口语词干）〈n.〉</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
-          <t>活的；生动的；精力充沛的</t>
+          <t>活；生活（口语词干）</t>
         </is>
       </c>
       <c r="E17" s="1" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B18" s="1" t="inlineStr">
         <is>
-          <t>[maːlə] 男人；雄性的〈n.〉</t>
+          <t>[maːlə] 次数；标记（复数）〈n.〉</t>
         </is>
       </c>
       <c r="C18" s="1" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="D18" s="1" t="inlineStr">
         <is>
-          <t>男人；雄性的</t>
+          <t>次数；标记（复数）</t>
         </is>
       </c>
       <c r="E18" s="1" t="inlineStr">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="B26" s="1" t="inlineStr">
         <is>
-          <t>[lɪnkə] 左翼的人；左派；左派的〈n.〉</t>
+          <t>[lɪnkə] 左翼人士；左派分子〈n.〉</t>
         </is>
       </c>
       <c r="C26" s="1" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
-          <t>左翼的人；左派；左派的</t>
+          <t>左翼人士；左派分子</t>
         </is>
       </c>
       <c r="E26" s="1" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="B34" s="1" t="inlineStr">
         <is>
-          <t>[fɛlən] 折缝；凶猛的〈n.〉</t>
+          <t>[fɛlən] 砍伐；裁决；砍伐树木〈n.〉</t>
         </is>
       </c>
       <c r="C34" s="1" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
-          <t>折缝；凶猛的</t>
+          <t>砍伐；裁决；砍伐树木</t>
         </is>
       </c>
       <c r="E34" s="1" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="B45" s="1" t="inlineStr">
         <is>
-          <t>[ʊnʃʊldɪɡə] 无罪的；不懂事的〈n.〉</t>
+          <t>[ʊnʃʊldɪɡə] 无辜者；清白的人〈n.〉</t>
         </is>
       </c>
       <c r="C45" s="1" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="D45" s="1" t="inlineStr">
         <is>
-          <t>无罪的；不懂事的</t>
+          <t>无辜者；清白的人</t>
         </is>
       </c>
       <c r="E45" s="1" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="B56" s="1" t="inlineStr">
         <is>
-          <t>[ʁiːzɪɡə] 获暴利的人；赚大钱〈adv.〉</t>
+          <t>[ʁiːzɪɡə] 巨大的；庞大的〈adv.〉</t>
         </is>
       </c>
       <c r="C56" s="1" t="inlineStr">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="D56" s="1" t="inlineStr">
         <is>
-          <t>获暴利的人；赚大钱</t>
+          <t>巨大的；庞大的</t>
         </is>
       </c>
       <c r="E56" s="1" t="inlineStr">
@@ -2707,7 +2707,7 @@
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>[ʁɛçnən] 算术；算术知识；算术的〈n.〉</t>
+          <t>[ʁɛçnən] 计算；算术〈n.〉</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="D72" s="1" t="inlineStr">
         <is>
-          <t>算术；算术知识；算术的</t>
+          <t>计算；算术</t>
         </is>
       </c>
       <c r="E72" s="1" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="B105" s="1" t="inlineStr">
         <is>
-          <t>[ʏblɪçə] 行为；举止；特性；性能〈adv.〉</t>
+          <t>[ʏblɪçə] 常见的；惯例的；通常的〈adv.〉</t>
         </is>
       </c>
       <c r="C105" s="1" t="inlineStr">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="D105" s="1" t="inlineStr">
         <is>
-          <t>行为；举止；特性；性能</t>
+          <t>常见的；惯例的；通常的</t>
         </is>
       </c>
       <c r="E105" s="1" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="B108" s="1" t="inlineStr">
         <is>
-          <t>[dʊmɐ] 愚蠢的；糊涂的〈n.m.〉</t>
+          <t>[dʊmɐ] 傻瓜；蠢人；笨蛋〈n.m.〉</t>
         </is>
       </c>
       <c r="C108" s="1" t="inlineStr">
@@ -3869,7 +3869,7 @@
       </c>
       <c r="D108" s="1" t="inlineStr">
         <is>
-          <t>愚蠢的；糊涂的</t>
+          <t>傻瓜；蠢人；笨蛋</t>
         </is>
       </c>
       <c r="E108" s="1" t="inlineStr">
@@ -4723,7 +4723,7 @@
       </c>
       <c r="B135" s="1" t="inlineStr">
         <is>
-          <t>[pasaɡiːʁə] 被雾笼罩的；被浓雾所阻不能航行的〈n.〉</t>
+          <t>[pasaɡiːʁə] 乘客〈n.〉</t>
         </is>
       </c>
       <c r="C135" s="1" t="inlineStr">
@@ -4733,7 +4733,7 @@
       </c>
       <c r="D135" s="1" t="inlineStr">
         <is>
-          <t>被雾笼罩的；被浓雾所阻不能航行的</t>
+          <t>乘客</t>
         </is>
       </c>
       <c r="E135" s="1" t="inlineStr">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="B162" s="1" t="inlineStr">
         <is>
-          <t>[anhɛnɡɐ] 信徒；发生联系的〈n.m.〉</t>
+          <t>[anhɛnɡɐ] 支持者；追随者；拖车；挂车；吊坠〈n.m.〉</t>
         </is>
       </c>
       <c r="C162" s="1" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="D162" s="1" t="inlineStr">
         <is>
-          <t>信徒；发生联系的</t>
+          <t>支持者；追随者；拖车；挂车；吊坠</t>
         </is>
       </c>
       <c r="E162" s="1" t="inlineStr">
@@ -5939,7 +5939,7 @@
       </c>
       <c r="B173" s="1" t="inlineStr">
         <is>
-          <t>[aʊsɡəbɪldət] 火车；列车；行列〈adv.〉</t>
+          <t>[aʊsɡəbɪldət] 受过培训的；受过训练的〈adv.〉</t>
         </is>
       </c>
       <c r="C173" s="1" t="inlineStr">
@@ -5949,7 +5949,7 @@
       </c>
       <c r="D173" s="1" t="inlineStr">
         <is>
-          <t>火车；列车；行列</t>
+          <t>受过培训的；受过训练的</t>
         </is>
       </c>
       <c r="E173" s="1" t="inlineStr">
@@ -6067,7 +6067,7 @@
       </c>
       <c r="B177" s="1" t="inlineStr">
         <is>
-          <t>[fʁɛmt] 外来的；非必要的；无关的；体外的〈n.〉</t>
+          <t>[fʁɛmt] 陌生人；外人〈n.〉</t>
         </is>
       </c>
       <c r="C177" s="1" t="inlineStr">
@@ -6077,7 +6077,7 @@
       </c>
       <c r="D177" s="1" t="inlineStr">
         <is>
-          <t>外来的；非必要的；无关的；体外的</t>
+          <t>陌生人；外人</t>
         </is>
       </c>
       <c r="E177" s="1" t="inlineStr">
@@ -6099,7 +6099,7 @@
       </c>
       <c r="B178" s="1" t="inlineStr">
         <is>
-          <t>[ɡeːnəʁat͡sjoːnən] 两代人之间的〈n.〉</t>
+          <t>[ɡeːnəʁat͡sjoːnən] 代；时代；世代（复数）〈n.〉</t>
         </is>
       </c>
       <c r="C178" s="1" t="inlineStr">
@@ -6109,7 +6109,7 @@
       </c>
       <c r="D178" s="1" t="inlineStr">
         <is>
-          <t>两代人之间的</t>
+          <t>代；时代；世代（复数）</t>
         </is>
       </c>
       <c r="E178" s="1" t="inlineStr">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="B190" s="1" t="inlineStr">
         <is>
-          <t>[fɪʁmən] 社团的；合伙的；公司的；团体的〈n.〉</t>
+          <t>[fɪʁmən] 公司；企业（复数）〈n.〉</t>
         </is>
       </c>
       <c r="C190" s="1" t="inlineStr">
@@ -6493,7 +6493,7 @@
       </c>
       <c r="D190" s="1" t="inlineStr">
         <is>
-          <t>社团的；合伙的；公司的；团体的</t>
+          <t>公司；企业（复数）</t>
         </is>
       </c>
       <c r="E190" s="1" t="inlineStr">
@@ -7059,7 +7059,7 @@
       </c>
       <c r="B208" s="1" t="inlineStr">
         <is>
-          <t>[naːt͡sjoːnalə] 国家的；国立的；全国性的〈n.〉</t>
+          <t>[naːt͡sjoːnalə] 个人基本情况；国民〈n.〉</t>
         </is>
       </c>
       <c r="C208" s="1" t="inlineStr">
@@ -7069,7 +7069,7 @@
       </c>
       <c r="D208" s="1" t="inlineStr">
         <is>
-          <t>国家的；国立的；全国性的</t>
+          <t>个人基本情况；国民</t>
         </is>
       </c>
       <c r="E208" s="1" t="inlineStr">
@@ -7283,7 +7283,7 @@
       </c>
       <c r="B215" s="1" t="inlineStr">
         <is>
-          <t>[vaʁmə] 带子；线；鞋带〈adv.〉</t>
+          <t>[vaʁmə] 温暖的；热情的〈adv.〉</t>
         </is>
       </c>
       <c r="C215" s="1" t="inlineStr">
@@ -7293,7 +7293,7 @@
       </c>
       <c r="D215" s="1" t="inlineStr">
         <is>
-          <t>带子；线；鞋带</t>
+          <t>温暖的；热情的</t>
         </is>
       </c>
       <c r="E215" s="1" t="inlineStr">
@@ -8179,7 +8179,7 @@
       </c>
       <c r="B243" s="1" t="inlineStr">
         <is>
-          <t>[bʁaːtən] 烤肉；烘烤；嘲笑；烘烤的〈n.m.〉</t>
+          <t>[bʁaːtən] 烤肉；烘烤肉〈n.m.〉</t>
         </is>
       </c>
       <c r="C243" s="1" t="inlineStr">
@@ -8189,7 +8189,7 @@
       </c>
       <c r="D243" s="1" t="inlineStr">
         <is>
-          <t>烤肉；烘烤；嘲笑；烘烤的</t>
+          <t>烤肉；烘烤肉</t>
         </is>
       </c>
       <c r="E243" s="1" t="inlineStr">
@@ -8595,7 +8595,7 @@
       </c>
       <c r="B256" s="1" t="inlineStr">
         <is>
-          <t>[ʃvaɪt͡sɐ] 瑞士人；瑞士风格的〈n.〉</t>
+          <t>[ʃvaɪt͡sɐ] 瑞士人〈n.〉</t>
         </is>
       </c>
       <c r="C256" s="1" t="inlineStr">
@@ -8605,7 +8605,7 @@
       </c>
       <c r="D256" s="1" t="inlineStr">
         <is>
-          <t>瑞士人；瑞士风格的</t>
+          <t>瑞士人</t>
         </is>
       </c>
       <c r="E256" s="1" t="inlineStr">
@@ -8691,7 +8691,7 @@
       </c>
       <c r="B259" s="1" t="inlineStr">
         <is>
-          <t>[aʊsəʁɪʁdɪʃə] 外国人；外侨；外国的；相异的〈n.〉</t>
+          <t>[aʊsəʁɪʁdɪʃə] 外星人；外星生物〈n.〉</t>
         </is>
       </c>
       <c r="C259" s="1" t="inlineStr">
@@ -8701,7 +8701,7 @@
       </c>
       <c r="D259" s="1" t="inlineStr">
         <is>
-          <t>外国人；外侨；外国的；相异的</t>
+          <t>外星人；外星生物</t>
         </is>
       </c>
       <c r="E259" s="1" t="inlineStr">
@@ -9235,7 +9235,7 @@
       </c>
       <c r="B276" s="1" t="inlineStr">
         <is>
-          <t>[fʁaɪt͡saɪt] 自由的；享受政治权力的；允许的〈n.f.〉</t>
+          <t>[fʁaɪt͡saɪt] 业余时间；空闲；闲暇〈n.f.〉</t>
         </is>
       </c>
       <c r="C276" s="1" t="inlineStr">
@@ -9245,7 +9245,7 @@
       </c>
       <c r="D276" s="1" t="inlineStr">
         <is>
-          <t>自由的；享受政治权力的；允许的</t>
+          <t>业余时间；空闲；闲暇</t>
         </is>
       </c>
       <c r="E276" s="1" t="inlineStr">
@@ -10067,7 +10067,7 @@
       </c>
       <c r="B302" s="1" t="inlineStr">
         <is>
-          <t>[lʊnɡən] 肺的；与肺有关的；有肺的〈n.〉</t>
+          <t>[lʊnɡən] 肺；肺部（复数）〈n.〉</t>
         </is>
       </c>
       <c r="C302" s="1" t="inlineStr">
@@ -10077,7 +10077,7 @@
       </c>
       <c r="D302" s="1" t="inlineStr">
         <is>
-          <t>肺的；与肺有关的；有肺的</t>
+          <t>肺；肺部（复数）</t>
         </is>
       </c>
       <c r="E302" s="1" t="inlineStr">
@@ -11443,7 +11443,7 @@
       </c>
       <c r="B345" s="1" t="inlineStr">
         <is>
-          <t>[ɡʁyːnəs] 绿色；未成熟的〈n.〉</t>
+          <t>[ɡʁyːnəs] 绿色之物；绿植；蔬菜〈n.〉</t>
         </is>
       </c>
       <c r="C345" s="1" t="inlineStr">
@@ -11453,7 +11453,7 @@
       </c>
       <c r="D345" s="1" t="inlineStr">
         <is>
-          <t>绿色；未成熟的</t>
+          <t>绿色之物；绿植；蔬菜</t>
         </is>
       </c>
       <c r="E345" s="1" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="B359" s="1" t="inlineStr">
         <is>
-          <t>[bas] 低沉的声音；男低音；椴树；低音的〈n.m.〉</t>
+          <t>[bas] 男低音；贝斯；低音吉他；低音〈n.m.〉</t>
         </is>
       </c>
       <c r="C359" s="1" t="inlineStr">
@@ -11901,7 +11901,7 @@
       </c>
       <c r="D359" s="1" t="inlineStr">
         <is>
-          <t>低沉的声音；男低音；椴树；低音的</t>
+          <t>男低音；贝斯；低音吉他；低音</t>
         </is>
       </c>
       <c r="E359" s="1" t="inlineStr">
@@ -12083,7 +12083,7 @@
       </c>
       <c r="B365" s="1" t="inlineStr">
         <is>
-          <t>[ʃvuːlə] 欢快的；艳丽的；快乐的〈n.m.〉</t>
+          <t>[ʃvuːlə] 男同性恋者〈n.m.〉</t>
         </is>
       </c>
       <c r="C365" s="1" t="inlineStr">
@@ -12093,7 +12093,7 @@
       </c>
       <c r="D365" s="1" t="inlineStr">
         <is>
-          <t>欢快的；艳丽的；快乐的</t>
+          <t>男同性恋者</t>
         </is>
       </c>
       <c r="E365" s="1" t="inlineStr">
@@ -12211,7 +12211,7 @@
       </c>
       <c r="B369" s="1" t="inlineStr">
         <is>
-          <t>[flʏsɪɡkaɪt] 液体；分泌液；流体；流动的〈n.f.〉</t>
+          <t>[flʏsɪɡkaɪt] 液体；流体〈n.f.〉</t>
         </is>
       </c>
       <c r="C369" s="1" t="inlineStr">
@@ -12221,7 +12221,7 @@
       </c>
       <c r="D369" s="1" t="inlineStr">
         <is>
-          <t>液体；分泌液；流体；流动的</t>
+          <t>液体；流体</t>
         </is>
       </c>
       <c r="E369" s="1" t="inlineStr">
@@ -12979,7 +12979,7 @@
       </c>
       <c r="B393" s="1" t="inlineStr">
         <is>
-          <t>[ɡlʏkspɪlt͡s] 幸运的；吉祥的；好运的〈n.m.〉</t>
+          <t>[ɡlʏkspɪlt͡s] 幸运儿；幸运的人〈n.m.〉</t>
         </is>
       </c>
       <c r="C393" s="1" t="inlineStr">
@@ -12989,7 +12989,7 @@
       </c>
       <c r="D393" s="1" t="inlineStr">
         <is>
-          <t>幸运的；吉祥的；好运的</t>
+          <t>幸运儿；幸运的人</t>
         </is>
       </c>
       <c r="E393" s="1" t="inlineStr">
@@ -13267,7 +13267,7 @@
       </c>
       <c r="B402" s="1" t="inlineStr">
         <is>
-          <t>[ʃvɪndəl] 假的；伪造的；伪的〈n.m.〉</t>
+          <t>[ʃvɪndəl] 眩晕；眩晕症；骗局〈n.m.〉</t>
         </is>
       </c>
       <c r="C402" s="1" t="inlineStr">
@@ -13277,7 +13277,7 @@
       </c>
       <c r="D402" s="1" t="inlineStr">
         <is>
-          <t>假的；伪造的；伪的</t>
+          <t>眩晕；眩晕症；骗局</t>
         </is>
       </c>
       <c r="E402" s="1" t="inlineStr">
@@ -13299,7 +13299,7 @@
       </c>
       <c r="B403" s="1" t="inlineStr">
         <is>
-          <t>[naːt͡sjoːnaːl] 国家的；国立的；全国性的〈n.〉</t>
+          <t>[naːt͡sjoːnaːl] 国家队；国家报〈n.〉</t>
         </is>
       </c>
       <c r="C403" s="1" t="inlineStr">
@@ -13309,7 +13309,7 @@
       </c>
       <c r="D403" s="1" t="inlineStr">
         <is>
-          <t>国家的；国立的；全国性的</t>
+          <t>国家队；国家报</t>
         </is>
       </c>
       <c r="E403" s="1" t="inlineStr">
@@ -13939,7 +13939,7 @@
       </c>
       <c r="B423" s="1" t="inlineStr">
         <is>
-          <t>[fɛʁbant] 美洲的〈n.〉</t>
+          <t>[fɛʁbant] 协会；联合会；绷带；包扎〈n.〉</t>
         </is>
       </c>
       <c r="C423" s="1" t="inlineStr">
@@ -13949,7 +13949,7 @@
       </c>
       <c r="D423" s="1" t="inlineStr">
         <is>
-          <t>美洲的</t>
+          <t>协会；联合会；绷带；包扎</t>
         </is>
       </c>
       <c r="E423" s="1" t="inlineStr">
@@ -13971,7 +13971,7 @@
       </c>
       <c r="B424" s="1" t="inlineStr">
         <is>
-          <t>[dɪɛːt] 受限制的；有限的〈n.f.〉</t>
+          <t>[dɪɛːt] 节食；特种饮食；议员津贴〈n.f.〉</t>
         </is>
       </c>
       <c r="C424" s="1" t="inlineStr">
@@ -13981,7 +13981,7 @@
       </c>
       <c r="D424" s="1" t="inlineStr">
         <is>
-          <t>受限制的；有限的</t>
+          <t>节食；特种饮食；议员津贴</t>
         </is>
       </c>
       <c r="E424" s="1" t="inlineStr">
@@ -14547,7 +14547,7 @@
       </c>
       <c r="B442" s="1" t="inlineStr">
         <is>
-          <t>[ɡʁaʊ] 灰色；灰色物〈adv.〉</t>
+          <t>[ɡʁaʊ] 灰色的；暗淡的〈adv.〉</t>
         </is>
       </c>
       <c r="C442" s="1" t="inlineStr">
@@ -14557,7 +14557,7 @@
       </c>
       <c r="D442" s="1" t="inlineStr">
         <is>
-          <t>灰色；灰色物</t>
+          <t>灰色的；暗淡的</t>
         </is>
       </c>
       <c r="E442" s="1" t="inlineStr">
@@ -14803,7 +14803,7 @@
       </c>
       <c r="B450" s="1" t="inlineStr">
         <is>
-          <t>[beːlaɪdɪɡʊnk] 恶言谩骂的；被滥用的；腐败的〈n.f.〉</t>
+          <t>[beːlaɪdɪɡʊnk] 侮辱；冒犯；凌辱〈n.f.〉</t>
         </is>
       </c>
       <c r="C450" s="1" t="inlineStr">
@@ -14813,7 +14813,7 @@
       </c>
       <c r="D450" s="1" t="inlineStr">
         <is>
-          <t>恶言谩骂的；被滥用的；腐败的</t>
+          <t>侮辱；冒犯；凌辱</t>
         </is>
       </c>
       <c r="E450" s="1" t="inlineStr">
@@ -14867,7 +14867,7 @@
       </c>
       <c r="B452" s="1" t="inlineStr">
         <is>
-          <t>[hoːəs] 名声〈adv.〉</t>
+          <t>[hoːəs] 高的；高贵的〈adv.〉</t>
         </is>
       </c>
       <c r="C452" s="1" t="inlineStr">
@@ -14877,7 +14877,7 @@
       </c>
       <c r="D452" s="1" t="inlineStr">
         <is>
-          <t>名声</t>
+          <t>高的；高贵的</t>
         </is>
       </c>
       <c r="E452" s="1" t="inlineStr">
@@ -15187,7 +15187,7 @@
       </c>
       <c r="B462" s="1" t="inlineStr">
         <is>
-          <t>[kʏsçən] 友好的；亲切的〈n.〉</t>
+          <t>[kʏsçən] 飞吻；轻吻；小吻〈n.〉</t>
         </is>
       </c>
       <c r="C462" s="1" t="inlineStr">
@@ -15197,7 +15197,7 @@
       </c>
       <c r="D462" s="1" t="inlineStr">
         <is>
-          <t>友好的；亲切的</t>
+          <t>飞吻；轻吻；小吻</t>
         </is>
       </c>
       <c r="E462" s="1" t="inlineStr">
@@ -15219,7 +15219,7 @@
       </c>
       <c r="B463" s="1" t="inlineStr">
         <is>
-          <t>[liːmɔnadə] 嘶嘶作响的；起泡沫的〈n.f.〉</t>
+          <t>[liːmɔnadə] 柠檬汽水；汽水〈n.f.〉</t>
         </is>
       </c>
       <c r="C463" s="1" t="inlineStr">
@@ -15229,7 +15229,7 @@
       </c>
       <c r="D463" s="1" t="inlineStr">
         <is>
-          <t>嘶嘶作响的；起泡沫的</t>
+          <t>柠檬汽水；汽水</t>
         </is>
       </c>
       <c r="E463" s="1" t="inlineStr">
@@ -16275,7 +16275,7 @@
       </c>
       <c r="B496" s="1" t="inlineStr">
         <is>
-          <t>[lʊksʊs] 奢侈；豪华；奢侈的；豪华的〈n.m.〉</t>
+          <t>[lʊksʊs] 奢华；奢侈品；阔气〈n.m.〉</t>
         </is>
       </c>
       <c r="C496" s="1" t="inlineStr">
@@ -16285,7 +16285,7 @@
       </c>
       <c r="D496" s="1" t="inlineStr">
         <is>
-          <t>奢侈；豪华；奢侈的；豪华的</t>
+          <t>奢华；奢侈品；阔气</t>
         </is>
       </c>
       <c r="E496" s="1" t="inlineStr">
@@ -17075,7 +17075,7 @@
       </c>
       <c r="B521" s="1" t="inlineStr">
         <is>
-          <t>[bɪldʊnk] 正式的；形式的；礼仪的〈n.f.〉</t>
+          <t>[bɪldʊnk] 教育；教养；形成；培养〈n.f.〉</t>
         </is>
       </c>
       <c r="C521" s="1" t="inlineStr">
@@ -17085,7 +17085,7 @@
       </c>
       <c r="D521" s="1" t="inlineStr">
         <is>
-          <t>正式的；形式的；礼仪的</t>
+          <t>教育；教养；形成；培养</t>
         </is>
       </c>
       <c r="E521" s="1" t="inlineStr">
@@ -17427,7 +17427,7 @@
       </c>
       <c r="B532" s="1" t="inlineStr">
         <is>
-          <t>[ʊʁspʁʏnɡliːç] 本地人；土产〈adj.〉</t>
+          <t>[ʊʁspʁʏnɡliːç] 最初的；原本的〈adj.〉</t>
         </is>
       </c>
       <c r="C532" s="1" t="inlineStr">
@@ -17437,7 +17437,7 @@
       </c>
       <c r="D532" s="1" t="inlineStr">
         <is>
-          <t>本地人；土产</t>
+          <t>最初的；原本的</t>
         </is>
       </c>
       <c r="E532" s="1" t="inlineStr">
@@ -18099,7 +18099,7 @@
       </c>
       <c r="B553" s="1" t="inlineStr">
         <is>
-          <t>[ʃveːʁəs] 严格的；尖锐的；严肃的〈n.〉</t>
+          <t>[ʃveːʁəs] 沉重之物；困难的事〈n.〉</t>
         </is>
       </c>
       <c r="C553" s="1" t="inlineStr">
@@ -18109,7 +18109,7 @@
       </c>
       <c r="D553" s="1" t="inlineStr">
         <is>
-          <t>严格的；尖锐的；严肃的</t>
+          <t>沉重之物；困难的事</t>
         </is>
       </c>
       <c r="E553" s="1" t="inlineStr">
@@ -19347,7 +19347,7 @@
       </c>
       <c r="B592" s="1" t="inlineStr">
         <is>
-          <t>[ʁɪpən] 肋骨的；具中脉的；肋的〈n.〉</t>
+          <t>[ʁɪpən] 肋骨；肋条（复数）〈n.〉</t>
         </is>
       </c>
       <c r="C592" s="1" t="inlineStr">
@@ -19357,7 +19357,7 @@
       </c>
       <c r="D592" s="1" t="inlineStr">
         <is>
-          <t>肋骨的；具中脉的；肋的</t>
+          <t>肋骨；肋条（复数）</t>
         </is>
       </c>
       <c r="E592" s="1" t="inlineStr">
@@ -20499,7 +20499,7 @@
       </c>
       <c r="B628" s="1" t="inlineStr">
         <is>
-          <t>[feː] 仙女；精灵；仙女的〈n.f.〉</t>
+          <t>[feː] 仙女；小仙子〈n.f.〉</t>
         </is>
       </c>
       <c r="C628" s="1" t="inlineStr">
@@ -20509,7 +20509,7 @@
       </c>
       <c r="D628" s="1" t="inlineStr">
         <is>
-          <t>仙女；精灵；仙女的</t>
+          <t>仙女；小仙子</t>
         </is>
       </c>
       <c r="E628" s="1" t="inlineStr">
@@ -20723,7 +20723,7 @@
       </c>
       <c r="B635" s="1" t="inlineStr">
         <is>
-          <t>[jamɐn] 抱怨的〈n.〉</t>
+          <t>[jamɐn] 叹息；悲叹；抱怨〈n.〉</t>
         </is>
       </c>
       <c r="C635" s="1" t="inlineStr">
@@ -20733,7 +20733,7 @@
       </c>
       <c r="D635" s="1" t="inlineStr">
         <is>
-          <t>抱怨的</t>
+          <t>叹息；悲叹；抱怨</t>
         </is>
       </c>
       <c r="E635" s="1" t="inlineStr">
@@ -20851,7 +20851,7 @@
       </c>
       <c r="B639" s="1" t="inlineStr">
         <is>
-          <t>[taʊbə] 聋的〈n.〉</t>
+          <t>[taʊbə] 鸽子；聋人〈n.〉</t>
         </is>
       </c>
       <c r="C639" s="1" t="inlineStr">
@@ -20861,7 +20861,7 @@
       </c>
       <c r="D639" s="1" t="inlineStr">
         <is>
-          <t>聋的</t>
+          <t>鸽子；聋人</t>
         </is>
       </c>
       <c r="E639" s="1" t="inlineStr">
@@ -20883,7 +20883,7 @@
       </c>
       <c r="B640" s="1" t="inlineStr">
         <is>
-          <t>[maɪs] 玉蜀黍；黄色的〈n.m.〉</t>
+          <t>[maɪs] 玉米；玉蜀黍〈n.m.〉</t>
         </is>
       </c>
       <c r="C640" s="1" t="inlineStr">
@@ -20893,7 +20893,7 @@
       </c>
       <c r="D640" s="1" t="inlineStr">
         <is>
-          <t>玉蜀黍；黄色的</t>
+          <t>玉米；玉蜀黍</t>
         </is>
       </c>
       <c r="E640" s="1" t="inlineStr">
@@ -20915,7 +20915,7 @@
       </c>
       <c r="B641" s="1" t="inlineStr">
         <is>
-          <t>[tʁiːp] 年轻的；无经验的〈n.m.〉</t>
+          <t>[tʁiːp] 驱力；冲动；芽；枝条〈n.m.〉</t>
         </is>
       </c>
       <c r="C641" s="1" t="inlineStr">
@@ -20925,7 +20925,7 @@
       </c>
       <c r="D641" s="1" t="inlineStr">
         <is>
-          <t>年轻的；无经验的</t>
+          <t>驱力；冲动；芽；枝条</t>
         </is>
       </c>
       <c r="E641" s="1" t="inlineStr">
@@ -21555,7 +21555,7 @@
       </c>
       <c r="B661" s="1" t="inlineStr">
         <is>
-          <t>[diːnɐ] 正式的；形式的；礼仪的〈n.〉</t>
+          <t>[diːnɐ] 正餐；晚宴〈n.〉</t>
         </is>
       </c>
       <c r="C661" s="1" t="inlineStr">
@@ -21565,7 +21565,7 @@
       </c>
       <c r="D661" s="1" t="inlineStr">
         <is>
-          <t>正式的；形式的；礼仪的</t>
+          <t>正餐；晚宴</t>
         </is>
       </c>
       <c r="E661" s="1" t="inlineStr">
@@ -21715,7 +21715,7 @@
       </c>
       <c r="B666" s="1" t="inlineStr">
         <is>
-          <t>[mɛçanɪkɐ] 机械工；技工；手工的〈n.m.〉</t>
+          <t>[mɛçanɪkɐ] 机械师；技工；机修工〈n.m.〉</t>
         </is>
       </c>
       <c r="C666" s="1" t="inlineStr">
@@ -21725,7 +21725,7 @@
       </c>
       <c r="D666" s="1" t="inlineStr">
         <is>
-          <t>机械工；技工；手工的</t>
+          <t>机械师；技工；机修工</t>
         </is>
       </c>
       <c r="E666" s="1" t="inlineStr">
@@ -21939,7 +21939,7 @@
       </c>
       <c r="B673" s="1" t="inlineStr">
         <is>
-          <t>[çiːʁʊʁk] 医生；内科的〈n.m.〉</t>
+          <t>[çiːʁʊʁk] 外科医生〈n.m.〉</t>
         </is>
       </c>
       <c r="C673" s="1" t="inlineStr">
@@ -21949,7 +21949,7 @@
       </c>
       <c r="D673" s="1" t="inlineStr">
         <is>
-          <t>医生；内科的</t>
+          <t>外科医生</t>
         </is>
       </c>
       <c r="E673" s="1" t="inlineStr">
@@ -22291,7 +22291,7 @@
       </c>
       <c r="B684" s="1" t="inlineStr">
         <is>
-          <t>[laɪçtəs] 拍击者；惊鸟器；苍蝇拍〈adv.〉</t>
+          <t>[laɪçtəs] 轻便的；容易的；轻微的〈adv.〉</t>
         </is>
       </c>
       <c r="C684" s="1" t="inlineStr">
@@ -22301,7 +22301,7 @@
       </c>
       <c r="D684" s="1" t="inlineStr">
         <is>
-          <t>拍击者；惊鸟器；苍蝇拍</t>
+          <t>轻便的；容易的；轻微的</t>
         </is>
       </c>
       <c r="E684" s="1" t="inlineStr">
@@ -22387,7 +22387,7 @@
       </c>
       <c r="B687" s="1" t="inlineStr">
         <is>
-          <t>[ɡeːɡənstant] 物体；目标；目的〈n.m.〉</t>
+          <t>[ɡeːɡənstant] 物体；物品；题材；对象〈n.m.〉</t>
         </is>
       </c>
       <c r="C687" s="1" t="inlineStr">
@@ -22397,7 +22397,7 @@
       </c>
       <c r="D687" s="1" t="inlineStr">
         <is>
-          <t>物体；目标；目的</t>
+          <t>物体；物品；题材；对象</t>
         </is>
       </c>
       <c r="E687" s="1" t="inlineStr">
@@ -22899,7 +22899,7 @@
       </c>
       <c r="B703" s="1" t="inlineStr">
         <is>
-          <t>[aːʁabɐ] 阿拉伯人；阿拉伯的〈n.m.〉</t>
+          <t>[aːʁabɐ] 阿拉伯人〈n.m.〉</t>
         </is>
       </c>
       <c r="C703" s="1" t="inlineStr">
@@ -22909,7 +22909,7 @@
       </c>
       <c r="D703" s="1" t="inlineStr">
         <is>
-          <t>阿拉伯人；阿拉伯的</t>
+          <t>阿拉伯人</t>
         </is>
       </c>
       <c r="E703" s="1" t="inlineStr">
@@ -22995,7 +22995,7 @@
       </c>
       <c r="B706" s="1" t="inlineStr">
         <is>
-          <t>[dʁɪtəl] 第三；三分之一；第三的〈n.〉</t>
+          <t>[dʁɪtəl] 三分之一〈n.〉</t>
         </is>
       </c>
       <c r="C706" s="1" t="inlineStr">
@@ -23005,7 +23005,7 @@
       </c>
       <c r="D706" s="1" t="inlineStr">
         <is>
-          <t>第三；三分之一；第三的</t>
+          <t>三分之一</t>
         </is>
       </c>
       <c r="E706" s="1" t="inlineStr">
@@ -24979,7 +24979,7 @@
       </c>
       <c r="B768" s="1" t="inlineStr">
         <is>
-          <t>[ɡeːakt] 生气〈adv.〉</t>
+          <t>[ɡeːakt] 切碎的；被黑客入侵的〈adv.〉</t>
         </is>
       </c>
       <c r="C768" s="1" t="inlineStr">
@@ -24989,7 +24989,7 @@
       </c>
       <c r="D768" s="1" t="inlineStr">
         <is>
-          <t>生气</t>
+          <t>切碎的；被黑客入侵的</t>
         </is>
       </c>
       <c r="E768" s="1" t="inlineStr">
@@ -25395,7 +25395,7 @@
       </c>
       <c r="B781" s="1" t="inlineStr">
         <is>
-          <t>[aɪçhœʁnçən] 松软的；模糊的；不肯定的〈n.〉</t>
+          <t>[aɪçhœʁnçən] 松鼠〈n.〉</t>
         </is>
       </c>
       <c r="C781" s="1" t="inlineStr">
@@ -25405,7 +25405,7 @@
       </c>
       <c r="D781" s="1" t="inlineStr">
         <is>
-          <t>松软的；模糊的；不肯定的</t>
+          <t>松鼠</t>
         </is>
       </c>
       <c r="E781" s="1" t="inlineStr">
@@ -25523,7 +25523,7 @@
       </c>
       <c r="B785" s="1" t="inlineStr">
         <is>
-          <t>[niːdʁɪç] 低点；低价；低〈adj.〉</t>
+          <t>[niːdʁɪç] 低矮的；低下的；低廉的〈adj.〉</t>
         </is>
       </c>
       <c r="C785" s="1" t="inlineStr">
@@ -25533,7 +25533,7 @@
       </c>
       <c r="D785" s="1" t="inlineStr">
         <is>
-          <t>低点；低价；低</t>
+          <t>低矮的；低下的；低廉的</t>
         </is>
       </c>
       <c r="E785" s="1" t="inlineStr">
@@ -26515,7 +26515,7 @@
       </c>
       <c r="B816" s="1" t="inlineStr">
         <is>
-          <t>[ʃtʁaft͡sətəl] 停车；停车的〈n.m.〉</t>
+          <t>[ʃtʁaft͡sətəl] 罚单；违规停车罚单〈n.m.〉</t>
         </is>
       </c>
       <c r="C816" s="1" t="inlineStr">
@@ -26525,7 +26525,7 @@
       </c>
       <c r="D816" s="1" t="inlineStr">
         <is>
-          <t>停车；停车的</t>
+          <t>罚单；违规停车罚单</t>
         </is>
       </c>
       <c r="E816" s="1" t="inlineStr">
@@ -27155,7 +27155,7 @@
       </c>
       <c r="B836" s="1" t="inlineStr">
         <is>
-          <t>[pʊlɔfɐ] 套衫；套穿的〈n.m.〉</t>
+          <t>[pʊlɔfɐ] 套头毛衣；套衫〈n.m.〉</t>
         </is>
       </c>
       <c r="C836" s="1" t="inlineStr">
@@ -27165,7 +27165,7 @@
       </c>
       <c r="D836" s="1" t="inlineStr">
         <is>
-          <t>套衫；套穿的</t>
+          <t>套头毛衣；套衫</t>
         </is>
       </c>
       <c r="E836" s="1" t="inlineStr">
@@ -27955,7 +27955,7 @@
       </c>
       <c r="B861" s="1" t="inlineStr">
         <is>
-          <t>[poːnʏ] 每日摘要的〈n.〉</t>
+          <t>[poːnʏ] 小马；矮种马；刘海〈n.〉</t>
         </is>
       </c>
       <c r="C861" s="1" t="inlineStr">
@@ -27965,7 +27965,7 @@
       </c>
       <c r="D861" s="1" t="inlineStr">
         <is>
-          <t>每日摘要的</t>
+          <t>小马；矮种马；刘海</t>
         </is>
       </c>
       <c r="E861" s="1" t="inlineStr">
@@ -28083,7 +28083,7 @@
       </c>
       <c r="B865" s="1" t="inlineStr">
         <is>
-          <t>[ɡlant͡s] 光辉；光彩；光泽；光辉的〈n.m.〉</t>
+          <t>[ɡlant͡s] 光泽；光彩；光芒〈n.m.〉</t>
         </is>
       </c>
       <c r="C865" s="1" t="inlineStr">
@@ -28093,7 +28093,7 @@
       </c>
       <c r="D865" s="1" t="inlineStr">
         <is>
-          <t>光辉；光彩；光泽；光辉的</t>
+          <t>光泽；光彩；光芒</t>
         </is>
       </c>
       <c r="E865" s="1" t="inlineStr">
@@ -28115,7 +28115,7 @@
       </c>
       <c r="B866" s="1" t="inlineStr">
         <is>
-          <t>[beːtɔʏbt] 使麻木；使麻痹〈adv.〉</t>
+          <t>[beːtɔʏbt] 麻木的；目瞪口呆的；麻醉的〈adv.〉</t>
         </is>
       </c>
       <c r="C866" s="1" t="inlineStr">
@@ -28125,7 +28125,7 @@
       </c>
       <c r="D866" s="1" t="inlineStr">
         <is>
-          <t>使麻木；使麻痹</t>
+          <t>麻木的；目瞪口呆的；麻醉的</t>
         </is>
       </c>
       <c r="E866" s="1" t="inlineStr">
@@ -28499,7 +28499,7 @@
       </c>
       <c r="B878" s="1" t="inlineStr">
         <is>
-          <t>[blaʊəs] 蓝色；蓝色的；下流的〈n.〉</t>
+          <t>[blaʊəs] 蓝色之物；蓝天〈n.〉</t>
         </is>
       </c>
       <c r="C878" s="1" t="inlineStr">
@@ -28509,7 +28509,7 @@
       </c>
       <c r="D878" s="1" t="inlineStr">
         <is>
-          <t>蓝色；蓝色的；下流的</t>
+          <t>蓝色之物；蓝天</t>
         </is>
       </c>
       <c r="E878" s="1" t="inlineStr">
@@ -28531,7 +28531,7 @@
       </c>
       <c r="B879" s="1" t="inlineStr">
         <is>
-          <t>[dʊnklɐ] 大斑点；污斑；疹块；污点〈adv.〉</t>
+          <t>[dʊnklɐ] 更黑暗的；更阴暗的〈adv.〉</t>
         </is>
       </c>
       <c r="C879" s="1" t="inlineStr">
@@ -28541,7 +28541,7 @@
       </c>
       <c r="D879" s="1" t="inlineStr">
         <is>
-          <t>大斑点；污斑；疹块；污点</t>
+          <t>更黑暗的；更阴暗的</t>
         </is>
       </c>
       <c r="E879" s="1" t="inlineStr">
@@ -29331,7 +29331,7 @@
       </c>
       <c r="B904" s="1" t="inlineStr">
         <is>
-          <t>[beːʁuːɪɡʊnɡsmɪtəl] 使安静的〈n.〉</t>
+          <t>[beːʁuːɪɡʊnɡsmɪtəl] 镇静剂；安眠药〈n.〉</t>
         </is>
       </c>
       <c r="C904" s="1" t="inlineStr">
@@ -29341,7 +29341,7 @@
       </c>
       <c r="D904" s="1" t="inlineStr">
         <is>
-          <t>使安静的</t>
+          <t>镇静剂；安眠药</t>
         </is>
       </c>
       <c r="E904" s="1" t="inlineStr">
@@ -29491,7 +29491,7 @@
       </c>
       <c r="B909" s="1" t="inlineStr">
         <is>
-          <t>[niːʁən] 肾脏的；肾的〈n.〉</t>
+          <t>[niːʁən] 肾脏；腰子（复数）〈n.〉</t>
         </is>
       </c>
       <c r="C909" s="1" t="inlineStr">
@@ -29501,7 +29501,7 @@
       </c>
       <c r="D909" s="1" t="inlineStr">
         <is>
-          <t>肾脏的；肾的</t>
+          <t>肾脏；腰子（复数）</t>
         </is>
       </c>
       <c r="E909" s="1" t="inlineStr">
@@ -30419,7 +30419,7 @@
       </c>
       <c r="B938" s="1" t="inlineStr">
         <is>
-          <t>[poːlɪtɪʃ] 炸药使用者〈adj.〉</t>
+          <t>[poːlɪtɪʃ] 政治的〈adj.〉</t>
         </is>
       </c>
       <c r="C938" s="1" t="inlineStr">
@@ -30429,7 +30429,7 @@
       </c>
       <c r="D938" s="1" t="inlineStr">
         <is>
-          <t>炸药使用者</t>
+          <t>政治的</t>
         </is>
       </c>
       <c r="E938" s="1" t="inlineStr">
@@ -31027,7 +31027,7 @@
       </c>
       <c r="B957" s="1" t="inlineStr">
         <is>
-          <t>[dʊʁksaɡə] 公众；民众；公众的；公共的〈n.f.〉</t>
+          <t>[dʊʁksaɡə] 广播通知；口头广播〈n.f.〉</t>
         </is>
       </c>
       <c r="C957" s="1" t="inlineStr">
@@ -31037,7 +31037,7 @@
       </c>
       <c r="D957" s="1" t="inlineStr">
         <is>
-          <t>公众；民众；公众的；公共的</t>
+          <t>广播通知；口头广播</t>
         </is>
       </c>
       <c r="E957" s="1" t="inlineStr">
@@ -31219,7 +31219,7 @@
       </c>
       <c r="B963" s="1" t="inlineStr">
         <is>
-          <t>[aːlaʁmstʊfə] 警觉的；灵敏的〈n.f.〉</t>
+          <t>[aːlaʁmstʊfə] 警报级别；警戒等级〈n.f.〉</t>
         </is>
       </c>
       <c r="C963" s="1" t="inlineStr">
@@ -31229,7 +31229,7 @@
       </c>
       <c r="D963" s="1" t="inlineStr">
         <is>
-          <t>警觉的；灵敏的</t>
+          <t>警报级别；警戒等级</t>
         </is>
       </c>
       <c r="E963" s="1" t="inlineStr">
@@ -31411,7 +31411,7 @@
       </c>
       <c r="B969" s="1" t="inlineStr">
         <is>
-          <t>[jaːpanɪʃə] 日本人；日语；日本的；日语的〈n.〉</t>
+          <t>[jaːpanɪʃə] 日语；日本事物〈n.〉</t>
         </is>
       </c>
       <c r="C969" s="1" t="inlineStr">
@@ -31421,7 +31421,7 @@
       </c>
       <c r="D969" s="1" t="inlineStr">
         <is>
-          <t>日本人；日语；日本的；日语的</t>
+          <t>日语；日本事物</t>
         </is>
       </c>
       <c r="E969" s="1" t="inlineStr">
@@ -31443,7 +31443,7 @@
       </c>
       <c r="B970" s="1" t="inlineStr">
         <is>
-          <t>[abɡəfɔʏəʁt] 火；炉火；电炉〈adv.〉</t>
+          <t>[abɡəfɔʏəʁt] 开火的；射出的；发射的〈adv.〉</t>
         </is>
       </c>
       <c r="C970" s="1" t="inlineStr">
@@ -31453,7 +31453,7 @@
       </c>
       <c r="D970" s="1" t="inlineStr">
         <is>
-          <t>火；炉火；电炉</t>
+          <t>开火的；射出的；发射的</t>
         </is>
       </c>
       <c r="E970" s="1" t="inlineStr">
@@ -31795,7 +31795,7 @@
       </c>
       <c r="B981" s="1" t="inlineStr">
         <is>
-          <t>[ɡlʏkstaːk] 快乐的；幸福的；愉快的〈n.m.〉</t>
+          <t>[ɡlʏkstaːk] 吉日；幸运日〈n.m.〉</t>
         </is>
       </c>
       <c r="C981" s="1" t="inlineStr">
@@ -31805,7 +31805,7 @@
       </c>
       <c r="D981" s="1" t="inlineStr">
         <is>
-          <t>快乐的；幸福的；愉快的</t>
+          <t>吉日；幸运日</t>
         </is>
       </c>
       <c r="E981" s="1" t="inlineStr">
@@ -32499,7 +32499,7 @@
       </c>
       <c r="B1003" s="1" t="inlineStr">
         <is>
-          <t>[blɪndə] 蒙蔽物；窗帘；盲目的；瞎的〈n.〉</t>
+          <t>[blɪndə] 盲人；失明者〈n.〉</t>
         </is>
       </c>
       <c r="C1003" s="1" t="inlineStr">
@@ -32509,7 +32509,7 @@
       </c>
       <c r="D1003" s="1" t="inlineStr">
         <is>
-          <t>蒙蔽物；窗帘；盲目的；瞎的</t>
+          <t>盲人；失明者</t>
         </is>
       </c>
       <c r="E1003" s="1" t="inlineStr">
@@ -32787,7 +32787,7 @@
       </c>
       <c r="B1012" s="1" t="inlineStr">
         <is>
-          <t>[ɡlʏklɪçəs] 偶然发现珍宝的运气；才能；易遇奇缘的运气〈adv.〉</t>
+          <t>[ɡlʏklɪçəs] 幸福的；吉祥的〈adv.〉</t>
         </is>
       </c>
       <c r="C1012" s="1" t="inlineStr">
@@ -32797,7 +32797,7 @@
       </c>
       <c r="D1012" s="1" t="inlineStr">
         <is>
-          <t>偶然发现珍宝的运气；才能；易遇奇缘的运气</t>
+          <t>幸福的；吉祥的</t>
         </is>
       </c>
       <c r="E1012" s="1" t="inlineStr">
@@ -33043,7 +33043,7 @@
       </c>
       <c r="B1020" s="1" t="inlineStr">
         <is>
-          <t>[fɔʁzɪçtɪɡɐ] 胆小鬼；缩手缩脚的人；小气鬼〈adv.〉</t>
+          <t>[fɔʁzɪçtɪɡɐ] 更小心的；更谨慎的〈adv.〉</t>
         </is>
       </c>
       <c r="C1020" s="1" t="inlineStr">
@@ -33053,7 +33053,7 @@
       </c>
       <c r="D1020" s="1" t="inlineStr">
         <is>
-          <t>胆小鬼；缩手缩脚的人；小气鬼</t>
+          <t>更小心的；更谨慎的</t>
         </is>
       </c>
       <c r="E1020" s="1" t="inlineStr">
@@ -33267,7 +33267,7 @@
       </c>
       <c r="B1027" s="1" t="inlineStr">
         <is>
-          <t>[tɔɪlətən] 厕所的；洗涤的；低级粗俗的〈n.〉</t>
+          <t>[tɔɪlətən] 厕所；洗手间（复数）〈n.〉</t>
         </is>
       </c>
       <c r="C1027" s="1" t="inlineStr">
@@ -33277,7 +33277,7 @@
       </c>
       <c r="D1027" s="1" t="inlineStr">
         <is>
-          <t>厕所的；洗涤的；低级粗俗的</t>
+          <t>厕所；洗手间（复数）</t>
         </is>
       </c>
       <c r="E1027" s="1" t="inlineStr">
@@ -33331,7 +33331,7 @@
       </c>
       <c r="B1029" s="1" t="inlineStr">
         <is>
-          <t>[pɔʁtaːl] 入口；大门；肝门的〈n.〉</t>
+          <t>[pɔʁtaːl] 大门；入口；门户网站〈n.〉</t>
         </is>
       </c>
       <c r="C1029" s="1" t="inlineStr">
@@ -33341,7 +33341,7 @@
       </c>
       <c r="D1029" s="1" t="inlineStr">
         <is>
-          <t>入口；大门；肝门的</t>
+          <t>大门；入口；门户网站</t>
         </is>
       </c>
       <c r="E1029" s="1" t="inlineStr">
@@ -33587,7 +33587,7 @@
       </c>
       <c r="B1037" s="1" t="inlineStr">
         <is>
-          <t>[ʃʊft] 恶棍；卑鄙的〈n.m.〉</t>
+          <t>[ʃʊft] 恶棍；无赖；坏蛋〈n.m.〉</t>
         </is>
       </c>
       <c r="C1037" s="1" t="inlineStr">
@@ -33597,7 +33597,7 @@
       </c>
       <c r="D1037" s="1" t="inlineStr">
         <is>
-          <t>恶棍；卑鄙的</t>
+          <t>恶棍；无赖；坏蛋</t>
         </is>
       </c>
       <c r="E1037" s="1" t="inlineStr">
@@ -33747,7 +33747,7 @@
       </c>
       <c r="B1042" s="1" t="inlineStr">
         <is>
-          <t>[taktiːk] 一项战术；顺序的〈n.f.〉</t>
+          <t>[taktiːk] 战术；策略；策略手段〈n.f.〉</t>
         </is>
       </c>
       <c r="C1042" s="1" t="inlineStr">
@@ -33757,7 +33757,7 @@
       </c>
       <c r="D1042" s="1" t="inlineStr">
         <is>
-          <t>一项战术；顺序的</t>
+          <t>战术；策略；策略手段</t>
         </is>
       </c>
       <c r="E1042" s="1" t="inlineStr">
@@ -33939,7 +33939,7 @@
       </c>
       <c r="B1048" s="1" t="inlineStr">
         <is>
-          <t>[pʁoːfəsɪɔnələ] 美容术〈adv.〉</t>
+          <t>[pʁoːfəsɪɔnələ] 专业的；职业的〈adv.〉</t>
         </is>
       </c>
       <c r="C1048" s="1" t="inlineStr">
@@ -33949,7 +33949,7 @@
       </c>
       <c r="D1048" s="1" t="inlineStr">
         <is>
-          <t>美容术</t>
+          <t>专业的；职业的</t>
         </is>
       </c>
       <c r="E1048" s="1" t="inlineStr">
@@ -34771,7 +34771,7 @@
       </c>
       <c r="B1074" s="1" t="inlineStr">
         <is>
-          <t>[kʁankɐ] &lt;美俚&gt;有精神病的人；道德败坏的人〈adv.〉</t>
+          <t>[kʁankɐ] 患病的；病态的〈adv.〉</t>
         </is>
       </c>
       <c r="C1074" s="1" t="inlineStr">
@@ -34781,7 +34781,7 @@
       </c>
       <c r="D1074" s="1" t="inlineStr">
         <is>
-          <t>&lt;美俚&gt;有精神病的人；道德败坏的人</t>
+          <t>患病的；病态的</t>
         </is>
       </c>
       <c r="E1074" s="1" t="inlineStr">
@@ -36115,7 +36115,7 @@
       </c>
       <c r="B1116" s="1" t="inlineStr">
         <is>
-          <t>[neːɡɐ] 黑人；黑人的〈n.m.〉</t>
+          <t>[neːɡɐ] 黑人（旧称/忌用）〈n.m.〉</t>
         </is>
       </c>
       <c r="C1116" s="1" t="inlineStr">
@@ -36125,7 +36125,7 @@
       </c>
       <c r="D1116" s="1" t="inlineStr">
         <is>
-          <t>黑人；黑人的</t>
+          <t>黑人（旧称/忌用）</t>
         </is>
       </c>
       <c r="E1116" s="1" t="inlineStr">
@@ -36243,7 +36243,7 @@
       </c>
       <c r="B1120" s="1" t="inlineStr">
         <is>
-          <t>[ɡeːʁɪçtsmədɪt͡sɪnɐ] 专门医师；专家；专业的；专家的〈n.m.〉</t>
+          <t>[ɡeːʁɪçtsmədɪt͡sɪnɐ] 法医〈n.m.〉</t>
         </is>
       </c>
       <c r="C1120" s="1" t="inlineStr">
@@ -36253,7 +36253,7 @@
       </c>
       <c r="D1120" s="1" t="inlineStr">
         <is>
-          <t>专门医师；专家；专业的；专家的</t>
+          <t>法医</t>
         </is>
       </c>
       <c r="E1120" s="1" t="inlineStr">
@@ -36531,7 +36531,7 @@
       </c>
       <c r="B1129" s="1" t="inlineStr">
         <is>
-          <t>[abfal] 拒绝；无用的〈n.m.〉</t>
+          <t>[abfal] 垃圾；废料；废物；下降〈n.m.〉</t>
         </is>
       </c>
       <c r="C1129" s="1" t="inlineStr">
@@ -36541,7 +36541,7 @@
       </c>
       <c r="D1129" s="1" t="inlineStr">
         <is>
-          <t>拒绝；无用的</t>
+          <t>垃圾；废料；废物；下降</t>
         </is>
       </c>
       <c r="E1129" s="1" t="inlineStr">
@@ -37619,7 +37619,7 @@
       </c>
       <c r="B1163" s="1" t="inlineStr">
         <is>
-          <t>[laːtaɪn] 拉丁人；拉丁语的〈n.〉</t>
+          <t>[laːtaɪn] 拉丁语〈n.〉</t>
         </is>
       </c>
       <c r="C1163" s="1" t="inlineStr">
@@ -37629,7 +37629,7 @@
       </c>
       <c r="D1163" s="1" t="inlineStr">
         <is>
-          <t>拉丁人；拉丁语的</t>
+          <t>拉丁语</t>
         </is>
       </c>
       <c r="E1163" s="1" t="inlineStr">
@@ -37811,7 +37811,7 @@
       </c>
       <c r="B1169" s="1" t="inlineStr">
         <is>
-          <t>[luːdɐ] 狡诈的；诡计多端的；巧妙的〈n.〉</t>
+          <t>[luːdɐ] 荡妇；泼妇；诱饵〈n.〉</t>
         </is>
       </c>
       <c r="C1169" s="1" t="inlineStr">
@@ -37821,7 +37821,7 @@
       </c>
       <c r="D1169" s="1" t="inlineStr">
         <is>
-          <t>狡诈的；诡计多端的；巧妙的</t>
+          <t>荡妇；泼妇；诱饵</t>
         </is>
       </c>
       <c r="E1169" s="1" t="inlineStr">
@@ -38899,7 +38899,7 @@
       </c>
       <c r="B1203" s="1" t="inlineStr">
         <is>
-          <t>[aɪɡəntlɪçə] 典型的；象征性的〈n.〉</t>
+          <t>[aɪɡəntlɪçə] 本质；实质；本来面目〈n.〉</t>
         </is>
       </c>
       <c r="C1203" s="1" t="inlineStr">
@@ -38909,7 +38909,7 @@
       </c>
       <c r="D1203" s="1" t="inlineStr">
         <is>
-          <t>典型的；象征性的</t>
+          <t>本质；实质；本来面目</t>
         </is>
       </c>
       <c r="E1203" s="1" t="inlineStr">
@@ -39123,7 +39123,7 @@
       </c>
       <c r="B1210" s="1" t="inlineStr">
         <is>
-          <t>[kaltəs] 正式茶点；晚茶〈adv.〉</t>
+          <t>[kaltəs] 寒冷的；冰凉的〈adv.〉</t>
         </is>
       </c>
       <c r="C1210" s="1" t="inlineStr">
@@ -39133,7 +39133,7 @@
       </c>
       <c r="D1210" s="1" t="inlineStr">
         <is>
-          <t>正式茶点；晚茶</t>
+          <t>寒冷的；冰凉的</t>
         </is>
       </c>
       <c r="E1210" s="1" t="inlineStr">
@@ -39283,7 +39283,7 @@
       </c>
       <c r="B1215" s="1" t="inlineStr">
         <is>
-          <t>[ɛʁkɛltʊnk] 通常的；共同的；通俗的〈n.f.〉</t>
+          <t>[ɛʁkɛltʊnk] 感冒；受凉〈n.f.〉</t>
         </is>
       </c>
       <c r="C1215" s="1" t="inlineStr">
@@ -39293,7 +39293,7 @@
       </c>
       <c r="D1215" s="1" t="inlineStr">
         <is>
-          <t>通常的；共同的；通俗的</t>
+          <t>感冒；受凉</t>
         </is>
       </c>
       <c r="E1215" s="1" t="inlineStr">
@@ -39475,7 +39475,7 @@
       </c>
       <c r="B1221" s="1" t="inlineStr">
         <is>
-          <t>[ɡeːɪʁnəʁʃʏtəʁʊnk] 脑的；大脑的；小脑的〈n.f.〉</t>
+          <t>[ɡeːɪʁnəʁʃʏtəʁʊnk] 脑震荡〈n.f.〉</t>
         </is>
       </c>
       <c r="C1221" s="1" t="inlineStr">
@@ -39485,7 +39485,7 @@
       </c>
       <c r="D1221" s="1" t="inlineStr">
         <is>
-          <t>脑的；大脑的；小脑的</t>
+          <t>脑震荡</t>
         </is>
       </c>
       <c r="E1221" s="1" t="inlineStr">
@@ -40211,7 +40211,7 @@
       </c>
       <c r="B1244" s="1" t="inlineStr">
         <is>
-          <t>[aɪnmalɪɡə] 在一处只演出一场；一夜演出〈adv.〉</t>
+          <t>[aɪnmalɪɡə] 一次性的；绝无仅有的；极佳的〈adv.〉</t>
         </is>
       </c>
       <c r="C1244" s="1" t="inlineStr">
@@ -40221,7 +40221,7 @@
       </c>
       <c r="D1244" s="1" t="inlineStr">
         <is>
-          <t>在一处只演出一场；一夜演出</t>
+          <t>一次性的；绝无仅有的；极佳的</t>
         </is>
       </c>
       <c r="E1244" s="1" t="inlineStr">
@@ -40307,7 +40307,7 @@
       </c>
       <c r="B1247" s="1" t="inlineStr">
         <is>
-          <t>[ʃvɛʁkʁaft] 向下的〈n.f.〉</t>
+          <t>[ʃvɛʁkʁaft] 重力；地心引力〈n.f.〉</t>
         </is>
       </c>
       <c r="C1247" s="1" t="inlineStr">
@@ -40317,7 +40317,7 @@
       </c>
       <c r="D1247" s="1" t="inlineStr">
         <is>
-          <t>向下的</t>
+          <t>重力；地心引力</t>
         </is>
       </c>
       <c r="E1247" s="1" t="inlineStr">
@@ -40403,7 +40403,7 @@
       </c>
       <c r="B1250" s="1" t="inlineStr">
         <is>
-          <t>[zœldnɐ] 唯利是图者；被雇的〈n.m.〉</t>
+          <t>[zœldnɐ] 雇佣兵〈n.m.〉</t>
         </is>
       </c>
       <c r="C1250" s="1" t="inlineStr">
@@ -40413,7 +40413,7 @@
       </c>
       <c r="D1250" s="1" t="inlineStr">
         <is>
-          <t>唯利是图者；被雇的</t>
+          <t>雇佣兵</t>
         </is>
       </c>
       <c r="E1250" s="1" t="inlineStr">
@@ -40435,7 +40435,7 @@
       </c>
       <c r="B1251" s="1" t="inlineStr">
         <is>
-          <t>[aʊfvəkən] 醒着的〈n.〉</t>
+          <t>[aʊfvəkən] 唤醒；叫醒〈n.〉</t>
         </is>
       </c>
       <c r="C1251" s="1" t="inlineStr">
@@ -40445,7 +40445,7 @@
       </c>
       <c r="D1251" s="1" t="inlineStr">
         <is>
-          <t>醒着的</t>
+          <t>唤醒；叫醒</t>
         </is>
       </c>
       <c r="E1251" s="1" t="inlineStr">
@@ -40467,7 +40467,7 @@
       </c>
       <c r="B1252" s="1" t="inlineStr">
         <is>
-          <t>[klʊɡʃaɪsɐ] 聪明的；漂亮的；刺痛的〈n.m.〉</t>
+          <t>[klʊɡʃaɪsɐ] 自作聪明的人；万事通〈n.m.〉</t>
         </is>
       </c>
       <c r="C1252" s="1" t="inlineStr">
@@ -40477,7 +40477,7 @@
       </c>
       <c r="D1252" s="1" t="inlineStr">
         <is>
-          <t>聪明的；漂亮的；刺痛的</t>
+          <t>自作聪明的人；万事通</t>
         </is>
       </c>
       <c r="E1252" s="1" t="inlineStr">
@@ -40691,7 +40691,7 @@
       </c>
       <c r="B1259" s="1" t="inlineStr">
         <is>
-          <t>[blaʊɐ] 蓝色；蓝色的；下流的〈n.〉</t>
+          <t>[blaʊɐ] 穿蓝衣者；蓝色事物〈n.〉</t>
         </is>
       </c>
       <c r="C1259" s="1" t="inlineStr">
@@ -40701,7 +40701,7 @@
       </c>
       <c r="D1259" s="1" t="inlineStr">
         <is>
-          <t>蓝色；蓝色的；下流的</t>
+          <t>穿蓝衣者；蓝色事物</t>
         </is>
       </c>
       <c r="E1259" s="1" t="inlineStr">
@@ -42899,7 +42899,7 @@
       </c>
       <c r="B1328" s="1" t="inlineStr">
         <is>
-          <t>[taɪlneːmɐ] 参加者；参加的〈n.m.〉</t>
+          <t>[taɪlneːmɐ] 参加者；参与者；选手〈n.m.〉</t>
         </is>
       </c>
       <c r="C1328" s="1" t="inlineStr">
@@ -42909,7 +42909,7 @@
       </c>
       <c r="D1328" s="1" t="inlineStr">
         <is>
-          <t>参加者；参加的</t>
+          <t>参加者；参与者；选手</t>
         </is>
       </c>
       <c r="E1328" s="1" t="inlineStr">
@@ -43027,7 +43027,7 @@
       </c>
       <c r="B1332" s="1" t="inlineStr">
         <is>
-          <t>[ʏblɐ] 气味；臭气；香气〈adv.〉</t>
+          <t>[ʏblɐ] 更糟的；更恶劣的〈adv.〉</t>
         </is>
       </c>
       <c r="C1332" s="1" t="inlineStr">
@@ -43037,7 +43037,7 @@
       </c>
       <c r="D1332" s="1" t="inlineStr">
         <is>
-          <t>气味；臭气；香气</t>
+          <t>更糟的；更恶劣的</t>
         </is>
       </c>
       <c r="E1332" s="1" t="inlineStr">
@@ -43443,7 +43443,7 @@
       </c>
       <c r="B1345" s="1" t="inlineStr">
         <is>
-          <t>[ɡeːzɪçtzaʊsdʁʊk] 美颜；表面的〈n.m.〉</t>
+          <t>[ɡeːzɪçtzaʊsdʁʊk] 面部表情；神色〈n.m.〉</t>
         </is>
       </c>
       <c r="C1345" s="1" t="inlineStr">
@@ -43453,7 +43453,7 @@
       </c>
       <c r="D1345" s="1" t="inlineStr">
         <is>
-          <t>美颜；表面的</t>
+          <t>面部表情；神色</t>
         </is>
       </c>
       <c r="E1345" s="1" t="inlineStr">
@@ -43475,7 +43475,7 @@
       </c>
       <c r="B1346" s="1" t="inlineStr">
         <is>
-          <t>[fɛʁnbədiːnʊnk] 遥远的；偏僻的；疏远的〈n.f.〉</t>
+          <t>[fɛʁnbədiːnʊnk] 遥控器；遥控〈n.f.〉</t>
         </is>
       </c>
       <c r="C1346" s="1" t="inlineStr">
@@ -43485,7 +43485,7 @@
       </c>
       <c r="D1346" s="1" t="inlineStr">
         <is>
-          <t>遥远的；偏僻的；疏远的</t>
+          <t>遥控器；遥控</t>
         </is>
       </c>
       <c r="E1346" s="1" t="inlineStr">
@@ -43571,7 +43571,7 @@
       </c>
       <c r="B1349" s="1" t="inlineStr">
         <is>
-          <t>[fɛʁləɡənhaɪt] 笨拙的；棘手的〈n.f.〉</t>
+          <t>[fɛʁləɡənhaɪt] 尴尬；窘迫；困窘〈n.f.〉</t>
         </is>
       </c>
       <c r="C1349" s="1" t="inlineStr">
@@ -43581,7 +43581,7 @@
       </c>
       <c r="D1349" s="1" t="inlineStr">
         <is>
-          <t>笨拙的；棘手的</t>
+          <t>尴尬；窘迫；困窘</t>
         </is>
       </c>
       <c r="E1349" s="1" t="inlineStr">
@@ -44307,7 +44307,7 @@
       </c>
       <c r="B1372" s="1" t="inlineStr">
         <is>
-          <t>[mɛnʃənləbən] 人；人类；人类的；似人类的〈n.〉</t>
+          <t>[mɛnʃənləbən] 人命；人的生命〈n.〉</t>
         </is>
       </c>
       <c r="C1372" s="1" t="inlineStr">
@@ -44317,7 +44317,7 @@
       </c>
       <c r="D1372" s="1" t="inlineStr">
         <is>
-          <t>人；人类；人类的；似人类的</t>
+          <t>人命；人的生命</t>
         </is>
       </c>
       <c r="E1372" s="1" t="inlineStr">
@@ -44339,7 +44339,7 @@
       </c>
       <c r="B1373" s="1" t="inlineStr">
         <is>
-          <t>[øːdə] 沙漠；应得的赏罚；功劳；沙漠的〈n.f.〉</t>
+          <t>[øːdə] 荒原；荒凉；单调乏味〈n.f.〉</t>
         </is>
       </c>
       <c r="C1373" s="1" t="inlineStr">
@@ -44349,7 +44349,7 @@
       </c>
       <c r="D1373" s="1" t="inlineStr">
         <is>
-          <t>沙漠；应得的赏罚；功劳；沙漠的</t>
+          <t>荒原；荒凉；单调乏味</t>
         </is>
       </c>
       <c r="E1373" s="1" t="inlineStr">
@@ -44563,7 +44563,7 @@
       </c>
       <c r="B1380" s="1" t="inlineStr">
         <is>
-          <t>[beːʁuːɪɡənt] 止痛药〈adv.〉</t>
+          <t>[beːʁuːɪɡənt] 令人宽慰的；让人安心的；镇静的〈adv.〉</t>
         </is>
       </c>
       <c r="C1380" s="1" t="inlineStr">
@@ -44573,7 +44573,7 @@
       </c>
       <c r="D1380" s="1" t="inlineStr">
         <is>
-          <t>止痛药</t>
+          <t>令人宽慰的；让人安心的；镇静的</t>
         </is>
       </c>
       <c r="E1380" s="1" t="inlineStr">
@@ -46067,7 +46067,7 @@
       </c>
       <c r="B1427" s="1" t="inlineStr">
         <is>
-          <t>[teːmən] 有特定主题的〈n.〉</t>
+          <t>[teːmən] 主题；课题；议题（复数）〈n.〉</t>
         </is>
       </c>
       <c r="C1427" s="1" t="inlineStr">
@@ -46077,7 +46077,7 @@
       </c>
       <c r="D1427" s="1" t="inlineStr">
         <is>
-          <t>有特定主题的</t>
+          <t>主题；课题；议题（复数）</t>
         </is>
       </c>
       <c r="E1427" s="1" t="inlineStr">
@@ -46547,7 +46547,7 @@
       </c>
       <c r="B1442" s="1" t="inlineStr">
         <is>
-          <t>[jɔɪnt] 连接处；接合；关节；共同的〈n.m.〉</t>
+          <t>[jɔɪnt] 大麻烟卷；接缝；接头〈n.m.〉</t>
         </is>
       </c>
       <c r="C1442" s="1" t="inlineStr">
@@ -46557,7 +46557,7 @@
       </c>
       <c r="D1442" s="1" t="inlineStr">
         <is>
-          <t>连接处；接合；关节；共同的</t>
+          <t>大麻烟卷；接缝；接头</t>
         </is>
       </c>
       <c r="E1442" s="1" t="inlineStr">
@@ -47123,7 +47123,7 @@
       </c>
       <c r="B1460" s="1" t="inlineStr">
         <is>
-          <t>[ɛnt͡ʃaɪdənt] 决定物〈adv.〉</t>
+          <t>[ɛnt͡ʃaɪdənt] 决定性的；至关紧要的〈adv.〉</t>
         </is>
       </c>
       <c r="C1460" s="1" t="inlineStr">
@@ -47133,7 +47133,7 @@
       </c>
       <c r="D1460" s="1" t="inlineStr">
         <is>
-          <t>决定物</t>
+          <t>决定性的；至关紧要的</t>
         </is>
       </c>
       <c r="E1460" s="1" t="inlineStr">
@@ -47347,7 +47347,7 @@
       </c>
       <c r="B1467" s="1" t="inlineStr">
         <is>
-          <t>[ʃvanɡəʁə] 怀孕的；充满的；思想丰富的〈n.f.〉</t>
+          <t>[ʃvanɡəʁə] 孕妇〈n.f.〉</t>
         </is>
       </c>
       <c r="C1467" s="1" t="inlineStr">
@@ -47357,7 +47357,7 @@
       </c>
       <c r="D1467" s="1" t="inlineStr">
         <is>
-          <t>怀孕的；充满的；思想丰富的</t>
+          <t>孕妇</t>
         </is>
       </c>
       <c r="E1467" s="1" t="inlineStr">
@@ -47699,7 +47699,7 @@
       </c>
       <c r="B1478" s="1" t="inlineStr">
         <is>
-          <t>[mɛnçən] 男人；雄性的〈n.〉</t>
+          <t>[mɛnçən] 雄性动物；小公兽；小男人〈n.〉</t>
         </is>
       </c>
       <c r="C1478" s="1" t="inlineStr">
@@ -47709,7 +47709,7 @@
       </c>
       <c r="D1478" s="1" t="inlineStr">
         <is>
-          <t>男人；雄性的</t>
+          <t>雄性动物；小公兽；小男人</t>
         </is>
       </c>
       <c r="E1478" s="1" t="inlineStr">
@@ -47763,7 +47763,7 @@
       </c>
       <c r="B1480" s="1" t="inlineStr">
         <is>
-          <t>[bɛamtɐ] 市民的；公民的；有礼貌的〈n.m.〉</t>
+          <t>[bɛamtɐ] 公务员；公职人员〈n.m.〉</t>
         </is>
       </c>
       <c r="C1480" s="1" t="inlineStr">
@@ -47773,7 +47773,7 @@
       </c>
       <c r="D1480" s="1" t="inlineStr">
         <is>
-          <t>市民的；公民的；有礼貌的</t>
+          <t>公务员；公职人员</t>
         </is>
       </c>
       <c r="E1480" s="1" t="inlineStr">
@@ -48211,7 +48211,7 @@
       </c>
       <c r="B1494" s="1" t="inlineStr">
         <is>
-          <t>[fɛʁmɛçtnɪs] 遗嘱的；据遗嘱的〈n.〉</t>
+          <t>[fɛʁmɛçtnɪs] 遗产；遗赠；遗愿〈n.〉</t>
         </is>
       </c>
       <c r="C1494" s="1" t="inlineStr">
@@ -48221,7 +48221,7 @@
       </c>
       <c r="D1494" s="1" t="inlineStr">
         <is>
-          <t>遗嘱的；据遗嘱的</t>
+          <t>遗产；遗赠；遗愿</t>
         </is>
       </c>
       <c r="E1494" s="1" t="inlineStr">
@@ -48339,7 +48339,7 @@
       </c>
       <c r="B1498" s="1" t="inlineStr">
         <is>
-          <t>[kaːpɪtaːl] 首都；大写字母；资本；首都的〈n.〉</t>
+          <t>[kaːpɪtaːl] 资本；资金；资产〈n.〉</t>
         </is>
       </c>
       <c r="C1498" s="1" t="inlineStr">
@@ -48349,7 +48349,7 @@
       </c>
       <c r="D1498" s="1" t="inlineStr">
         <is>
-          <t>首都；大写字母；资本；首都的</t>
+          <t>资本；资金；资产</t>
         </is>
       </c>
       <c r="E1498" s="1" t="inlineStr">
@@ -48755,7 +48755,7 @@
       </c>
       <c r="B1511" s="1" t="inlineStr">
         <is>
-          <t>[iːtaliːnɪʃə] 意大利语；意大利的〈n.〉</t>
+          <t>[iːtaliːnɪʃə] 意大利语；意大利风格〈n.〉</t>
         </is>
       </c>
       <c r="C1511" s="1" t="inlineStr">
@@ -48765,7 +48765,7 @@
       </c>
       <c r="D1511" s="1" t="inlineStr">
         <is>
-          <t>意大利语；意大利的</t>
+          <t>意大利语；意大利风格</t>
         </is>
       </c>
       <c r="E1511" s="1" t="inlineStr">
@@ -49139,7 +49139,7 @@
       </c>
       <c r="B1523" s="1" t="inlineStr">
         <is>
-          <t>[ʃtʊmə] 哑子；哑音字母；弱音器；哑的〈n.〉</t>
+          <t>[ʃtʊmə] 哑巴；哑人〈n.〉</t>
         </is>
       </c>
       <c r="C1523" s="1" t="inlineStr">
@@ -49149,7 +49149,7 @@
       </c>
       <c r="D1523" s="1" t="inlineStr">
         <is>
-          <t>哑子；哑音字母；弱音器；哑的</t>
+          <t>哑巴；哑人</t>
         </is>
       </c>
       <c r="E1523" s="1" t="inlineStr">
@@ -49555,7 +49555,7 @@
       </c>
       <c r="B1536" s="1" t="inlineStr">
         <is>
-          <t>[ɡeːmaɪnə] 通常的；共同的；通俗的〈n.〉</t>
+          <t>[ɡeːmaɪnə] 恶人；平民；下等人〈n.〉</t>
         </is>
       </c>
       <c r="C1536" s="1" t="inlineStr">
@@ -49565,7 +49565,7 @@
       </c>
       <c r="D1536" s="1" t="inlineStr">
         <is>
-          <t>通常的；共同的；通俗的</t>
+          <t>恶人；平民；下等人</t>
         </is>
       </c>
       <c r="E1536" s="1" t="inlineStr">
@@ -49651,7 +49651,7 @@
       </c>
       <c r="B1539" s="1" t="inlineStr">
         <is>
-          <t>[kʁɪstal] 水晶；水晶装饰品；结晶；水晶的〈n.m.〉</t>
+          <t>[kʁɪstal] 水晶；结晶体〈n.m.〉</t>
         </is>
       </c>
       <c r="C1539" s="1" t="inlineStr">
@@ -49661,7 +49661,7 @@
       </c>
       <c r="D1539" s="1" t="inlineStr">
         <is>
-          <t>水晶；水晶装饰品；结晶；水晶的</t>
+          <t>水晶；结晶体</t>
         </is>
       </c>
       <c r="E1539" s="1" t="inlineStr">
@@ -50099,7 +50099,7 @@
       </c>
       <c r="B1553" s="1" t="inlineStr">
         <is>
-          <t>[ɡeːʁɪnk] 一点点；少许；一会儿〈adv.〉</t>
+          <t>[ɡeːʁɪnk] 微小的；微弱的；少的〈adv.〉</t>
         </is>
       </c>
       <c r="C1553" s="1" t="inlineStr">
@@ -50109,7 +50109,7 @@
       </c>
       <c r="D1553" s="1" t="inlineStr">
         <is>
-          <t>一点点；少许；一会儿</t>
+          <t>微小的；微弱的；少的</t>
         </is>
       </c>
       <c r="E1553" s="1" t="inlineStr">
@@ -50995,7 +50995,7 @@
       </c>
       <c r="B1581" s="1" t="inlineStr">
         <is>
-          <t>[fantaziː] 想象力；幻想；喜好；想象的〈n.〉</t>
+          <t>[fantaziː] 想象力；幻想；奇想〈n.〉</t>
         </is>
       </c>
       <c r="C1581" s="1" t="inlineStr">
@@ -51005,7 +51005,7 @@
       </c>
       <c r="D1581" s="1" t="inlineStr">
         <is>
-          <t>想象力；幻想；喜好；想象的</t>
+          <t>想象力；幻想；奇想</t>
         </is>
       </c>
       <c r="E1581" s="1" t="inlineStr">
@@ -51219,7 +51219,7 @@
       </c>
       <c r="B1588" s="1" t="inlineStr">
         <is>
-          <t>[ɡʁaʊə] 灰色；灰色的〈n.〉</t>
+          <t>[ɡʁaʊə] 灰色事物；灰暗〈n.〉</t>
         </is>
       </c>
       <c r="C1588" s="1" t="inlineStr">
@@ -51229,7 +51229,7 @@
       </c>
       <c r="D1588" s="1" t="inlineStr">
         <is>
-          <t>灰色；灰色的</t>
+          <t>灰色事物；灰暗</t>
         </is>
       </c>
       <c r="E1588" s="1" t="inlineStr">
@@ -51667,7 +51667,7 @@
       </c>
       <c r="B1602" s="1" t="inlineStr">
         <is>
-          <t>[abstɪmən] 投票；选举；投票的；选举的〈n.〉</t>
+          <t>[abstɪmən] 投票表决；协调；调准〈n.〉</t>
         </is>
       </c>
       <c r="C1602" s="1" t="inlineStr">
@@ -51677,7 +51677,7 @@
       </c>
       <c r="D1602" s="1" t="inlineStr">
         <is>
-          <t>投票；选举；投票的；选举的</t>
+          <t>投票表决；协调；调准</t>
         </is>
       </c>
       <c r="E1602" s="1" t="inlineStr">
@@ -51763,7 +51763,7 @@
       </c>
       <c r="B1605" s="1" t="inlineStr">
         <is>
-          <t>[ʁʏk] 后面；背后；后方；后面的〈n.〉</t>
+          <t>[ʁʏk] 回程；退回；反向〈n.〉</t>
         </is>
       </c>
       <c r="C1605" s="1" t="inlineStr">
@@ -51773,7 +51773,7 @@
       </c>
       <c r="D1605" s="1" t="inlineStr">
         <is>
-          <t>后面；背后；后方；后面的</t>
+          <t>回程；退回；反向</t>
         </is>
       </c>
       <c r="E1605" s="1" t="inlineStr">
@@ -52435,7 +52435,7 @@
       </c>
       <c r="B1626" s="1" t="inlineStr">
         <is>
-          <t>[zɔʏxə] 传染病；传染性的〈n.f.〉</t>
+          <t>[zɔʏxə] 瘟疫；流行病；传染病〈n.f.〉</t>
         </is>
       </c>
       <c r="C1626" s="1" t="inlineStr">
@@ -52445,7 +52445,7 @@
       </c>
       <c r="D1626" s="1" t="inlineStr">
         <is>
-          <t>传染病；传染性的</t>
+          <t>瘟疫；流行病；传染病</t>
         </is>
       </c>
       <c r="E1626" s="1" t="inlineStr">
@@ -52467,7 +52467,7 @@
       </c>
       <c r="B1627" s="1" t="inlineStr">
         <is>
-          <t>[t͡saʊbəʁspʁuːx] 魔术；魔法；魔术的；有魔力的〈n.m.〉</t>
+          <t>[t͡saʊbəʁspʁuːx] 咒语；魔法口诀〈n.m.〉</t>
         </is>
       </c>
       <c r="C1627" s="1" t="inlineStr">
@@ -52477,7 +52477,7 @@
       </c>
       <c r="D1627" s="1" t="inlineStr">
         <is>
-          <t>魔术；魔法；魔术的；有魔力的</t>
+          <t>咒语；魔法口诀</t>
         </is>
       </c>
       <c r="E1627" s="1" t="inlineStr">
@@ -52819,7 +52819,7 @@
       </c>
       <c r="B1638" s="1" t="inlineStr">
         <is>
-          <t>[mɪtəlpʊnkt] 中心；中心点；中锋；中央的〈n.m.〉</t>
+          <t>[mɪtəlpʊnkt] 中心点；核心；焦点〈n.m.〉</t>
         </is>
       </c>
       <c r="C1638" s="1" t="inlineStr">
@@ -52829,7 +52829,7 @@
       </c>
       <c r="D1638" s="1" t="inlineStr">
         <is>
-          <t>中心；中心点；中锋；中央的</t>
+          <t>中心点；核心；焦点</t>
         </is>
       </c>
       <c r="E1638" s="1" t="inlineStr">
@@ -53171,7 +53171,7 @@
       </c>
       <c r="B1649" s="1" t="inlineStr">
         <is>
-          <t>[fɔʁmʊlaːɐ] 空格；空白；空白的；空虚的〈n.〉</t>
+          <t>[fɔʁmʊlaːɐ] 表格；表单〈n.〉</t>
         </is>
       </c>
       <c r="C1649" s="1" t="inlineStr">
@@ -53181,7 +53181,7 @@
       </c>
       <c r="D1649" s="1" t="inlineStr">
         <is>
-          <t>空格；空白；空白的；空虚的</t>
+          <t>表格；表单</t>
         </is>
       </c>
       <c r="E1649" s="1" t="inlineStr">
@@ -53779,7 +53779,7 @@
       </c>
       <c r="B1668" s="1" t="inlineStr">
         <is>
-          <t>[tɔnə] 公尺的；公制的；计量的；测量的〈n.f.〉</t>
+          <t>[tɔnə] 吨；大桶〈n.f.〉</t>
         </is>
       </c>
       <c r="C1668" s="1" t="inlineStr">
@@ -53789,7 +53789,7 @@
       </c>
       <c r="D1668" s="1" t="inlineStr">
         <is>
-          <t>公尺的；公制的；计量的；测量的</t>
+          <t>吨；大桶</t>
         </is>
       </c>
       <c r="E1668" s="1" t="inlineStr">
@@ -54419,7 +54419,7 @@
       </c>
       <c r="B1688" s="1" t="inlineStr">
         <is>
-          <t>[eːləktʁɪʃə] 电的；有关电的〈n.〉</t>
+          <t>[eːləktʁɪʃə] 电动车；电车；电〈n.〉</t>
         </is>
       </c>
       <c r="C1688" s="1" t="inlineStr">
@@ -54429,7 +54429,7 @@
       </c>
       <c r="D1688" s="1" t="inlineStr">
         <is>
-          <t>电的；有关电的</t>
+          <t>电动车；电车；电</t>
         </is>
       </c>
       <c r="E1688" s="1" t="inlineStr">
@@ -55187,7 +55187,7 @@
       </c>
       <c r="B1712" s="1" t="inlineStr">
         <is>
-          <t>[leːbənzʊntəʁhalt] 生活；生计；生存；活的〈n.m.〉</t>
+          <t>[leːbənzʊntəʁhalt] 生活费；生计〈n.m.〉</t>
         </is>
       </c>
       <c r="C1712" s="1" t="inlineStr">
@@ -55197,7 +55197,7 @@
       </c>
       <c r="D1712" s="1" t="inlineStr">
         <is>
-          <t>生活；生计；生存；活的</t>
+          <t>生活费；生计</t>
         </is>
       </c>
       <c r="E1712" s="1" t="inlineStr">
@@ -55283,7 +55283,7 @@
       </c>
       <c r="B1715" s="1" t="inlineStr">
         <is>
-          <t>[nʊməʁnʃɪlt] 分期连载作品；一连串的〈n.〉</t>
+          <t>[nʊməʁnʃɪlt] 车牌；车辆号牌〈n.〉</t>
         </is>
       </c>
       <c r="C1715" s="1" t="inlineStr">
@@ -55293,7 +55293,7 @@
       </c>
       <c r="D1715" s="1" t="inlineStr">
         <is>
-          <t>分期连载作品；一连串的</t>
+          <t>车牌；车辆号牌</t>
         </is>
       </c>
       <c r="E1715" s="1" t="inlineStr">
@@ -55379,7 +55379,7 @@
       </c>
       <c r="B1718" s="1" t="inlineStr">
         <is>
-          <t>[aʊtɔʁən] 著作者的〈n.〉</t>
+          <t>[aʊtɔʁən] 作者；作家（复数）〈n.〉</t>
         </is>
       </c>
       <c r="C1718" s="1" t="inlineStr">
@@ -55389,7 +55389,7 @@
       </c>
       <c r="D1718" s="1" t="inlineStr">
         <is>
-          <t>著作者的</t>
+          <t>作者；作家（复数）</t>
         </is>
       </c>
       <c r="E1718" s="1" t="inlineStr">
@@ -56403,7 +56403,7 @@
       </c>
       <c r="B1750" s="1" t="inlineStr">
         <is>
-          <t>[vaɪbliːç] 女性；女人〈adj.〉</t>
+          <t>[vaɪbliːç] 女性的；雌性的〈adj.〉</t>
         </is>
       </c>
       <c r="C1750" s="1" t="inlineStr">
@@ -56413,7 +56413,7 @@
       </c>
       <c r="D1750" s="1" t="inlineStr">
         <is>
-          <t>女性；女人</t>
+          <t>女性的；雌性的</t>
         </is>
       </c>
       <c r="E1750" s="1" t="inlineStr">
@@ -56563,7 +56563,7 @@
       </c>
       <c r="B1755" s="1" t="inlineStr">
         <is>
-          <t>[aɪnzamɐ] 独居的〈n.〉</t>
+          <t>[aɪnzamɐ] 孤独者；独行侠〈n.〉</t>
         </is>
       </c>
       <c r="C1755" s="1" t="inlineStr">
@@ -56573,7 +56573,7 @@
       </c>
       <c r="D1755" s="1" t="inlineStr">
         <is>
-          <t>独居的</t>
+          <t>孤独者；独行侠</t>
         </is>
       </c>
       <c r="E1755" s="1" t="inlineStr">
@@ -57043,7 +57043,7 @@
       </c>
       <c r="B1770" s="1" t="inlineStr">
         <is>
-          <t>[t͡svaɪɐ] 两党的〈n.〉</t>
+          <t>[t͡svaɪɐ] 两人组；二重奏；双人艇〈n.〉</t>
         </is>
       </c>
       <c r="C1770" s="1" t="inlineStr">
@@ -57053,7 +57053,7 @@
       </c>
       <c r="D1770" s="1" t="inlineStr">
         <is>
-          <t>两党的</t>
+          <t>两人组；二重奏；双人艇</t>
         </is>
       </c>
       <c r="E1770" s="1" t="inlineStr">
@@ -57523,7 +57523,7 @@
       </c>
       <c r="B1785" s="1" t="inlineStr">
         <is>
-          <t>[klɪpə] 海岸的；沿海的；沿岸的〈n.f.〉</t>
+          <t>[klɪpə] 悬崖；峭壁；暗礁〈n.f.〉</t>
         </is>
       </c>
       <c r="C1785" s="1" t="inlineStr">
@@ -57533,7 +57533,7 @@
       </c>
       <c r="D1785" s="1" t="inlineStr">
         <is>
-          <t>海岸的；沿海的；沿岸的</t>
+          <t>悬崖；峭壁；暗礁</t>
         </is>
       </c>
       <c r="E1785" s="1" t="inlineStr">
@@ -57747,7 +57747,7 @@
       </c>
       <c r="B1792" s="1" t="inlineStr">
         <is>
-          <t>[ɛʁfɔlɡʁaɪçə] 乐队彩车；流行〈adv.〉</t>
+          <t>[ɛʁfɔlɡʁaɪçə] 成功的〈adv.〉</t>
         </is>
       </c>
       <c r="C1792" s="1" t="inlineStr">
@@ -57757,7 +57757,7 @@
       </c>
       <c r="D1792" s="1" t="inlineStr">
         <is>
-          <t>乐队彩车；流行</t>
+          <t>成功的</t>
         </is>
       </c>
       <c r="E1792" s="1" t="inlineStr">
@@ -57779,7 +57779,7 @@
       </c>
       <c r="B1793" s="1" t="inlineStr">
         <is>
-          <t>[ɪmpfstɔf] 牛痘苗；疫苗；疫苗的；牛痘的〈n.m.〉</t>
+          <t>[ɪmpfstɔf] 疫苗〈n.m.〉</t>
         </is>
       </c>
       <c r="C1793" s="1" t="inlineStr">
@@ -57789,7 +57789,7 @@
       </c>
       <c r="D1793" s="1" t="inlineStr">
         <is>
-          <t>牛痘苗；疫苗；疫苗的；牛痘的</t>
+          <t>疫苗</t>
         </is>
       </c>
       <c r="E1793" s="1" t="inlineStr">
@@ -57811,7 +57811,7 @@
       </c>
       <c r="B1794" s="1" t="inlineStr">
         <is>
-          <t>[bɛstəçʊnk] 活跃的；起作用的；积极的〈n.f.〉</t>
+          <t>[bɛstəçʊnk] 贿赂；行贿；受贿〈n.f.〉</t>
         </is>
       </c>
       <c r="C1794" s="1" t="inlineStr">
@@ -57821,7 +57821,7 @@
       </c>
       <c r="D1794" s="1" t="inlineStr">
         <is>
-          <t>活跃的；起作用的；积极的</t>
+          <t>贿赂；行贿；受贿</t>
         </is>
       </c>
       <c r="E1794" s="1" t="inlineStr">
@@ -57875,7 +57875,7 @@
       </c>
       <c r="B1796" s="1" t="inlineStr">
         <is>
-          <t>[kaːzɪnɔ] 受委任的；现役的〈n.〉</t>
+          <t>[kaːzɪnɔ] 赌场；军官俱乐部〈n.〉</t>
         </is>
       </c>
       <c r="C1796" s="1" t="inlineStr">
@@ -57885,7 +57885,7 @@
       </c>
       <c r="D1796" s="1" t="inlineStr">
         <is>
-          <t>受委任的；现役的</t>
+          <t>赌场；军官俱乐部</t>
         </is>
       </c>
       <c r="E1796" s="1" t="inlineStr">
@@ -58419,7 +58419,7 @@
       </c>
       <c r="B1813" s="1" t="inlineStr">
         <is>
-          <t>[aʊsbʁəçən] 脱离；一碰就散开；脱落的〈n.〉</t>
+          <t>[aʊsbʁəçən] 逃脱；突围；爆发〈n.〉</t>
         </is>
       </c>
       <c r="C1813" s="1" t="inlineStr">
@@ -58429,7 +58429,7 @@
       </c>
       <c r="D1813" s="1" t="inlineStr">
         <is>
-          <t>脱离；一碰就散开；脱落的</t>
+          <t>逃脱；突围；爆发</t>
         </is>
       </c>
       <c r="E1813" s="1" t="inlineStr">
@@ -59187,7 +59187,7 @@
       </c>
       <c r="B1837" s="1" t="inlineStr">
         <is>
-          <t>[fliːɡəndə] 眼睛；视力；看〈adv.〉</t>
+          <t>[fliːɡəndə] 飞行的；飞翔的〈adv.〉</t>
         </is>
       </c>
       <c r="C1837" s="1" t="inlineStr">
@@ -59197,7 +59197,7 @@
       </c>
       <c r="D1837" s="1" t="inlineStr">
         <is>
-          <t>眼睛；视力；看</t>
+          <t>飞行的；飞翔的</t>
         </is>
       </c>
       <c r="E1837" s="1" t="inlineStr">
@@ -59347,7 +59347,7 @@
       </c>
       <c r="B1842" s="1" t="inlineStr">
         <is>
-          <t>[maːnʊskʁɪpt] 手稿；原稿；底稿；手写的〈n.〉</t>
+          <t>[maːnʊskʁɪpt] 手稿；原稿；底稿〈n.〉</t>
         </is>
       </c>
       <c r="C1842" s="1" t="inlineStr">
@@ -59357,7 +59357,7 @@
       </c>
       <c r="D1842" s="1" t="inlineStr">
         <is>
-          <t>手稿；原稿；底稿；手写的</t>
+          <t>手稿；原稿；底稿</t>
         </is>
       </c>
       <c r="E1842" s="1" t="inlineStr">
@@ -59443,7 +59443,7 @@
       </c>
       <c r="B1845" s="1" t="inlineStr">
         <is>
-          <t>[ʁeːdʊt͡siːʁən] 尖端细的〈n.〉</t>
+          <t>[ʁeːdʊt͡siːʁən] 缩减；降低；削减〈n.〉</t>
         </is>
       </c>
       <c r="C1845" s="1" t="inlineStr">
@@ -59453,7 +59453,7 @@
       </c>
       <c r="D1845" s="1" t="inlineStr">
         <is>
-          <t>尖端细的</t>
+          <t>缩减；降低；削减</t>
         </is>
       </c>
       <c r="E1845" s="1" t="inlineStr">
@@ -59891,7 +59891,7 @@
       </c>
       <c r="B1859" s="1" t="inlineStr">
         <is>
-          <t>[ɡeːmaɪnɐ] 金的；含金的；金色的〈n.〉</t>
+          <t>[ɡeːmaɪnɐ] 普通人；士兵〈n.〉</t>
         </is>
       </c>
       <c r="C1859" s="1" t="inlineStr">
@@ -59901,7 +59901,7 @@
       </c>
       <c r="D1859" s="1" t="inlineStr">
         <is>
-          <t>金的；含金的；金色的</t>
+          <t>普通人；士兵</t>
         </is>
       </c>
       <c r="E1859" s="1" t="inlineStr">
@@ -60979,7 +60979,7 @@
       </c>
       <c r="B1893" s="1" t="inlineStr">
         <is>
-          <t>[ɡʁyːnɐ] 红的；红色的；红肿的〈n.〉</t>
+          <t>[ɡʁyːnɐ] 绿党成员；绿色的人〈n.〉</t>
         </is>
       </c>
       <c r="C1893" s="1" t="inlineStr">
@@ -60989,7 +60989,7 @@
       </c>
       <c r="D1893" s="1" t="inlineStr">
         <is>
-          <t>红的；红色的；红肿的</t>
+          <t>绿党成员；绿色的人</t>
         </is>
       </c>
       <c r="E1893" s="1" t="inlineStr">
@@ -61299,7 +61299,7 @@
       </c>
       <c r="B1903" s="1" t="inlineStr">
         <is>
-          <t>[aɪnt͡səlhaft] 独居的〈n.f.〉</t>
+          <t>[aɪnt͡səlhaft] 单独监禁；关禁闭〈n.f.〉</t>
         </is>
       </c>
       <c r="C1903" s="1" t="inlineStr">
@@ -61309,7 +61309,7 @@
       </c>
       <c r="D1903" s="1" t="inlineStr">
         <is>
-          <t>独居的</t>
+          <t>单独监禁；关禁闭</t>
         </is>
       </c>
       <c r="E1903" s="1" t="inlineStr">
@@ -61619,7 +61619,7 @@
       </c>
       <c r="B1913" s="1" t="inlineStr">
         <is>
-          <t>[ʃɪfs] 舰队；水兵；海景画；海的〈n.〉</t>
+          <t>[ʃɪfs] 船舶；船只（属格/构词成分）〈n.〉</t>
         </is>
       </c>
       <c r="C1913" s="1" t="inlineStr">
@@ -61629,7 +61629,7 @@
       </c>
       <c r="D1913" s="1" t="inlineStr">
         <is>
-          <t>舰队；水兵；海景画；海的</t>
+          <t>船舶；船只（属格/构词成分）</t>
         </is>
       </c>
       <c r="E1913" s="1" t="inlineStr">
@@ -61811,7 +61811,7 @@
       </c>
       <c r="B1919" s="1" t="inlineStr">
         <is>
-          <t>[ʁɪndɐ] 牛的；似牛的；迟钝的〈n.〉</t>
+          <t>[ʁɪndɐ] 牛；肉牛（复数）〈n.〉</t>
         </is>
       </c>
       <c r="C1919" s="1" t="inlineStr">
@@ -61821,7 +61821,7 @@
       </c>
       <c r="D1919" s="1" t="inlineStr">
         <is>
-          <t>牛的；似牛的；迟钝的</t>
+          <t>牛；肉牛（复数）</t>
         </is>
       </c>
       <c r="E1919" s="1" t="inlineStr">
@@ -63187,7 +63187,7 @@
       </c>
       <c r="B1962" s="1" t="inlineStr">
         <is>
-          <t>[handfɔl] 少数；一把；棘手事〈adj.〉</t>
+          <t>[handfɔl] 一把；一小撮〈adj.〉</t>
         </is>
       </c>
       <c r="C1962" s="1" t="inlineStr">
@@ -63197,7 +63197,7 @@
       </c>
       <c r="D1962" s="1" t="inlineStr">
         <is>
-          <t>少数；一把；棘手事</t>
+          <t>一把；一小撮</t>
         </is>
       </c>
       <c r="E1962" s="1" t="inlineStr">
@@ -64179,7 +64179,7 @@
       </c>
       <c r="B1993" s="1" t="inlineStr">
         <is>
-          <t>[zoːfɔʁtɪɡə] 污点；地点；斑点〈adv.〉</t>
+          <t>[zoːfɔʁtɪɡə] 立即的；即刻的〈adv.〉</t>
         </is>
       </c>
       <c r="C1993" s="1" t="inlineStr">
@@ -64189,7 +64189,7 @@
       </c>
       <c r="D1993" s="1" t="inlineStr">
         <is>
-          <t>污点；地点；斑点</t>
+          <t>立即的；即刻的</t>
         </is>
       </c>
       <c r="E1993" s="1" t="inlineStr">
@@ -64403,7 +64403,7 @@
       </c>
       <c r="B2000" s="1" t="inlineStr">
         <is>
-          <t>[jaːdə] 玉；翡翠；老马；绿色的〈n.〉</t>
+          <t>[jaːdə] 玉；翡翠〈n.〉</t>
         </is>
       </c>
       <c r="C2000" s="1" t="inlineStr">
@@ -64413,7 +64413,7 @@
       </c>
       <c r="D2000" s="1" t="inlineStr">
         <is>
-          <t>玉；翡翠；老马；绿色的</t>
+          <t>玉；翡翠</t>
         </is>
       </c>
       <c r="E2000" s="1" t="inlineStr">
@@ -65267,7 +65267,7 @@
       </c>
       <c r="B2027" s="1" t="inlineStr">
         <is>
-          <t>[lanɡzamə] 荷兰人〈adv.〉</t>
+          <t>[lanɡzamə] 缓慢的〈adv.〉</t>
         </is>
       </c>
       <c r="C2027" s="1" t="inlineStr">
@@ -65277,7 +65277,7 @@
       </c>
       <c r="D2027" s="1" t="inlineStr">
         <is>
-          <t>荷兰人</t>
+          <t>缓慢的</t>
         </is>
       </c>
       <c r="E2027" s="1" t="inlineStr">
@@ -66675,7 +66675,7 @@
       </c>
       <c r="B2071" s="1" t="inlineStr">
         <is>
-          <t>[ʁøːmɪʃə] 罗马的〈n.〉</t>
+          <t>[ʁøːmɪʃə] 罗马事物；罗马风格〈n.〉</t>
         </is>
       </c>
       <c r="C2071" s="1" t="inlineStr">
@@ -66685,7 +66685,7 @@
       </c>
       <c r="D2071" s="1" t="inlineStr">
         <is>
-          <t>罗马的</t>
+          <t>罗马事物；罗马风格</t>
         </is>
       </c>
       <c r="E2071" s="1" t="inlineStr">
@@ -67667,7 +67667,7 @@
       </c>
       <c r="B2102" s="1" t="inlineStr">
         <is>
-          <t>[bluːtɪç] 出血；流血；渗色〈adj.〉</t>
+          <t>[bluːtɪç] 流血的；血腥的；残暴的〈adj.〉</t>
         </is>
       </c>
       <c r="C2102" s="1" t="inlineStr">
@@ -67677,7 +67677,7 @@
       </c>
       <c r="D2102" s="1" t="inlineStr">
         <is>
-          <t>出血；流血；渗色</t>
+          <t>流血的；血腥的；残暴的</t>
         </is>
       </c>
       <c r="E2102" s="1" t="inlineStr">
@@ -67763,7 +67763,7 @@
       </c>
       <c r="B2105" s="1" t="inlineStr">
         <is>
-          <t>[ʊnbəkantɐ] 不知道的；未知的〈n.〉</t>
+          <t>[ʊnbəkantɐ] 陌生人；无名氏〈n.〉</t>
         </is>
       </c>
       <c r="C2105" s="1" t="inlineStr">
@@ -67773,7 +67773,7 @@
       </c>
       <c r="D2105" s="1" t="inlineStr">
         <is>
-          <t>不知道的；未知的</t>
+          <t>陌生人；无名氏</t>
         </is>
       </c>
       <c r="E2105" s="1" t="inlineStr">
@@ -68051,7 +68051,7 @@
       </c>
       <c r="B2114" s="1" t="inlineStr">
         <is>
-          <t>[t͡svɪlɪnk] 双胞胎中一人；成对的〈n.m.〉</t>
+          <t>[t͡svɪlɪnk] 双胞胎之一；孪生儿〈n.m.〉</t>
         </is>
       </c>
       <c r="C2114" s="1" t="inlineStr">
@@ -68061,7 +68061,7 @@
       </c>
       <c r="D2114" s="1" t="inlineStr">
         <is>
-          <t>双胞胎中一人；成对的</t>
+          <t>双胞胎之一；孪生儿</t>
         </is>
       </c>
       <c r="E2114" s="1" t="inlineStr">
@@ -68531,7 +68531,7 @@
       </c>
       <c r="B2129" s="1" t="inlineStr">
         <is>
-          <t>[ɔf] 台后；幕内；台后的；幕内的〈n.〉</t>
+          <t>[ɔf] 画外音；幕后；场外〈n.〉</t>
         </is>
       </c>
       <c r="C2129" s="1" t="inlineStr">
@@ -68541,7 +68541,7 @@
       </c>
       <c r="D2129" s="1" t="inlineStr">
         <is>
-          <t>台后；幕内；台后的；幕内的</t>
+          <t>画外音；幕后；场外</t>
         </is>
       </c>
       <c r="E2129" s="1" t="inlineStr">
@@ -68723,7 +68723,7 @@
       </c>
       <c r="B2135" s="1" t="inlineStr">
         <is>
-          <t>[ʃvaɪnçən] 小猪；贪心的；似猪的；邋遢的〈n.〉</t>
+          <t>[ʃvaɪnçən] 小猪；乳猪〈n.〉</t>
         </is>
       </c>
       <c r="C2135" s="1" t="inlineStr">
@@ -68733,7 +68733,7 @@
       </c>
       <c r="D2135" s="1" t="inlineStr">
         <is>
-          <t>小猪；贪心的；似猪的；邋遢的</t>
+          <t>小猪；乳猪</t>
         </is>
       </c>
       <c r="E2135" s="1" t="inlineStr">
@@ -68755,7 +68755,7 @@
       </c>
       <c r="B2136" s="1" t="inlineStr">
         <is>
-          <t>[dɪʁk] 极好的；主要的〈n.f.〉</t>
+          <t>[dɪʁk] 迪克（男子名）；短剑〈n.f.〉</t>
         </is>
       </c>
       <c r="C2136" s="1" t="inlineStr">
@@ -68765,7 +68765,7 @@
       </c>
       <c r="D2136" s="1" t="inlineStr">
         <is>
-          <t>极好的；主要的</t>
+          <t>迪克（男子名）；短剑</t>
         </is>
       </c>
       <c r="E2136" s="1" t="inlineStr">
@@ -68819,7 +68819,7 @@
       </c>
       <c r="B2138" s="1" t="inlineStr">
         <is>
-          <t>[flɛʃçən] 小的；少的；小型的〈n.〉</t>
+          <t>[flɛʃçən] 小瓶；小药瓶；小奶瓶〈n.〉</t>
         </is>
       </c>
       <c r="C2138" s="1" t="inlineStr">
@@ -68829,7 +68829,7 @@
       </c>
       <c r="D2138" s="1" t="inlineStr">
         <is>
-          <t>小的；少的；小型的</t>
+          <t>小瓶；小药瓶；小奶瓶</t>
         </is>
       </c>
       <c r="E2138" s="1" t="inlineStr">
@@ -69395,7 +69395,7 @@
       </c>
       <c r="B2156" s="1" t="inlineStr">
         <is>
-          <t>[fɛʁʃlʏsəlt] 秘密成员；秘密赞同者〈adj.〉</t>
+          <t>[fɛʁʃlʏsəlt] 加密的；编码的〈adj.〉</t>
         </is>
       </c>
       <c r="C2156" s="1" t="inlineStr">
@@ -69405,7 +69405,7 @@
       </c>
       <c r="D2156" s="1" t="inlineStr">
         <is>
-          <t>秘密成员；秘密赞同者</t>
+          <t>加密的；编码的</t>
         </is>
       </c>
       <c r="E2156" s="1" t="inlineStr">
@@ -69779,7 +69779,7 @@
       </c>
       <c r="B2168" s="1" t="inlineStr">
         <is>
-          <t>[viːdɐ] 踢；反冲；后座力〈adv.〉</t>
+          <t>[viːdɐ] 反对；违背〈adv.〉</t>
         </is>
       </c>
       <c r="C2168" s="1" t="inlineStr">
@@ -69789,7 +69789,7 @@
       </c>
       <c r="D2168" s="1" t="inlineStr">
         <is>
-          <t>踢；反冲；后座力</t>
+          <t>反对；违背</t>
         </is>
       </c>
       <c r="E2168" s="1" t="inlineStr">
@@ -70259,7 +70259,7 @@
       </c>
       <c r="B2183" s="1" t="inlineStr">
         <is>
-          <t>[ɪntʊɪt͡sjoːn] 直觉的〈n.f.〉</t>
+          <t>[ɪntʊɪt͡sjoːn] 直觉；第六感〈n.f.〉</t>
         </is>
       </c>
       <c r="C2183" s="1" t="inlineStr">
@@ -70269,7 +70269,7 @@
       </c>
       <c r="D2183" s="1" t="inlineStr">
         <is>
-          <t>直觉的</t>
+          <t>直觉；第六感</t>
         </is>
       </c>
       <c r="E2183" s="1" t="inlineStr">
@@ -70611,7 +70611,7 @@
       </c>
       <c r="B2194" s="1" t="inlineStr">
         <is>
-          <t>[koːpiːʁən] 誊写；复写；仿形的〈n.〉</t>
+          <t>[koːpiːʁən] 复印；复制；拷贝〈n.〉</t>
         </is>
       </c>
       <c r="C2194" s="1" t="inlineStr">
@@ -70621,7 +70621,7 @@
       </c>
       <c r="D2194" s="1" t="inlineStr">
         <is>
-          <t>誊写；复写；仿形的</t>
+          <t>复印；复制；拷贝</t>
         </is>
       </c>
       <c r="E2194" s="1" t="inlineStr">
@@ -70675,7 +70675,7 @@
       </c>
       <c r="B2196" s="1" t="inlineStr">
         <is>
-          <t>[beːʁatʊnk] 商议的；咨询的；任专职顾问的〈n.f.〉</t>
+          <t>[beːʁatʊnk] 咨询；协商；顾问服务〈n.f.〉</t>
         </is>
       </c>
       <c r="C2196" s="1" t="inlineStr">
@@ -70685,7 +70685,7 @@
       </c>
       <c r="D2196" s="1" t="inlineStr">
         <is>
-          <t>商议的；咨询的；任专职顾问的</t>
+          <t>咨询；协商；顾问服务</t>
         </is>
       </c>
       <c r="E2196" s="1" t="inlineStr">
@@ -72179,7 +72179,7 @@
       </c>
       <c r="B2243" s="1" t="inlineStr">
         <is>
-          <t>[ɡlat͡sə] 秃头的；光秃的；单调的〈n.f.〉</t>
+          <t>[ɡlat͡sə] 秃顶；光头〈n.f.〉</t>
         </is>
       </c>
       <c r="C2243" s="1" t="inlineStr">
@@ -72189,7 +72189,7 @@
       </c>
       <c r="D2243" s="1" t="inlineStr">
         <is>
-          <t>秃头的；光秃的；单调的</t>
+          <t>秃顶；光头</t>
         </is>
       </c>
       <c r="E2243" s="1" t="inlineStr">
@@ -72467,7 +72467,7 @@
       </c>
       <c r="B2252" s="1" t="inlineStr">
         <is>
-          <t>[ɛmpfɛnɡɐ] 领受的；容易接受的〈n.m.〉</t>
+          <t>[ɛmpfɛnɡɐ] 收件人；接收者；接收机〈n.m.〉</t>
         </is>
       </c>
       <c r="C2252" s="1" t="inlineStr">
@@ -72477,7 +72477,7 @@
       </c>
       <c r="D2252" s="1" t="inlineStr">
         <is>
-          <t>领受的；容易接受的</t>
+          <t>收件人；接收者；接收机</t>
         </is>
       </c>
       <c r="E2252" s="1" t="inlineStr">
@@ -72659,7 +72659,7 @@
       </c>
       <c r="B2258" s="1" t="inlineStr">
         <is>
-          <t>[ɡeːnətɪʃ] 创始；遗传学；生殖〈adj.〉</t>
+          <t>[ɡeːnətɪʃ] 基因的；遗传的〈adj.〉</t>
         </is>
       </c>
       <c r="C2258" s="1" t="inlineStr">
@@ -72669,7 +72669,7 @@
       </c>
       <c r="D2258" s="1" t="inlineStr">
         <is>
-          <t>创始；遗传学；生殖</t>
+          <t>基因的；遗传的</t>
         </is>
       </c>
       <c r="E2258" s="1" t="inlineStr">
@@ -74579,7 +74579,7 @@
       </c>
       <c r="B2318" s="1" t="inlineStr">
         <is>
-          <t>[ʁeːpʊblɪkanɐ] 共和主义者；共和国的〈n.m.〉</t>
+          <t>[ʁeːpʊblɪkanɐ] 共和党人；共和主义者〈n.m.〉</t>
         </is>
       </c>
       <c r="C2318" s="1" t="inlineStr">
@@ -74589,7 +74589,7 @@
       </c>
       <c r="D2318" s="1" t="inlineStr">
         <is>
-          <t>共和主义者；共和国的</t>
+          <t>共和党人；共和主义者</t>
         </is>
       </c>
       <c r="E2318" s="1" t="inlineStr">
@@ -74707,7 +74707,7 @@
       </c>
       <c r="B2322" s="1" t="inlineStr">
         <is>
-          <t>[beːtoːn] 凝结物；实在的〈n.m.〉</t>
+          <t>[beːtoːn] 混凝土〈n.m.〉</t>
         </is>
       </c>
       <c r="C2322" s="1" t="inlineStr">
@@ -74717,7 +74717,7 @@
       </c>
       <c r="D2322" s="1" t="inlineStr">
         <is>
-          <t>凝结物；实在的</t>
+          <t>混凝土</t>
         </is>
       </c>
       <c r="E2322" s="1" t="inlineStr">
@@ -74931,7 +74931,7 @@
       </c>
       <c r="B2329" s="1" t="inlineStr">
         <is>
-          <t>[ɔʏsəʁə] 外面；外表；外界；外面的〈n.〉</t>
+          <t>[ɔʏsəʁə] 外表；外貌；外部〈n.〉</t>
         </is>
       </c>
       <c r="C2329" s="1" t="inlineStr">
@@ -74941,7 +74941,7 @@
       </c>
       <c r="D2329" s="1" t="inlineStr">
         <is>
-          <t>外面；外表；外界；外面的</t>
+          <t>外表；外貌；外部</t>
         </is>
       </c>
       <c r="E2329" s="1" t="inlineStr">
@@ -75283,7 +75283,7 @@
       </c>
       <c r="B2340" s="1" t="inlineStr">
         <is>
-          <t>[fʏlə] 充分；很多；丰富；很多的〈n.f.〉</t>
+          <t>[fʏlə] 丰富；充沛；大量〈n.f.〉</t>
         </is>
       </c>
       <c r="C2340" s="1" t="inlineStr">
@@ -75293,7 +75293,7 @@
       </c>
       <c r="D2340" s="1" t="inlineStr">
         <is>
-          <t>充分；很多；丰富；很多的</t>
+          <t>丰富；充沛；大量</t>
         </is>
       </c>
       <c r="E2340" s="1" t="inlineStr">
@@ -75539,7 +75539,7 @@
       </c>
       <c r="B2348" s="1" t="inlineStr">
         <is>
-          <t>[kɔntɪnənt] 大陆；洲；自制的〈n.m.〉</t>
+          <t>[kɔntɪnənt] 大陆；大洲〈n.m.〉</t>
         </is>
       </c>
       <c r="C2348" s="1" t="inlineStr">
@@ -75549,7 +75549,7 @@
       </c>
       <c r="D2348" s="1" t="inlineStr">
         <is>
-          <t>大陆；洲；自制的</t>
+          <t>大陆；大洲</t>
         </is>
       </c>
       <c r="E2348" s="1" t="inlineStr">
@@ -76051,7 +76051,7 @@
       </c>
       <c r="B2364" s="1" t="inlineStr">
         <is>
-          <t>[vɪndəl] 尿布；菜盆；起毛的；多毛的〈n.f.〉</t>
+          <t>[vɪndəl] 尿布；纸尿裤〈n.f.〉</t>
         </is>
       </c>
       <c r="C2364" s="1" t="inlineStr">
@@ -76061,7 +76061,7 @@
       </c>
       <c r="D2364" s="1" t="inlineStr">
         <is>
-          <t>尿布；菜盆；起毛的；多毛的</t>
+          <t>尿布；纸尿裤</t>
         </is>
       </c>
       <c r="E2364" s="1" t="inlineStr">

--- a/languages/de/output/import/德语B1.xlsx
+++ b/languages/de/output/import/德语B1.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="词汇表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="词汇表" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="B7" s="1" t="inlineStr">
         <is>
-          <t>[aʊsaɡən] 谓语；使基于〈v.〉</t>
+          <t>[aʊsaɡən] 陈述；作证；说明〈v.〉</t>
         </is>
       </c>
       <c r="C7" s="1" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
-          <t>谓语；使基于</t>
+          <t>陈述；作证；说明</t>
         </is>
       </c>
       <c r="E7" s="1" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>[dɪamantən] 钻石；菱形〈adj.〉</t>
+          <t>[dɪamantən] Diamant（钻石）的变格形式；形容词形式为 diamantenen（钻石的）〈adj.〉</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
-          <t>钻石；菱形</t>
+          <t>Diamant（钻石）的变格形式；形容词形式为 diamantenen（钻石的）</t>
         </is>
       </c>
       <c r="E12" s="1" t="inlineStr">
@@ -851,7 +851,7 @@
       </c>
       <c r="B14" s="1" t="inlineStr">
         <is>
-          <t>[fɛʁzət͡st] 的变〈adv.〉</t>
+          <t>[fɛʁzət͡st] 错开的；移置的〈adv.〉</t>
         </is>
       </c>
       <c r="C14" s="1" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
-          <t>的变</t>
+          <t>错开的；移置的</t>
         </is>
       </c>
       <c r="E14" s="1" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>[leːp] 活；生活（口语词干）〈n.〉</t>
+          <t>[leːp] 应为 Leben：生命；生活〈n.〉〈n.〉</t>
         </is>
       </c>
       <c r="C17" s="1" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
-          <t>活；生活（口语词干）</t>
+          <t>应为 Leben：生命；生活〈n.〉</t>
         </is>
       </c>
       <c r="E17" s="1" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B19" s="1" t="inlineStr">
         <is>
-          <t>[ɡɛtʁaɡən] 怠惰的；疲倦的；无力的〈v.〉</t>
+          <t>[ɡɛtʁaɡən] 携带的；穿戴的；庄重的〈v.〉</t>
         </is>
       </c>
       <c r="C19" s="1" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="D19" s="1" t="inlineStr">
         <is>
-          <t>怠惰的；疲倦的；无力的</t>
+          <t>携带的；穿戴的；庄重的</t>
         </is>
       </c>
       <c r="E19" s="1" t="inlineStr">
@@ -1075,7 +1075,7 @@
       </c>
       <c r="B21" s="1" t="inlineStr">
         <is>
-          <t>[ɡeːnaʊɐ] 更多；多的；程度较大的〈adv.〉</t>
+          <t>[ɡeːnaʊɐ] 更精确的；更准确的〈adv.〉</t>
         </is>
       </c>
       <c r="C21" s="1" t="inlineStr">
@@ -1085,7 +1085,7 @@
       </c>
       <c r="D21" s="1" t="inlineStr">
         <is>
-          <t>更多；多的；程度较大的</t>
+          <t>更精确的；更准确的</t>
         </is>
       </c>
       <c r="E21" s="1" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="B22" s="1" t="inlineStr">
         <is>
-          <t>[fʁɔʏ] 不要；禁忌〈n.〉</t>
+          <t>[fʁɔʏ] 非标准词条，应为 Freude（快乐）〈n.〉</t>
         </is>
       </c>
       <c r="C22" s="1" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
-          <t>不要；禁忌</t>
+          <t>非标准词条，应为 Freude（快乐）</t>
         </is>
       </c>
       <c r="E22" s="1" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="B24" s="1" t="inlineStr">
         <is>
-          <t>[taʃən] 掌上型；手持型〈n.〉</t>
+          <t>[taʃən] 口袋；袋子；提包〈n.〉</t>
         </is>
       </c>
       <c r="C24" s="1" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="D24" s="1" t="inlineStr">
         <is>
-          <t>掌上型；手持型</t>
+          <t>口袋；袋子；提包</t>
         </is>
       </c>
       <c r="E24" s="1" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="B25" s="1" t="inlineStr">
         <is>
-          <t>[ɡeːnʏɡt] 意志；决心；意愿〈n.〉</t>
+          <t>[ɡeːnʏɡt] 足够；足以；满足〈n.〉</t>
         </is>
       </c>
       <c r="C25" s="1" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="D25" s="1" t="inlineStr">
         <is>
-          <t>意志；决心；意愿</t>
+          <t>足够；足以；满足</t>
         </is>
       </c>
       <c r="E25" s="1" t="inlineStr">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="B27" s="1" t="inlineStr">
         <is>
-          <t>[fʁant͡sɔzən] 青蛙〈n.〉</t>
+          <t>[fʁant͡sɔzən] 法国人〈n.〉</t>
         </is>
       </c>
       <c r="C27" s="1" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
-          <t>青蛙</t>
+          <t>法国人</t>
         </is>
       </c>
       <c r="E27" s="1" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="B28" s="1" t="inlineStr">
         <is>
-          <t>[dʊnkəln] 深奥地；鲜为人知地；隐秘地〈adv.〉</t>
+          <t>[dʊnkəln] 变暗；变黑；天色变暗〈adv.〉</t>
         </is>
       </c>
       <c r="C28" s="1" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="D28" s="1" t="inlineStr">
         <is>
-          <t>深奥地；鲜为人知地；隐秘地</t>
+          <t>变暗；变黑；天色变暗</t>
         </is>
       </c>
       <c r="E28" s="1" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="B29" s="1" t="inlineStr">
         <is>
-          <t>[ʁɔlən] 卷；滚动；名单〈n.〉</t>
+          <t>[ʁɔlən] 卷；滚轮；角色（Rolle的复数）〈n.f.〉〈n.〉</t>
         </is>
       </c>
       <c r="C29" s="1" t="inlineStr">
@@ -1341,7 +1341,7 @@
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
-          <t>卷；滚动；名单</t>
+          <t>卷；滚轮；角色（Rolle的复数）〈n.f.〉</t>
         </is>
       </c>
       <c r="E29" s="1" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="B31" s="1" t="inlineStr">
         <is>
-          <t>[zʏndən] 邪恶；罪恶；祸害〈n.〉</t>
+          <t>[zʏndən] 罪孽；罪恶（Sünde 的复数）〈n.f.〉〈n.〉</t>
         </is>
       </c>
       <c r="C31" s="1" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="D31" s="1" t="inlineStr">
         <is>
-          <t>邪恶；罪恶；祸害</t>
+          <t>罪孽；罪恶（Sünde 的复数）〈n.f.〉</t>
         </is>
       </c>
       <c r="E31" s="1" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="B35" s="1" t="inlineStr">
         <is>
-          <t>[ʁatən] 胡说；瞎扯〈n.〉</t>
+          <t>[ʁatən] 老鼠；大鼠〈n.〉</t>
         </is>
       </c>
       <c r="C35" s="1" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="D35" s="1" t="inlineStr">
         <is>
-          <t>胡说；瞎扯</t>
+          <t>老鼠；大鼠</t>
         </is>
       </c>
       <c r="E35" s="1" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="B40" s="1" t="inlineStr">
         <is>
-          <t>[ɡeːaɪmə] 描写间谍密探的；搞特务活动的；间谍的〈adv.〉</t>
+          <t>[ɡeːaɪmə] 秘密的；隐秘的〈adv.〉</t>
         </is>
       </c>
       <c r="C40" s="1" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="D40" s="1" t="inlineStr">
         <is>
-          <t>描写间谍密探的；搞特务活动的；间谍的</t>
+          <t>秘密的；隐秘的</t>
         </is>
       </c>
       <c r="E40" s="1" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="B42" s="1" t="inlineStr">
         <is>
-          <t>[vaɪsɐ] 啄木鸟〈adv.〉</t>
+          <t>[vaɪsɐ] 更白的〈adv.〉</t>
         </is>
       </c>
       <c r="C42" s="1" t="inlineStr">
@@ -1757,7 +1757,7 @@
       </c>
       <c r="D42" s="1" t="inlineStr">
         <is>
-          <t>啄木鸟</t>
+          <t>更白的</t>
         </is>
       </c>
       <c r="E42" s="1" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="B43" s="1" t="inlineStr">
         <is>
-          <t>[fasə] 制造；安排；创造〈n.〉</t>
+          <t>[fasə] 桶；木桶〈n.〉</t>
         </is>
       </c>
       <c r="C43" s="1" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="D43" s="1" t="inlineStr">
         <is>
-          <t>制造；安排；创造</t>
+          <t>桶；木桶</t>
         </is>
       </c>
       <c r="E43" s="1" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="B47" s="1" t="inlineStr">
         <is>
-          <t>[ɡlʏklɪçə] 金的；含金的；金色的〈adv.〉</t>
+          <t>[ɡlʏklɪçə] 幸福的；快乐的〈adj.〉〈adv.〉</t>
         </is>
       </c>
       <c r="C47" s="1" t="inlineStr">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="D47" s="1" t="inlineStr">
         <is>
-          <t>金的；含金的；金色的</t>
+          <t>幸福的；快乐的〈adj.〉</t>
         </is>
       </c>
       <c r="E47" s="1" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="B48" s="1" t="inlineStr">
         <is>
-          <t>[ʃtuːdɛntən] 睡衣；法衣〈n.〉</t>
+          <t>[ʃtuːdɛntən] 大学生；学生〈n.〉</t>
         </is>
       </c>
       <c r="C48" s="1" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="D48" s="1" t="inlineStr">
         <is>
-          <t>睡衣；法衣</t>
+          <t>大学生；学生</t>
         </is>
       </c>
       <c r="E48" s="1" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="B50" s="1" t="inlineStr">
         <is>
-          <t>[mɪtɡliːdɐ] 国会议员〈n.〉</t>
+          <t>[mɪtɡliːdɐ] 成员；会员（Mitglied 的复数）〈n.〉</t>
         </is>
       </c>
       <c r="C50" s="1" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="D50" s="1" t="inlineStr">
         <is>
-          <t>国会议员</t>
+          <t>成员；会员（Mitglied 的复数）</t>
         </is>
       </c>
       <c r="E50" s="1" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="B51" s="1" t="inlineStr">
         <is>
-          <t>[ɡlʏklɪçɐ] 意外事件〈adv.〉</t>
+          <t>[ɡlʏklɪçɐ] 更幸福的；更幸运的〈adj.〉〈adv.〉</t>
         </is>
       </c>
       <c r="C51" s="1" t="inlineStr">
@@ -2045,7 +2045,7 @@
       </c>
       <c r="D51" s="1" t="inlineStr">
         <is>
-          <t>意外事件</t>
+          <t>更幸福的；更幸运的〈adj.〉</t>
         </is>
       </c>
       <c r="E51" s="1" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="B54" s="1" t="inlineStr">
         <is>
-          <t>[kɔnzəkvənt͡sən] 适当的；拨出；占用〈n.〉</t>
+          <t>[kɔnzəkvənt͡sən] 后果；结果〈n.〉</t>
         </is>
       </c>
       <c r="C54" s="1" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="D54" s="1" t="inlineStr">
         <is>
-          <t>适当的；拨出；占用</t>
+          <t>后果；结果</t>
         </is>
       </c>
       <c r="E54" s="1" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="B57" s="1" t="inlineStr">
         <is>
-          <t>[fɛlzən] 块；片；篇〈n.m.〉</t>
+          <t>[fɛlzən] 岩石；巨岩〈n.m.〉</t>
         </is>
       </c>
       <c r="C57" s="1" t="inlineStr">
@@ -2237,7 +2237,7 @@
       </c>
       <c r="D57" s="1" t="inlineStr">
         <is>
-          <t>块；片；篇</t>
+          <t>岩石；巨岩</t>
         </is>
       </c>
       <c r="E57" s="1" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="B60" s="1" t="inlineStr">
         <is>
-          <t>[tɛmpɔ] 修剪；夹子；回形针〈n.〉</t>
+          <t>[tɛmpɔ] 速度；节奏〈n.〉</t>
         </is>
       </c>
       <c r="C60" s="1" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="D60" s="1" t="inlineStr">
         <is>
-          <t>修剪；夹子；回形针</t>
+          <t>速度；节奏</t>
         </is>
       </c>
       <c r="E60" s="1" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="B69" s="1" t="inlineStr">
         <is>
-          <t>[aʊsfluːk] 旅行；绊倒；摔倒〈n.m.〉</t>
+          <t>[aʊsfluːk] 远足；郊游；短途旅行〈n.m.〉</t>
         </is>
       </c>
       <c r="C69" s="1" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="D69" s="1" t="inlineStr">
         <is>
-          <t>旅行；绊倒；摔倒</t>
+          <t>远足；郊游；短途旅行</t>
         </is>
       </c>
       <c r="E69" s="1" t="inlineStr">
@@ -2707,7 +2707,7 @@
       </c>
       <c r="B72" s="1" t="inlineStr">
         <is>
-          <t>[ʁɛçnən] 计算；算术〈n.〉</t>
+          <t>[ʁɛçnən] 计算；算〈v.〉〈n.〉</t>
         </is>
       </c>
       <c r="C72" s="1" t="inlineStr">
@@ -2717,7 +2717,7 @@
       </c>
       <c r="D72" s="1" t="inlineStr">
         <is>
-          <t>计算；算术</t>
+          <t>计算；算〈v.〉</t>
         </is>
       </c>
       <c r="E72" s="1" t="inlineStr">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="B76" s="1" t="inlineStr">
         <is>
-          <t>[beːnœtɪɡən] 需要的东西；缺乏；贫困〈v.〉</t>
+          <t>[beːnœtɪɡən] 需要〈v.〉</t>
         </is>
       </c>
       <c r="C76" s="1" t="inlineStr">
@@ -2845,7 +2845,7 @@
       </c>
       <c r="D76" s="1" t="inlineStr">
         <is>
-          <t>需要的东西；缺乏；贫困</t>
+          <t>需要</t>
         </is>
       </c>
       <c r="E76" s="1" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B79" s="1" t="inlineStr">
         <is>
-          <t>[daʊmən] 笨拙地摆弄；用拇指翻旧〈n.m.〉</t>
+          <t>[daʊmən] 拇指〈n.m.〉</t>
         </is>
       </c>
       <c r="C79" s="1" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="D79" s="1" t="inlineStr">
         <is>
-          <t>笨拙地摆弄；用拇指翻旧</t>
+          <t>拇指</t>
         </is>
       </c>
       <c r="E79" s="1" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="B83" s="1" t="inlineStr">
         <is>
-          <t>[maʁkə] 标志；分数；马克〈n.f.〉</t>
+          <t>[maʁkə] 标记；商标；品牌〈n.f.〉</t>
         </is>
       </c>
       <c r="C83" s="1" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="D83" s="1" t="inlineStr">
         <is>
-          <t>标志；分数；马克</t>
+          <t>标记；商标；品牌</t>
         </is>
       </c>
       <c r="E83" s="1" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="B85" s="1" t="inlineStr">
         <is>
-          <t>[juːdə] 犹太人；守财奴〈n.m.〉</t>
+          <t>[juːdə] 犹太人〈n.m.〉〈n.m.〉</t>
         </is>
       </c>
       <c r="C85" s="1" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="D85" s="1" t="inlineStr">
         <is>
-          <t>犹太人；守财奴</t>
+          <t>犹太人〈n.m.〉</t>
         </is>
       </c>
       <c r="E85" s="1" t="inlineStr">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="B87" s="1" t="inlineStr">
         <is>
-          <t>[fɛʁʃlɔsən] 不会接受的；反应不快的；接受能力不强的〈v.〉</t>
+          <t>[fɛʁʃlɔsən] 锁上的；关闭的；缄默的〈v.〉</t>
         </is>
       </c>
       <c r="C87" s="1" t="inlineStr">
@@ -3197,7 +3197,7 @@
       </c>
       <c r="D87" s="1" t="inlineStr">
         <is>
-          <t>不会接受的；反应不快的；接受能力不强的</t>
+          <t>锁上的；关闭的；缄默的</t>
         </is>
       </c>
       <c r="E87" s="1" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="B94" s="1" t="inlineStr">
         <is>
-          <t>[haːʁən] 车棚；小屋；脱落之物〈v.〉</t>
+          <t>[haːʁən] 脱毛；长毛发〈v.〉〈v.〉</t>
         </is>
       </c>
       <c r="C94" s="1" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="D94" s="1" t="inlineStr">
         <is>
-          <t>车棚；小屋；脱落之物</t>
+          <t>脱毛；长毛发〈v.〉</t>
         </is>
       </c>
       <c r="E94" s="1" t="inlineStr">
@@ -3635,12 +3635,12 @@
       </c>
       <c r="B101" s="1" t="inlineStr">
         <is>
-          <t>[vhɪskʏ] 威士忌酒〈n.m.〉</t>
+          <t>[vɪskʏ] 威士忌酒〈n.m.〉</t>
         </is>
       </c>
       <c r="C101" s="1" t="inlineStr">
         <is>
-          <t>vhɪskʏ</t>
+          <t>vɪskʏ</t>
         </is>
       </c>
       <c r="D101" s="1" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="B107" s="1" t="inlineStr">
         <is>
-          <t>[ɡʁyːnə] 草；草原；牧场〈n.〉</t>
+          <t>[ɡʁyːnə] 绿色；绿党〈n.〉</t>
         </is>
       </c>
       <c r="C107" s="1" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="D107" s="1" t="inlineStr">
         <is>
-          <t>草；草原；牧场</t>
+          <t>绿色；绿党</t>
         </is>
       </c>
       <c r="E107" s="1" t="inlineStr">
@@ -3923,7 +3923,7 @@
       </c>
       <c r="B110" s="1" t="inlineStr">
         <is>
-          <t>[bɛstant] 树干；祖先；血统〈n.m.〉</t>
+          <t>[bɛstant] 库存；存量；储备；存在〈n.m.〉</t>
         </is>
       </c>
       <c r="C110" s="1" t="inlineStr">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="D110" s="1" t="inlineStr">
         <is>
-          <t>树干；祖先；血统</t>
+          <t>库存；存量；储备；存在</t>
         </is>
       </c>
       <c r="E110" s="1" t="inlineStr">
@@ -3987,7 +3987,7 @@
       </c>
       <c r="B112" s="1" t="inlineStr">
         <is>
-          <t>[ʃnɛlə] 派遣；急件；调度〈adv.〉</t>
+          <t>[ʃnɛlə] 快的；快速的〈adv.〉</t>
         </is>
       </c>
       <c r="C112" s="1" t="inlineStr">
@@ -3997,7 +3997,7 @@
       </c>
       <c r="D112" s="1" t="inlineStr">
         <is>
-          <t>派遣；急件；调度</t>
+          <t>快的；快速的</t>
         </is>
       </c>
       <c r="E112" s="1" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="B114" s="1" t="inlineStr">
         <is>
-          <t>[laʊtəs] 大声叫嚷；大声喊叫〈adv.〉</t>
+          <t>[laʊtəs] 大声的；响亮的〈adv.〉</t>
         </is>
       </c>
       <c r="C114" s="1" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="D114" s="1" t="inlineStr">
         <is>
-          <t>大声叫嚷；大声喊叫</t>
+          <t>大声的；响亮的</t>
         </is>
       </c>
       <c r="E114" s="1" t="inlineStr">
@@ -4083,7 +4083,7 @@
       </c>
       <c r="B115" s="1" t="inlineStr">
         <is>
-          <t>[aʊft͡saɪçnʊnɡən] 火车；列车；行列〈n.〉</t>
+          <t>[aʊft͡saɪçnʊnɡən] 记录；笔记；记载〈n.〉</t>
         </is>
       </c>
       <c r="C115" s="1" t="inlineStr">
@@ -4093,7 +4093,7 @@
       </c>
       <c r="D115" s="1" t="inlineStr">
         <is>
-          <t>火车；列车；行列</t>
+          <t>记录；笔记；记载</t>
         </is>
       </c>
       <c r="E115" s="1" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="B117" s="1" t="inlineStr">
         <is>
-          <t>[fɔʁfaːʁən] 先；居先；先行〈n.〉</t>
+          <t>[fɔʁfaːʁən] 祖先（Vorfahr的复数）；行驶（动词fahren）〈n./v.〉〈n.〉</t>
         </is>
       </c>
       <c r="C117" s="1" t="inlineStr">
@@ -4157,7 +4157,7 @@
       </c>
       <c r="D117" s="1" t="inlineStr">
         <is>
-          <t>先；居先；先行</t>
+          <t>祖先（Vorfahr的复数）；行驶（动词fahren）〈n./v.〉</t>
         </is>
       </c>
       <c r="E117" s="1" t="inlineStr">
@@ -4339,7 +4339,7 @@
       </c>
       <c r="B123" s="1" t="inlineStr">
         <is>
-          <t>[ɡeːlœʃt] 被冷落的；诅咒的；被忽视的〈adj.〉</t>
+          <t>[ɡeːlœʃt] 已删除的；被抹去的〈adj.〉</t>
         </is>
       </c>
       <c r="C123" s="1" t="inlineStr">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="D123" s="1" t="inlineStr">
         <is>
-          <t>被冷落的；诅咒的；被忽视的</t>
+          <t>已删除的；被抹去的</t>
         </is>
       </c>
       <c r="E123" s="1" t="inlineStr">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="B127" s="1" t="inlineStr">
         <is>
-          <t>[voːbaɪ] 和；与〈adv.〉</t>
+          <t>[voːbaɪ] 其中；在此过程中〈adv.〉</t>
         </is>
       </c>
       <c r="C127" s="1" t="inlineStr">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="D127" s="1" t="inlineStr">
         <is>
-          <t>和；与</t>
+          <t>其中；在此过程中</t>
         </is>
       </c>
       <c r="E127" s="1" t="inlineStr">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="B132" s="1" t="inlineStr">
         <is>
-          <t>[t͡suːʁʏkʁʊfən] 职业；行业；呼唤〈n.〉</t>
+          <t>[t͡suːʁʏkʁʊfən] 召回；回电话；唤回〈n.〉</t>
         </is>
       </c>
       <c r="C132" s="1" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="D132" s="1" t="inlineStr">
         <is>
-          <t>职业；行业；呼唤</t>
+          <t>召回；回电话；唤回</t>
         </is>
       </c>
       <c r="E132" s="1" t="inlineStr">
@@ -4659,7 +4659,7 @@
       </c>
       <c r="B133" s="1" t="inlineStr">
         <is>
-          <t>[ʁyːʁt] 在；向；对；地址转换器〈n.〉</t>
+          <t>[ʁyːʁt] 搅拌；搅动；感动（rühren 的变位形式）〈n.〉</t>
         </is>
       </c>
       <c r="C133" s="1" t="inlineStr">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="D133" s="1" t="inlineStr">
         <is>
-          <t>在；向；对；地址转换器</t>
+          <t>搅拌；搅动；感动（rühren 的变位形式）</t>
         </is>
       </c>
       <c r="E133" s="1" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="B136" s="1" t="inlineStr">
         <is>
-          <t>[ʃaːfə] 羊；胆小者〈n.〉</t>
+          <t>[ʃaːfə] 羊（Schaf 的复数形式）〈n.〉</t>
         </is>
       </c>
       <c r="C136" s="1" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="D136" s="1" t="inlineStr">
         <is>
-          <t>羊；胆小者</t>
+          <t>羊（Schaf 的复数形式）</t>
         </is>
       </c>
       <c r="E136" s="1" t="inlineStr">
@@ -4979,7 +4979,7 @@
       </c>
       <c r="B143" s="1" t="inlineStr">
         <is>
-          <t>[beːalt] 生计；维持；保持〈n.〉</t>
+          <t>[beːalt] Behalt 不是德语名词；动词 behalten 意为“保留；记住”〈n.〉</t>
         </is>
       </c>
       <c r="C143" s="1" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="D143" s="1" t="inlineStr">
         <is>
-          <t>生计；维持；保持</t>
+          <t>Behalt 不是德语名词；动词 behalten 意为“保留；记住”</t>
         </is>
       </c>
       <c r="E143" s="1" t="inlineStr">
@@ -5043,7 +5043,7 @@
       </c>
       <c r="B145" s="1" t="inlineStr">
         <is>
-          <t>[ɡeːbʊndən] 跃；回跳；范围〈adj.〉</t>
+          <t>[ɡeːbʊndən] 被捆绑的；装订成册的；受约束的〈adj.〉</t>
         </is>
       </c>
       <c r="C145" s="1" t="inlineStr">
@@ -5053,7 +5053,7 @@
       </c>
       <c r="D145" s="1" t="inlineStr">
         <is>
-          <t>跃；回跳；范围</t>
+          <t>被捆绑的；装订成册的；受约束的</t>
         </is>
       </c>
       <c r="E145" s="1" t="inlineStr">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="B149" s="1" t="inlineStr">
         <is>
-          <t>[vɛlən] 兴风作浪〈n.〉</t>
+          <t>[vɛlən] 波浪（Welle 的复数）〈n.〉</t>
         </is>
       </c>
       <c r="C149" s="1" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="D149" s="1" t="inlineStr">
         <is>
-          <t>兴风作浪</t>
+          <t>波浪（Welle 的复数）</t>
         </is>
       </c>
       <c r="E149" s="1" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="B150" s="1" t="inlineStr">
         <is>
-          <t>[hɔfnʊnɡən] 伪造；歪曲；说谎〈n.〉</t>
+          <t>[hɔfnʊnɡən] 希望（Hoffnung 的复数）〈n.f.〉〈n.〉</t>
         </is>
       </c>
       <c r="C150" s="1" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="D150" s="1" t="inlineStr">
         <is>
-          <t>伪造；歪曲；说谎</t>
+          <t>希望（Hoffnung 的复数）〈n.f.〉</t>
         </is>
       </c>
       <c r="E150" s="1" t="inlineStr">
@@ -5267,7 +5267,7 @@
       </c>
       <c r="B152" s="1" t="inlineStr">
         <is>
-          <t>[aʊshaltən] 伸出；提出；提供〈v.〉</t>
+          <t>[aʊshaltən] 忍受；忍耐；坚持〈v.〉</t>
         </is>
       </c>
       <c r="C152" s="1" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="D152" s="1" t="inlineStr">
         <is>
-          <t>伸出；提出；提供</t>
+          <t>忍受；忍耐；坚持</t>
         </is>
       </c>
       <c r="E152" s="1" t="inlineStr">
@@ -5427,7 +5427,7 @@
       </c>
       <c r="B157" s="1" t="inlineStr">
         <is>
-          <t>[ɡeːʁəɡəlt] 规则的；常例的；有秩序的〈adv.〉</t>
+          <t>[ɡeːʁəɡəlt] 有条理的；按规定安排好的〈adv.〉</t>
         </is>
       </c>
       <c r="C157" s="1" t="inlineStr">
@@ -5437,7 +5437,7 @@
       </c>
       <c r="D157" s="1" t="inlineStr">
         <is>
-          <t>规则的；常例的；有秩序的</t>
+          <t>有条理的；按规定安排好的</t>
         </is>
       </c>
       <c r="E157" s="1" t="inlineStr">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="B159" s="1" t="inlineStr">
         <is>
-          <t>[aɪnt͡səlhaɪtən] 苦心经营；精巧；确立〈n.〉</t>
+          <t>[aɪnt͡səlhaɪtən] 细节；详情〈n.〉</t>
         </is>
       </c>
       <c r="C159" s="1" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="D159" s="1" t="inlineStr">
         <is>
-          <t>苦心经营；精巧；确立</t>
+          <t>细节；详情</t>
         </is>
       </c>
       <c r="E159" s="1" t="inlineStr">
@@ -5523,17 +5523,17 @@
       </c>
       <c r="B160" s="1" t="inlineStr">
         <is>
-          <t>[bʊkstabən] 位置；空间；距离〈n.〉</t>
+          <t>[bʊxʃtaːbən] 字母〈n.〉</t>
         </is>
       </c>
       <c r="C160" s="1" t="inlineStr">
         <is>
-          <t>bʊkstabən</t>
+          <t>bʊxʃtaːbən</t>
         </is>
       </c>
       <c r="D160" s="1" t="inlineStr">
         <is>
-          <t>位置；空间；距离</t>
+          <t>字母</t>
         </is>
       </c>
       <c r="E160" s="1" t="inlineStr">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="B164" s="1" t="inlineStr">
         <is>
-          <t>[ɡɛspəʁt] 难得到的；难接近的；难达成的〈adv.〉</t>
+          <t>[ɡɛspəʁt] 封锁的；锁定的；禁用的〈adv.〉</t>
         </is>
       </c>
       <c r="C164" s="1" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="D164" s="1" t="inlineStr">
         <is>
-          <t>难得到的；难接近的；难达成的</t>
+          <t>封锁的；锁定的；禁用的</t>
         </is>
       </c>
       <c r="E164" s="1" t="inlineStr">
@@ -5715,7 +5715,7 @@
       </c>
       <c r="B166" s="1" t="inlineStr">
         <is>
-          <t>[pʁaɪzə] 使变硬；使坚强〈n.〉</t>
+          <t>[pʁaɪzə] Preis（价格）的复数形式；价格〈n.pl.〉〈n.〉</t>
         </is>
       </c>
       <c r="C166" s="1" t="inlineStr">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="D166" s="1" t="inlineStr">
         <is>
-          <t>使变硬；使坚强</t>
+          <t>Preis（价格）的复数形式；价格〈n.pl.〉</t>
         </is>
       </c>
       <c r="E166" s="1" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="B169" s="1" t="inlineStr">
         <is>
-          <t>[ɛntspʁɪçt] 做；工作〈n.〉</t>
+          <t>[ɛntspʁɪçt] 符合；相当于；对应〈n.〉</t>
         </is>
       </c>
       <c r="C169" s="1" t="inlineStr">
@@ -5821,7 +5821,7 @@
       </c>
       <c r="D169" s="1" t="inlineStr">
         <is>
-          <t>做；工作</t>
+          <t>符合；相当于；对应</t>
         </is>
       </c>
       <c r="E169" s="1" t="inlineStr">
@@ -5843,7 +5843,7 @@
       </c>
       <c r="B170" s="1" t="inlineStr">
         <is>
-          <t>[aʊfʁəɡən] 擦伤；气恼；摩擦；擦痛〈v.〉</t>
+          <t>[aʊfʁəɡən] 使激动；使不安；使生气〈v.〉</t>
         </is>
       </c>
       <c r="C170" s="1" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="D170" s="1" t="inlineStr">
         <is>
-          <t>擦伤；气恼；摩擦；擦痛</t>
+          <t>使激动；使不安；使生气</t>
         </is>
       </c>
       <c r="E170" s="1" t="inlineStr">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="B171" s="1" t="inlineStr">
         <is>
-          <t>[viːn] 维也纳〈n.f.〉</t>
+          <t>[viːn] 维也纳〈n.〉（中性，das Wien）〈n.f.〉</t>
         </is>
       </c>
       <c r="C171" s="1" t="inlineStr">
@@ -5885,7 +5885,7 @@
       </c>
       <c r="D171" s="1" t="inlineStr">
         <is>
-          <t>维也纳</t>
+          <t>维也纳〈n.〉（中性，das Wien）</t>
         </is>
       </c>
       <c r="E171" s="1" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="B179" s="1" t="inlineStr">
         <is>
-          <t>[hɛʁdə] 兽群；鸟群；一群人〈n.f.〉</t>
+          <t>[hɛʁdə] 兽群〈n.m.〉（der Herde，复数 Herden）〈n.f.〉</t>
         </is>
       </c>
       <c r="C179" s="1" t="inlineStr">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="D179" s="1" t="inlineStr">
         <is>
-          <t>兽群；鸟群；一群人</t>
+          <t>兽群〈n.m.〉（der Herde，复数 Herden）</t>
         </is>
       </c>
       <c r="E179" s="1" t="inlineStr">
@@ -6163,7 +6163,7 @@
       </c>
       <c r="B180" s="1" t="inlineStr">
         <is>
-          <t>[fɛstɡeːaltən] 它；信息论；输入终端；智能终端〈n.〉</t>
+          <t>[fɛstɡeːaltən] 抓住；固定；拘留〈n.〉</t>
         </is>
       </c>
       <c r="C180" s="1" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="D180" s="1" t="inlineStr">
         <is>
-          <t>它；信息论；输入终端；智能终端</t>
+          <t>抓住；固定；拘留</t>
         </is>
       </c>
       <c r="E180" s="1" t="inlineStr">
@@ -6195,7 +6195,7 @@
       </c>
       <c r="B181" s="1" t="inlineStr">
         <is>
-          <t>[toːtalə] 胡乱的猜测；远景〈n.f.〉</t>
+          <t>[toːtalə] 全景；远景镜头〈n.f.〉</t>
         </is>
       </c>
       <c r="C181" s="1" t="inlineStr">
@@ -6205,7 +6205,7 @@
       </c>
       <c r="D181" s="1" t="inlineStr">
         <is>
-          <t>胡乱的猜测；远景</t>
+          <t>全景；远景镜头</t>
         </is>
       </c>
       <c r="E181" s="1" t="inlineStr">
@@ -6227,7 +6227,7 @@
       </c>
       <c r="B182" s="1" t="inlineStr">
         <is>
-          <t>[bandɪtən] 边缘；边境；边界〈n.〉</t>
+          <t>[bandɪtən] 强盗；匪徒〈n.〉</t>
         </is>
       </c>
       <c r="C182" s="1" t="inlineStr">
@@ -6237,7 +6237,7 @@
       </c>
       <c r="D182" s="1" t="inlineStr">
         <is>
-          <t>边缘；边境；边界</t>
+          <t>强盗；匪徒</t>
         </is>
       </c>
       <c r="E182" s="1" t="inlineStr">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="B188" s="1" t="inlineStr">
         <is>
-          <t>[fɛʁstɔsən] 被抛弃的人；遭难的〈v.〉</t>
+          <t>[fɛʁstɔsən] 驱逐；抛弃〈v.〉</t>
         </is>
       </c>
       <c r="C188" s="1" t="inlineStr">
@@ -6429,7 +6429,7 @@
       </c>
       <c r="D188" s="1" t="inlineStr">
         <is>
-          <t>被抛弃的人；遭难的</t>
+          <t>驱逐；抛弃</t>
         </is>
       </c>
       <c r="E188" s="1" t="inlineStr">
@@ -6579,7 +6579,7 @@
       </c>
       <c r="B193" s="1" t="inlineStr">
         <is>
-          <t>[ʃvɛçən] 树液；体液；活力〈v.〉</t>
+          <t>[ʃvɛçən] 削弱；使虚弱〈v.〉</t>
         </is>
       </c>
       <c r="C193" s="1" t="inlineStr">
@@ -6589,7 +6589,7 @@
       </c>
       <c r="D193" s="1" t="inlineStr">
         <is>
-          <t>树液；体液；活力</t>
+          <t>削弱；使虚弱</t>
         </is>
       </c>
       <c r="E193" s="1" t="inlineStr">
@@ -6643,7 +6643,7 @@
       </c>
       <c r="B195" s="1" t="inlineStr">
         <is>
-          <t>[ʁɪnɡə] 蒸馏室；寂静；剧照；蒸馏〈n.〉</t>
+          <t>[ʁɪnɡə] 环；戒指；圆圈〈n.〉</t>
         </is>
       </c>
       <c r="C195" s="1" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="D195" s="1" t="inlineStr">
         <is>
-          <t>蒸馏室；寂静；剧照；蒸馏</t>
+          <t>环；戒指；圆圈</t>
         </is>
       </c>
       <c r="E195" s="1" t="inlineStr">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="B197" s="1" t="inlineStr">
         <is>
-          <t>[nʊt͡sə] 鲤鱼；木工铅笔〈n.〉</t>
+          <t>[nʊt͡sə] 利用；使用；益处〈n.〉</t>
         </is>
       </c>
       <c r="C197" s="1" t="inlineStr">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="D197" s="1" t="inlineStr">
         <is>
-          <t>鲤鱼；木工铅笔</t>
+          <t>利用；使用；益处</t>
         </is>
       </c>
       <c r="E197" s="1" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="B199" s="1" t="inlineStr">
         <is>
-          <t>[fɔʁdəʁə] 不要；禁忌〈n.〉</t>
+          <t>[fɔʁdəʁə] （动词原形 fordern）要求；索取〈n.〉</t>
         </is>
       </c>
       <c r="C199" s="1" t="inlineStr">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="D199" s="1" t="inlineStr">
         <is>
-          <t>不要；禁忌</t>
+          <t>（动词原形 fordern）要求；索取</t>
         </is>
       </c>
       <c r="E199" s="1" t="inlineStr">
@@ -6899,7 +6899,7 @@
       </c>
       <c r="B203" s="1" t="inlineStr">
         <is>
-          <t>[fɛʁpʁʏɡəln] 打；挫败；搏动；打浆〈n.〉</t>
+          <t>[fɛʁpʁʏɡəln] 痛打；殴打〈n.〉</t>
         </is>
       </c>
       <c r="C203" s="1" t="inlineStr">
@@ -6909,7 +6909,7 @@
       </c>
       <c r="D203" s="1" t="inlineStr">
         <is>
-          <t>打；挫败；搏动；打浆</t>
+          <t>痛打；殴打</t>
         </is>
       </c>
       <c r="E203" s="1" t="inlineStr">
@@ -7027,7 +7027,7 @@
       </c>
       <c r="B207" s="1" t="inlineStr">
         <is>
-          <t>[bɪʃoːf] 主教；象；热果子酒〈n.m.〉</t>
+          <t>[bɪʃoːf] 主教；热果子酒（热宾治酒）〈n.m.〉（国际象棋的“象”是 Läufer）〈n.m.〉</t>
         </is>
       </c>
       <c r="C207" s="1" t="inlineStr">
@@ -7037,7 +7037,7 @@
       </c>
       <c r="D207" s="1" t="inlineStr">
         <is>
-          <t>主教；象；热果子酒</t>
+          <t>主教；热果子酒（热宾治酒）〈n.m.〉（国际象棋的“象”是 Läufer）</t>
         </is>
       </c>
       <c r="E207" s="1" t="inlineStr">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="B211" s="1" t="inlineStr">
         <is>
-          <t>[akst] 斧；斧头；削减〈n.f.〉</t>
+          <t>[akst] 斧；斧头〈n.f.〉〈n.f.〉</t>
         </is>
       </c>
       <c r="C211" s="1" t="inlineStr">
@@ -7165,7 +7165,7 @@
       </c>
       <c r="D211" s="1" t="inlineStr">
         <is>
-          <t>斧；斧头；削减</t>
+          <t>斧；斧头〈n.f.〉</t>
         </is>
       </c>
       <c r="E211" s="1" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="B218" s="1" t="inlineStr">
         <is>
-          <t>[aʊfhɛnɡən] 障碍；烦恼；大难题；意外停机〈n.〉</t>
+          <t>[aʊfhɛnɡən] 悬挂；挂起〈n.〉</t>
         </is>
       </c>
       <c r="C218" s="1" t="inlineStr">
@@ -7389,7 +7389,7 @@
       </c>
       <c r="D218" s="1" t="inlineStr">
         <is>
-          <t>障碍；烦恼；大难题；意外停机</t>
+          <t>悬挂；挂起</t>
         </is>
       </c>
       <c r="E218" s="1" t="inlineStr">
@@ -7539,7 +7539,7 @@
       </c>
       <c r="B223" s="1" t="inlineStr">
         <is>
-          <t>[ʃtandpʊnkt] 站立；站住；停顿〈n.m.〉</t>
+          <t>[ʃtandpʊnkt] 立场；观点〈n.m.〉</t>
         </is>
       </c>
       <c r="C223" s="1" t="inlineStr">
@@ -7549,7 +7549,7 @@
       </c>
       <c r="D223" s="1" t="inlineStr">
         <is>
-          <t>站立；站住；停顿</t>
+          <t>立场；观点</t>
         </is>
       </c>
       <c r="E223" s="1" t="inlineStr">
@@ -8051,7 +8051,7 @@
       </c>
       <c r="B239" s="1" t="inlineStr">
         <is>
-          <t>[abvəkslʊnk] 变化；找回的零钱；找头〈n.f.〉</t>
+          <t>[abvəkslʊnk] 变化；多样化；消遣〈n.f.〉</t>
         </is>
       </c>
       <c r="C239" s="1" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="D239" s="1" t="inlineStr">
         <is>
-          <t>变化；找回的零钱；找头</t>
+          <t>变化；多样化；消遣</t>
         </is>
       </c>
       <c r="E239" s="1" t="inlineStr">
@@ -8403,7 +8403,7 @@
       </c>
       <c r="B250" s="1" t="inlineStr">
         <is>
-          <t>[ʃtadtʁaːt] 城镇；市；镇〈n.m.〉</t>
+          <t>[ʃtadtʁaːt] 市议会；市议员〈n.m.〉</t>
         </is>
       </c>
       <c r="C250" s="1" t="inlineStr">
@@ -8413,7 +8413,7 @@
       </c>
       <c r="D250" s="1" t="inlineStr">
         <is>
-          <t>城镇；市；镇</t>
+          <t>市议会；市议员</t>
         </is>
       </c>
       <c r="E250" s="1" t="inlineStr">
@@ -8499,7 +8499,7 @@
       </c>
       <c r="B253" s="1" t="inlineStr">
         <is>
-          <t>[ʁeːɡiː] 制造；生产；产物；产生〈n.f.〉</t>
+          <t>[ʁeːɡiː] 导演；执导；指导〈n.f.〉</t>
         </is>
       </c>
       <c r="C253" s="1" t="inlineStr">
@@ -8509,7 +8509,7 @@
       </c>
       <c r="D253" s="1" t="inlineStr">
         <is>
-          <t>制造；生产；产物；产生</t>
+          <t>导演；执导；指导</t>
         </is>
       </c>
       <c r="E253" s="1" t="inlineStr">
@@ -8531,7 +8531,7 @@
       </c>
       <c r="B254" s="1" t="inlineStr">
         <is>
-          <t>[mɛʁk] 水；雨水；海水〈n.m.〉</t>
+          <t>[mɛʁk] merken 的命令式；亦作姓氏〈m.〉〈n.m.〉</t>
         </is>
       </c>
       <c r="C254" s="1" t="inlineStr">
@@ -8541,7 +8541,7 @@
       </c>
       <c r="D254" s="1" t="inlineStr">
         <is>
-          <t>水；雨水；海水</t>
+          <t>merken 的命令式；亦作姓氏〈m.〉</t>
         </is>
       </c>
       <c r="E254" s="1" t="inlineStr">
@@ -8659,7 +8659,7 @@
       </c>
       <c r="B258" s="1" t="inlineStr">
         <is>
-          <t>[tʊsɪ] 母牛；母兽；威胁〈n.f.〉</t>
+          <t>[tʊsɪ] 〈口，贬〉妞；娘们；女人〈n.f.〉</t>
         </is>
       </c>
       <c r="C258" s="1" t="inlineStr">
@@ -8669,7 +8669,7 @@
       </c>
       <c r="D258" s="1" t="inlineStr">
         <is>
-          <t>母牛；母兽；威胁</t>
+          <t>〈口，贬〉妞；娘们；女人</t>
         </is>
       </c>
       <c r="E258" s="1" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="B260" s="1" t="inlineStr">
         <is>
-          <t>[eːəmalɪɡɐ] 男毕业生；男校友〈adv.〉</t>
+          <t>[eːəmalɪɡɐ] 以前的；从前的；前任的〈adv.〉</t>
         </is>
       </c>
       <c r="C260" s="1" t="inlineStr">
@@ -8733,7 +8733,7 @@
       </c>
       <c r="D260" s="1" t="inlineStr">
         <is>
-          <t>男毕业生；男校友</t>
+          <t>以前的；从前的；前任的</t>
         </is>
       </c>
       <c r="E260" s="1" t="inlineStr">
@@ -8787,7 +8787,7 @@
       </c>
       <c r="B262" s="1" t="inlineStr">
         <is>
-          <t>[ɡeːfəçt] 诺言；约会；婚约〈n.〉</t>
+          <t>[ɡeːfəçt] 战斗；交战〈n.〉</t>
         </is>
       </c>
       <c r="C262" s="1" t="inlineStr">
@@ -8797,7 +8797,7 @@
       </c>
       <c r="D262" s="1" t="inlineStr">
         <is>
-          <t>诺言；约会；婚约</t>
+          <t>战斗；交战</t>
         </is>
       </c>
       <c r="E262" s="1" t="inlineStr">
@@ -8819,7 +8819,7 @@
       </c>
       <c r="B263" s="1" t="inlineStr">
         <is>
-          <t>[ʃtʁiːç] 谷粒；颗粒；谷类〈n.m.〉</t>
+          <t>[ʃtʁiːç] 线条；笔画；一道；条纹〈n.m.〉</t>
         </is>
       </c>
       <c r="C263" s="1" t="inlineStr">
@@ -8829,7 +8829,7 @@
       </c>
       <c r="D263" s="1" t="inlineStr">
         <is>
-          <t>谷粒；颗粒；谷类</t>
+          <t>线条；笔画；一道；条纹</t>
         </is>
       </c>
       <c r="E263" s="1" t="inlineStr">
@@ -8979,12 +8979,12 @@
       </c>
       <c r="B268" s="1" t="inlineStr">
         <is>
-          <t>[aʊstəlʊnk] 表现；展览会；展览品；投药〈n.f.〉</t>
+          <t>[aʊstəlʊŋ] 表现；展览会；展览品；投药〈n.f.〉</t>
         </is>
       </c>
       <c r="C268" s="1" t="inlineStr">
         <is>
-          <t>aʊstəlʊnk</t>
+          <t>aʊstəlʊŋ</t>
         </is>
       </c>
       <c r="D268" s="1" t="inlineStr">
@@ -9043,7 +9043,7 @@
       </c>
       <c r="B270" s="1" t="inlineStr">
         <is>
-          <t>[ʁaʃ] 使突然中断；猛咬；争夺〈adv.〉</t>
+          <t>[ʁaʃ] 迅速的；快的〈adv.〉</t>
         </is>
       </c>
       <c r="C270" s="1" t="inlineStr">
@@ -9053,7 +9053,7 @@
       </c>
       <c r="D270" s="1" t="inlineStr">
         <is>
-          <t>使突然中断；猛咬；争夺</t>
+          <t>迅速的；快的</t>
         </is>
       </c>
       <c r="E270" s="1" t="inlineStr">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="B274" s="1" t="inlineStr">
         <is>
-          <t>[aʊfhəbən] 纷扰；忙乱；麻烦〈n.〉</t>
+          <t>[aʊfhəbən] 拾起；捡起；取消；废除〈n.〉</t>
         </is>
       </c>
       <c r="C274" s="1" t="inlineStr">
@@ -9181,7 +9181,7 @@
       </c>
       <c r="D274" s="1" t="inlineStr">
         <is>
-          <t>纷扰；忙乱；麻烦</t>
+          <t>拾起；捡起；取消；废除</t>
         </is>
       </c>
       <c r="E274" s="1" t="inlineStr">
@@ -9363,7 +9363,7 @@
       </c>
       <c r="B280" s="1" t="inlineStr">
         <is>
-          <t>[aʊst͡saɪt] 暂停；超时〈n.f.〉</t>
+          <t>[aʊst͡saɪt] （短暂的）休息；暂停〈n.f.〉〈n.f.〉</t>
         </is>
       </c>
       <c r="C280" s="1" t="inlineStr">
@@ -9373,7 +9373,7 @@
       </c>
       <c r="D280" s="1" t="inlineStr">
         <is>
-          <t>暂停；超时</t>
+          <t>（短暂的）休息；暂停〈n.f.〉</t>
         </is>
       </c>
       <c r="E280" s="1" t="inlineStr">
@@ -9427,7 +9427,7 @@
       </c>
       <c r="B282" s="1" t="inlineStr">
         <is>
-          <t>[blɛtɐ] 涂箔于〈n.〉</t>
+          <t>[blɛtɐ] 叶子；叶片；纸张〈n.〉</t>
         </is>
       </c>
       <c r="C282" s="1" t="inlineStr">
@@ -9437,7 +9437,7 @@
       </c>
       <c r="D282" s="1" t="inlineStr">
         <is>
-          <t>涂箔于</t>
+          <t>叶子；叶片；纸张</t>
         </is>
       </c>
       <c r="E282" s="1" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="B284" s="1" t="inlineStr">
         <is>
-          <t>[kɔnt͡səpt] 观念；概念〈n.〉</t>
+          <t>[kɔnt͡səpt] 构想；方案；草案〈n.〉〈n.〉</t>
         </is>
       </c>
       <c r="C284" s="1" t="inlineStr">
@@ -9501,7 +9501,7 @@
       </c>
       <c r="D284" s="1" t="inlineStr">
         <is>
-          <t>观念；概念</t>
+          <t>构想；方案；草案〈n.〉</t>
         </is>
       </c>
       <c r="E284" s="1" t="inlineStr">
@@ -9555,7 +9555,7 @@
       </c>
       <c r="B286" s="1" t="inlineStr">
         <is>
-          <t>[faːdən] 看穿〈n.m.〉</t>
+          <t>[faːdən] 线；丝线；线索〈n.m.〉</t>
         </is>
       </c>
       <c r="C286" s="1" t="inlineStr">
@@ -9565,7 +9565,7 @@
       </c>
       <c r="D286" s="1" t="inlineStr">
         <is>
-          <t>看穿</t>
+          <t>线；丝线；线索</t>
         </is>
       </c>
       <c r="E286" s="1" t="inlineStr">
@@ -9651,7 +9651,7 @@
       </c>
       <c r="B289" s="1" t="inlineStr">
         <is>
-          <t>[ʃʁɪft] 身体；人；尸体〈n.f.〉</t>
+          <t>[ʃʁɪft] 文字；书写；字体〈n.f.〉</t>
         </is>
       </c>
       <c r="C289" s="1" t="inlineStr">
@@ -9661,7 +9661,7 @@
       </c>
       <c r="D289" s="1" t="inlineStr">
         <is>
-          <t>身体；人；尸体</t>
+          <t>文字；书写；字体</t>
         </is>
       </c>
       <c r="E289" s="1" t="inlineStr">
@@ -9683,7 +9683,7 @@
       </c>
       <c r="B290" s="1" t="inlineStr">
         <is>
-          <t>[bʁiːtɪʃə] 英国英语〈n.〉</t>
+          <t>[bʁiːtɪʃə] 英国人（名词化的形容词）〈n.〉</t>
         </is>
       </c>
       <c r="C290" s="1" t="inlineStr">
@@ -9693,7 +9693,7 @@
       </c>
       <c r="D290" s="1" t="inlineStr">
         <is>
-          <t>英国英语</t>
+          <t>英国人（名词化的形容词）</t>
         </is>
       </c>
       <c r="E290" s="1" t="inlineStr">
@@ -9811,17 +9811,17 @@
       </c>
       <c r="B294" s="1" t="inlineStr">
         <is>
-          <t>[ʁaɪnɪɡʊnk] 的复数；零星工作；零活儿〈n.f.〉</t>
+          <t>[ʁaɪnɪɡʊŋ] 清洁；清洗；干洗店〈n.f.〉</t>
         </is>
       </c>
       <c r="C294" s="1" t="inlineStr">
         <is>
-          <t>ʁaɪnɪɡʊnk</t>
+          <t>ʁaɪnɪɡʊŋ</t>
         </is>
       </c>
       <c r="D294" s="1" t="inlineStr">
         <is>
-          <t>的复数；零星工作；零活儿</t>
+          <t>清洁；清洗；干洗店</t>
         </is>
       </c>
       <c r="E294" s="1" t="inlineStr">
@@ -9971,7 +9971,7 @@
       </c>
       <c r="B299" s="1" t="inlineStr">
         <is>
-          <t>[baːdəvanə] 沐浴；浴室；浴〈n.f.〉</t>
+          <t>[baːdəvanə] 浴缸〈n.f.〉</t>
         </is>
       </c>
       <c r="C299" s="1" t="inlineStr">
@@ -9981,7 +9981,7 @@
       </c>
       <c r="D299" s="1" t="inlineStr">
         <is>
-          <t>沐浴；浴室；浴</t>
+          <t>浴缸</t>
         </is>
       </c>
       <c r="E299" s="1" t="inlineStr">
@@ -10099,7 +10099,7 @@
       </c>
       <c r="B303" s="1" t="inlineStr">
         <is>
-          <t>[hiːʁbaɪ] 一会儿；虽然；消磨〈adv.〉</t>
+          <t>[hiːʁbaɪ] 在此；对此；借此〈adv.〉〈adv.〉</t>
         </is>
       </c>
       <c r="C303" s="1" t="inlineStr">
@@ -10109,7 +10109,7 @@
       </c>
       <c r="D303" s="1" t="inlineStr">
         <is>
-          <t>一会儿；虽然；消磨</t>
+          <t>在此；对此；借此〈adv.〉</t>
         </is>
       </c>
       <c r="E303" s="1" t="inlineStr">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="B309" s="1" t="inlineStr">
         <is>
-          <t>[mɪtɡeːən] 前进；进行〈v.〉</t>
+          <t>[mɪtɡeːən] 同行；一同前往〈v.〉</t>
         </is>
       </c>
       <c r="C309" s="1" t="inlineStr">
@@ -10301,7 +10301,7 @@
       </c>
       <c r="D309" s="1" t="inlineStr">
         <is>
-          <t>前进；进行</t>
+          <t>同行；一同前往</t>
         </is>
       </c>
       <c r="E309" s="1" t="inlineStr">
@@ -10355,7 +10355,7 @@
       </c>
       <c r="B311" s="1" t="inlineStr">
         <is>
-          <t>[ʃtɛçən] 赛跑开始〈n.〉</t>
+          <t>[ʃtɛçən] 刺；蜇；决胜赛；加赛〈n.〉</t>
         </is>
       </c>
       <c r="C311" s="1" t="inlineStr">
@@ -10365,7 +10365,7 @@
       </c>
       <c r="D311" s="1" t="inlineStr">
         <is>
-          <t>赛跑开始</t>
+          <t>刺；蜇；决胜赛；加赛</t>
         </is>
       </c>
       <c r="E311" s="1" t="inlineStr">
@@ -10483,7 +10483,7 @@
       </c>
       <c r="B315" s="1" t="inlineStr">
         <is>
-          <t>[mɛçtɪɡɐ] 变浓；变厚；变得模糊〈adv.〉</t>
+          <t>[mɛçtɪɡɐ] 更强大的；更有力的〈adv.〉</t>
         </is>
       </c>
       <c r="C315" s="1" t="inlineStr">
@@ -10493,7 +10493,7 @@
       </c>
       <c r="D315" s="1" t="inlineStr">
         <is>
-          <t>变浓；变厚；变得模糊</t>
+          <t>更强大的；更有力的</t>
         </is>
       </c>
       <c r="E315" s="1" t="inlineStr">
@@ -10515,7 +10515,7 @@
       </c>
       <c r="B316" s="1" t="inlineStr">
         <is>
-          <t>[ʃʏsəl] 盖碗；焙盘〈n.f.〉</t>
+          <t>[ʃʏsəl] 碗；盆〈n.f.〉</t>
         </is>
       </c>
       <c r="C316" s="1" t="inlineStr">
@@ -10525,7 +10525,7 @@
       </c>
       <c r="D316" s="1" t="inlineStr">
         <is>
-          <t>盖碗；焙盘</t>
+          <t>碗；盆</t>
         </is>
       </c>
       <c r="E316" s="1" t="inlineStr">
@@ -10579,7 +10579,7 @@
       </c>
       <c r="B318" s="1" t="inlineStr">
         <is>
-          <t>[beːʁatən] 引导者；导游；指南〈v.〉</t>
+          <t>[beːʁatən] 建议；咨询；商议〈v.〉</t>
         </is>
       </c>
       <c r="C318" s="1" t="inlineStr">
@@ -10589,7 +10589,7 @@
       </c>
       <c r="D318" s="1" t="inlineStr">
         <is>
-          <t>引导者；导游；指南</t>
+          <t>建议；咨询；商议</t>
         </is>
       </c>
       <c r="E318" s="1" t="inlineStr">
@@ -10675,7 +10675,7 @@
       </c>
       <c r="B321" s="1" t="inlineStr">
         <is>
-          <t>[maʁʃiːʁən] 三月；进行；行军〈v.〉</t>
+          <t>[maʁʃiːʁən] 行军；行进〈v.〉</t>
         </is>
       </c>
       <c r="C321" s="1" t="inlineStr">
@@ -10685,7 +10685,7 @@
       </c>
       <c r="D321" s="1" t="inlineStr">
         <is>
-          <t>三月；进行；行军</t>
+          <t>行军；行进</t>
         </is>
       </c>
       <c r="E321" s="1" t="inlineStr">
@@ -10771,7 +10771,7 @@
       </c>
       <c r="B324" s="1" t="inlineStr">
         <is>
-          <t>[fʊnkən] 无线电；收音机；无线电报〈v.〉</t>
+          <t>[fʊnkən] 发无线电报；发出火花〈v.〉</t>
         </is>
       </c>
       <c r="C324" s="1" t="inlineStr">
@@ -10781,7 +10781,7 @@
       </c>
       <c r="D324" s="1" t="inlineStr">
         <is>
-          <t>无线电；收音机；无线电报</t>
+          <t>发无线电报；发出火花</t>
         </is>
       </c>
       <c r="E324" s="1" t="inlineStr">
@@ -10867,7 +10867,7 @@
       </c>
       <c r="B327" s="1" t="inlineStr">
         <is>
-          <t>[pʁyːɡəl] 鞭打；击落浇冒口〈n.〉</t>
+          <t>[pʁyːɡəl] 棍棒；殴打〈n.〉</t>
         </is>
       </c>
       <c r="C327" s="1" t="inlineStr">
@@ -10877,7 +10877,7 @@
       </c>
       <c r="D327" s="1" t="inlineStr">
         <is>
-          <t>鞭打；击落浇冒口</t>
+          <t>棍棒；殴打</t>
         </is>
       </c>
       <c r="E327" s="1" t="inlineStr">
@@ -10899,7 +10899,7 @@
       </c>
       <c r="B328" s="1" t="inlineStr">
         <is>
-          <t>[lɔʏtən] 环；环形物；拳击场〈n.〉</t>
+          <t>[lɔʏtən] 鸣钟；敲钟；按铃〈n.〉</t>
         </is>
       </c>
       <c r="C328" s="1" t="inlineStr">
@@ -10909,7 +10909,7 @@
       </c>
       <c r="D328" s="1" t="inlineStr">
         <is>
-          <t>环；环形物；拳击场</t>
+          <t>鸣钟；敲钟；按铃</t>
         </is>
       </c>
       <c r="E328" s="1" t="inlineStr">
@@ -10995,7 +10995,7 @@
       </c>
       <c r="B331" s="1" t="inlineStr">
         <is>
-          <t>[ʁɛçtfəʁtɪɡən] 替...辩护；两端对齐〈v.〉</t>
+          <t>[ʁɛçtfəʁtɪɡən] 为...辩护；证明...正当〈v.〉</t>
         </is>
       </c>
       <c r="C331" s="1" t="inlineStr">
@@ -11005,7 +11005,7 @@
       </c>
       <c r="D331" s="1" t="inlineStr">
         <is>
-          <t>替...辩护；两端对齐</t>
+          <t>为...辩护；证明...正当</t>
         </is>
       </c>
       <c r="E331" s="1" t="inlineStr">
@@ -11059,7 +11059,7 @@
       </c>
       <c r="B333" s="1" t="inlineStr">
         <is>
-          <t>[ɛʁtʁɪnkən] 淹没〈v.〉</t>
+          <t>[ɛʁtʁɪnkən] 溺水；淹死〈v.〉</t>
         </is>
       </c>
       <c r="C333" s="1" t="inlineStr">
@@ -11069,7 +11069,7 @@
       </c>
       <c r="D333" s="1" t="inlineStr">
         <is>
-          <t>淹没</t>
+          <t>溺水；淹死</t>
         </is>
       </c>
       <c r="E333" s="1" t="inlineStr">
@@ -11091,7 +11091,7 @@
       </c>
       <c r="B334" s="1" t="inlineStr">
         <is>
-          <t>[zɔʁɡfɛltɪç] 精细的；详尽的〈adj.〉</t>
+          <t>[zɔʁɡfɛltɪç] 仔细的；认真的；周密的〈adj.〉</t>
         </is>
       </c>
       <c r="C334" s="1" t="inlineStr">
@@ -11101,7 +11101,7 @@
       </c>
       <c r="D334" s="1" t="inlineStr">
         <is>
-          <t>精细的；详尽的</t>
+          <t>仔细的；认真的；周密的</t>
         </is>
       </c>
       <c r="E334" s="1" t="inlineStr">
@@ -11123,7 +11123,7 @@
       </c>
       <c r="B335" s="1" t="inlineStr">
         <is>
-          <t>[ʃpʊk] 唾液；唾吐；小雨〈n.〉</t>
+          <t>[ʃpʊk] 坏运气，倒霉（口语）；（旧）唾液（通常用 Spucke）〈n.〉</t>
         </is>
       </c>
       <c r="C335" s="1" t="inlineStr">
@@ -11133,7 +11133,7 @@
       </c>
       <c r="D335" s="1" t="inlineStr">
         <is>
-          <t>唾液；唾吐；小雨</t>
+          <t>坏运气，倒霉（口语）；（旧）唾液（通常用 Spucke）</t>
         </is>
       </c>
       <c r="E335" s="1" t="inlineStr">
@@ -11155,7 +11155,7 @@
       </c>
       <c r="B336" s="1" t="inlineStr">
         <is>
-          <t>[faɪnə] 增大；隆起的部分；巨浪〈adv.〉</t>
+          <t>[faɪnə] 细的；精细的；优质的〈adv.〉</t>
         </is>
       </c>
       <c r="C336" s="1" t="inlineStr">
@@ -11165,7 +11165,7 @@
       </c>
       <c r="D336" s="1" t="inlineStr">
         <is>
-          <t>增大；隆起的部分；巨浪</t>
+          <t>细的；精细的；优质的</t>
         </is>
       </c>
       <c r="E336" s="1" t="inlineStr">
@@ -11507,7 +11507,7 @@
       </c>
       <c r="B347" s="1" t="inlineStr">
         <is>
-          <t>[zoːsə] 酱油；调味汁〈n.f.〉</t>
+          <t>[zoːsə] 调味汁；酱汁〈n.f.〉〈n.f.〉</t>
         </is>
       </c>
       <c r="C347" s="1" t="inlineStr">
@@ -11517,7 +11517,7 @@
       </c>
       <c r="D347" s="1" t="inlineStr">
         <is>
-          <t>酱油；调味汁</t>
+          <t>调味汁；酱汁〈n.f.〉</t>
         </is>
       </c>
       <c r="E347" s="1" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="B358" s="1" t="inlineStr">
         <is>
-          <t>[lɛnkən] 引导者；导游；指南〈v.〉</t>
+          <t>[lɛnkən] 驾驶；操纵；引导；转移〈v.〉</t>
         </is>
       </c>
       <c r="C358" s="1" t="inlineStr">
@@ -11869,7 +11869,7 @@
       </c>
       <c r="D358" s="1" t="inlineStr">
         <is>
-          <t>引导者；导游；指南</t>
+          <t>驾驶；操纵；引导；转移</t>
         </is>
       </c>
       <c r="E358" s="1" t="inlineStr">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="B368" s="1" t="inlineStr">
         <is>
-          <t>[ʃteːənblaɪbən] 厩；停车处；牧师职位〈v.〉</t>
+          <t>[ʃteːənblaɪbən] 停住；停下；停止〈v.〉</t>
         </is>
       </c>
       <c r="C368" s="1" t="inlineStr">
@@ -12189,7 +12189,7 @@
       </c>
       <c r="D368" s="1" t="inlineStr">
         <is>
-          <t>厩；停车处；牧师职位</t>
+          <t>停住；停下；停止</t>
         </is>
       </c>
       <c r="E368" s="1" t="inlineStr">
@@ -12403,17 +12403,17 @@
       </c>
       <c r="B375" s="1" t="inlineStr">
         <is>
-          <t>[ɔʊtfiːt] 齿轮；开动〈n.〉</t>
+          <t>[aʊtfɪt] 全套服装；装备〈n.〉</t>
         </is>
       </c>
       <c r="C375" s="1" t="inlineStr">
         <is>
-          <t>ɔʊtfiːt</t>
+          <t>aʊtfɪt</t>
         </is>
       </c>
       <c r="D375" s="1" t="inlineStr">
         <is>
-          <t>齿轮；开动</t>
+          <t>全套服装；装备</t>
         </is>
       </c>
       <c r="E375" s="1" t="inlineStr">
@@ -12595,7 +12595,7 @@
       </c>
       <c r="B381" s="1" t="inlineStr">
         <is>
-          <t>[naːtʏʁlɪçə] 磨损；折磨；耗损〈adv.〉</t>
+          <t>[naːtʏʁlɪçə] 自然的；天然的〈adv.〉</t>
         </is>
       </c>
       <c r="C381" s="1" t="inlineStr">
@@ -12605,7 +12605,7 @@
       </c>
       <c r="D381" s="1" t="inlineStr">
         <is>
-          <t>磨损；折磨；耗损</t>
+          <t>自然的；天然的</t>
         </is>
       </c>
       <c r="E381" s="1" t="inlineStr">
@@ -12691,7 +12691,7 @@
       </c>
       <c r="B384" s="1" t="inlineStr">
         <is>
-          <t>[ʃaʁfə] 棱〈adv.〉</t>
+          <t>[ʃaʁfə] 锋利的；尖锐的；辛辣的〈adv.〉</t>
         </is>
       </c>
       <c r="C384" s="1" t="inlineStr">
@@ -12701,7 +12701,7 @@
       </c>
       <c r="D384" s="1" t="inlineStr">
         <is>
-          <t>棱</t>
+          <t>锋利的；尖锐的；辛辣的</t>
         </is>
       </c>
       <c r="E384" s="1" t="inlineStr">
@@ -12755,7 +12755,7 @@
       </c>
       <c r="B386" s="1" t="inlineStr">
         <is>
-          <t>[ʁeːɡɪoːn] 圣经带〈n.f.〉</t>
+          <t>[ʁeːɡɪoːn] 地区；区域；地带〈n.f.〉</t>
         </is>
       </c>
       <c r="C386" s="1" t="inlineStr">
@@ -12765,7 +12765,7 @@
       </c>
       <c r="D386" s="1" t="inlineStr">
         <is>
-          <t>圣经带</t>
+          <t>地区；区域；地带</t>
         </is>
       </c>
       <c r="E386" s="1" t="inlineStr">
@@ -12851,7 +12851,7 @@
       </c>
       <c r="B389" s="1" t="inlineStr">
         <is>
-          <t>[jamɐ] 坏脾气〈n.m.〉</t>
+          <t>[jamɐ] 哀叹；悲叹；悲惨；苦难〈n.m.〉</t>
         </is>
       </c>
       <c r="C389" s="1" t="inlineStr">
@@ -12861,7 +12861,7 @@
       </c>
       <c r="D389" s="1" t="inlineStr">
         <is>
-          <t>坏脾气</t>
+          <t>哀叹；悲叹；悲惨；苦难</t>
         </is>
       </c>
       <c r="E389" s="1" t="inlineStr">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="B394" s="1" t="inlineStr">
         <is>
-          <t>[plat͡sən] 热；热度；体温〈n.〉</t>
+          <t>[plat͡sən] 爆裂；破裂；告吹〈n.〉</t>
         </is>
       </c>
       <c r="C394" s="1" t="inlineStr">
@@ -13021,7 +13021,7 @@
       </c>
       <c r="D394" s="1" t="inlineStr">
         <is>
-          <t>热；热度；体温</t>
+          <t>爆裂；破裂；告吹</t>
         </is>
       </c>
       <c r="E394" s="1" t="inlineStr">
@@ -13171,7 +13171,7 @@
       </c>
       <c r="B399" s="1" t="inlineStr">
         <is>
-          <t>[lyːk] 不要；禁忌〈n.〉</t>
+          <t>[lyːk] 谎言；谎话〈n.〉</t>
         </is>
       </c>
       <c r="C399" s="1" t="inlineStr">
@@ -13181,7 +13181,7 @@
       </c>
       <c r="D399" s="1" t="inlineStr">
         <is>
-          <t>不要；禁忌</t>
+          <t>谎言；谎话</t>
         </is>
       </c>
       <c r="E399" s="1" t="inlineStr">
@@ -13235,7 +13235,7 @@
       </c>
       <c r="B401" s="1" t="inlineStr">
         <is>
-          <t>[abzət͡sən] 空投〈n.〉</t>
+          <t>[abzət͡sən] 免职；罢免；放下〈n.〉</t>
         </is>
       </c>
       <c r="C401" s="1" t="inlineStr">
@@ -13245,7 +13245,7 @@
       </c>
       <c r="D401" s="1" t="inlineStr">
         <is>
-          <t>空投</t>
+          <t>免职；罢免；放下</t>
         </is>
       </c>
       <c r="E401" s="1" t="inlineStr">
@@ -13331,7 +13331,7 @@
       </c>
       <c r="B404" s="1" t="inlineStr">
         <is>
-          <t>[aʁbaɪtslɔs] 注册的；登记过的；记名的〈adv.〉</t>
+          <t>[aʁbaɪtslɔs] 失业的；无工作的〈adv.〉</t>
         </is>
       </c>
       <c r="C404" s="1" t="inlineStr">
@@ -13341,7 +13341,7 @@
       </c>
       <c r="D404" s="1" t="inlineStr">
         <is>
-          <t>注册的；登记过的；记名的</t>
+          <t>失业的；无工作的</t>
         </is>
       </c>
       <c r="E404" s="1" t="inlineStr">
@@ -13363,7 +13363,7 @@
       </c>
       <c r="B405" s="1" t="inlineStr">
         <is>
-          <t>[ɡɛtʁɛnkə] 卖；背叛；销售〈n.〉</t>
+          <t>[ɡɛtʁɛnkə] 饮料〈n.〉</t>
         </is>
       </c>
       <c r="C405" s="1" t="inlineStr">
@@ -13373,7 +13373,7 @@
       </c>
       <c r="D405" s="1" t="inlineStr">
         <is>
-          <t>卖；背叛；销售</t>
+          <t>饮料</t>
         </is>
       </c>
       <c r="E405" s="1" t="inlineStr">
@@ -13523,7 +13523,7 @@
       </c>
       <c r="B410" s="1" t="inlineStr">
         <is>
-          <t>[bɛstɪmtəs] 口袋；钱袋；钱〈adv.〉</t>
+          <t>[bɛstɪmtəs] 特定的；确定的〈adv.〉</t>
         </is>
       </c>
       <c r="C410" s="1" t="inlineStr">
@@ -13533,7 +13533,7 @@
       </c>
       <c r="D410" s="1" t="inlineStr">
         <is>
-          <t>口袋；钱袋；钱</t>
+          <t>特定的；确定的</t>
         </is>
       </c>
       <c r="E410" s="1" t="inlineStr">
@@ -13587,7 +13587,7 @@
       </c>
       <c r="B412" s="1" t="inlineStr">
         <is>
-          <t>[kʁiːçən] 面；表面；水面〈n.〉</t>
+          <t>[kʁiːçən] 爬行；匍匐〈n.〉</t>
         </is>
       </c>
       <c r="C412" s="1" t="inlineStr">
@@ -13597,7 +13597,7 @@
       </c>
       <c r="D412" s="1" t="inlineStr">
         <is>
-          <t>面；表面；水面</t>
+          <t>爬行；匍匐</t>
         </is>
       </c>
       <c r="E412" s="1" t="inlineStr">
@@ -13619,7 +13619,7 @@
       </c>
       <c r="B413" s="1" t="inlineStr">
         <is>
-          <t>[vaɪsəs] 海松树脂；软膏壶〈adv.〉</t>
+          <t>[vaɪsəs] 白色的〈adv.〉</t>
         </is>
       </c>
       <c r="C413" s="1" t="inlineStr">
@@ -13629,7 +13629,7 @@
       </c>
       <c r="D413" s="1" t="inlineStr">
         <is>
-          <t>海松树脂；软膏壶</t>
+          <t>白色的</t>
         </is>
       </c>
       <c r="E413" s="1" t="inlineStr">
@@ -13683,7 +13683,7 @@
       </c>
       <c r="B415" s="1" t="inlineStr">
         <is>
-          <t>[t͡saʊbəʁaɪ] 壮举；功绩〈n.f.〉</t>
+          <t>[t͡saʊbəʁaɪ] 魔术；魔法；巫术〈n.f.〉</t>
         </is>
       </c>
       <c r="C415" s="1" t="inlineStr">
@@ -13693,7 +13693,7 @@
       </c>
       <c r="D415" s="1" t="inlineStr">
         <is>
-          <t>壮举；功绩</t>
+          <t>魔术；魔法；巫术</t>
         </is>
       </c>
       <c r="E415" s="1" t="inlineStr">
@@ -14003,7 +14003,7 @@
       </c>
       <c r="B425" s="1" t="inlineStr">
         <is>
-          <t>[eːəmalɪɡə] 女毕业生；女校友〈adv.〉</t>
+          <t>[eːəmalɪɡə] 以前的；从前的；前任的〈adv.〉</t>
         </is>
       </c>
       <c r="C425" s="1" t="inlineStr">
@@ -14013,7 +14013,7 @@
       </c>
       <c r="D425" s="1" t="inlineStr">
         <is>
-          <t>女毕业生；女校友</t>
+          <t>以前的；从前的；前任的</t>
         </is>
       </c>
       <c r="E425" s="1" t="inlineStr">
@@ -14163,7 +14163,7 @@
       </c>
       <c r="B430" s="1" t="inlineStr">
         <is>
-          <t>[fɛlɪç] 应得的东西；应得的〈adj.〉</t>
+          <t>[fɛlɪç] 到期的；应付的；应缴纳的〈adj.〉</t>
         </is>
       </c>
       <c r="C430" s="1" t="inlineStr">
@@ -14173,7 +14173,7 @@
       </c>
       <c r="D430" s="1" t="inlineStr">
         <is>
-          <t>应得的东西；应得的</t>
+          <t>到期的；应付的；应缴纳的</t>
         </is>
       </c>
       <c r="E430" s="1" t="inlineStr">
@@ -14195,7 +14195,7 @@
       </c>
       <c r="B431" s="1" t="inlineStr">
         <is>
-          <t>[knaɪpə] 非法经营的酒吧〈n.f.〉</t>
+          <t>[knaɪpə] 小酒馆；酒馆〈n.f.〉</t>
         </is>
       </c>
       <c r="C431" s="1" t="inlineStr">
@@ -14205,7 +14205,7 @@
       </c>
       <c r="D431" s="1" t="inlineStr">
         <is>
-          <t>非法经营的酒吧</t>
+          <t>小酒馆；酒馆</t>
         </is>
       </c>
       <c r="E431" s="1" t="inlineStr">
@@ -14291,7 +14291,7 @@
       </c>
       <c r="B434" s="1" t="inlineStr">
         <is>
-          <t>[ɪntəʁnat͡sjoːnalə] 国际（组织）；国际歌〈n.〉</t>
+          <t>[ɪntəʁnat͡sjoːnalə] 国际（组织）；国际歌〈n.f.〉〈n.〉</t>
         </is>
       </c>
       <c r="C434" s="1" t="inlineStr">
@@ -14301,7 +14301,7 @@
       </c>
       <c r="D434" s="1" t="inlineStr">
         <is>
-          <t>国际（组织）；国际歌</t>
+          <t>国际（组织）；国际歌〈n.f.〉</t>
         </is>
       </c>
       <c r="E434" s="1" t="inlineStr">
@@ -14323,7 +14323,7 @@
       </c>
       <c r="B435" s="1" t="inlineStr">
         <is>
-          <t>[veːən] 收缩；缩减；缩略词〈n.〉</t>
+          <t>[veːən] 阵痛；吹拂〈n.〉</t>
         </is>
       </c>
       <c r="C435" s="1" t="inlineStr">
@@ -14333,7 +14333,7 @@
       </c>
       <c r="D435" s="1" t="inlineStr">
         <is>
-          <t>收缩；缩减；缩略词</t>
+          <t>阵痛；吹拂</t>
         </is>
       </c>
       <c r="E435" s="1" t="inlineStr">
@@ -14419,7 +14419,7 @@
       </c>
       <c r="B438" s="1" t="inlineStr">
         <is>
-          <t>[ɡeːɡənt͡suːk] 交换；交换局；交换机〈n.m.〉</t>
+          <t>[ɡeːɡənt͡suːk] 反击；回击；返程列车〈n.m.〉</t>
         </is>
       </c>
       <c r="C438" s="1" t="inlineStr">
@@ -14429,7 +14429,7 @@
       </c>
       <c r="D438" s="1" t="inlineStr">
         <is>
-          <t>交换；交换局；交换机</t>
+          <t>反击；回击；返程列车</t>
         </is>
       </c>
       <c r="E438" s="1" t="inlineStr">
@@ -14515,7 +14515,7 @@
       </c>
       <c r="B441" s="1" t="inlineStr">
         <is>
-          <t>[fʁaɪlasən] 从…撤去堤坝；使从堤中涌出；使如决堤般流出〈v.〉</t>
+          <t>[fʁaɪlasən] 释放；放走；放开〈v.〉</t>
         </is>
       </c>
       <c r="C441" s="1" t="inlineStr">
@@ -14525,7 +14525,7 @@
       </c>
       <c r="D441" s="1" t="inlineStr">
         <is>
-          <t>从…撤去堤坝；使从堤中涌出；使如决堤般流出</t>
+          <t>释放；放走；放开</t>
         </is>
       </c>
       <c r="E441" s="1" t="inlineStr">
@@ -14803,12 +14803,12 @@
       </c>
       <c r="B450" s="1" t="inlineStr">
         <is>
-          <t>[beːlaɪdɪɡʊnk] 侮辱；冒犯；凌辱〈n.f.〉</t>
+          <t>[beːlaɪdɪɡʊŋ] 侮辱；冒犯；凌辱〈n.f.〉</t>
         </is>
       </c>
       <c r="C450" s="1" t="inlineStr">
         <is>
-          <t>beːlaɪdɪɡʊnk</t>
+          <t>beːlaɪdɪɡʊŋ</t>
         </is>
       </c>
       <c r="D450" s="1" t="inlineStr">
@@ -14835,7 +14835,7 @@
       </c>
       <c r="B451" s="1" t="inlineStr">
         <is>
-          <t>[ʊnhaɪmlɪçə] 命运；不可思议；离奇〈n.〉</t>
+          <t>[ʊnhaɪmlɪçə] 阴森；诡异；神秘可怕的事物〈n.〉</t>
         </is>
       </c>
       <c r="C451" s="1" t="inlineStr">
@@ -14845,7 +14845,7 @@
       </c>
       <c r="D451" s="1" t="inlineStr">
         <is>
-          <t>命运；不可思议；离奇</t>
+          <t>阴森；诡异；神秘可怕的事物</t>
         </is>
       </c>
       <c r="E451" s="1" t="inlineStr">
@@ -14995,7 +14995,7 @@
       </c>
       <c r="B456" s="1" t="inlineStr">
         <is>
-          <t>[ɛnɡlɪʃə] 长的；长久的；冗长的〈adv.〉</t>
+          <t>[ɛnɡlɪʃə] 英国的；英语的〈adv.〉</t>
         </is>
       </c>
       <c r="C456" s="1" t="inlineStr">
@@ -15005,7 +15005,7 @@
       </c>
       <c r="D456" s="1" t="inlineStr">
         <is>
-          <t>长的；长久的；冗长的</t>
+          <t>英国的；英语的</t>
         </is>
       </c>
       <c r="E456" s="1" t="inlineStr">
@@ -15091,7 +15091,7 @@
       </c>
       <c r="B459" s="1" t="inlineStr">
         <is>
-          <t>[andəʁtalp] 一；一个；一致的〈adv.〉</t>
+          <t>[andəʁtalp] 一个半；一又二分之一〈adv.〉</t>
         </is>
       </c>
       <c r="C459" s="1" t="inlineStr">
@@ -15101,7 +15101,7 @@
       </c>
       <c r="D459" s="1" t="inlineStr">
         <is>
-          <t>一；一个；一致的</t>
+          <t>一个半；一又二分之一</t>
         </is>
       </c>
       <c r="E459" s="1" t="inlineStr">
@@ -15251,12 +15251,12 @@
       </c>
       <c r="B464" s="1" t="inlineStr">
         <is>
-          <t>[tɛkvɪla] 蒸馏酒；龙舌兰酒〈n.m.〉</t>
+          <t>[tɛkila] 蒸馏酒；龙舌兰酒〈n.m.〉</t>
         </is>
       </c>
       <c r="C464" s="1" t="inlineStr">
         <is>
-          <t>tɛkvɪla</t>
+          <t>tɛkila</t>
         </is>
       </c>
       <c r="D464" s="1" t="inlineStr">
@@ -15411,7 +15411,7 @@
       </c>
       <c r="B469" s="1" t="inlineStr">
         <is>
-          <t>[ʁoːtəs] 红十字；红十字会〈n.〉</t>
+          <t>[ʁoːtəs] 红色；红色物〈n.〉</t>
         </is>
       </c>
       <c r="C469" s="1" t="inlineStr">
@@ -15421,7 +15421,7 @@
       </c>
       <c r="D469" s="1" t="inlineStr">
         <is>
-          <t>红十字；红十字会</t>
+          <t>红色；红色物</t>
         </is>
       </c>
       <c r="E469" s="1" t="inlineStr">
@@ -15539,7 +15539,7 @@
       </c>
       <c r="B473" s="1" t="inlineStr">
         <is>
-          <t>[mɪstʁaʊɪʃ] 不信任的；怀疑的；可疑的〈adj.〉</t>
+          <t>[mɪstʁaʊɪʃ] 不信任的；多疑的；猜疑的〈adj.〉〈adj.〉</t>
         </is>
       </c>
       <c r="C473" s="1" t="inlineStr">
@@ -15549,7 +15549,7 @@
       </c>
       <c r="D473" s="1" t="inlineStr">
         <is>
-          <t>不信任的；怀疑的；可疑的</t>
+          <t>不信任的；多疑的；猜疑的〈adj.〉</t>
         </is>
       </c>
       <c r="E473" s="1" t="inlineStr">
@@ -15731,7 +15731,7 @@
       </c>
       <c r="B479" s="1" t="inlineStr">
         <is>
-          <t>[fʁɪʃəs] 驿马；替班；中继〈adv.〉</t>
+          <t>[fʁɪʃəs] 新鲜的；清新的〈adv.〉</t>
         </is>
       </c>
       <c r="C479" s="1" t="inlineStr">
@@ -15741,7 +15741,7 @@
       </c>
       <c r="D479" s="1" t="inlineStr">
         <is>
-          <t>驿马；替班；中继</t>
+          <t>新鲜的；清新的</t>
         </is>
       </c>
       <c r="E479" s="1" t="inlineStr">
@@ -15923,7 +15923,7 @@
       </c>
       <c r="B485" s="1" t="inlineStr">
         <is>
-          <t>[ʁɛn] 赛马；赛车；空转；急转〈n.〉</t>
+          <t>[ʁɛn] Rennen 的词干，独立词应为 Rennen：赛跑；竞赛〈n.〉〈n.〉</t>
         </is>
       </c>
       <c r="C485" s="1" t="inlineStr">
@@ -15933,7 +15933,7 @@
       </c>
       <c r="D485" s="1" t="inlineStr">
         <is>
-          <t>赛马；赛车；空转；急转</t>
+          <t>Rennen 的词干，独立词应为 Rennen：赛跑；竞赛〈n.〉</t>
         </is>
       </c>
       <c r="E485" s="1" t="inlineStr">
@@ -15955,7 +15955,7 @@
       </c>
       <c r="B486" s="1" t="inlineStr">
         <is>
-          <t>[pɪnk] 热的；热心的；辣的〈adv.〉</t>
+          <t>[pɪnk] 粉红色；粉红色的〈adv.〉</t>
         </is>
       </c>
       <c r="C486" s="1" t="inlineStr">
@@ -15965,7 +15965,7 @@
       </c>
       <c r="D486" s="1" t="inlineStr">
         <is>
-          <t>热的；热心的；辣的</t>
+          <t>粉红色；粉红色的</t>
         </is>
       </c>
       <c r="E486" s="1" t="inlineStr">
@@ -16115,7 +16115,7 @@
       </c>
       <c r="B491" s="1" t="inlineStr">
         <is>
-          <t>[yːbəʁdɔzɪs] 使过分沉溺〈n.f.〉</t>
+          <t>[yːbəʁdɔzɪs] 过量；超剂量〈n.f.〉</t>
         </is>
       </c>
       <c r="C491" s="1" t="inlineStr">
@@ -16125,7 +16125,7 @@
       </c>
       <c r="D491" s="1" t="inlineStr">
         <is>
-          <t>使过分沉溺</t>
+          <t>过量；超剂量</t>
         </is>
       </c>
       <c r="E491" s="1" t="inlineStr">
@@ -16179,7 +16179,7 @@
       </c>
       <c r="B493" s="1" t="inlineStr">
         <is>
-          <t>[aɪnʃaltən] 力；体力；力量〈n.〉</t>
+          <t>[aɪnʃaltən] 打开；接通；介入〈n.〉</t>
         </is>
       </c>
       <c r="C493" s="1" t="inlineStr">
@@ -16189,7 +16189,7 @@
       </c>
       <c r="D493" s="1" t="inlineStr">
         <is>
-          <t>力；体力；力量</t>
+          <t>打开；接通；介入</t>
         </is>
       </c>
       <c r="E493" s="1" t="inlineStr">
@@ -16691,7 +16691,7 @@
       </c>
       <c r="B509" s="1" t="inlineStr">
         <is>
-          <t>[ʁoːɐ] 班机；划线者；定期船〈n.〉</t>
+          <t>[ʁoːɐ] 管子；管道〈n.〉</t>
         </is>
       </c>
       <c r="C509" s="1" t="inlineStr">
@@ -16701,7 +16701,7 @@
       </c>
       <c r="D509" s="1" t="inlineStr">
         <is>
-          <t>班机；划线者；定期船</t>
+          <t>管子；管道</t>
         </is>
       </c>
       <c r="E509" s="1" t="inlineStr">
@@ -16915,7 +16915,7 @@
       </c>
       <c r="B516" s="1" t="inlineStr">
         <is>
-          <t>[fiːs] 污秽的；下流的；险恶的〈adj.〉</t>
+          <t>[fiːs] 卑鄙的；恶劣的；讨厌的〈adj.〉〈adj.〉</t>
         </is>
       </c>
       <c r="C516" s="1" t="inlineStr">
@@ -16925,7 +16925,7 @@
       </c>
       <c r="D516" s="1" t="inlineStr">
         <is>
-          <t>污秽的；下流的；险恶的</t>
+          <t>卑鄙的；恶劣的；讨厌的〈adj.〉</t>
         </is>
       </c>
       <c r="E516" s="1" t="inlineStr">
@@ -16979,7 +16979,7 @@
       </c>
       <c r="B518" s="1" t="inlineStr">
         <is>
-          <t>[ɡɛʃləçt] 房子；住宅；机构〈n.〉</t>
+          <t>[ɡɛʃləçt] 性别；种类；世系〈n.〉</t>
         </is>
       </c>
       <c r="C518" s="1" t="inlineStr">
@@ -16989,7 +16989,7 @@
       </c>
       <c r="D518" s="1" t="inlineStr">
         <is>
-          <t>房子；住宅；机构</t>
+          <t>性别；种类；世系</t>
         </is>
       </c>
       <c r="E518" s="1" t="inlineStr">
@@ -17107,7 +17107,7 @@
       </c>
       <c r="B522" s="1" t="inlineStr">
         <is>
-          <t>[pɛʁzœnlɪçɐ] 血汗产权〈adv.〉</t>
+          <t>[pɛʁzœnlɪçɐ] 更个人的；更私人的〈adv.〉</t>
         </is>
       </c>
       <c r="C522" s="1" t="inlineStr">
@@ -17117,7 +17117,7 @@
       </c>
       <c r="D522" s="1" t="inlineStr">
         <is>
-          <t>血汗产权</t>
+          <t>更个人的；更私人的</t>
         </is>
       </c>
       <c r="E522" s="1" t="inlineStr">
@@ -17171,7 +17171,7 @@
       </c>
       <c r="B524" s="1" t="inlineStr">
         <is>
-          <t>[hɪnbʁɪnɡən] 拿；取；抓〈v.〉</t>
+          <t>[hɪnbʁɪnɡən] 把…带去；送去〈v.〉〈v.〉</t>
         </is>
       </c>
       <c r="C524" s="1" t="inlineStr">
@@ -17181,7 +17181,7 @@
       </c>
       <c r="D524" s="1" t="inlineStr">
         <is>
-          <t>拿；取；抓</t>
+          <t>把…带去；送去〈v.〉</t>
         </is>
       </c>
       <c r="E524" s="1" t="inlineStr">
@@ -17203,7 +17203,7 @@
       </c>
       <c r="B525" s="1" t="inlineStr">
         <is>
-          <t>[aːməʁɪkanɪʃɐ] 阻挠议事的活动；掠夺兵；暴兵〈adv.〉</t>
+          <t>[aːməʁɪkanɪʃɐ] 美国的；美洲的〈adv.〉</t>
         </is>
       </c>
       <c r="C525" s="1" t="inlineStr">
@@ -17213,7 +17213,7 @@
       </c>
       <c r="D525" s="1" t="inlineStr">
         <is>
-          <t>阻挠议事的活动；掠夺兵；暴兵</t>
+          <t>美国的；美洲的</t>
         </is>
       </c>
       <c r="E525" s="1" t="inlineStr">
@@ -17235,7 +17235,7 @@
       </c>
       <c r="B526" s="1" t="inlineStr">
         <is>
-          <t>[ʏblə] 态度；看法；姿势；体态〈adv.〉</t>
+          <t>[ʏblə] 恶劣的；坏的；不祥的〈adv.〉</t>
         </is>
       </c>
       <c r="C526" s="1" t="inlineStr">
@@ -17245,7 +17245,7 @@
       </c>
       <c r="D526" s="1" t="inlineStr">
         <is>
-          <t>态度；看法；姿势；体态</t>
+          <t>恶劣的；坏的；不祥的</t>
         </is>
       </c>
       <c r="E526" s="1" t="inlineStr">
@@ -17267,7 +17267,7 @@
       </c>
       <c r="B527" s="1" t="inlineStr">
         <is>
-          <t>[fɔltʁəfɐ] 直接的；指挥〈n.m.〉</t>
+          <t>[fɔltʁəfɐ] 正中目标；完全命中；猜中〈n.m.〉〈n.m.〉</t>
         </is>
       </c>
       <c r="C527" s="1" t="inlineStr">
@@ -17277,7 +17277,7 @@
       </c>
       <c r="D527" s="1" t="inlineStr">
         <is>
-          <t>直接的；指挥</t>
+          <t>正中目标；完全命中；猜中〈n.m.〉</t>
         </is>
       </c>
       <c r="E527" s="1" t="inlineStr">
@@ -17299,7 +17299,7 @@
       </c>
       <c r="B528" s="1" t="inlineStr">
         <is>
-          <t>[toːtalɐ] 交通全面大堵塞〈adv.〉</t>
+          <t>[toːtalɐ] 完全的；彻底的；总的〈adv.〉</t>
         </is>
       </c>
       <c r="C528" s="1" t="inlineStr">
@@ -17309,7 +17309,7 @@
       </c>
       <c r="D528" s="1" t="inlineStr">
         <is>
-          <t>交通全面大堵塞</t>
+          <t>完全的；彻底的；总的</t>
         </is>
       </c>
       <c r="E528" s="1" t="inlineStr">
@@ -17395,7 +17395,7 @@
       </c>
       <c r="B531" s="1" t="inlineStr">
         <is>
-          <t>[ʊnfɛːɪç] 缺乏；无；不足〈adj.〉</t>
+          <t>[ʊnfɛːɪç] 无能力的；不能胜任的〈adj.〉</t>
         </is>
       </c>
       <c r="C531" s="1" t="inlineStr">
@@ -17405,7 +17405,7 @@
       </c>
       <c r="D531" s="1" t="inlineStr">
         <is>
-          <t>缺乏；无；不足</t>
+          <t>无能力的；不能胜任的</t>
         </is>
       </c>
       <c r="E531" s="1" t="inlineStr">
@@ -17587,7 +17587,7 @@
       </c>
       <c r="B537" s="1" t="inlineStr">
         <is>
-          <t>[ʊntəʁt͡saɪçnən] 符号；招牌；征兆〈v.〉</t>
+          <t>[ʊntəʁt͡saɪçnən] 签署；签字〈v.〉</t>
         </is>
       </c>
       <c r="C537" s="1" t="inlineStr">
@@ -17597,7 +17597,7 @@
       </c>
       <c r="D537" s="1" t="inlineStr">
         <is>
-          <t>符号；招牌；征兆</t>
+          <t>签署；签字</t>
         </is>
       </c>
       <c r="E537" s="1" t="inlineStr">
@@ -17619,7 +17619,7 @@
       </c>
       <c r="B538" s="1" t="inlineStr">
         <is>
-          <t>[beːlastən] 应用；申请；志愿书〈n.〉</t>
+          <t>[beːlastən] 使负担；加载；指控〈n.〉</t>
         </is>
       </c>
       <c r="C538" s="1" t="inlineStr">
@@ -17629,7 +17629,7 @@
       </c>
       <c r="D538" s="1" t="inlineStr">
         <is>
-          <t>应用；申请；志愿书</t>
+          <t>使负担；加载；指控</t>
         </is>
       </c>
       <c r="E538" s="1" t="inlineStr">
@@ -17683,7 +17683,7 @@
       </c>
       <c r="B540" s="1" t="inlineStr">
         <is>
-          <t>[kvɐ] 十字架；十字架形物件；交叉〈adv.〉</t>
+          <t>[kvɐ] 横向的；斜的；横穿〈adv.〉</t>
         </is>
       </c>
       <c r="C540" s="1" t="inlineStr">
@@ -17693,7 +17693,7 @@
       </c>
       <c r="D540" s="1" t="inlineStr">
         <is>
-          <t>十字架；十字架形物件；交叉</t>
+          <t>横向的；斜的；横穿</t>
         </is>
       </c>
       <c r="E540" s="1" t="inlineStr">
@@ -17811,7 +17811,7 @@
       </c>
       <c r="B544" s="1" t="inlineStr">
         <is>
-          <t>[kœpfən] 标题；起始字；方向；上标题〈n.〉</t>
+          <t>[kœpfən] 顶球；斩首〈n.〉</t>
         </is>
       </c>
       <c r="C544" s="1" t="inlineStr">
@@ -17821,7 +17821,7 @@
       </c>
       <c r="D544" s="1" t="inlineStr">
         <is>
-          <t>标题；起始字；方向；上标题</t>
+          <t>顶球；斩首</t>
         </is>
       </c>
       <c r="E544" s="1" t="inlineStr">
@@ -17971,12 +17971,12 @@
       </c>
       <c r="B549" s="1" t="inlineStr">
         <is>
-          <t>[oːɪɔ] 俄亥俄〈n.m.〉</t>
+          <t>[oːhaɪ̯o] 俄亥俄〈n.m.〉</t>
         </is>
       </c>
       <c r="C549" s="1" t="inlineStr">
         <is>
-          <t>oːɪɔ</t>
+          <t>oːhaɪ̯o</t>
         </is>
       </c>
       <c r="D549" s="1" t="inlineStr">
@@ -18003,7 +18003,7 @@
       </c>
       <c r="B550" s="1" t="inlineStr">
         <is>
-          <t>[zaːmən] 种子；籽；萌芽〈n.〉</t>
+          <t>[zaːmən] 种子；籽；萌芽〈n.m.〉〈n.〉</t>
         </is>
       </c>
       <c r="C550" s="1" t="inlineStr">
@@ -18013,7 +18013,7 @@
       </c>
       <c r="D550" s="1" t="inlineStr">
         <is>
-          <t>种子；籽；萌芽</t>
+          <t>种子；籽；萌芽〈n.m.〉</t>
         </is>
       </c>
       <c r="E550" s="1" t="inlineStr">
@@ -18387,7 +18387,7 @@
       </c>
       <c r="B562" s="1" t="inlineStr">
         <is>
-          <t>[abstələn] 切掉；删去；切断〈v.〉</t>
+          <t>[abstələn] 关掉；切断；排除（故障）〈v.〉</t>
         </is>
       </c>
       <c r="C562" s="1" t="inlineStr">
@@ -18397,7 +18397,7 @@
       </c>
       <c r="D562" s="1" t="inlineStr">
         <is>
-          <t>切掉；删去；切断</t>
+          <t>关掉；切断；排除（故障）</t>
         </is>
       </c>
       <c r="E562" s="1" t="inlineStr">
@@ -18419,7 +18419,7 @@
       </c>
       <c r="B563" s="1" t="inlineStr">
         <is>
-          <t>[pʁoːdʊt͡siːʁən] 生产品；物产；后代；产生〈n.〉</t>
+          <t>[pʁoːdʊt͡siːʁən] 生产；制作；产生〈v.〉（名词形式为 Produktion）〈n.〉</t>
         </is>
       </c>
       <c r="C563" s="1" t="inlineStr">
@@ -18429,7 +18429,7 @@
       </c>
       <c r="D563" s="1" t="inlineStr">
         <is>
-          <t>生产品；物产；后代；产生</t>
+          <t>生产；制作；产生〈v.〉（名词形式为 Produktion）</t>
         </is>
       </c>
       <c r="E563" s="1" t="inlineStr">
@@ -18451,7 +18451,7 @@
       </c>
       <c r="B564" s="1" t="inlineStr">
         <is>
-          <t>[mʏlɐ] 厂主；蛾；铣床〈n.m.〉</t>
+          <t>[mʏlɐ] 磨坊主；磨坊工人〈n.m.〉</t>
         </is>
       </c>
       <c r="C564" s="1" t="inlineStr">
@@ -18461,7 +18461,7 @@
       </c>
       <c r="D564" s="1" t="inlineStr">
         <is>
-          <t>厂主；蛾；铣床</t>
+          <t>磨坊主；磨坊工人</t>
         </is>
       </c>
       <c r="E564" s="1" t="inlineStr">
@@ -18515,7 +18515,7 @@
       </c>
       <c r="B566" s="1" t="inlineStr">
         <is>
-          <t>[ʊmkʁaɪs] 外接圆〈n.m.〉</t>
+          <t>[ʊmkʁaɪs] 周围；附近；环境〈n.m.〉</t>
         </is>
       </c>
       <c r="C566" s="1" t="inlineStr">
@@ -18525,7 +18525,7 @@
       </c>
       <c r="D566" s="1" t="inlineStr">
         <is>
-          <t>外接圆</t>
+          <t>周围；附近；环境</t>
         </is>
       </c>
       <c r="E566" s="1" t="inlineStr">
@@ -18579,7 +18579,7 @@
       </c>
       <c r="B568" s="1" t="inlineStr">
         <is>
-          <t>[bɪldɐn] 形状；形体；类型〈v.〉</t>
+          <t>[bɪldɐn] 形成；构成；培养；教育〈v.〉</t>
         </is>
       </c>
       <c r="C568" s="1" t="inlineStr">
@@ -18589,7 +18589,7 @@
       </c>
       <c r="D568" s="1" t="inlineStr">
         <is>
-          <t>形状；形体；类型</t>
+          <t>形成；构成；培养；教育</t>
         </is>
       </c>
       <c r="E568" s="1" t="inlineStr">
@@ -18707,7 +18707,7 @@
       </c>
       <c r="B572" s="1" t="inlineStr">
         <is>
-          <t>[jaʁt] 码；庭院；工场；堆置场〈n.m.〉</t>
+          <t>[jaʁt] 码（长度单位）〈n.m.〉〈n.m.〉</t>
         </is>
       </c>
       <c r="C572" s="1" t="inlineStr">
@@ -18717,7 +18717,7 @@
       </c>
       <c r="D572" s="1" t="inlineStr">
         <is>
-          <t>码；庭院；工场；堆置场</t>
+          <t>码（长度单位）〈n.m.〉</t>
         </is>
       </c>
       <c r="E572" s="1" t="inlineStr">
@@ -18899,7 +18899,7 @@
       </c>
       <c r="B578" s="1" t="inlineStr">
         <is>
-          <t>[joːanəs] 盥洗室；厕所；嫖客〈n.〉</t>
+          <t>[joːanəs] 约翰〈人名〉〈n.〉</t>
         </is>
       </c>
       <c r="C578" s="1" t="inlineStr">
@@ -18909,7 +18909,7 @@
       </c>
       <c r="D578" s="1" t="inlineStr">
         <is>
-          <t>盥洗室；厕所；嫖客</t>
+          <t>约翰〈人名〉</t>
         </is>
       </c>
       <c r="E578" s="1" t="inlineStr">
@@ -19123,7 +19123,7 @@
       </c>
       <c r="B585" s="1" t="inlineStr">
         <is>
-          <t>[beːdʏʁfnɪs] 冲动；推动力〈n.〉</t>
+          <t>[beːdʏʁfnɪs] 需要；需求〈n.〉</t>
         </is>
       </c>
       <c r="C585" s="1" t="inlineStr">
@@ -19133,7 +19133,7 @@
       </c>
       <c r="D585" s="1" t="inlineStr">
         <is>
-          <t>冲动；推动力</t>
+          <t>需要；需求</t>
         </is>
       </c>
       <c r="E585" s="1" t="inlineStr">
@@ -19475,7 +19475,7 @@
       </c>
       <c r="B596" s="1" t="inlineStr">
         <is>
-          <t>[fɛʁmasəln] 混合；使微醉〈v.〉</t>
+          <t>[fɛʁmasəln] 搞砸；弄糟〈v.〉</t>
         </is>
       </c>
       <c r="C596" s="1" t="inlineStr">
@@ -19485,7 +19485,7 @@
       </c>
       <c r="D596" s="1" t="inlineStr">
         <is>
-          <t>混合；使微醉</t>
+          <t>搞砸；弄糟</t>
         </is>
       </c>
       <c r="E596" s="1" t="inlineStr">
@@ -19539,7 +19539,7 @@
       </c>
       <c r="B598" s="1" t="inlineStr">
         <is>
-          <t>[ɡʁam] 克；绿豆；鹰嘴豆〈n.〉</t>
+          <t>[ɡʁam] 克〈n.〉</t>
         </is>
       </c>
       <c r="C598" s="1" t="inlineStr">
@@ -19549,7 +19549,7 @@
       </c>
       <c r="D598" s="1" t="inlineStr">
         <is>
-          <t>克；绿豆；鹰嘴豆</t>
+          <t>克</t>
         </is>
       </c>
       <c r="E598" s="1" t="inlineStr">
@@ -19603,7 +19603,7 @@
       </c>
       <c r="B600" s="1" t="inlineStr">
         <is>
-          <t>[bɪldət] 窗体；表单〈n.〉</t>
+          <t>[bɪldət] 形成；构成；培养；教育〈n.〉</t>
         </is>
       </c>
       <c r="C600" s="1" t="inlineStr">
@@ -19613,7 +19613,7 @@
       </c>
       <c r="D600" s="1" t="inlineStr">
         <is>
-          <t>窗体；表单</t>
+          <t>形成；构成；培养；教育</t>
         </is>
       </c>
       <c r="E600" s="1" t="inlineStr">
@@ -19923,7 +19923,7 @@
       </c>
       <c r="B610" s="1" t="inlineStr">
         <is>
-          <t>[løːzəɡəlt] 赎金；赎身；赎回；赎〈n.〉</t>
+          <t>[løːzəɡəlt] 赎金〈n.〉〈n.〉</t>
         </is>
       </c>
       <c r="C610" s="1" t="inlineStr">
@@ -19933,7 +19933,7 @@
       </c>
       <c r="D610" s="1" t="inlineStr">
         <is>
-          <t>赎金；赎身；赎回；赎</t>
+          <t>赎金〈n.〉</t>
         </is>
       </c>
       <c r="E610" s="1" t="inlineStr">
@@ -19955,7 +19955,7 @@
       </c>
       <c r="B611" s="1" t="inlineStr">
         <is>
-          <t>[vaɪçən] 渐渐枯竭〈v.〉</t>
+          <t>[vaɪçən] 软化；让步；退缩〈v.〉</t>
         </is>
       </c>
       <c r="C611" s="1" t="inlineStr">
@@ -19965,7 +19965,7 @@
       </c>
       <c r="D611" s="1" t="inlineStr">
         <is>
-          <t>渐渐枯竭</t>
+          <t>软化；让步；退缩</t>
         </is>
       </c>
       <c r="E611" s="1" t="inlineStr">
@@ -20019,7 +20019,7 @@
       </c>
       <c r="B613" s="1" t="inlineStr">
         <is>
-          <t>[kʊpəl] 天体观测窗；天文航行舱〈n.f.〉</t>
+          <t>[kʊpəl] 圆顶；穹顶〈n.f.〉</t>
         </is>
       </c>
       <c r="C613" s="1" t="inlineStr">
@@ -20029,7 +20029,7 @@
       </c>
       <c r="D613" s="1" t="inlineStr">
         <is>
-          <t>天体观测窗；天文航行舱</t>
+          <t>圆顶；穹顶</t>
         </is>
       </c>
       <c r="E613" s="1" t="inlineStr">
@@ -20051,7 +20051,7 @@
       </c>
       <c r="B614" s="1" t="inlineStr">
         <is>
-          <t>[ɡɛvəʁkʃaft] 贸易；商业；交易〈n.f.〉</t>
+          <t>[ɡɛvəʁkʃaft] 工会〈n.f.〉</t>
         </is>
       </c>
       <c r="C614" s="1" t="inlineStr">
@@ -20061,7 +20061,7 @@
       </c>
       <c r="D614" s="1" t="inlineStr">
         <is>
-          <t>贸易；商业；交易</t>
+          <t>工会</t>
         </is>
       </c>
       <c r="E614" s="1" t="inlineStr">
@@ -20179,7 +20179,7 @@
       </c>
       <c r="B618" s="1" t="inlineStr">
         <is>
-          <t>[knaʁən] 广口瓶；震动〈v.〉</t>
+          <t>[knaʁən] 发出吱吱声；嘎吱作响〈v.〉</t>
         </is>
       </c>
       <c r="C618" s="1" t="inlineStr">
@@ -20189,7 +20189,7 @@
       </c>
       <c r="D618" s="1" t="inlineStr">
         <is>
-          <t>广口瓶；震动</t>
+          <t>发出吱吱声；嘎吱作响</t>
         </is>
       </c>
       <c r="E618" s="1" t="inlineStr">
@@ -20243,7 +20243,7 @@
       </c>
       <c r="B620" s="1" t="inlineStr">
         <is>
-          <t>[naxkɔmən] 攀登；上升；爬〈n.〉</t>
+          <t>[naxkɔmən] 后代；子孙〈n.〉</t>
         </is>
       </c>
       <c r="C620" s="1" t="inlineStr">
@@ -20253,7 +20253,7 @@
       </c>
       <c r="D620" s="1" t="inlineStr">
         <is>
-          <t>攀登；上升；爬</t>
+          <t>后代；子孙</t>
         </is>
       </c>
       <c r="E620" s="1" t="inlineStr">
@@ -20627,7 +20627,7 @@
       </c>
       <c r="B632" s="1" t="inlineStr">
         <is>
-          <t>[fɛʁaɪzən] 走开〈v.〉</t>
+          <t>[fɛʁaɪzən] 外出旅行；离家出行〈v.〉</t>
         </is>
       </c>
       <c r="C632" s="1" t="inlineStr">
@@ -20637,7 +20637,7 @@
       </c>
       <c r="D632" s="1" t="inlineStr">
         <is>
-          <t>走开</t>
+          <t>外出旅行；离家出行</t>
         </is>
       </c>
       <c r="E632" s="1" t="inlineStr">
@@ -20755,7 +20755,7 @@
       </c>
       <c r="B636" s="1" t="inlineStr">
         <is>
-          <t>[maʊlvʊʁf] 痣；鼹鼠；防波堤〈n.m.〉</t>
+          <t>[maʊlvʊʁf] 鼹鼠〈n.m.〉</t>
         </is>
       </c>
       <c r="C636" s="1" t="inlineStr">
@@ -20765,7 +20765,7 @@
       </c>
       <c r="D636" s="1" t="inlineStr">
         <is>
-          <t>痣；鼹鼠；防波堤</t>
+          <t>鼹鼠</t>
         </is>
       </c>
       <c r="E636" s="1" t="inlineStr">
@@ -21107,7 +21107,7 @@
       </c>
       <c r="B647" s="1" t="inlineStr">
         <is>
-          <t>[vanə] 在大桶里处理〈n.f.〉</t>
+          <t>[vanə] 浴缸；盆；槽〈n.f.〉</t>
         </is>
       </c>
       <c r="C647" s="1" t="inlineStr">
@@ -21117,7 +21117,7 @@
       </c>
       <c r="D647" s="1" t="inlineStr">
         <is>
-          <t>在大桶里处理</t>
+          <t>浴缸；盆；槽</t>
         </is>
       </c>
       <c r="E647" s="1" t="inlineStr">
@@ -21203,7 +21203,7 @@
       </c>
       <c r="B650" s="1" t="inlineStr">
         <is>
-          <t>[fɛʁbəsəʁt] 增大的；加强的〈adv.〉</t>
+          <t>[fɛʁbəsəʁt] 改进的；改善的〈adv.〉</t>
         </is>
       </c>
       <c r="C650" s="1" t="inlineStr">
@@ -21213,7 +21213,7 @@
       </c>
       <c r="D650" s="1" t="inlineStr">
         <is>
-          <t>增大的；加强的</t>
+          <t>改进的；改善的</t>
         </is>
       </c>
       <c r="E650" s="1" t="inlineStr">
@@ -21331,7 +21331,7 @@
       </c>
       <c r="B654" s="1" t="inlineStr">
         <is>
-          <t>[klɪʁən] 砰；报时的最后一声〈n.〉</t>
+          <t>[klɪʁən] （金属、玻璃等）发出清脆的碰撞声〈v.〉；名词 das Klirren 指叮当声〈n.〉</t>
         </is>
       </c>
       <c r="C654" s="1" t="inlineStr">
@@ -21341,7 +21341,7 @@
       </c>
       <c r="D654" s="1" t="inlineStr">
         <is>
-          <t>砰；报时的最后一声</t>
+          <t>（金属、玻璃等）发出清脆的碰撞声〈v.〉；名词 das Klirren 指叮当声</t>
         </is>
       </c>
       <c r="E654" s="1" t="inlineStr">
@@ -21459,7 +21459,7 @@
       </c>
       <c r="B658" s="1" t="inlineStr">
         <is>
-          <t>[ʁaɪt͡səndə] 挂〈adv.〉</t>
+          <t>[ʁaɪt͡səndə] 迷人的；可爱的〈adv.〉</t>
         </is>
       </c>
       <c r="C658" s="1" t="inlineStr">
@@ -21469,7 +21469,7 @@
       </c>
       <c r="D658" s="1" t="inlineStr">
         <is>
-          <t>挂</t>
+          <t>迷人的；可爱的</t>
         </is>
       </c>
       <c r="E658" s="1" t="inlineStr">
@@ -21619,7 +21619,7 @@
       </c>
       <c r="B663" s="1" t="inlineStr">
         <is>
-          <t>[kɔsta] 哥斯达黎加〈n.〉</t>
+          <t>[kɔsta] 肋骨（解剖学）〈n.f.〉〈n.〉</t>
         </is>
       </c>
       <c r="C663" s="1" t="inlineStr">
@@ -21629,7 +21629,7 @@
       </c>
       <c r="D663" s="1" t="inlineStr">
         <is>
-          <t>哥斯达黎加</t>
+          <t>肋骨（解剖学）〈n.f.〉</t>
         </is>
       </c>
       <c r="E663" s="1" t="inlineStr">
@@ -21971,7 +21971,7 @@
       </c>
       <c r="B674" s="1" t="inlineStr">
         <is>
-          <t>[vaːl] 猛揍〈n.m.〉</t>
+          <t>[vaːl] 鲸〈n.m.〉</t>
         </is>
       </c>
       <c r="C674" s="1" t="inlineStr">
@@ -21981,7 +21981,7 @@
       </c>
       <c r="D674" s="1" t="inlineStr">
         <is>
-          <t>猛揍</t>
+          <t>鲸</t>
         </is>
       </c>
       <c r="E674" s="1" t="inlineStr">
@@ -22035,7 +22035,7 @@
       </c>
       <c r="B676" s="1" t="inlineStr">
         <is>
-          <t>[ʃvɛnt͡sə] 角落；转角〈n.f.〉</t>
+          <t>[ʃvɛnt͡sə] 尾巴〈n.f.〉</t>
         </is>
       </c>
       <c r="C676" s="1" t="inlineStr">
@@ -22045,7 +22045,7 @@
       </c>
       <c r="D676" s="1" t="inlineStr">
         <is>
-          <t>角落；转角</t>
+          <t>尾巴</t>
         </is>
       </c>
       <c r="E676" s="1" t="inlineStr">
@@ -22259,7 +22259,7 @@
       </c>
       <c r="B683" s="1" t="inlineStr">
         <is>
-          <t>[pɛʁlən] 嘶嘶响；兴奋〈v.〉</t>
+          <t>[pɛʁlən] 像珍珠般闪耀；滴落〈v.〉〈v.〉</t>
         </is>
       </c>
       <c r="C683" s="1" t="inlineStr">
@@ -22269,7 +22269,7 @@
       </c>
       <c r="D683" s="1" t="inlineStr">
         <is>
-          <t>嘶嘶响；兴奋</t>
+          <t>像珍珠般闪耀；滴落〈v.〉</t>
         </is>
       </c>
       <c r="E683" s="1" t="inlineStr">
@@ -22483,7 +22483,7 @@
       </c>
       <c r="B690" s="1" t="inlineStr">
         <is>
-          <t>[kaːpiːɐ] 不；拒绝；否决票；没有〈n.〉</t>
+          <t>[kaːpiːɐ] 应为动词不定式 kapieren：懂得；理解〈v.〉〈n.〉</t>
         </is>
       </c>
       <c r="C690" s="1" t="inlineStr">
@@ -22493,7 +22493,7 @@
       </c>
       <c r="D690" s="1" t="inlineStr">
         <is>
-          <t>不；拒绝；否决票；没有</t>
+          <t>应为动词不定式 kapieren：懂得；理解〈v.〉</t>
         </is>
       </c>
       <c r="E690" s="1" t="inlineStr">
@@ -22515,7 +22515,7 @@
       </c>
       <c r="B691" s="1" t="inlineStr">
         <is>
-          <t>[kœçiːn] 家常小甜饼；饼干；普通小饼〈n.f.〉</t>
+          <t>[kœçiːn] 女厨师；厨娘〈n.f.〉</t>
         </is>
       </c>
       <c r="C691" s="1" t="inlineStr">
@@ -22525,7 +22525,7 @@
       </c>
       <c r="D691" s="1" t="inlineStr">
         <is>
-          <t>家常小甜饼；饼干；普通小饼</t>
+          <t>女厨师；厨娘</t>
         </is>
       </c>
       <c r="E691" s="1" t="inlineStr">
@@ -22611,7 +22611,7 @@
       </c>
       <c r="B694" s="1" t="inlineStr">
         <is>
-          <t>[fɔʁspʁəçən] 听；听力；试听；审计命令〈n.〉</t>
+          <t>[fɔʁspʁəçən] 试演；试镜；求见〈n.〉</t>
         </is>
       </c>
       <c r="C694" s="1" t="inlineStr">
@@ -22621,7 +22621,7 @@
       </c>
       <c r="D694" s="1" t="inlineStr">
         <is>
-          <t>听；听力；试听；审计命令</t>
+          <t>试演；试镜；求见</t>
         </is>
       </c>
       <c r="E694" s="1" t="inlineStr">
@@ -22931,7 +22931,7 @@
       </c>
       <c r="B704" s="1" t="inlineStr">
         <is>
-          <t>[peːʁʏkə] 假发；激怒〈n.f.〉</t>
+          <t>[peːʁʏkə] 假发〈n.f.〉</t>
         </is>
       </c>
       <c r="C704" s="1" t="inlineStr">
@@ -22941,7 +22941,7 @@
       </c>
       <c r="D704" s="1" t="inlineStr">
         <is>
-          <t>假发；激怒</t>
+          <t>假发</t>
         </is>
       </c>
       <c r="E704" s="1" t="inlineStr">
@@ -23027,7 +23027,7 @@
       </c>
       <c r="B707" s="1" t="inlineStr">
         <is>
-          <t>[liːfəʁvaɡən] 递送；交付；分娩〈n.m.〉</t>
+          <t>[liːfəʁvaɡən] 厢式送货车；送货卡车〈n.m.〉</t>
         </is>
       </c>
       <c r="C707" s="1" t="inlineStr">
@@ -23037,7 +23037,7 @@
       </c>
       <c r="D707" s="1" t="inlineStr">
         <is>
-          <t>递送；交付；分娩</t>
+          <t>厢式送货车；送货卡车</t>
         </is>
       </c>
       <c r="E707" s="1" t="inlineStr">
@@ -23091,7 +23091,7 @@
       </c>
       <c r="B709" s="1" t="inlineStr">
         <is>
-          <t>[dʁank] 强迫；强制〈n.m.〉</t>
+          <t>[dʁank] 冲动；渴望〈n.m.〉</t>
         </is>
       </c>
       <c r="C709" s="1" t="inlineStr">
@@ -23101,7 +23101,7 @@
       </c>
       <c r="D709" s="1" t="inlineStr">
         <is>
-          <t>强迫；强制</t>
+          <t>冲动；渴望</t>
         </is>
       </c>
       <c r="E709" s="1" t="inlineStr">
@@ -23219,7 +23219,7 @@
       </c>
       <c r="B713" s="1" t="inlineStr">
         <is>
-          <t>[ʃtʊʁt͡s] 种植者；农作物〈n.m.〉</t>
+          <t>[ʃtʊʁt͡s] 跌落；坠落；倒塌〈n.m.〉〈n.m.〉</t>
         </is>
       </c>
       <c r="C713" s="1" t="inlineStr">
@@ -23229,7 +23229,7 @@
       </c>
       <c r="D713" s="1" t="inlineStr">
         <is>
-          <t>种植者；农作物</t>
+          <t>跌落；坠落；倒塌〈n.m.〉</t>
         </is>
       </c>
       <c r="E713" s="1" t="inlineStr">
@@ -23283,7 +23283,7 @@
       </c>
       <c r="B715" s="1" t="inlineStr">
         <is>
-          <t>[vaʃ] 有；怀有；拿〈n.〉</t>
+          <t>[vaʃ] 洗涤（只作构词成分，如 Waschwasser）；无独立动词义〈n.〉〈n.〉</t>
         </is>
       </c>
       <c r="C715" s="1" t="inlineStr">
@@ -23293,7 +23293,7 @@
       </c>
       <c r="D715" s="1" t="inlineStr">
         <is>
-          <t>有；怀有；拿</t>
+          <t>洗涤（只作构词成分，如 Waschwasser）；无独立动词义〈n.〉</t>
         </is>
       </c>
       <c r="E715" s="1" t="inlineStr">
@@ -23475,7 +23475,7 @@
       </c>
       <c r="B721" s="1" t="inlineStr">
         <is>
-          <t>[fɛʁɡəltʊnk] 免除；解除；赦免〈n.f.〉</t>
+          <t>[fɛʁɡəltʊnk] 报复；报应〈n.f.〉</t>
         </is>
       </c>
       <c r="C721" s="1" t="inlineStr">
@@ -23485,7 +23485,7 @@
       </c>
       <c r="D721" s="1" t="inlineStr">
         <is>
-          <t>免除；解除；赦免</t>
+          <t>报复；报应</t>
         </is>
       </c>
       <c r="E721" s="1" t="inlineStr">
@@ -23571,7 +23571,7 @@
       </c>
       <c r="B724" s="1" t="inlineStr">
         <is>
-          <t>[vɪçtɪɡəʁəs] 有；怀有；拿〈n.〉</t>
+          <t>[vɪçtɪɡəʁəs] 更重要的事〈n.〉</t>
         </is>
       </c>
       <c r="C724" s="1" t="inlineStr">
@@ -23581,7 +23581,7 @@
       </c>
       <c r="D724" s="1" t="inlineStr">
         <is>
-          <t>有；怀有；拿</t>
+          <t>更重要的事</t>
         </is>
       </c>
       <c r="E724" s="1" t="inlineStr">
@@ -23603,7 +23603,7 @@
       </c>
       <c r="B725" s="1" t="inlineStr">
         <is>
-          <t>[ʃʊldɡəfyːlə] 良心的责备；后悔；悔恨〈n.〉</t>
+          <t>[ʃʊldɡəfyːlə] 内疚；负罪感〈n.pl.〉〈n.〉</t>
         </is>
       </c>
       <c r="C725" s="1" t="inlineStr">
@@ -23613,7 +23613,7 @@
       </c>
       <c r="D725" s="1" t="inlineStr">
         <is>
-          <t>良心的责备；后悔；悔恨</t>
+          <t>内疚；负罪感〈n.pl.〉</t>
         </is>
       </c>
       <c r="E725" s="1" t="inlineStr">
@@ -23667,7 +23667,7 @@
       </c>
       <c r="B727" s="1" t="inlineStr">
         <is>
-          <t>[fluːt] 流程；流动；流量〈n.f.〉</t>
+          <t>[fluːt] 洪水；潮水；浪潮〈n.f.〉</t>
         </is>
       </c>
       <c r="C727" s="1" t="inlineStr">
@@ -23677,7 +23677,7 @@
       </c>
       <c r="D727" s="1" t="inlineStr">
         <is>
-          <t>流程；流动；流量</t>
+          <t>洪水；潮水；浪潮</t>
         </is>
       </c>
       <c r="E727" s="1" t="inlineStr">
@@ -23731,12 +23731,12 @@
       </c>
       <c r="B729" s="1" t="inlineStr">
         <is>
-          <t>[kleːfəlant] 克利夫兰〈n.〉</t>
+          <t>[kleːvlənt] 克利夫兰〈n.〉</t>
         </is>
       </c>
       <c r="C729" s="1" t="inlineStr">
         <is>
-          <t>kleːfəlant</t>
+          <t>kleːvlənt</t>
         </is>
       </c>
       <c r="D729" s="1" t="inlineStr">
@@ -24019,7 +24019,7 @@
       </c>
       <c r="B738" s="1" t="inlineStr">
         <is>
-          <t>[mɔʁdfal] 谋杀；损毁〈n.m.〉</t>
+          <t>[mɔʁdfal] 谋杀案；凶杀案〈n.m.〉</t>
         </is>
       </c>
       <c r="C738" s="1" t="inlineStr">
@@ -24029,7 +24029,7 @@
       </c>
       <c r="D738" s="1" t="inlineStr">
         <is>
-          <t>谋杀；损毁</t>
+          <t>谋杀案；凶杀案</t>
         </is>
       </c>
       <c r="E738" s="1" t="inlineStr">
@@ -24147,7 +24147,7 @@
       </c>
       <c r="B742" s="1" t="inlineStr">
         <is>
-          <t>[t͡saɪt͡ʃʁɪft] 期刊的；间歇〈n.f.〉</t>
+          <t>[t͡saɪt͡ʃʁɪft] 杂志；期刊〈n.f.〉</t>
         </is>
       </c>
       <c r="C742" s="1" t="inlineStr">
@@ -24157,7 +24157,7 @@
       </c>
       <c r="D742" s="1" t="inlineStr">
         <is>
-          <t>期刊的；间歇</t>
+          <t>杂志；期刊</t>
         </is>
       </c>
       <c r="E742" s="1" t="inlineStr">
@@ -24211,7 +24211,7 @@
       </c>
       <c r="B744" s="1" t="inlineStr">
         <is>
-          <t>[ʃlaːmasəl] 食堂；伙食；用膳〈n.〉</t>
+          <t>[ʃlaːmasəl] 困境；麻烦；乱糟糟的局面〈n.〉</t>
         </is>
       </c>
       <c r="C744" s="1" t="inlineStr">
@@ -24221,7 +24221,7 @@
       </c>
       <c r="D744" s="1" t="inlineStr">
         <is>
-          <t>食堂；伙食；用膳</t>
+          <t>困境；麻烦；乱糟糟的局面</t>
         </is>
       </c>
       <c r="E744" s="1" t="inlineStr">
@@ -24467,7 +24467,7 @@
       </c>
       <c r="B752" s="1" t="inlineStr">
         <is>
-          <t>[t͡suːzɛt͡slɪçə] 首都；大写字母；资本；首都的〈adv.〉</t>
+          <t>[t͡suːzɛt͡slɪçə] 额外的；附加的〈adv.〉</t>
         </is>
       </c>
       <c r="C752" s="1" t="inlineStr">
@@ -24477,7 +24477,7 @@
       </c>
       <c r="D752" s="1" t="inlineStr">
         <is>
-          <t>首都；大写字母；资本；首都的</t>
+          <t>额外的；附加的</t>
         </is>
       </c>
       <c r="E752" s="1" t="inlineStr">
@@ -24755,7 +24755,7 @@
       </c>
       <c r="B761" s="1" t="inlineStr">
         <is>
-          <t>[yːbəʁkvəʁən] 十字架；十字架形物件；交叉〈v.〉</t>
+          <t>[yːbəʁkvəʁən] 横穿；横渡；越过〈v.〉</t>
         </is>
       </c>
       <c r="C761" s="1" t="inlineStr">
@@ -24765,7 +24765,7 @@
       </c>
       <c r="D761" s="1" t="inlineStr">
         <is>
-          <t>十字架；十字架形物件；交叉</t>
+          <t>横穿；横渡；越过</t>
         </is>
       </c>
       <c r="E761" s="1" t="inlineStr">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="B762" s="1" t="inlineStr">
         <is>
-          <t>[kʁɔʏt͡sʊnk] 四向停车〈n.〉</t>
+          <t>[kʁɔʏt͡sʊnk] 十字路口；交叉点；杂交〈n.〉</t>
         </is>
       </c>
       <c r="C762" s="1" t="inlineStr">
@@ -24797,7 +24797,7 @@
       </c>
       <c r="D762" s="1" t="inlineStr">
         <is>
-          <t>四向停车</t>
+          <t>十字路口；交叉点；杂交</t>
         </is>
       </c>
       <c r="E762" s="1" t="inlineStr">
@@ -24819,7 +24819,7 @@
       </c>
       <c r="B763" s="1" t="inlineStr">
         <is>
-          <t>[vaɪçə] 点；小数点；标点〈n.f.〉</t>
+          <t>[vaɪçə] 道岔；岔道〈n.f.〉</t>
         </is>
       </c>
       <c r="C763" s="1" t="inlineStr">
@@ -24829,7 +24829,7 @@
       </c>
       <c r="D763" s="1" t="inlineStr">
         <is>
-          <t>点；小数点；标点</t>
+          <t>道岔；岔道</t>
         </is>
       </c>
       <c r="E763" s="1" t="inlineStr">
@@ -24851,7 +24851,7 @@
       </c>
       <c r="B764" s="1" t="inlineStr">
         <is>
-          <t>[pʊnktən] 得分；抓痕；二十个〈v.〉</t>
+          <t>[pʊnktən] 得分〈v.〉</t>
         </is>
       </c>
       <c r="C764" s="1" t="inlineStr">
@@ -24861,7 +24861,7 @@
       </c>
       <c r="D764" s="1" t="inlineStr">
         <is>
-          <t>得分；抓痕；二十个</t>
+          <t>得分</t>
         </is>
       </c>
       <c r="E764" s="1" t="inlineStr">
@@ -24979,12 +24979,12 @@
       </c>
       <c r="B768" s="1" t="inlineStr">
         <is>
-          <t>[ɡeːakt] 切碎的；被黑客入侵的〈adv.〉</t>
+          <t>[ɡəhakt] 切碎的；被黑客入侵的〈adv.〉</t>
         </is>
       </c>
       <c r="C768" s="1" t="inlineStr">
         <is>
-          <t>ɡeːakt</t>
+          <t>ɡəhakt</t>
         </is>
       </c>
       <c r="D768" s="1" t="inlineStr">
@@ -25203,7 +25203,7 @@
       </c>
       <c r="B775" s="1" t="inlineStr">
         <is>
-          <t>[boːn] 证人；保证人；证明者〈n.m.〉</t>
+          <t>[boːn] 优惠券；票券〈n.m.〉</t>
         </is>
       </c>
       <c r="C775" s="1" t="inlineStr">
@@ -25213,7 +25213,7 @@
       </c>
       <c r="D775" s="1" t="inlineStr">
         <is>
-          <t>证人；保证人；证明者</t>
+          <t>优惠券；票券</t>
         </is>
       </c>
       <c r="E775" s="1" t="inlineStr">
@@ -25235,7 +25235,7 @@
       </c>
       <c r="B776" s="1" t="inlineStr">
         <is>
-          <t>[ʃvɪt͡sən] 汗；汗水；水珠〈v.〉</t>
+          <t>[ʃvɪt͡sən] 出汗；流汗〈v.〉</t>
         </is>
       </c>
       <c r="C776" s="1" t="inlineStr">
@@ -25245,7 +25245,7 @@
       </c>
       <c r="D776" s="1" t="inlineStr">
         <is>
-          <t>汗；汗水；水珠</t>
+          <t>出汗；流汗</t>
         </is>
       </c>
       <c r="E776" s="1" t="inlineStr">
@@ -25427,7 +25427,7 @@
       </c>
       <c r="B782" s="1" t="inlineStr">
         <is>
-          <t>[t͡sɛʁbʁəçən] 休息；中断；破裂处〈v.〉</t>
+          <t>[t͡sɛʁbʁəçən] 打碎；折断；破裂〈v.〉</t>
         </is>
       </c>
       <c r="C782" s="1" t="inlineStr">
@@ -25437,7 +25437,7 @@
       </c>
       <c r="D782" s="1" t="inlineStr">
         <is>
-          <t>休息；中断；破裂处</t>
+          <t>打碎；折断；破裂</t>
         </is>
       </c>
       <c r="E782" s="1" t="inlineStr">
@@ -25555,12 +25555,12 @@
       </c>
       <c r="B786" s="1" t="inlineStr">
         <is>
-          <t>[fʊlkaːn] 火山〈n.m.〉</t>
+          <t>[vʊlkaːn] 火山〈n.m.〉</t>
         </is>
       </c>
       <c r="C786" s="1" t="inlineStr">
         <is>
-          <t>fʊlkaːn</t>
+          <t>vʊlkaːn</t>
         </is>
       </c>
       <c r="D786" s="1" t="inlineStr">
@@ -25811,7 +25811,7 @@
       </c>
       <c r="B794" s="1" t="inlineStr">
         <is>
-          <t>[mɪtaɡspaʊzə] 午餐〈n.f.〉</t>
+          <t>[mɪtaɡspaʊzə] 午休；午间休息〈n.f.〉</t>
         </is>
       </c>
       <c r="C794" s="1" t="inlineStr">
@@ -25821,7 +25821,7 @@
       </c>
       <c r="D794" s="1" t="inlineStr">
         <is>
-          <t>午餐</t>
+          <t>午休；午间休息</t>
         </is>
       </c>
       <c r="E794" s="1" t="inlineStr">
@@ -25843,7 +25843,7 @@
       </c>
       <c r="B795" s="1" t="inlineStr">
         <is>
-          <t>[vɛtkampf] 竞赛；争论；竞争；争取〈n.m.〉</t>
+          <t>[vɛtkampf] 竞赛；竞争；比赛〈n.m.〉〈n.m.〉</t>
         </is>
       </c>
       <c r="C795" s="1" t="inlineStr">
@@ -25853,7 +25853,7 @@
       </c>
       <c r="D795" s="1" t="inlineStr">
         <is>
-          <t>竞赛；争论；竞争；争取</t>
+          <t>竞赛；竞争；比赛〈n.m.〉</t>
         </is>
       </c>
       <c r="E795" s="1" t="inlineStr">
@@ -26067,7 +26067,7 @@
       </c>
       <c r="B802" s="1" t="inlineStr">
         <is>
-          <t>[fɔʁtzət͡sən] 穷追；追问〈v.〉</t>
+          <t>[fɔʁtzət͡sən] 继续；接着进行〈v.〉</t>
         </is>
       </c>
       <c r="C802" s="1" t="inlineStr">
@@ -26077,7 +26077,7 @@
       </c>
       <c r="D802" s="1" t="inlineStr">
         <is>
-          <t>穷追；追问</t>
+          <t>继续；接着进行</t>
         </is>
       </c>
       <c r="E802" s="1" t="inlineStr">
@@ -26099,7 +26099,7 @@
       </c>
       <c r="B803" s="1" t="inlineStr">
         <is>
-          <t>[anpasən] 西服料〈n.〉</t>
+          <t>[anpasən] 使适应；调整；使适合〈n.〉</t>
         </is>
       </c>
       <c r="C803" s="1" t="inlineStr">
@@ -26109,7 +26109,7 @@
       </c>
       <c r="D803" s="1" t="inlineStr">
         <is>
-          <t>西服料</t>
+          <t>使适应；调整；使适合</t>
         </is>
       </c>
       <c r="E803" s="1" t="inlineStr">
@@ -26195,7 +26195,7 @@
       </c>
       <c r="B806" s="1" t="inlineStr">
         <is>
-          <t>[tʁaʊ] 我；电流；中断；指令〈n.〉</t>
+          <t>[tʁaʊ] 信任；敢于（trauen 的命令式）〈n.〉</t>
         </is>
       </c>
       <c r="C806" s="1" t="inlineStr">
@@ -26205,7 +26205,7 @@
       </c>
       <c r="D806" s="1" t="inlineStr">
         <is>
-          <t>我；电流；中断；指令</t>
+          <t>信任；敢于（trauen 的命令式）</t>
         </is>
       </c>
       <c r="E806" s="1" t="inlineStr">
@@ -26291,7 +26291,7 @@
       </c>
       <c r="B809" s="1" t="inlineStr">
         <is>
-          <t>[mɛnʃlɪçkaɪt] 人性；人类；博爱〈n.f.〉</t>
+          <t>[mɛnʃlɪçkaɪt] 人性；人道；仁慈〈n.f.〉〈n.f.〉</t>
         </is>
       </c>
       <c r="C809" s="1" t="inlineStr">
@@ -26301,7 +26301,7 @@
       </c>
       <c r="D809" s="1" t="inlineStr">
         <is>
-          <t>人性；人类；博爱</t>
+          <t>人性；人道；仁慈〈n.f.〉</t>
         </is>
       </c>
       <c r="E809" s="1" t="inlineStr">
@@ -26387,7 +26387,7 @@
       </c>
       <c r="B812" s="1" t="inlineStr">
         <is>
-          <t>[pʁeːmiːʁə] 首次〈n.f.〉</t>
+          <t>[pʁeːmiːʁə] 首演；首次公演〈n.f.〉〈n.f.〉</t>
         </is>
       </c>
       <c r="C812" s="1" t="inlineStr">
@@ -26397,7 +26397,7 @@
       </c>
       <c r="D812" s="1" t="inlineStr">
         <is>
-          <t>首次</t>
+          <t>首演；首次公演〈n.f.〉</t>
         </is>
       </c>
       <c r="E812" s="1" t="inlineStr">
@@ -26419,7 +26419,7 @@
       </c>
       <c r="B813" s="1" t="inlineStr">
         <is>
-          <t>[ʃvɪnɡən] 摇摆；振幅；音律〈n.〉</t>
+          <t>[ʃvɪnɡən] 摇摆；挥动；荡秋千（schwingen的动名词）〈n.〉</t>
         </is>
       </c>
       <c r="C813" s="1" t="inlineStr">
@@ -26429,7 +26429,7 @@
       </c>
       <c r="D813" s="1" t="inlineStr">
         <is>
-          <t>摇摆；振幅；音律</t>
+          <t>摇摆；挥动；荡秋千（schwingen的动名词）</t>
         </is>
       </c>
       <c r="E813" s="1" t="inlineStr">
@@ -26611,7 +26611,7 @@
       </c>
       <c r="B819" s="1" t="inlineStr">
         <is>
-          <t>[kʁʏstaːl] &lt;俚&gt;去氧麻黄硷粉〈n.〉</t>
+          <t>[kʁʏstaːl] 水晶；结晶〈n.〉</t>
         </is>
       </c>
       <c r="C819" s="1" t="inlineStr">
@@ -26621,7 +26621,7 @@
       </c>
       <c r="D819" s="1" t="inlineStr">
         <is>
-          <t>&lt;俚&gt;去氧麻黄硷粉</t>
+          <t>水晶；结晶</t>
         </is>
       </c>
       <c r="E819" s="1" t="inlineStr">
@@ -26771,7 +26771,7 @@
       </c>
       <c r="B824" s="1" t="inlineStr">
         <is>
-          <t>[leːbənslaʊf] 课程；学程〈n.m.〉</t>
+          <t>[leːbənslaʊf] 履历；简历〈n.m.〉</t>
         </is>
       </c>
       <c r="C824" s="1" t="inlineStr">
@@ -26781,7 +26781,7 @@
       </c>
       <c r="D824" s="1" t="inlineStr">
         <is>
-          <t>课程；学程</t>
+          <t>履历；简历</t>
         </is>
       </c>
       <c r="E824" s="1" t="inlineStr">
@@ -26803,7 +26803,7 @@
       </c>
       <c r="B825" s="1" t="inlineStr">
         <is>
-          <t>[ʁeːlatiːf] 亲戚；相对的〈adj.〉</t>
+          <t>[ʁeːlatiːf] 相对的；比较的〈adj.〉</t>
         </is>
       </c>
       <c r="C825" s="1" t="inlineStr">
@@ -26813,7 +26813,7 @@
       </c>
       <c r="D825" s="1" t="inlineStr">
         <is>
-          <t>亲戚；相对的</t>
+          <t>相对的；比较的</t>
         </is>
       </c>
       <c r="E825" s="1" t="inlineStr">
@@ -27027,7 +27027,7 @@
       </c>
       <c r="B832" s="1" t="inlineStr">
         <is>
-          <t>[tʁanspɔʁtiːʁən] 运输；运输工具；激动〈v.〉</t>
+          <t>[tʁanspɔʁtiːʁən] 运输；运送；输送〈v.〉</t>
         </is>
       </c>
       <c r="C832" s="1" t="inlineStr">
@@ -27037,7 +27037,7 @@
       </c>
       <c r="D832" s="1" t="inlineStr">
         <is>
-          <t>运输；运输工具；激动</t>
+          <t>运输；运送；输送</t>
         </is>
       </c>
       <c r="E832" s="1" t="inlineStr">
@@ -27059,7 +27059,7 @@
       </c>
       <c r="B833" s="1" t="inlineStr">
         <is>
-          <t>[ʃpɔntaːn] 特定场合〈n.〉</t>
+          <t>[ʃpɔntaːn] 自发的；即兴的〈n.〉</t>
         </is>
       </c>
       <c r="C833" s="1" t="inlineStr">
@@ -27069,7 +27069,7 @@
       </c>
       <c r="D833" s="1" t="inlineStr">
         <is>
-          <t>特定场合</t>
+          <t>自发的；即兴的</t>
         </is>
       </c>
       <c r="E833" s="1" t="inlineStr">
@@ -27187,7 +27187,7 @@
       </c>
       <c r="B837" s="1" t="inlineStr">
         <is>
-          <t>[anspʁəçən] 反应；反作用；反动〈n.〉</t>
+          <t>[anspʁəçən] 招呼；搭话〈v.ansprechen〉〈n.〉</t>
         </is>
       </c>
       <c r="C837" s="1" t="inlineStr">
@@ -27197,7 +27197,7 @@
       </c>
       <c r="D837" s="1" t="inlineStr">
         <is>
-          <t>反应；反作用；反动</t>
+          <t>招呼；搭话〈v.ansprechen〉</t>
         </is>
       </c>
       <c r="E837" s="1" t="inlineStr">
@@ -27251,7 +27251,7 @@
       </c>
       <c r="B839" s="1" t="inlineStr">
         <is>
-          <t>[ʃtʏʁmən] 投掷；打击；快速〈v.〉</t>
+          <t>[ʃtʏʁmən] 猛攻；冲锋；刮大风〈v.〉</t>
         </is>
       </c>
       <c r="C839" s="1" t="inlineStr">
@@ -27261,7 +27261,7 @@
       </c>
       <c r="D839" s="1" t="inlineStr">
         <is>
-          <t>投掷；打击；快速</t>
+          <t>猛攻；冲锋；刮大风</t>
         </is>
       </c>
       <c r="E839" s="1" t="inlineStr">
@@ -27411,7 +27411,7 @@
       </c>
       <c r="B844" s="1" t="inlineStr">
         <is>
-          <t>[ɡɔldən] 金毛猎犬〈n.〉</t>
+          <t>[ɡɔldən] 金色的；黄金的〈n.〉</t>
         </is>
       </c>
       <c r="C844" s="1" t="inlineStr">
@@ -27421,7 +27421,7 @@
       </c>
       <c r="D844" s="1" t="inlineStr">
         <is>
-          <t>金毛猎犬</t>
+          <t>金色的；黄金的</t>
         </is>
       </c>
       <c r="E844" s="1" t="inlineStr">
@@ -27475,7 +27475,7 @@
       </c>
       <c r="B846" s="1" t="inlineStr">
         <is>
-          <t>[kant͡slɐ] 记录者；登记者；登记官员；登记员〈n.m.〉</t>
+          <t>[kant͡slɐ] 总理；首相；大臣〈n.m.〉</t>
         </is>
       </c>
       <c r="C846" s="1" t="inlineStr">
@@ -27485,7 +27485,7 @@
       </c>
       <c r="D846" s="1" t="inlineStr">
         <is>
-          <t>记录者；登记者；登记官员；登记员</t>
+          <t>总理；首相；大臣</t>
         </is>
       </c>
       <c r="E846" s="1" t="inlineStr">
@@ -27571,7 +27571,7 @@
       </c>
       <c r="B849" s="1" t="inlineStr">
         <is>
-          <t>[ʃlɪtən] 滑；滑道；山崩〈n.m.〉</t>
+          <t>[ʃlɪtən] 雪橇；滑橇〈n.m.〉</t>
         </is>
       </c>
       <c r="C849" s="1" t="inlineStr">
@@ -27581,7 +27581,7 @@
       </c>
       <c r="D849" s="1" t="inlineStr">
         <is>
-          <t>滑；滑道；山崩</t>
+          <t>雪橇；滑橇</t>
         </is>
       </c>
       <c r="E849" s="1" t="inlineStr">
@@ -27667,7 +27667,7 @@
       </c>
       <c r="B852" s="1" t="inlineStr">
         <is>
-          <t>[fɔʁɡəstɐn] 天；日子；白天〈adv.〉</t>
+          <t>[fɔʁɡəstɐn] 前天〈adv.〉</t>
         </is>
       </c>
       <c r="C852" s="1" t="inlineStr">
@@ -27677,7 +27677,7 @@
       </c>
       <c r="D852" s="1" t="inlineStr">
         <is>
-          <t>天；日子；白天</t>
+          <t>前天</t>
         </is>
       </c>
       <c r="E852" s="1" t="inlineStr">
@@ -27699,7 +27699,7 @@
       </c>
       <c r="B853" s="1" t="inlineStr">
         <is>
-          <t>[bɛtʁaɪbən] 鼓动；煽动；教唆；主使〈n.〉</t>
+          <t>[bɛtʁaɪbən] 经营；运营；从事；推动〈n.〉</t>
         </is>
       </c>
       <c r="C853" s="1" t="inlineStr">
@@ -27709,7 +27709,7 @@
       </c>
       <c r="D853" s="1" t="inlineStr">
         <is>
-          <t>鼓动；煽动；教唆；主使</t>
+          <t>经营；运营；从事；推动</t>
         </is>
       </c>
       <c r="E853" s="1" t="inlineStr">
@@ -28019,7 +28019,7 @@
       </c>
       <c r="B863" s="1" t="inlineStr">
         <is>
-          <t>[ʊntəʁvəlt] 黑社会；强盗世界〈n.〉</t>
+          <t>[ʊntəʁvəlt] 阴间；冥界；黑社会〈n.f.〉〈n.〉</t>
         </is>
       </c>
       <c r="C863" s="1" t="inlineStr">
@@ -28029,7 +28029,7 @@
       </c>
       <c r="D863" s="1" t="inlineStr">
         <is>
-          <t>黑社会；强盗世界</t>
+          <t>阴间；冥界；黑社会〈n.f.〉</t>
         </is>
       </c>
       <c r="E863" s="1" t="inlineStr">
@@ -28179,7 +28179,7 @@
       </c>
       <c r="B868" s="1" t="inlineStr">
         <is>
-          <t>[aʊsɡəliːfəʁt] 船；装船〈adv.〉</t>
+          <t>[aʊsɡəliːfəʁt] 已交货的；任人摆布的〈adv.〉</t>
         </is>
       </c>
       <c r="C868" s="1" t="inlineStr">
@@ -28189,7 +28189,7 @@
       </c>
       <c r="D868" s="1" t="inlineStr">
         <is>
-          <t>船；装船</t>
+          <t>已交货的；任人摆布的</t>
         </is>
       </c>
       <c r="E868" s="1" t="inlineStr">
@@ -28435,7 +28435,7 @@
       </c>
       <c r="B876" s="1" t="inlineStr">
         <is>
-          <t>[mak] 莫蒂〈男子名〉〈n.〉</t>
+          <t>[mak] 怪癖；毛病；裂缝〈n.〉</t>
         </is>
       </c>
       <c r="C876" s="1" t="inlineStr">
@@ -28445,7 +28445,7 @@
       </c>
       <c r="D876" s="1" t="inlineStr">
         <is>
-          <t>莫蒂〈男子名〉</t>
+          <t>怪癖；毛病；裂缝</t>
         </is>
       </c>
       <c r="E876" s="1" t="inlineStr">
@@ -28787,17 +28787,17 @@
       </c>
       <c r="B887" s="1" t="inlineStr">
         <is>
-          <t>[mɔʊnt] 埃佛勒斯峰〈n.〉</t>
+          <t>[maʊnt] （用于山名）山；峰〈n.m.〉〈n.〉</t>
         </is>
       </c>
       <c r="C887" s="1" t="inlineStr">
         <is>
-          <t>mɔʊnt</t>
+          <t>maʊnt</t>
         </is>
       </c>
       <c r="D887" s="1" t="inlineStr">
         <is>
-          <t>埃佛勒斯峰</t>
+          <t>（用于山名）山；峰〈n.m.〉</t>
         </is>
       </c>
       <c r="E887" s="1" t="inlineStr">
@@ -28819,7 +28819,7 @@
       </c>
       <c r="B888" s="1" t="inlineStr">
         <is>
-          <t>[fɛʁpflɪçtʊnɡən] 碍事的人或物；负债〈n.〉</t>
+          <t>[fɛʁpflɪçtʊnɡən] 义务；债务；承诺〈n.〉</t>
         </is>
       </c>
       <c r="C888" s="1" t="inlineStr">
@@ -28829,7 +28829,7 @@
       </c>
       <c r="D888" s="1" t="inlineStr">
         <is>
-          <t>碍事的人或物；负债</t>
+          <t>义务；债务；承诺</t>
         </is>
       </c>
       <c r="E888" s="1" t="inlineStr">
@@ -28979,7 +28979,7 @@
       </c>
       <c r="B893" s="1" t="inlineStr">
         <is>
-          <t>[aʊfʃʁaɪbən] 写下；写文章贬低；降低地位〈v.〉</t>
+          <t>[aʊfʃʁaɪbən] 写下；记下〈v.〉</t>
         </is>
       </c>
       <c r="C893" s="1" t="inlineStr">
@@ -28989,7 +28989,7 @@
       </c>
       <c r="D893" s="1" t="inlineStr">
         <is>
-          <t>写下；写文章贬低；降低地位</t>
+          <t>写下；记下</t>
         </is>
       </c>
       <c r="E893" s="1" t="inlineStr">
@@ -29075,17 +29075,17 @@
       </c>
       <c r="B896" s="1" t="inlineStr">
         <is>
-          <t>[niːfɛaʊ] 平面；扁平物；机翼〈n.〉</t>
+          <t>[niːvoː] 水平；水准〈n.〉</t>
         </is>
       </c>
       <c r="C896" s="1" t="inlineStr">
         <is>
-          <t>niːfɛaʊ</t>
+          <t>niːvoː</t>
         </is>
       </c>
       <c r="D896" s="1" t="inlineStr">
         <is>
-          <t>平面；扁平物；机翼</t>
+          <t>水平；水准</t>
         </is>
       </c>
       <c r="E896" s="1" t="inlineStr">
@@ -29107,17 +29107,17 @@
       </c>
       <c r="B897" s="1" t="inlineStr">
         <is>
-          <t>[faːndʊnk] 法律；法则；定律〈n.f.〉</t>
+          <t>[faːndʊŋ] 搜捕；缉查；追查〈n.f.〉</t>
         </is>
       </c>
       <c r="C897" s="1" t="inlineStr">
         <is>
-          <t>faːndʊnk</t>
+          <t>faːndʊŋ</t>
         </is>
       </c>
       <c r="D897" s="1" t="inlineStr">
         <is>
-          <t>法律；法则；定律</t>
+          <t>搜捕；缉查；追查</t>
         </is>
       </c>
       <c r="E897" s="1" t="inlineStr">
@@ -29203,7 +29203,7 @@
       </c>
       <c r="B900" s="1" t="inlineStr">
         <is>
-          <t>[matʁat͡sə] 床垫；空气垫；沉床；褥子〈n.f.〉</t>
+          <t>[matʁat͡sə] 床垫〈n.f.〉</t>
         </is>
       </c>
       <c r="C900" s="1" t="inlineStr">
@@ -29213,7 +29213,7 @@
       </c>
       <c r="D900" s="1" t="inlineStr">
         <is>
-          <t>床垫；空气垫；沉床；褥子</t>
+          <t>床垫</t>
         </is>
       </c>
       <c r="E900" s="1" t="inlineStr">
@@ -29235,7 +29235,7 @@
       </c>
       <c r="B901" s="1" t="inlineStr">
         <is>
-          <t>[mɔʁdvafə] 谋杀；损毁〈n.f.〉</t>
+          <t>[mɔʁdvafə] 凶器；杀人武器〈f.〉〈n.f.〉</t>
         </is>
       </c>
       <c r="C901" s="1" t="inlineStr">
@@ -29245,7 +29245,7 @@
       </c>
       <c r="D901" s="1" t="inlineStr">
         <is>
-          <t>谋杀；损毁</t>
+          <t>凶器；杀人武器〈f.〉</t>
         </is>
       </c>
       <c r="E901" s="1" t="inlineStr">
@@ -29267,7 +29267,7 @@
       </c>
       <c r="B902" s="1" t="inlineStr">
         <is>
-          <t>[fiːnant͡siːlə] 付款；支付的款项；偿还〈adv.〉</t>
+          <t>[fiːnant͡siːlə] 财政的；金融的；财务的〈adv.〉</t>
         </is>
       </c>
       <c r="C902" s="1" t="inlineStr">
@@ -29277,7 +29277,7 @@
       </c>
       <c r="D902" s="1" t="inlineStr">
         <is>
-          <t>付款；支付的款项；偿还</t>
+          <t>财政的；金融的；财务的</t>
         </is>
       </c>
       <c r="E902" s="1" t="inlineStr">
@@ -29363,7 +29363,7 @@
       </c>
       <c r="B905" s="1" t="inlineStr">
         <is>
-          <t>[kʊʁt͡sfʁɪstɪç] 短的；近的；矮的〈adj.〉</t>
+          <t>[kʊʁt͡sfʁɪstɪç] 短期的；临时的〈adj.〉</t>
         </is>
       </c>
       <c r="C905" s="1" t="inlineStr">
@@ -29373,7 +29373,7 @@
       </c>
       <c r="D905" s="1" t="inlineStr">
         <is>
-          <t>短的；近的；矮的</t>
+          <t>短期的；临时的</t>
         </is>
       </c>
       <c r="E905" s="1" t="inlineStr">
@@ -29395,7 +29395,7 @@
       </c>
       <c r="B906" s="1" t="inlineStr">
         <is>
-          <t>[ɛʁlanɡən] 伸出；延伸；区域〈v.〉</t>
+          <t>[ɛʁlanɡən] 获得；取得；达到〈v.〉</t>
         </is>
       </c>
       <c r="C906" s="1" t="inlineStr">
@@ -29405,7 +29405,7 @@
       </c>
       <c r="D906" s="1" t="inlineStr">
         <is>
-          <t>伸出；延伸；区域</t>
+          <t>获得；取得；达到</t>
         </is>
       </c>
       <c r="E906" s="1" t="inlineStr">
@@ -29459,7 +29459,7 @@
       </c>
       <c r="B908" s="1" t="inlineStr">
         <is>
-          <t>[ɡɛvaɡt] 刀口锐利的；尖利的；急躁的〈adv.〉</t>
+          <t>[ɡɛvaɡt] 大胆的；冒险的〈adv.〉</t>
         </is>
       </c>
       <c r="C908" s="1" t="inlineStr">
@@ -29469,7 +29469,7 @@
       </c>
       <c r="D908" s="1" t="inlineStr">
         <is>
-          <t>刀口锐利的；尖利的；急躁的</t>
+          <t>大胆的；冒险的</t>
         </is>
       </c>
       <c r="E908" s="1" t="inlineStr">
@@ -29555,7 +29555,7 @@
       </c>
       <c r="B911" s="1" t="inlineStr">
         <is>
-          <t>[aɪnpakən] 外套；围巾；包裹物〈v.〉</t>
+          <t>[aɪnpakən] 包装；打包；把…包起来〈v.〉</t>
         </is>
       </c>
       <c r="C911" s="1" t="inlineStr">
@@ -29565,7 +29565,7 @@
       </c>
       <c r="D911" s="1" t="inlineStr">
         <is>
-          <t>外套；围巾；包裹物</t>
+          <t>包装；打包；把…包起来</t>
         </is>
       </c>
       <c r="E911" s="1" t="inlineStr">
@@ -29587,7 +29587,7 @@
       </c>
       <c r="B912" s="1" t="inlineStr">
         <is>
-          <t>[baloːn] 激增〈n.m.〉</t>
+          <t>[baloːn] 气球〈n.m.〉</t>
         </is>
       </c>
       <c r="C912" s="1" t="inlineStr">
@@ -29597,7 +29597,7 @@
       </c>
       <c r="D912" s="1" t="inlineStr">
         <is>
-          <t>激增</t>
+          <t>气球</t>
         </is>
       </c>
       <c r="E912" s="1" t="inlineStr">
@@ -29651,7 +29651,7 @@
       </c>
       <c r="B914" s="1" t="inlineStr">
         <is>
-          <t>[ʁuːdəl] 包裹；一伙；一副〈n.〉</t>
+          <t>[ʁuːdəl] 兽群；一群（狼、犬等）〈n.〉</t>
         </is>
       </c>
       <c r="C914" s="1" t="inlineStr">
@@ -29661,7 +29661,7 @@
       </c>
       <c r="D914" s="1" t="inlineStr">
         <is>
-          <t>包裹；一伙；一副</t>
+          <t>兽群；一群（狼、犬等）</t>
         </is>
       </c>
       <c r="E914" s="1" t="inlineStr">
@@ -29779,12 +29779,12 @@
       </c>
       <c r="B918" s="1" t="inlineStr">
         <is>
-          <t>[zɛnɡəʁiːn] 女歌手；女诗人〈n.f.〉</t>
+          <t>[zɛːŋəʁɪn] 女歌手；女诗人〈n.f.〉</t>
         </is>
       </c>
       <c r="C918" s="1" t="inlineStr">
         <is>
-          <t>zɛnɡəʁiːn</t>
+          <t>zɛːŋəʁɪn</t>
         </is>
       </c>
       <c r="D918" s="1" t="inlineStr">
@@ -29843,12 +29843,12 @@
       </c>
       <c r="B920" s="1" t="inlineStr">
         <is>
-          <t>[liːmɔʊzɪnə] 轿车〈n.f.〉</t>
+          <t>[limoziːnə] 轿车〈n.f.〉</t>
         </is>
       </c>
       <c r="C920" s="1" t="inlineStr">
         <is>
-          <t>liːmɔʊzɪnə</t>
+          <t>limoziːnə</t>
         </is>
       </c>
       <c r="D920" s="1" t="inlineStr">
@@ -30163,7 +30163,7 @@
       </c>
       <c r="B930" s="1" t="inlineStr">
         <is>
-          <t>[pʁeːdɪɡt] 说教；训诫〈n.f.〉</t>
+          <t>[pʁeːdɪɡt] 布道；讲道〈n.f.〉〈n.f.〉</t>
         </is>
       </c>
       <c r="C930" s="1" t="inlineStr">
@@ -30173,7 +30173,7 @@
       </c>
       <c r="D930" s="1" t="inlineStr">
         <is>
-          <t>说教；训诫</t>
+          <t>布道；讲道〈n.f.〉</t>
         </is>
       </c>
       <c r="E930" s="1" t="inlineStr">
@@ -30227,7 +30227,7 @@
       </c>
       <c r="B932" s="1" t="inlineStr">
         <is>
-          <t>[ɛʁviːzən] 的过去分词〈adj.〉</t>
+          <t>[ɛʁviːzən] 证明；证实；表明〈adj.〉</t>
         </is>
       </c>
       <c r="C932" s="1" t="inlineStr">
@@ -30237,7 +30237,7 @@
       </c>
       <c r="D932" s="1" t="inlineStr">
         <is>
-          <t>的过去分词</t>
+          <t>证明；证实；表明</t>
         </is>
       </c>
       <c r="E932" s="1" t="inlineStr">
@@ -30451,7 +30451,7 @@
       </c>
       <c r="B939" s="1" t="inlineStr">
         <is>
-          <t>[ɡɛvøːnlɪçə] 较少的；较小的；次要的〈adv.〉</t>
+          <t>[ɡɛvøːnlɪçə] 普通的；平常的；通常的〈adv.〉</t>
         </is>
       </c>
       <c r="C939" s="1" t="inlineStr">
@@ -30461,7 +30461,7 @@
       </c>
       <c r="D939" s="1" t="inlineStr">
         <is>
-          <t>较少的；较小的；次要的</t>
+          <t>普通的；平常的；通常的</t>
         </is>
       </c>
       <c r="E939" s="1" t="inlineStr">
@@ -30579,12 +30579,12 @@
       </c>
       <c r="B943" s="1" t="inlineStr">
         <is>
-          <t>[ʁaːfən] 狂吼；叫嚷〈v.〉</t>
+          <t>[ʁaːvən] 狂吼；叫嚷〈v.〉</t>
         </is>
       </c>
       <c r="C943" s="1" t="inlineStr">
         <is>
-          <t>ʁaːfən</t>
+          <t>ʁaːvən</t>
         </is>
       </c>
       <c r="D943" s="1" t="inlineStr">
@@ -30643,7 +30643,7 @@
       </c>
       <c r="B945" s="1" t="inlineStr">
         <is>
-          <t>[ʊnklaːɐ] 无辩义作用的；无区别的〈adv.〉</t>
+          <t>[ʊnklaːɐ] 不清楚的；不明确的〈adv.〉</t>
         </is>
       </c>
       <c r="C945" s="1" t="inlineStr">
@@ -30653,7 +30653,7 @@
       </c>
       <c r="D945" s="1" t="inlineStr">
         <is>
-          <t>无辩义作用的；无区别的</t>
+          <t>不清楚的；不明确的</t>
         </is>
       </c>
       <c r="E945" s="1" t="inlineStr">
@@ -31155,7 +31155,7 @@
       </c>
       <c r="B961" s="1" t="inlineStr">
         <is>
-          <t>[aʊftʁaɪbən] 上升；高地；增高；升起〈v.〉</t>
+          <t>[aʊftʁaɪbən] 弄到；搞到；驱赶上去〈v.〉</t>
         </is>
       </c>
       <c r="C961" s="1" t="inlineStr">
@@ -31165,7 +31165,7 @@
       </c>
       <c r="D961" s="1" t="inlineStr">
         <is>
-          <t>上升；高地；增高；升起</t>
+          <t>弄到；搞到；驱赶上去</t>
         </is>
       </c>
       <c r="E961" s="1" t="inlineStr">
@@ -31283,7 +31283,7 @@
       </c>
       <c r="B965" s="1" t="inlineStr">
         <is>
-          <t>[ʁʏstʊnk] 套装；诉讼；请求〈n.f.〉</t>
+          <t>[ʁʏstʊnk] 盔甲；装甲；军备〈n.f.〉</t>
         </is>
       </c>
       <c r="C965" s="1" t="inlineStr">
@@ -31293,7 +31293,7 @@
       </c>
       <c r="D965" s="1" t="inlineStr">
         <is>
-          <t>套装；诉讼；请求</t>
+          <t>盔甲；装甲；军备</t>
         </is>
       </c>
       <c r="E965" s="1" t="inlineStr">
@@ -31347,7 +31347,7 @@
       </c>
       <c r="B967" s="1" t="inlineStr">
         <is>
-          <t>[ɡɛvoːnhaɪt] 习惯；风俗；海关〈n.f.〉</t>
+          <t>[ɡɛvoːnhaɪt] 习惯；习性〈n.f.〉</t>
         </is>
       </c>
       <c r="C967" s="1" t="inlineStr">
@@ -31357,7 +31357,7 @@
       </c>
       <c r="D967" s="1" t="inlineStr">
         <is>
-          <t>习惯；风俗；海关</t>
+          <t>习惯；习性</t>
         </is>
       </c>
       <c r="E967" s="1" t="inlineStr">
@@ -31379,7 +31379,7 @@
       </c>
       <c r="B968" s="1" t="inlineStr">
         <is>
-          <t>[kɪndəʁmɛdçən] 保姆；母山羊〈n.〉</t>
+          <t>[kɪndəʁmɛdçən] 保姆；保育员〈n.〉</t>
         </is>
       </c>
       <c r="C968" s="1" t="inlineStr">
@@ -31389,7 +31389,7 @@
       </c>
       <c r="D968" s="1" t="inlineStr">
         <is>
-          <t>保姆；母山羊</t>
+          <t>保姆；保育员</t>
         </is>
       </c>
       <c r="E968" s="1" t="inlineStr">
@@ -31891,7 +31891,7 @@
       </c>
       <c r="B984" s="1" t="inlineStr">
         <is>
-          <t>[aɪnhɔlən] 引出；诱出；抽出〈n.〉</t>
+          <t>[aɪnhɔlən] 追上；赶上；获取；征求〈n.〉</t>
         </is>
       </c>
       <c r="C984" s="1" t="inlineStr">
@@ -31901,7 +31901,7 @@
       </c>
       <c r="D984" s="1" t="inlineStr">
         <is>
-          <t>引出；诱出；抽出</t>
+          <t>追上；赶上；获取；征求</t>
         </is>
       </c>
       <c r="E984" s="1" t="inlineStr">
@@ -31987,7 +31987,7 @@
       </c>
       <c r="B987" s="1" t="inlineStr">
         <is>
-          <t>[nɛʁf] 精神；勇气；叶脉〈n.m.〉</t>
+          <t>[nɛʁf] 神经〈n.m.〉</t>
         </is>
       </c>
       <c r="C987" s="1" t="inlineStr">
@@ -31997,7 +31997,7 @@
       </c>
       <c r="D987" s="1" t="inlineStr">
         <is>
-          <t>精神；勇气；叶脉</t>
+          <t>神经</t>
         </is>
       </c>
       <c r="E987" s="1" t="inlineStr">
@@ -32051,7 +32051,7 @@
       </c>
       <c r="B989" s="1" t="inlineStr">
         <is>
-          <t>[ɡeːlanɡvaɪlt] 感觉；觉得；触摸〈adv.〉</t>
+          <t>[ɡeːlanɡvaɪlt] 感到无聊的；厌倦的〈adv.〉</t>
         </is>
       </c>
       <c r="C989" s="1" t="inlineStr">
@@ -32061,7 +32061,7 @@
       </c>
       <c r="D989" s="1" t="inlineStr">
         <is>
-          <t>感觉；觉得；触摸</t>
+          <t>感到无聊的；厌倦的</t>
         </is>
       </c>
       <c r="E989" s="1" t="inlineStr">
@@ -32147,7 +32147,7 @@
       </c>
       <c r="B992" s="1" t="inlineStr">
         <is>
-          <t>[pfleːɡən] 收养的；抚育〈v.〉</t>
+          <t>[pfleːɡən] 照料；护理；保养〈v.〉</t>
         </is>
       </c>
       <c r="C992" s="1" t="inlineStr">
@@ -32157,7 +32157,7 @@
       </c>
       <c r="D992" s="1" t="inlineStr">
         <is>
-          <t>收养的；抚育</t>
+          <t>照料；护理；保养</t>
         </is>
       </c>
       <c r="E992" s="1" t="inlineStr">
@@ -32179,7 +32179,7 @@
       </c>
       <c r="B993" s="1" t="inlineStr">
         <is>
-          <t>[jən] 日元；渴望；嗜好〈n.m.〉</t>
+          <t>[jən] 日元〈n.m.〉</t>
         </is>
       </c>
       <c r="C993" s="1" t="inlineStr">
@@ -32189,7 +32189,7 @@
       </c>
       <c r="D993" s="1" t="inlineStr">
         <is>
-          <t>日元；渴望；嗜好</t>
+          <t>日元</t>
         </is>
       </c>
       <c r="E993" s="1" t="inlineStr">
@@ -32211,7 +32211,7 @@
       </c>
       <c r="B994" s="1" t="inlineStr">
         <is>
-          <t>[pɛʁspəktɪfə] 类似；同位〈adv.〉</t>
+          <t>[pɛʁspəktɪfə] 视角；观点；透视〈adv.〉</t>
         </is>
       </c>
       <c r="C994" s="1" t="inlineStr">
@@ -32221,7 +32221,7 @@
       </c>
       <c r="D994" s="1" t="inlineStr">
         <is>
-          <t>类似；同位</t>
+          <t>视角；观点；透视</t>
         </is>
       </c>
       <c r="E994" s="1" t="inlineStr">
@@ -32243,7 +32243,7 @@
       </c>
       <c r="B995" s="1" t="inlineStr">
         <is>
-          <t>[ʃpɛʁma] 精液；精虫；鲸油〈n.〉</t>
+          <t>[ʃpɛʁma] 精液；精子〈n.〉</t>
         </is>
       </c>
       <c r="C995" s="1" t="inlineStr">
@@ -32253,7 +32253,7 @@
       </c>
       <c r="D995" s="1" t="inlineStr">
         <is>
-          <t>精液；精虫；鲸油</t>
+          <t>精液；精子</t>
         </is>
       </c>
       <c r="E995" s="1" t="inlineStr">
@@ -32403,7 +32403,7 @@
       </c>
       <c r="B1000" s="1" t="inlineStr">
         <is>
-          <t>[aɪnlasən] 跑；赛跑；奔跑〈v.〉</t>
+          <t>[aɪnlasən] 放入；让…进入；从事于；参与〈v.〉</t>
         </is>
       </c>
       <c r="C1000" s="1" t="inlineStr">
@@ -32413,7 +32413,7 @@
       </c>
       <c r="D1000" s="1" t="inlineStr">
         <is>
-          <t>跑；赛跑；奔跑</t>
+          <t>放入；让…进入；从事于；参与</t>
         </is>
       </c>
       <c r="E1000" s="1" t="inlineStr">
@@ -32691,7 +32691,7 @@
       </c>
       <c r="B1009" s="1" t="inlineStr">
         <is>
-          <t>[fʁɛçhaɪt] 颊；厚颜；脸蛋〈n.f.〉</t>
+          <t>[fʁɛçhaɪt] 无礼；放肆；厚颜〈n.f.〉</t>
         </is>
       </c>
       <c r="C1009" s="1" t="inlineStr">
@@ -32701,7 +32701,7 @@
       </c>
       <c r="D1009" s="1" t="inlineStr">
         <is>
-          <t>颊；厚颜；脸蛋</t>
+          <t>无礼；放肆；厚颜</t>
         </is>
       </c>
       <c r="E1009" s="1" t="inlineStr">
@@ -32851,7 +32851,7 @@
       </c>
       <c r="B1014" s="1" t="inlineStr">
         <is>
-          <t>[ɛʁmœɡlɪçt] 有动力装置的；用动力推动的；产生动力的〈adv.〉</t>
+          <t>[ɛʁmœɡlɪçt] 使可能；使成为可能〈adv.〉</t>
         </is>
       </c>
       <c r="C1014" s="1" t="inlineStr">
@@ -32861,7 +32861,7 @@
       </c>
       <c r="D1014" s="1" t="inlineStr">
         <is>
-          <t>有动力装置的；用动力推动的；产生动力的</t>
+          <t>使可能；使成为可能</t>
         </is>
       </c>
       <c r="E1014" s="1" t="inlineStr">
@@ -32979,7 +32979,7 @@
       </c>
       <c r="B1018" s="1" t="inlineStr">
         <is>
-          <t>[kɔʁɪɡiːʁən] 权利；右边；正义〈v.〉</t>
+          <t>[kɔʁɪɡiːʁən] 改正；纠正；批改〈v.〉</t>
         </is>
       </c>
       <c r="C1018" s="1" t="inlineStr">
@@ -32989,7 +32989,7 @@
       </c>
       <c r="D1018" s="1" t="inlineStr">
         <is>
-          <t>权利；右边；正义</t>
+          <t>改正；纠正；批改</t>
         </is>
       </c>
       <c r="E1018" s="1" t="inlineStr">
@@ -33075,7 +33075,7 @@
       </c>
       <c r="B1021" s="1" t="inlineStr">
         <is>
-          <t>[pɪlt͡sə] 真菌；霉菌〈n.〉</t>
+          <t>[pɪlt͡sə] 蘑菇；真菌〈n.m.复数〉〈n.〉</t>
         </is>
       </c>
       <c r="C1021" s="1" t="inlineStr">
@@ -33085,7 +33085,7 @@
       </c>
       <c r="D1021" s="1" t="inlineStr">
         <is>
-          <t>真菌；霉菌</t>
+          <t>蘑菇；真菌〈n.m.复数〉</t>
         </is>
       </c>
       <c r="E1021" s="1" t="inlineStr">
@@ -33459,7 +33459,7 @@
       </c>
       <c r="B1033" s="1" t="inlineStr">
         <is>
-          <t>[taʃənlampə] 口袋；钱袋；钱〈n.f.〉</t>
+          <t>[taʃənlampə] 手电筒〈n.f.〉</t>
         </is>
       </c>
       <c r="C1033" s="1" t="inlineStr">
@@ -33469,7 +33469,7 @@
       </c>
       <c r="D1033" s="1" t="inlineStr">
         <is>
-          <t>口袋；钱袋；钱</t>
+          <t>手电筒</t>
         </is>
       </c>
       <c r="E1033" s="1" t="inlineStr">
@@ -33491,7 +33491,7 @@
       </c>
       <c r="B1034" s="1" t="inlineStr">
         <is>
-          <t>[zaɪnt] 圣路易斯河〈n.〉</t>
+          <t>[zaɪnt] 圣（用于地名前缀，源自法语）〈n.〉</t>
         </is>
       </c>
       <c r="C1034" s="1" t="inlineStr">
@@ -33501,7 +33501,7 @@
       </c>
       <c r="D1034" s="1" t="inlineStr">
         <is>
-          <t>圣路易斯河</t>
+          <t>圣（用于地名前缀，源自法语）</t>
         </is>
       </c>
       <c r="E1034" s="1" t="inlineStr">
@@ -33971,7 +33971,7 @@
       </c>
       <c r="B1049" s="1" t="inlineStr">
         <is>
-          <t>[miːlɪtɛʁɪʃə] 侦察；勘察队；勘查〈adv.〉</t>
+          <t>[miːlɪtɛʁɪʃə] 军事的〈adv.〉</t>
         </is>
       </c>
       <c r="C1049" s="1" t="inlineStr">
@@ -33981,7 +33981,7 @@
       </c>
       <c r="D1049" s="1" t="inlineStr">
         <is>
-          <t>侦察；勘察队；勘查</t>
+          <t>军事的</t>
         </is>
       </c>
       <c r="E1049" s="1" t="inlineStr">
@@ -34067,7 +34067,7 @@
       </c>
       <c r="B1052" s="1" t="inlineStr">
         <is>
-          <t>[fʁaɪəs] 全部；完整；充满的；完全的〈adv.〉</t>
+          <t>[fʁaɪəs] 自由的；不受约束的〈adv.〉</t>
         </is>
       </c>
       <c r="C1052" s="1" t="inlineStr">
@@ -34077,7 +34077,7 @@
       </c>
       <c r="D1052" s="1" t="inlineStr">
         <is>
-          <t>全部；完整；充满的；完全的</t>
+          <t>自由的；不受约束的</t>
         </is>
       </c>
       <c r="E1052" s="1" t="inlineStr">
@@ -34099,7 +34099,7 @@
       </c>
       <c r="B1053" s="1" t="inlineStr">
         <is>
-          <t>[ɡiːɐ] 的变形〈n.f.〉</t>
+          <t>[ɡiːɐ] 贪婪；渴望；贪欲〈n.f.〉</t>
         </is>
       </c>
       <c r="C1053" s="1" t="inlineStr">
@@ -34109,7 +34109,7 @@
       </c>
       <c r="D1053" s="1" t="inlineStr">
         <is>
-          <t>的变形</t>
+          <t>贪婪；渴望；贪欲</t>
         </is>
       </c>
       <c r="E1053" s="1" t="inlineStr">
@@ -34419,7 +34419,7 @@
       </c>
       <c r="B1063" s="1" t="inlineStr">
         <is>
-          <t>[kleːbən] 棍；棒；刺〈v.〉</t>
+          <t>[kleːbən] 粘贴；粘住；用胶粘〈v.〉</t>
         </is>
       </c>
       <c r="C1063" s="1" t="inlineStr">
@@ -34429,7 +34429,7 @@
       </c>
       <c r="D1063" s="1" t="inlineStr">
         <is>
-          <t>棍；棒；刺</t>
+          <t>粘贴；粘住；用胶粘</t>
         </is>
       </c>
       <c r="E1063" s="1" t="inlineStr">
@@ -34739,7 +34739,7 @@
       </c>
       <c r="B1073" s="1" t="inlineStr">
         <is>
-          <t>[fɔʁbəʁaɪtʊnk] 行程安排；时间表制定；调度〈n.f.〉</t>
+          <t>[fɔʁbəʁaɪtʊnk] 准备；预备〈n.f.〉〈n.f.〉</t>
         </is>
       </c>
       <c r="C1073" s="1" t="inlineStr">
@@ -34749,7 +34749,7 @@
       </c>
       <c r="D1073" s="1" t="inlineStr">
         <is>
-          <t>行程安排；时间表制定；调度</t>
+          <t>准备；预备〈n.f.〉</t>
         </is>
       </c>
       <c r="E1073" s="1" t="inlineStr">
@@ -35091,7 +35091,7 @@
       </c>
       <c r="B1084" s="1" t="inlineStr">
         <is>
-          <t>[aʁbaɪtst͡sɪmɐ] 学习；研究；学科〈n.〉</t>
+          <t>[aʁbaɪtst͡sɪmɐ] 书房〈n.〉</t>
         </is>
       </c>
       <c r="C1084" s="1" t="inlineStr">
@@ -35101,7 +35101,7 @@
       </c>
       <c r="D1084" s="1" t="inlineStr">
         <is>
-          <t>学习；研究；学科</t>
+          <t>书房</t>
         </is>
       </c>
       <c r="E1084" s="1" t="inlineStr">
@@ -35283,7 +35283,7 @@
       </c>
       <c r="B1090" s="1" t="inlineStr">
         <is>
-          <t>[ɛnɡɐ] 狭窄部分；隘路；狭窄的；仔细的〈adv.〉</t>
+          <t>[ɛnɡɐ] 狭窄的；紧密的；亲密的〈adv.〉</t>
         </is>
       </c>
       <c r="C1090" s="1" t="inlineStr">
@@ -35293,7 +35293,7 @@
       </c>
       <c r="D1090" s="1" t="inlineStr">
         <is>
-          <t>狭窄部分；隘路；狭窄的；仔细的</t>
+          <t>狭窄的；紧密的；亲密的</t>
         </is>
       </c>
       <c r="E1090" s="1" t="inlineStr">
@@ -35475,7 +35475,7 @@
       </c>
       <c r="B1096" s="1" t="inlineStr">
         <is>
-          <t>[anʃlʊs] 港口；埠；舱门〈n.m.〉</t>
+          <t>[anʃlʊs] 连接；连接处；接口〈n.m.〉</t>
         </is>
       </c>
       <c r="C1096" s="1" t="inlineStr">
@@ -35485,7 +35485,7 @@
       </c>
       <c r="D1096" s="1" t="inlineStr">
         <is>
-          <t>港口；埠；舱门</t>
+          <t>连接；连接处；接口</t>
         </is>
       </c>
       <c r="E1096" s="1" t="inlineStr">
@@ -35507,7 +35507,7 @@
       </c>
       <c r="B1097" s="1" t="inlineStr">
         <is>
-          <t>[ant͡sʏndən] 照明；照明设备；舞台灯光〈n.〉</t>
+          <t>[ant͡sʏndən] 点燃；点火〈n.〉</t>
         </is>
       </c>
       <c r="C1097" s="1" t="inlineStr">
@@ -35517,7 +35517,7 @@
       </c>
       <c r="D1097" s="1" t="inlineStr">
         <is>
-          <t>照明；照明设备；舞台灯光</t>
+          <t>点燃；点火</t>
         </is>
       </c>
       <c r="E1097" s="1" t="inlineStr">
@@ -35635,7 +35635,7 @@
       </c>
       <c r="B1101" s="1" t="inlineStr">
         <is>
-          <t>[abɡələɡt] 遭遗弃的；版面计算〈adv.〉</t>
+          <t>[abɡələɡt] 放下；搁置；存放〈adv.〉</t>
         </is>
       </c>
       <c r="C1101" s="1" t="inlineStr">
@@ -35645,7 +35645,7 @@
       </c>
       <c r="D1101" s="1" t="inlineStr">
         <is>
-          <t>遭遗弃的；版面计算</t>
+          <t>放下；搁置；存放</t>
         </is>
       </c>
       <c r="E1101" s="1" t="inlineStr">
@@ -35795,7 +35795,7 @@
       </c>
       <c r="B1106" s="1" t="inlineStr">
         <is>
-          <t>[bɛaʁbaɪtən] 厚度；板层；使用；使劲挥舞〈v.〉</t>
+          <t>[bɛaʁbaɪtən] 加工；处理；编辑〈v.〉</t>
         </is>
       </c>
       <c r="C1106" s="1" t="inlineStr">
@@ -35805,7 +35805,7 @@
       </c>
       <c r="D1106" s="1" t="inlineStr">
         <is>
-          <t>厚度；板层；使用；使劲挥舞</t>
+          <t>加工；处理；编辑</t>
         </is>
       </c>
       <c r="E1106" s="1" t="inlineStr">
@@ -35859,7 +35859,7 @@
       </c>
       <c r="B1108" s="1" t="inlineStr">
         <is>
-          <t>[ɡɛvøːnlɪçɐ] 甜蜜；糖果；情人；甜的〈adv.〉</t>
+          <t>[ɡɛvøːnlɪçɐ] 普通的；平常的〈adj.〉〈adv.〉</t>
         </is>
       </c>
       <c r="C1108" s="1" t="inlineStr">
@@ -35869,7 +35869,7 @@
       </c>
       <c r="D1108" s="1" t="inlineStr">
         <is>
-          <t>甜蜜；糖果；情人；甜的</t>
+          <t>普通的；平常的〈adj.〉</t>
         </is>
       </c>
       <c r="E1108" s="1" t="inlineStr">
@@ -36307,7 +36307,7 @@
       </c>
       <c r="B1122" s="1" t="inlineStr">
         <is>
-          <t>[ʁaɪnəs] 软脂酸十六酯〈adv.〉</t>
+          <t>[ʁaɪnəs] 纯的；纯净的〈adv.〉</t>
         </is>
       </c>
       <c r="C1122" s="1" t="inlineStr">
@@ -36317,7 +36317,7 @@
       </c>
       <c r="D1122" s="1" t="inlineStr">
         <is>
-          <t>软脂酸十六酯</t>
+          <t>纯的；纯净的</t>
         </is>
       </c>
       <c r="E1122" s="1" t="inlineStr">
@@ -36339,17 +36339,17 @@
       </c>
       <c r="B1123" s="1" t="inlineStr">
         <is>
-          <t>[ɡeːɡənlaɪstʊnk] 回来；返回；来回票〈n.f.〉</t>
+          <t>[ɡeːɡənlaɪstʊŋ] 回报；对等给付；报酬〈n.f.〉</t>
         </is>
       </c>
       <c r="C1123" s="1" t="inlineStr">
         <is>
-          <t>ɡeːɡənlaɪstʊnk</t>
+          <t>ɡeːɡənlaɪstʊŋ</t>
         </is>
       </c>
       <c r="D1123" s="1" t="inlineStr">
         <is>
-          <t>回来；返回；来回票</t>
+          <t>回报；对等给付；报酬</t>
         </is>
       </c>
       <c r="E1123" s="1" t="inlineStr">
@@ -36563,7 +36563,7 @@
       </c>
       <c r="B1130" s="1" t="inlineStr">
         <is>
-          <t>[haʊptʁɔlə] 领袖；酋长；长官〈n.f.〉</t>
+          <t>[haʊptʁɔlə] 主角；主要角色〈n.f.〉</t>
         </is>
       </c>
       <c r="C1130" s="1" t="inlineStr">
@@ -36573,7 +36573,7 @@
       </c>
       <c r="D1130" s="1" t="inlineStr">
         <is>
-          <t>领袖；酋长；长官</t>
+          <t>主角；主要角色</t>
         </is>
       </c>
       <c r="E1130" s="1" t="inlineStr">
@@ -36595,7 +36595,7 @@
       </c>
       <c r="B1131" s="1" t="inlineStr">
         <is>
-          <t>[taʁt͡saːn] 健壮、灵活的男子〈n.〉</t>
+          <t>[taʁt͡saːn] 泰山（人名）；健壮灵活的男子〈n.〉</t>
         </is>
       </c>
       <c r="C1131" s="1" t="inlineStr">
@@ -36605,7 +36605,7 @@
       </c>
       <c r="D1131" s="1" t="inlineStr">
         <is>
-          <t>健壮、灵活的男子</t>
+          <t>泰山（人名）；健壮灵活的男子</t>
         </is>
       </c>
       <c r="E1131" s="1" t="inlineStr">
@@ -36659,7 +36659,7 @@
       </c>
       <c r="B1133" s="1" t="inlineStr">
         <is>
-          <t>[flɪʁtən] 卖弄风骚的人；急动〈v.〉</t>
+          <t>[flɪʁtən] 调情；卖弄风情〈v.〉</t>
         </is>
       </c>
       <c r="C1133" s="1" t="inlineStr">
@@ -36669,7 +36669,7 @@
       </c>
       <c r="D1133" s="1" t="inlineStr">
         <is>
-          <t>卖弄风骚的人；急动</t>
+          <t>调情；卖弄风情</t>
         </is>
       </c>
       <c r="E1133" s="1" t="inlineStr">
@@ -36883,7 +36883,7 @@
       </c>
       <c r="B1140" s="1" t="inlineStr">
         <is>
-          <t>[mʊntɐ] 唤起〈adj.〉</t>
+          <t>[mʊntɐ] 活泼的；清醒的；精神饱满的〈adj.〉</t>
         </is>
       </c>
       <c r="C1140" s="1" t="inlineStr">
@@ -36893,7 +36893,7 @@
       </c>
       <c r="D1140" s="1" t="inlineStr">
         <is>
-          <t>唤起</t>
+          <t>活泼的；清醒的；精神饱满的</t>
         </is>
       </c>
       <c r="E1140" s="1" t="inlineStr">
@@ -36979,12 +36979,12 @@
       </c>
       <c r="B1143" s="1" t="inlineStr">
         <is>
-          <t>[pʁoːfɪnt͡s] 省；地方；职权〈n.f.〉</t>
+          <t>[pʁovɪnt͡s] 省；地方；职权〈n.f.〉</t>
         </is>
       </c>
       <c r="C1143" s="1" t="inlineStr">
         <is>
-          <t>pʁoːfɪnt͡s</t>
+          <t>pʁovɪnt͡s</t>
         </is>
       </c>
       <c r="D1143" s="1" t="inlineStr">
@@ -37107,7 +37107,7 @@
       </c>
       <c r="B1147" s="1" t="inlineStr">
         <is>
-          <t>[fiːnant͡siːʁt] 资源充足的〈adj.〉</t>
+          <t>[fiːnant͡siːʁt] 已资助的；获得经费的〈adj.〉</t>
         </is>
       </c>
       <c r="C1147" s="1" t="inlineStr">
@@ -37117,7 +37117,7 @@
       </c>
       <c r="D1147" s="1" t="inlineStr">
         <is>
-          <t>资源充足的</t>
+          <t>已资助的；获得经费的</t>
         </is>
       </c>
       <c r="E1147" s="1" t="inlineStr">
@@ -37299,7 +37299,7 @@
       </c>
       <c r="B1153" s="1" t="inlineStr">
         <is>
-          <t>[noːtaʁt͡st] 紧急状况；紧急事件〈n.m.〉</t>
+          <t>[noːtaʁt͡st] 急救医生；急诊医生〈n.m.〉</t>
         </is>
       </c>
       <c r="C1153" s="1" t="inlineStr">
@@ -37309,7 +37309,7 @@
       </c>
       <c r="D1153" s="1" t="inlineStr">
         <is>
-          <t>紧急状况；紧急事件</t>
+          <t>急救医生；急诊医生</t>
         </is>
       </c>
       <c r="E1153" s="1" t="inlineStr">
@@ -37331,7 +37331,7 @@
       </c>
       <c r="B1154" s="1" t="inlineStr">
         <is>
-          <t>[kʁiːmɪnəlɐ] 盗用公款者〈n.m.〉</t>
+          <t>[kʁiːmɪnəlɐ] 罪犯；刑事犯〈n.m.〉</t>
         </is>
       </c>
       <c r="C1154" s="1" t="inlineStr">
@@ -37341,7 +37341,7 @@
       </c>
       <c r="D1154" s="1" t="inlineStr">
         <is>
-          <t>盗用公款者</t>
+          <t>罪犯；刑事犯</t>
         </is>
       </c>
       <c r="E1154" s="1" t="inlineStr">
@@ -37459,17 +37459,17 @@
       </c>
       <c r="B1158" s="1" t="inlineStr">
         <is>
-          <t>[moːnatəlank] 月份〈adv.〉</t>
+          <t>[moːnatəlaŋ] 数月之久的〈adv.〉</t>
         </is>
       </c>
       <c r="C1158" s="1" t="inlineStr">
         <is>
-          <t>moːnatəlank</t>
+          <t>moːnatəlaŋ</t>
         </is>
       </c>
       <c r="D1158" s="1" t="inlineStr">
         <is>
-          <t>月份</t>
+          <t>数月之久的</t>
         </is>
       </c>
       <c r="E1158" s="1" t="inlineStr">
@@ -37523,7 +37523,7 @@
       </c>
       <c r="B1160" s="1" t="inlineStr">
         <is>
-          <t>[aɪnləɡən] 介绍；传入；采用〈n.〉</t>
+          <t>[aɪnləɡən] 放入；插入；腌制〈n.〉</t>
         </is>
       </c>
       <c r="C1160" s="1" t="inlineStr">
@@ -37533,7 +37533,7 @@
       </c>
       <c r="D1160" s="1" t="inlineStr">
         <is>
-          <t>介绍；传入；采用</t>
+          <t>放入；插入；腌制</t>
         </is>
       </c>
       <c r="E1160" s="1" t="inlineStr">
@@ -37715,7 +37715,7 @@
       </c>
       <c r="B1166" s="1" t="inlineStr">
         <is>
-          <t>[kœʁpəʁlɪçə] 行使；执行；运动〈adv.〉</t>
+          <t>[kœʁpəʁlɪçə] 身体的；体力的；肉体的〈adv.〉</t>
         </is>
       </c>
       <c r="C1166" s="1" t="inlineStr">
@@ -37725,7 +37725,7 @@
       </c>
       <c r="D1166" s="1" t="inlineStr">
         <is>
-          <t>行使；执行；运动</t>
+          <t>身体的；体力的；肉体的</t>
         </is>
       </c>
       <c r="E1166" s="1" t="inlineStr">
@@ -37875,7 +37875,7 @@
       </c>
       <c r="B1171" s="1" t="inlineStr">
         <is>
-          <t>[ɛksəmplaːɐ] 例子；样本；实例〈n.〉</t>
+          <t>[ɛksəmplaːɐ] 册；本；份；标本；样本〈n.〉〈n.〉</t>
         </is>
       </c>
       <c r="C1171" s="1" t="inlineStr">
@@ -37885,7 +37885,7 @@
       </c>
       <c r="D1171" s="1" t="inlineStr">
         <is>
-          <t>例子；样本；实例</t>
+          <t>册；本；份；标本；样本〈n.〉</t>
         </is>
       </c>
       <c r="E1171" s="1" t="inlineStr">
@@ -37939,7 +37939,7 @@
       </c>
       <c r="B1173" s="1" t="inlineStr">
         <is>
-          <t>[fiːnant͡siːʁən] 一卷钞票〈v.〉</t>
+          <t>[fiːnant͡siːʁən] 提供资金；资助；筹资〈v.〉</t>
         </is>
       </c>
       <c r="C1173" s="1" t="inlineStr">
@@ -37949,7 +37949,7 @@
       </c>
       <c r="D1173" s="1" t="inlineStr">
         <is>
-          <t>一卷钞票</t>
+          <t>提供资金；资助；筹资</t>
         </is>
       </c>
       <c r="E1173" s="1" t="inlineStr">
@@ -38099,7 +38099,7 @@
       </c>
       <c r="B1178" s="1" t="inlineStr">
         <is>
-          <t>[ɡʊstaːf] 一种轻型旅行袋；格拉德斯通；格莱斯顿〈n.〉</t>
+          <t>[ɡʊstaːf] 古斯塔夫（人名）〈n.〉</t>
         </is>
       </c>
       <c r="C1178" s="1" t="inlineStr">
@@ -38109,7 +38109,7 @@
       </c>
       <c r="D1178" s="1" t="inlineStr">
         <is>
-          <t>一种轻型旅行袋；格拉德斯通；格莱斯顿</t>
+          <t>古斯塔夫（人名）</t>
         </is>
       </c>
       <c r="E1178" s="1" t="inlineStr">
@@ -38259,7 +38259,7 @@
       </c>
       <c r="B1183" s="1" t="inlineStr">
         <is>
-          <t>[hɛlə] 飘；摆动；拍打〈adv.〉</t>
+          <t>[hɛlə] 明亮的；浅色的〈adj.〉〈adv.〉</t>
         </is>
       </c>
       <c r="C1183" s="1" t="inlineStr">
@@ -38269,7 +38269,7 @@
       </c>
       <c r="D1183" s="1" t="inlineStr">
         <is>
-          <t>飘；摆动；拍打</t>
+          <t>明亮的；浅色的〈adj.〉</t>
         </is>
       </c>
       <c r="E1183" s="1" t="inlineStr">
@@ -38579,7 +38579,7 @@
       </c>
       <c r="B1193" s="1" t="inlineStr">
         <is>
-          <t>[ʃɛʁt͡sən] 笑柄；嘲笑〈v.〉</t>
+          <t>[ʃɛʁt͡sən] 开玩笑；说笑话〈v.〉</t>
         </is>
       </c>
       <c r="C1193" s="1" t="inlineStr">
@@ -38589,7 +38589,7 @@
       </c>
       <c r="D1193" s="1" t="inlineStr">
         <is>
-          <t>笑柄；嘲笑</t>
+          <t>开玩笑；说笑话</t>
         </is>
       </c>
       <c r="E1193" s="1" t="inlineStr">
@@ -38963,7 +38963,7 @@
       </c>
       <c r="B1205" s="1" t="inlineStr">
         <is>
-          <t>[zɛltənə] 稀土族〈adv.〉</t>
+          <t>[zɛltənə] 稀有的；罕见的；稀少的〈adv.〉</t>
         </is>
       </c>
       <c r="C1205" s="1" t="inlineStr">
@@ -38973,7 +38973,7 @@
       </c>
       <c r="D1205" s="1" t="inlineStr">
         <is>
-          <t>稀土族</t>
+          <t>稀有的；罕见的；稀少的</t>
         </is>
       </c>
       <c r="E1205" s="1" t="inlineStr">
@@ -39091,7 +39091,7 @@
       </c>
       <c r="B1209" s="1" t="inlineStr">
         <is>
-          <t>[zaːbɪnə] 萨宾人〈n.〉</t>
+          <t>[zaːbɪnə] 萨宾娜（女子名）；萨宾人〈n.〉</t>
         </is>
       </c>
       <c r="C1209" s="1" t="inlineStr">
@@ -39101,7 +39101,7 @@
       </c>
       <c r="D1209" s="1" t="inlineStr">
         <is>
-          <t>萨宾人</t>
+          <t>萨宾娜（女子名）；萨宾人</t>
         </is>
       </c>
       <c r="E1209" s="1" t="inlineStr">
@@ -39219,7 +39219,7 @@
       </c>
       <c r="B1213" s="1" t="inlineStr">
         <is>
-          <t>[mɔʁdkɔmɪsɪoːn] 谋杀；损毁〈n.f.〉</t>
+          <t>[mɔʁdkɔmɪsɪoːn] 凶杀案调查组；刑侦专案组〈n.f.〉</t>
         </is>
       </c>
       <c r="C1213" s="1" t="inlineStr">
@@ -39229,7 +39229,7 @@
       </c>
       <c r="D1213" s="1" t="inlineStr">
         <is>
-          <t>谋杀；损毁</t>
+          <t>凶杀案调查组；刑侦专案组</t>
         </is>
       </c>
       <c r="E1213" s="1" t="inlineStr">
@@ -39347,7 +39347,7 @@
       </c>
       <c r="B1217" s="1" t="inlineStr">
         <is>
-          <t>[bʊnt] 衣领；颈圈；控制；扭住衣领〈n.m.〉</t>
+          <t>[bʊnt] 联盟；联邦；（衣物的）束带、罗口〈n.m.〉</t>
         </is>
       </c>
       <c r="C1217" s="1" t="inlineStr">
@@ -39357,7 +39357,7 @@
       </c>
       <c r="D1217" s="1" t="inlineStr">
         <is>
-          <t>衣领；颈圈；控制；扭住衣领</t>
+          <t>联盟；联邦；（衣物的）束带、罗口</t>
         </is>
       </c>
       <c r="E1217" s="1" t="inlineStr">
@@ -39379,7 +39379,7 @@
       </c>
       <c r="B1218" s="1" t="inlineStr">
         <is>
-          <t>[kataʁɪna] 侧翻筋斗；轮转烟火〈n.〉</t>
+          <t>[kataʁɪna] 卡塔琳娜〈人名〉〈n.〉</t>
         </is>
       </c>
       <c r="C1218" s="1" t="inlineStr">
@@ -39389,7 +39389,7 @@
       </c>
       <c r="D1218" s="1" t="inlineStr">
         <is>
-          <t>侧翻筋斗；轮转烟火</t>
+          <t>卡塔琳娜〈人名〉</t>
         </is>
       </c>
       <c r="E1218" s="1" t="inlineStr">
@@ -39411,7 +39411,7 @@
       </c>
       <c r="B1219" s="1" t="inlineStr">
         <is>
-          <t>[anʁɪçtən] 盘子；碟；菜肴；皿〈v.〉</t>
+          <t>[anʁɪçtən] 造成（损害）；摆盘〈v.〉</t>
         </is>
       </c>
       <c r="C1219" s="1" t="inlineStr">
@@ -39421,7 +39421,7 @@
       </c>
       <c r="D1219" s="1" t="inlineStr">
         <is>
-          <t>盘子；碟；菜肴；皿</t>
+          <t>造成（损害）；摆盘</t>
         </is>
       </c>
       <c r="E1219" s="1" t="inlineStr">
@@ -39507,7 +39507,7 @@
       </c>
       <c r="B1222" s="1" t="inlineStr">
         <is>
-          <t>[leːnən] 瘦肉；倾斜；倾斜度；瘦的〈v.〉</t>
+          <t>[leːnən] 倚靠；倾斜〈v.〉</t>
         </is>
       </c>
       <c r="C1222" s="1" t="inlineStr">
@@ -39517,7 +39517,7 @@
       </c>
       <c r="D1222" s="1" t="inlineStr">
         <is>
-          <t>瘦肉；倾斜；倾斜度；瘦的</t>
+          <t>倚靠；倾斜</t>
         </is>
       </c>
       <c r="E1222" s="1" t="inlineStr">
@@ -39603,17 +39603,17 @@
       </c>
       <c r="B1225" s="1" t="inlineStr">
         <is>
-          <t>[taːɡəlank] 永久的；永恒的〈adj.〉</t>
+          <t>[taːɡəlaŋ] 连续数日的；数天之久的〈adj.〉</t>
         </is>
       </c>
       <c r="C1225" s="1" t="inlineStr">
         <is>
-          <t>taːɡəlank</t>
+          <t>taːɡəlaŋ</t>
         </is>
       </c>
       <c r="D1225" s="1" t="inlineStr">
         <is>
-          <t>永久的；永恒的</t>
+          <t>连续数日的；数天之久的</t>
         </is>
       </c>
       <c r="E1225" s="1" t="inlineStr">
@@ -39923,7 +39923,7 @@
       </c>
       <c r="B1235" s="1" t="inlineStr">
         <is>
-          <t>[ɡyːtɪç] 深情的；充满情爱的〈adj.〉</t>
+          <t>[ɡyːtɪç] 仁慈的；和善的〈adj.〉〈adj.〉</t>
         </is>
       </c>
       <c r="C1235" s="1" t="inlineStr">
@@ -39933,7 +39933,7 @@
       </c>
       <c r="D1235" s="1" t="inlineStr">
         <is>
-          <t>深情的；充满情爱的</t>
+          <t>仁慈的；和善的〈adj.〉</t>
         </is>
       </c>
       <c r="E1235" s="1" t="inlineStr">
@@ -39987,7 +39987,7 @@
       </c>
       <c r="B1237" s="1" t="inlineStr">
         <is>
-          <t>[ʁʊmhɛnɡən] 挂出〈v.〉</t>
+          <t>[ʁʊmhɛnɡən] 闲逛；游荡；无所事事〈v.〉</t>
         </is>
       </c>
       <c r="C1237" s="1" t="inlineStr">
@@ -39997,7 +39997,7 @@
       </c>
       <c r="D1237" s="1" t="inlineStr">
         <is>
-          <t>挂出</t>
+          <t>闲逛；游荡；无所事事</t>
         </is>
       </c>
       <c r="E1237" s="1" t="inlineStr">
@@ -40083,7 +40083,7 @@
       </c>
       <c r="B1240" s="1" t="inlineStr">
         <is>
-          <t>[nɛʁfɪç] 精力充沛的；元气旺盛的；茁壮的〈adj.〉</t>
+          <t>[nɛʁfɪç] 烦人的；恼人的〈adj.〉</t>
         </is>
       </c>
       <c r="C1240" s="1" t="inlineStr">
@@ -40093,7 +40093,7 @@
       </c>
       <c r="D1240" s="1" t="inlineStr">
         <is>
-          <t>精力充沛的；元气旺盛的；茁壮的</t>
+          <t>烦人的；恼人的</t>
         </is>
       </c>
       <c r="E1240" s="1" t="inlineStr">
@@ -40147,7 +40147,7 @@
       </c>
       <c r="B1242" s="1" t="inlineStr">
         <is>
-          <t>[niːdəʁɡəʃlaɡən] 荒凉的〈adj.〉</t>
+          <t>[niːdəʁɡəʃlaɡən] 沮丧的；消沉的；垂头丧气的〈adj.〉</t>
         </is>
       </c>
       <c r="C1242" s="1" t="inlineStr">
@@ -40157,7 +40157,7 @@
       </c>
       <c r="D1242" s="1" t="inlineStr">
         <is>
-          <t>荒凉的</t>
+          <t>沮丧的；消沉的；垂头丧气的</t>
         </is>
       </c>
       <c r="E1242" s="1" t="inlineStr">
@@ -40499,7 +40499,7 @@
       </c>
       <c r="B1253" s="1" t="inlineStr">
         <is>
-          <t>[t͡saʊbɐn] 进行；履行；完成〈v.〉</t>
+          <t>[t͡saʊbɐn] 变魔术；施魔法〈v.〉</t>
         </is>
       </c>
       <c r="C1253" s="1" t="inlineStr">
@@ -40509,7 +40509,7 @@
       </c>
       <c r="D1253" s="1" t="inlineStr">
         <is>
-          <t>进行；履行；完成</t>
+          <t>变魔术；施魔法</t>
         </is>
       </c>
       <c r="E1253" s="1" t="inlineStr">
@@ -40531,7 +40531,7 @@
       </c>
       <c r="B1254" s="1" t="inlineStr">
         <is>
-          <t>[ɡaːbəl] 轭；牛轭〈n.f.〉</t>
+          <t>[ɡaːbəl] 叉子；餐叉〈n.f.〉</t>
         </is>
       </c>
       <c r="C1254" s="1" t="inlineStr">
@@ -40541,7 +40541,7 @@
       </c>
       <c r="D1254" s="1" t="inlineStr">
         <is>
-          <t>轭；牛轭</t>
+          <t>叉子；餐叉</t>
         </is>
       </c>
       <c r="E1254" s="1" t="inlineStr">
@@ -40563,7 +40563,7 @@
       </c>
       <c r="B1255" s="1" t="inlineStr">
         <is>
-          <t>[ʃvɛçɐ] 枯萎；凋谢〈adv.〉</t>
+          <t>[ʃvɛçɐ] 更弱的；较虚弱的〈adv.〉</t>
         </is>
       </c>
       <c r="C1255" s="1" t="inlineStr">
@@ -40573,7 +40573,7 @@
       </c>
       <c r="D1255" s="1" t="inlineStr">
         <is>
-          <t>枯萎；凋谢</t>
+          <t>更弱的；较虚弱的</t>
         </is>
       </c>
       <c r="E1255" s="1" t="inlineStr">
@@ -40691,7 +40691,7 @@
       </c>
       <c r="B1259" s="1" t="inlineStr">
         <is>
-          <t>[blaʊɐ] 穿蓝衣者；蓝色事物〈n.〉</t>
+          <t>[blaʊɐ] 无此独立名词，仅为形容词 blau 的变格形式〈n.〉</t>
         </is>
       </c>
       <c r="C1259" s="1" t="inlineStr">
@@ -40701,7 +40701,7 @@
       </c>
       <c r="D1259" s="1" t="inlineStr">
         <is>
-          <t>穿蓝衣者；蓝色事物</t>
+          <t>无此独立名词，仅为形容词 blau 的变格形式</t>
         </is>
       </c>
       <c r="E1259" s="1" t="inlineStr">
@@ -41299,7 +41299,7 @@
       </c>
       <c r="B1278" s="1" t="inlineStr">
         <is>
-          <t>[ʃtaːdɪoːn] 病期〈n.〉</t>
+          <t>[ʃtaːdɪoːn] 体育场；运动场〈n.〉</t>
         </is>
       </c>
       <c r="C1278" s="1" t="inlineStr">
@@ -41309,7 +41309,7 @@
       </c>
       <c r="D1278" s="1" t="inlineStr">
         <is>
-          <t>病期</t>
+          <t>体育场；运动场</t>
         </is>
       </c>
       <c r="E1278" s="1" t="inlineStr">
@@ -41459,7 +41459,7 @@
       </c>
       <c r="B1283" s="1" t="inlineStr">
         <is>
-          <t>[plɛt͡sçən] 一点点；少许；一会儿〈n.〉</t>
+          <t>[plɛt͡sçən] 小地方；小饼干〈n.〉</t>
         </is>
       </c>
       <c r="C1283" s="1" t="inlineStr">
@@ -41469,7 +41469,7 @@
       </c>
       <c r="D1283" s="1" t="inlineStr">
         <is>
-          <t>一点点；少许；一会儿</t>
+          <t>小地方；小饼干</t>
         </is>
       </c>
       <c r="E1283" s="1" t="inlineStr">
@@ -41491,7 +41491,7 @@
       </c>
       <c r="B1284" s="1" t="inlineStr">
         <is>
-          <t>[kɔʁʊpt͡sjoːn] 劣等品；卑鄙的人；肮脏〈n.f.〉</t>
+          <t>[kɔʁʊpt͡sjoːn] 腐败；贪污；受贿〈n.f.〉</t>
         </is>
       </c>
       <c r="C1284" s="1" t="inlineStr">
@@ -41501,7 +41501,7 @@
       </c>
       <c r="D1284" s="1" t="inlineStr">
         <is>
-          <t>劣等品；卑鄙的人；肮脏</t>
+          <t>腐败；贪污；受贿</t>
         </is>
       </c>
       <c r="E1284" s="1" t="inlineStr">
@@ -41555,7 +41555,7 @@
       </c>
       <c r="B1286" s="1" t="inlineStr">
         <is>
-          <t>[anʃliːsənt] 下列各项；部下〈adv.〉</t>
+          <t>[anʃliːsənt] 随后；接着〈adv.〉</t>
         </is>
       </c>
       <c r="C1286" s="1" t="inlineStr">
@@ -41565,7 +41565,7 @@
       </c>
       <c r="D1286" s="1" t="inlineStr">
         <is>
-          <t>下列各项；部下</t>
+          <t>随后；接着</t>
         </is>
       </c>
       <c r="E1286" s="1" t="inlineStr">
@@ -41587,7 +41587,7 @@
       </c>
       <c r="B1287" s="1" t="inlineStr">
         <is>
-          <t>[ɡʁuːbə] 深坑；矿井；果核〈n.f.〉</t>
+          <t>[ɡʁuːbə] 坑；矿井；坑穴〈n.f.〉〈n.f.〉</t>
         </is>
       </c>
       <c r="C1287" s="1" t="inlineStr">
@@ -41597,7 +41597,7 @@
       </c>
       <c r="D1287" s="1" t="inlineStr">
         <is>
-          <t>深坑；矿井；果核</t>
+          <t>坑；矿井；坑穴〈n.f.〉</t>
         </is>
       </c>
       <c r="E1287" s="1" t="inlineStr">
@@ -41971,17 +41971,17 @@
       </c>
       <c r="B1299" s="1" t="inlineStr">
         <is>
-          <t>[kʏndɪɡʊnk] 注意；布告；通知〈n.f.〉</t>
+          <t>[kʏndɪɡʊŋ] 解约通知；解雇；终止〈n.f.〉</t>
         </is>
       </c>
       <c r="C1299" s="1" t="inlineStr">
         <is>
-          <t>kʏndɪɡʊnk</t>
+          <t>kʏndɪɡʊŋ</t>
         </is>
       </c>
       <c r="D1299" s="1" t="inlineStr">
         <is>
-          <t>注意；布告；通知</t>
+          <t>解约通知；解雇；终止</t>
         </is>
       </c>
       <c r="E1299" s="1" t="inlineStr">
@@ -42067,7 +42067,7 @@
       </c>
       <c r="B1302" s="1" t="inlineStr">
         <is>
-          <t>[anɡəbən] 弹性；适应性；给；授予〈v.〉</t>
+          <t>[anɡəbən] 说明；申报；炫耀〈v.〉</t>
         </is>
       </c>
       <c r="C1302" s="1" t="inlineStr">
@@ -42077,7 +42077,7 @@
       </c>
       <c r="D1302" s="1" t="inlineStr">
         <is>
-          <t>弹性；适应性；给；授予</t>
+          <t>说明；申报；炫耀</t>
         </is>
       </c>
       <c r="E1302" s="1" t="inlineStr">
@@ -42291,7 +42291,7 @@
       </c>
       <c r="B1309" s="1" t="inlineStr">
         <is>
-          <t>[fɛʁmɪtlʊnk] 操作员；行家；经纪人〈n.f.〉</t>
+          <t>[fɛʁmɪtlʊnk] 调解；中介；介绍〈n.f.〉</t>
         </is>
       </c>
       <c r="C1309" s="1" t="inlineStr">
@@ -42301,7 +42301,7 @@
       </c>
       <c r="D1309" s="1" t="inlineStr">
         <is>
-          <t>操作员；行家；经纪人</t>
+          <t>调解；中介；介绍</t>
         </is>
       </c>
       <c r="E1309" s="1" t="inlineStr">
@@ -42419,7 +42419,7 @@
       </c>
       <c r="B1313" s="1" t="inlineStr">
         <is>
-          <t>[aʊfpʁal] 跳；跳跃；弹力〈n.m.〉</t>
+          <t>[aʊfpʁal] 撞击；碰撞；冲击〈n.m.〉</t>
         </is>
       </c>
       <c r="C1313" s="1" t="inlineStr">
@@ -42429,7 +42429,7 @@
       </c>
       <c r="D1313" s="1" t="inlineStr">
         <is>
-          <t>跳；跳跃；弹力</t>
+          <t>撞击；碰撞；冲击</t>
         </is>
       </c>
       <c r="E1313" s="1" t="inlineStr">
@@ -42483,7 +42483,7 @@
       </c>
       <c r="B1315" s="1" t="inlineStr">
         <is>
-          <t>[fɔʁvʊʁf] 断言；主张；申辩；声明〈n.m.〉</t>
+          <t>[fɔʁvʊʁf] 责备；指责；非难〈n.m.〉</t>
         </is>
       </c>
       <c r="C1315" s="1" t="inlineStr">
@@ -42493,7 +42493,7 @@
       </c>
       <c r="D1315" s="1" t="inlineStr">
         <is>
-          <t>断言；主张；申辩；声明</t>
+          <t>责备；指责；非难</t>
         </is>
       </c>
       <c r="E1315" s="1" t="inlineStr">
@@ -42579,7 +42579,7 @@
       </c>
       <c r="B1318" s="1" t="inlineStr">
         <is>
-          <t>[zɔndə] 探索；调查；探针〈n.f.〉</t>
+          <t>[zɔndə] 探针；探测器〈n.f.〉〈n.f.〉</t>
         </is>
       </c>
       <c r="C1318" s="1" t="inlineStr">
@@ -42589,7 +42589,7 @@
       </c>
       <c r="D1318" s="1" t="inlineStr">
         <is>
-          <t>探索；调查；探针</t>
+          <t>探针；探测器〈n.f.〉</t>
         </is>
       </c>
       <c r="E1318" s="1" t="inlineStr">
@@ -42963,7 +42963,7 @@
       </c>
       <c r="B1330" s="1" t="inlineStr">
         <is>
-          <t>[ʁuːdɪ] 贺拉斯〈n.〉</t>
+          <t>[ʁuːdɪ] 鲁迪（人名，Rudolf 的昵称）〈n.〉</t>
         </is>
       </c>
       <c r="C1330" s="1" t="inlineStr">
@@ -42973,7 +42973,7 @@
       </c>
       <c r="D1330" s="1" t="inlineStr">
         <is>
-          <t>贺拉斯</t>
+          <t>鲁迪（人名，Rudolf 的昵称）</t>
         </is>
       </c>
       <c r="E1330" s="1" t="inlineStr">
@@ -43123,7 +43123,7 @@
       </c>
       <c r="B1335" s="1" t="inlineStr">
         <is>
-          <t>[ʃoːnən] 爱护；保重（schonen 变化形式）〈n.〉</t>
+          <t>[ʃoːnən] 爱护；保重（动词 schonen 的不定式，非名词）〈n.〉</t>
         </is>
       </c>
       <c r="C1335" s="1" t="inlineStr">
@@ -43133,7 +43133,7 @@
       </c>
       <c r="D1335" s="1" t="inlineStr">
         <is>
-          <t>爱护；保重（schonen 变化形式）</t>
+          <t>爱护；保重（动词 schonen 的不定式，非名词）</t>
         </is>
       </c>
       <c r="E1335" s="1" t="inlineStr">
@@ -43251,7 +43251,7 @@
       </c>
       <c r="B1339" s="1" t="inlineStr">
         <is>
-          <t>[t͡suːʁʏkbəkɔmən] 开垦；改造；感化〈v.〉</t>
+          <t>[t͡suːʁʏkbəkɔmən] 取回；收回〈v.〉</t>
         </is>
       </c>
       <c r="C1339" s="1" t="inlineStr">
@@ -43261,7 +43261,7 @@
       </c>
       <c r="D1339" s="1" t="inlineStr">
         <is>
-          <t>开垦；改造；感化</t>
+          <t>取回；收回</t>
         </is>
       </c>
       <c r="E1339" s="1" t="inlineStr">
@@ -43315,7 +43315,7 @@
       </c>
       <c r="B1341" s="1" t="inlineStr">
         <is>
-          <t>[anmaxən] 投掷；抛；摇摆〈v.〉</t>
+          <t>[anmaxən] 打开；点燃〈v.〉</t>
         </is>
       </c>
       <c r="C1341" s="1" t="inlineStr">
@@ -43325,7 +43325,7 @@
       </c>
       <c r="D1341" s="1" t="inlineStr">
         <is>
-          <t>投掷；抛；摇摆</t>
+          <t>打开；点燃</t>
         </is>
       </c>
       <c r="E1341" s="1" t="inlineStr">
@@ -43411,7 +43411,7 @@
       </c>
       <c r="B1344" s="1" t="inlineStr">
         <is>
-          <t>[ʃtʏt͡spʊnkt] 底部；垒；基础〈n.m.〉</t>
+          <t>[ʃtʏt͡spʊnkt] 据点；基地〈n.m.〉〈n.m.〉</t>
         </is>
       </c>
       <c r="C1344" s="1" t="inlineStr">
@@ -43421,7 +43421,7 @@
       </c>
       <c r="D1344" s="1" t="inlineStr">
         <is>
-          <t>底部；垒；基础</t>
+          <t>据点；基地〈n.m.〉</t>
         </is>
       </c>
       <c r="E1344" s="1" t="inlineStr">
@@ -43507,7 +43507,7 @@
       </c>
       <c r="B1347" s="1" t="inlineStr">
         <is>
-          <t>[fɛʁstɛʁkt] 以债券作保证的；有担保的〈adj.〉</t>
+          <t>[fɛʁstɛʁkt] 加强了的；增强的；加固的〈adj.〉</t>
         </is>
       </c>
       <c r="C1347" s="1" t="inlineStr">
@@ -43517,7 +43517,7 @@
       </c>
       <c r="D1347" s="1" t="inlineStr">
         <is>
-          <t>以债券作保证的；有担保的</t>
+          <t>加强了的；增强的；加固的</t>
         </is>
       </c>
       <c r="E1347" s="1" t="inlineStr">
@@ -43667,7 +43667,7 @@
       </c>
       <c r="B1352" s="1" t="inlineStr">
         <is>
-          <t>[beːʁaɪt͡ʃaft] 可依靠的人；被喜爱的食品；备用品〈n.f.〉</t>
+          <t>[beːʁaɪt͡ʃaft] 准备就绪；乐意；待命〈n.f.〉</t>
         </is>
       </c>
       <c r="C1352" s="1" t="inlineStr">
@@ -43677,7 +43677,7 @@
       </c>
       <c r="D1352" s="1" t="inlineStr">
         <is>
-          <t>可依靠的人；被喜爱的食品；备用品</t>
+          <t>准备就绪；乐意；待命</t>
         </is>
       </c>
       <c r="E1352" s="1" t="inlineStr">
@@ -43795,7 +43795,7 @@
       </c>
       <c r="B1356" s="1" t="inlineStr">
         <is>
-          <t>[ɡeːɡənstɛndə] 材料；材料费；材料科学〈n.〉</t>
+          <t>[ɡeːɡənstɛndə] 物品；物件〈n.〉</t>
         </is>
       </c>
       <c r="C1356" s="1" t="inlineStr">
@@ -43805,7 +43805,7 @@
       </c>
       <c r="D1356" s="1" t="inlineStr">
         <is>
-          <t>材料；材料费；材料科学</t>
+          <t>物品；物件</t>
         </is>
       </c>
       <c r="E1356" s="1" t="inlineStr">
@@ -43891,7 +43891,7 @@
       </c>
       <c r="B1359" s="1" t="inlineStr">
         <is>
-          <t>[kɔstənlɔs] 自由的；享受政治权力的；允许的〈adv.〉</t>
+          <t>[kɔstənlɔs] 免费的；无偿的〈adv.〉</t>
         </is>
       </c>
       <c r="C1359" s="1" t="inlineStr">
@@ -43901,7 +43901,7 @@
       </c>
       <c r="D1359" s="1" t="inlineStr">
         <is>
-          <t>自由的；享受政治权力的；允许的</t>
+          <t>免费的；无偿的</t>
         </is>
       </c>
       <c r="E1359" s="1" t="inlineStr">
@@ -43987,7 +43987,7 @@
       </c>
       <c r="B1362" s="1" t="inlineStr">
         <is>
-          <t>[dʊʁçdʁeːən] 纺纱；纺丝〈n.〉</t>
+          <t>[dʊʁçdʁeːən] （发动机）空转；发疯；失控〈v.〉〈n.〉</t>
         </is>
       </c>
       <c r="C1362" s="1" t="inlineStr">
@@ -43997,7 +43997,7 @@
       </c>
       <c r="D1362" s="1" t="inlineStr">
         <is>
-          <t>纺纱；纺丝</t>
+          <t>（发动机）空转；发疯；失控〈v.〉</t>
         </is>
       </c>
       <c r="E1362" s="1" t="inlineStr">
@@ -44179,7 +44179,7 @@
       </c>
       <c r="B1368" s="1" t="inlineStr">
         <is>
-          <t>[ɡɛʃɛftspaʁtnɐ] 生意；事情；业务〈n.m.〉</t>
+          <t>[ɡɛʃɛftspaʁtnɐ] 商业伙伴；生意伙伴〈n.m.〉</t>
         </is>
       </c>
       <c r="C1368" s="1" t="inlineStr">
@@ -44189,7 +44189,7 @@
       </c>
       <c r="D1368" s="1" t="inlineStr">
         <is>
-          <t>生意；事情；业务</t>
+          <t>商业伙伴；生意伙伴</t>
         </is>
       </c>
       <c r="E1368" s="1" t="inlineStr">
@@ -44243,12 +44243,12 @@
       </c>
       <c r="B1370" s="1" t="inlineStr">
         <is>
-          <t>[beːlastʊnk] 阻碍；妨害物；累赘〈n.f.〉</t>
+          <t>[beːlastʊŋ] 阻碍；妨害物；累赘〈n.f.〉</t>
         </is>
       </c>
       <c r="C1370" s="1" t="inlineStr">
         <is>
-          <t>beːlastʊnk</t>
+          <t>beːlastʊŋ</t>
         </is>
       </c>
       <c r="D1370" s="1" t="inlineStr">
@@ -44403,7 +44403,7 @@
       </c>
       <c r="B1375" s="1" t="inlineStr">
         <is>
-          <t>[zɛkt͡sjoːn] 区段；部分；区域〈n.f.〉</t>
+          <t>[zɛkt͡sjoːn] 解剖；部门；分会；章节〈n.f.〉</t>
         </is>
       </c>
       <c r="C1375" s="1" t="inlineStr">
@@ -44413,7 +44413,7 @@
       </c>
       <c r="D1375" s="1" t="inlineStr">
         <is>
-          <t>区段；部分；区域</t>
+          <t>解剖；部门；分会；章节</t>
         </is>
       </c>
       <c r="E1375" s="1" t="inlineStr">
@@ -44499,7 +44499,7 @@
       </c>
       <c r="B1378" s="1" t="inlineStr">
         <is>
-          <t>[vɪlhəlm] 征服者威廉一世；诺曼王朝威廉一世〈n.〉</t>
+          <t>[vɪlhəlm] 威廉〈n.〉</t>
         </is>
       </c>
       <c r="C1378" s="1" t="inlineStr">
@@ -44509,7 +44509,7 @@
       </c>
       <c r="D1378" s="1" t="inlineStr">
         <is>
-          <t>征服者威廉一世；诺曼王朝威廉一世</t>
+          <t>威廉</t>
         </is>
       </c>
       <c r="E1378" s="1" t="inlineStr">
@@ -44787,7 +44787,7 @@
       </c>
       <c r="B1387" s="1" t="inlineStr">
         <is>
-          <t>[bɛɡlaɪçən] 整理；安放〈v.〉</t>
+          <t>[bɛɡlaɪçən] 结清；清偿〈v.〉</t>
         </is>
       </c>
       <c r="C1387" s="1" t="inlineStr">
@@ -44797,7 +44797,7 @@
       </c>
       <c r="D1387" s="1" t="inlineStr">
         <is>
-          <t>整理；安放</t>
+          <t>结清；清偿</t>
         </is>
       </c>
       <c r="E1387" s="1" t="inlineStr">
@@ -44851,7 +44851,7 @@
       </c>
       <c r="B1389" s="1" t="inlineStr">
         <is>
-          <t>[toːtɔ] 提；负；携带〈n.〉</t>
+          <t>[toːtɔ] 足球彩票；体育博彩〈n.〉</t>
         </is>
       </c>
       <c r="C1389" s="1" t="inlineStr">
@@ -44861,7 +44861,7 @@
       </c>
       <c r="D1389" s="1" t="inlineStr">
         <is>
-          <t>提；负；携带</t>
+          <t>足球彩票；体育博彩</t>
         </is>
       </c>
       <c r="E1389" s="1" t="inlineStr">
@@ -44883,7 +44883,7 @@
       </c>
       <c r="B1390" s="1" t="inlineStr">
         <is>
-          <t>[føːɡəlçən] 一点点；少许；一会儿〈n.〉</t>
+          <t>[føːɡəlçən] 小鸟〈n.〉</t>
         </is>
       </c>
       <c r="C1390" s="1" t="inlineStr">
@@ -44893,7 +44893,7 @@
       </c>
       <c r="D1390" s="1" t="inlineStr">
         <is>
-          <t>一点点；少许；一会儿</t>
+          <t>小鸟</t>
         </is>
       </c>
       <c r="E1390" s="1" t="inlineStr">
@@ -45043,17 +45043,17 @@
       </c>
       <c r="B1395" s="1" t="inlineStr">
         <is>
-          <t>[pɛnzʏlfanɪa] 共和国；联邦；国民整体〈n.〉</t>
+          <t>[pɛnzɪlveɪnia] 宾夕法尼亚州〈n.〉</t>
         </is>
       </c>
       <c r="C1395" s="1" t="inlineStr">
         <is>
-          <t>pɛnzʏlfanɪa</t>
+          <t>pɛnzɪlveɪnia</t>
         </is>
       </c>
       <c r="D1395" s="1" t="inlineStr">
         <is>
-          <t>共和国；联邦；国民整体</t>
+          <t>宾夕法尼亚州</t>
         </is>
       </c>
       <c r="E1395" s="1" t="inlineStr">
@@ -45075,7 +45075,7 @@
       </c>
       <c r="B1396" s="1" t="inlineStr">
         <is>
-          <t>[aʊft͡siːən] 风；气息；气味〈v.〉</t>
+          <t>[aʊft͡siːən] 抚养；养育；上发条；拉上〈v.〉</t>
         </is>
       </c>
       <c r="C1396" s="1" t="inlineStr">
@@ -45085,7 +45085,7 @@
       </c>
       <c r="D1396" s="1" t="inlineStr">
         <is>
-          <t>风；气息；气味</t>
+          <t>抚养；养育；上发条；拉上</t>
         </is>
       </c>
       <c r="E1396" s="1" t="inlineStr">
@@ -45203,7 +45203,7 @@
       </c>
       <c r="B1400" s="1" t="inlineStr">
         <is>
-          <t>[bɛʃʏt͡sɐ] 小圆盾；防卫物〈n.m.〉</t>
+          <t>[bɛʃʏt͡sɐ] 保护者；守护者〈n.m.〉</t>
         </is>
       </c>
       <c r="C1400" s="1" t="inlineStr">
@@ -45213,7 +45213,7 @@
       </c>
       <c r="D1400" s="1" t="inlineStr">
         <is>
-          <t>小圆盾；防卫物</t>
+          <t>保护者；守护者</t>
         </is>
       </c>
       <c r="E1400" s="1" t="inlineStr">
@@ -45587,7 +45587,7 @@
       </c>
       <c r="B1412" s="1" t="inlineStr">
         <is>
-          <t>[kaʁtoːn] 薄纸板；咭纸；特等纸板；卡纸板〈n.m.〉</t>
+          <t>[kaʁtoːn] 薄纸板；卡纸板〈m.〉〈n.m.〉</t>
         </is>
       </c>
       <c r="C1412" s="1" t="inlineStr">
@@ -45597,7 +45597,7 @@
       </c>
       <c r="D1412" s="1" t="inlineStr">
         <is>
-          <t>薄纸板；咭纸；特等纸板；卡纸板</t>
+          <t>薄纸板；卡纸板〈m.〉</t>
         </is>
       </c>
       <c r="E1412" s="1" t="inlineStr">
@@ -45779,7 +45779,7 @@
       </c>
       <c r="B1418" s="1" t="inlineStr">
         <is>
-          <t>[ɛʁɪçtən] 植物；作物；工厂〈v.〉</t>
+          <t>[ɛʁɪçtən] 建立；建造；设立〈v.〉</t>
         </is>
       </c>
       <c r="C1418" s="1" t="inlineStr">
@@ -45789,7 +45789,7 @@
       </c>
       <c r="D1418" s="1" t="inlineStr">
         <is>
-          <t>植物；作物；工厂</t>
+          <t>建立；建造；设立</t>
         </is>
       </c>
       <c r="E1418" s="1" t="inlineStr">
@@ -45907,7 +45907,7 @@
       </c>
       <c r="B1422" s="1" t="inlineStr">
         <is>
-          <t>[ɛntvʊʁf] 气流；草稿；汇票〈n.m.〉</t>
+          <t>[ɛntvʊʁf] 草稿；草案；设计图〈n.m.〉</t>
         </is>
       </c>
       <c r="C1422" s="1" t="inlineStr">
@@ -45917,7 +45917,7 @@
       </c>
       <c r="D1422" s="1" t="inlineStr">
         <is>
-          <t>气流；草稿；汇票</t>
+          <t>草稿；草案；设计图</t>
         </is>
       </c>
       <c r="E1422" s="1" t="inlineStr">
@@ -46035,12 +46035,12 @@
       </c>
       <c r="B1426" s="1" t="inlineStr">
         <is>
-          <t>[pakʊnk] 小包；一批信件；大量〈n.f.〉</t>
+          <t>[pakʊŋ] 小包；一批信件；大量〈n.f.〉</t>
         </is>
       </c>
       <c r="C1426" s="1" t="inlineStr">
         <is>
-          <t>pakʊnk</t>
+          <t>pakʊŋ</t>
         </is>
       </c>
       <c r="D1426" s="1" t="inlineStr">
@@ -46131,7 +46131,7 @@
       </c>
       <c r="B1429" s="1" t="inlineStr">
         <is>
-          <t>[ʊnbəʁəçənbaːɐ] 不可胜数地；无数地〈adv.〉</t>
+          <t>[ʊnbəʁəçənbaːɐ] 不可预测的；难以预料的；变化无常的〈adv.〉</t>
         </is>
       </c>
       <c r="C1429" s="1" t="inlineStr">
@@ -46141,7 +46141,7 @@
       </c>
       <c r="D1429" s="1" t="inlineStr">
         <is>
-          <t>不可胜数地；无数地</t>
+          <t>不可预测的；难以预料的；变化无常的</t>
         </is>
       </c>
       <c r="E1429" s="1" t="inlineStr">
@@ -46483,7 +46483,7 @@
       </c>
       <c r="B1440" s="1" t="inlineStr">
         <is>
-          <t>[aʊtɔʃlʏsəl] 汽车；客车；车〈n.m.〉</t>
+          <t>[aʊtɔʃlʏsəl] 汽车钥匙〈n.m.〉</t>
         </is>
       </c>
       <c r="C1440" s="1" t="inlineStr">
@@ -46493,7 +46493,7 @@
       </c>
       <c r="D1440" s="1" t="inlineStr">
         <is>
-          <t>汽车；客车；车</t>
+          <t>汽车钥匙</t>
         </is>
       </c>
       <c r="E1440" s="1" t="inlineStr">
@@ -46579,7 +46579,7 @@
       </c>
       <c r="B1443" s="1" t="inlineStr">
         <is>
-          <t>[ɡɛdʁɛnɡt] 压碎的；倒碎的〈adv.〉</t>
+          <t>[ɡɛdʁɛnɡt] 拥挤的；密集的；（文体）简练的〈adv.〉</t>
         </is>
       </c>
       <c r="C1443" s="1" t="inlineStr">
@@ -46589,7 +46589,7 @@
       </c>
       <c r="D1443" s="1" t="inlineStr">
         <is>
-          <t>压碎的；倒碎的</t>
+          <t>拥挤的；密集的；（文体）简练的</t>
         </is>
       </c>
       <c r="E1443" s="1" t="inlineStr">
@@ -46739,7 +46739,7 @@
       </c>
       <c r="B1448" s="1" t="inlineStr">
         <is>
-          <t>[aʊsnaːmsvaɪzə] 被；经；由〈adv.〉</t>
+          <t>[aʊsnaːmsvaɪzə] 例外地；破例地〈adv.〉</t>
         </is>
       </c>
       <c r="C1448" s="1" t="inlineStr">
@@ -46749,7 +46749,7 @@
       </c>
       <c r="D1448" s="1" t="inlineStr">
         <is>
-          <t>被；经；由</t>
+          <t>例外地；破例地</t>
         </is>
       </c>
       <c r="E1448" s="1" t="inlineStr">
@@ -46995,12 +46995,12 @@
       </c>
       <c r="B1456" s="1" t="inlineStr">
         <is>
-          <t>[beːɡaɪstəʁʊnk] 巨大的热情；热心〈n.f.〉</t>
+          <t>[beːɡaɪstəʁʊŋ] 巨大的热情；热心〈n.f.〉</t>
         </is>
       </c>
       <c r="C1456" s="1" t="inlineStr">
         <is>
-          <t>beːɡaɪstəʁʊnk</t>
+          <t>beːɡaɪstəʁʊŋ</t>
         </is>
       </c>
       <c r="D1456" s="1" t="inlineStr">
@@ -47059,7 +47059,7 @@
       </c>
       <c r="B1458" s="1" t="inlineStr">
         <is>
-          <t>[beːɡabt] 适当地；适宜地〈adv.〉</t>
+          <t>[beːɡabt] 有天赋的；有才能的〈adv.〉</t>
         </is>
       </c>
       <c r="C1458" s="1" t="inlineStr">
@@ -47069,7 +47069,7 @@
       </c>
       <c r="D1458" s="1" t="inlineStr">
         <is>
-          <t>适当地；适宜地</t>
+          <t>有天赋的；有才能的</t>
         </is>
       </c>
       <c r="E1458" s="1" t="inlineStr">
@@ -47251,7 +47251,7 @@
       </c>
       <c r="B1464" s="1" t="inlineStr">
         <is>
-          <t>[pasəndə] 比赛；火柴〈adv.〉</t>
+          <t>[pasəndə] 合适的；相配的；恰当的〈adv.〉</t>
         </is>
       </c>
       <c r="C1464" s="1" t="inlineStr">
@@ -47261,7 +47261,7 @@
       </c>
       <c r="D1464" s="1" t="inlineStr">
         <is>
-          <t>比赛；火柴</t>
+          <t>合适的；相配的；恰当的</t>
         </is>
       </c>
       <c r="E1464" s="1" t="inlineStr">
@@ -47379,7 +47379,7 @@
       </c>
       <c r="B1468" s="1" t="inlineStr">
         <is>
-          <t>[ʊnfuːk] 损害；伤害；灾祸〈n.m.〉</t>
+          <t>[ʊnfuːk] 恶作剧；胡闹；胡说〈n.m.〉</t>
         </is>
       </c>
       <c r="C1468" s="1" t="inlineStr">
@@ -47389,7 +47389,7 @@
       </c>
       <c r="D1468" s="1" t="inlineStr">
         <is>
-          <t>损害；伤害；灾祸</t>
+          <t>恶作剧；胡闹；胡说</t>
         </is>
       </c>
       <c r="E1468" s="1" t="inlineStr">
@@ -47443,7 +47443,7 @@
       </c>
       <c r="B1470" s="1" t="inlineStr">
         <is>
-          <t>[ɛʁɡʁɪfən] 发疯；渴望做某事；镇静〈v.〉</t>
+          <t>[ɛʁɡʁɪfən] 抓住；握住；采取；深受感动的〈v.〉</t>
         </is>
       </c>
       <c r="C1470" s="1" t="inlineStr">
@@ -47453,7 +47453,7 @@
       </c>
       <c r="D1470" s="1" t="inlineStr">
         <is>
-          <t>发疯；渴望做某事；镇静</t>
+          <t>抓住；握住；采取；深受感动的</t>
         </is>
       </c>
       <c r="E1470" s="1" t="inlineStr">
@@ -47507,7 +47507,7 @@
       </c>
       <c r="B1472" s="1" t="inlineStr">
         <is>
-          <t>[ɛkst͡sələnt] 最佳部分；初期〈adj.〉</t>
+          <t>[ɛkst͡sələnt] 优秀的；卓越的；杰出的〈adj.〉</t>
         </is>
       </c>
       <c r="C1472" s="1" t="inlineStr">
@@ -47517,7 +47517,7 @@
       </c>
       <c r="D1472" s="1" t="inlineStr">
         <is>
-          <t>最佳部分；初期</t>
+          <t>优秀的；卓越的；杰出的</t>
         </is>
       </c>
       <c r="E1472" s="1" t="inlineStr">
@@ -47571,12 +47571,12 @@
       </c>
       <c r="B1474" s="1" t="inlineStr">
         <is>
-          <t>[buːzɪnəs] 生意；事情；业务〈n.〉</t>
+          <t>[bɪznɪs] 生意；事情；业务〈n.〉</t>
         </is>
       </c>
       <c r="C1474" s="1" t="inlineStr">
         <is>
-          <t>buːzɪnəs</t>
+          <t>bɪznɪs</t>
         </is>
       </c>
       <c r="D1474" s="1" t="inlineStr">
@@ -47731,7 +47731,7 @@
       </c>
       <c r="B1479" s="1" t="inlineStr">
         <is>
-          <t>[zɛnkən] 低的；下级的〈v.〉</t>
+          <t>[zɛnkən] 降低；使下沉；减少〈v.〉</t>
         </is>
       </c>
       <c r="C1479" s="1" t="inlineStr">
@@ -47741,7 +47741,7 @@
       </c>
       <c r="D1479" s="1" t="inlineStr">
         <is>
-          <t>低的；下级的</t>
+          <t>降低；使下沉；减少</t>
         </is>
       </c>
       <c r="E1479" s="1" t="inlineStr">
@@ -48019,7 +48019,7 @@
       </c>
       <c r="B1488" s="1" t="inlineStr">
         <is>
-          <t>[t͡sɛːl] 测光模式；计量；测量〈n.〉</t>
+          <t>[t͡sɛːl] 非独立词条；数数为动词 zählen，数字为 die Zahl〈n.f.〉〈n.〉</t>
         </is>
       </c>
       <c r="C1488" s="1" t="inlineStr">
@@ -48029,7 +48029,7 @@
       </c>
       <c r="D1488" s="1" t="inlineStr">
         <is>
-          <t>测光模式；计量；测量</t>
+          <t>非独立词条；数数为动词 zählen，数字为 die Zahl〈n.f.〉</t>
         </is>
       </c>
       <c r="E1488" s="1" t="inlineStr">
@@ -48083,7 +48083,7 @@
       </c>
       <c r="B1490" s="1" t="inlineStr">
         <is>
-          <t>[ʃtʁɛkən] 伸展；张开；连绵〈n.〉</t>
+          <t>[ʃtʁɛkən] 伸展；张开；连绵〈v.〉〈n.〉</t>
         </is>
       </c>
       <c r="C1490" s="1" t="inlineStr">
@@ -48093,7 +48093,7 @@
       </c>
       <c r="D1490" s="1" t="inlineStr">
         <is>
-          <t>伸展；张开；连绵</t>
+          <t>伸展；张开；连绵〈v.〉</t>
         </is>
       </c>
       <c r="E1490" s="1" t="inlineStr">
@@ -48147,7 +48147,7 @@
       </c>
       <c r="B1492" s="1" t="inlineStr">
         <is>
-          <t>[aʊsfʏlən] 完成；完井；结束；完工〈n.〉</t>
+          <t>[aʊsfʏlən] 填写；填满〈n.〉</t>
         </is>
       </c>
       <c r="C1492" s="1" t="inlineStr">
@@ -48157,7 +48157,7 @@
       </c>
       <c r="D1492" s="1" t="inlineStr">
         <is>
-          <t>完成；完井；结束；完工</t>
+          <t>填写；填满</t>
         </is>
       </c>
       <c r="E1492" s="1" t="inlineStr">
@@ -48243,17 +48243,17 @@
       </c>
       <c r="B1495" s="1" t="inlineStr">
         <is>
-          <t>[beːtaɪlɪɡʊnk] 拥护；支持；辩护〈n.f.〉</t>
+          <t>[beːtaɪlɪɡʊŋ] 参与；参加；股份；份额〈n.f.〉</t>
         </is>
       </c>
       <c r="C1495" s="1" t="inlineStr">
         <is>
-          <t>beːtaɪlɪɡʊnk</t>
+          <t>beːtaɪlɪɡʊŋ</t>
         </is>
       </c>
       <c r="D1495" s="1" t="inlineStr">
         <is>
-          <t>拥护；支持；辩护</t>
+          <t>参与；参加；股份；份额</t>
         </is>
       </c>
       <c r="E1495" s="1" t="inlineStr">
@@ -48275,7 +48275,7 @@
       </c>
       <c r="B1496" s="1" t="inlineStr">
         <is>
-          <t>[bɛnɡəl] 小孩；小不点〈n.m.〉</t>
+          <t>[bɛnɡəl] 顽童；淘气鬼；（旧）棍棒〈n.m.〉</t>
         </is>
       </c>
       <c r="C1496" s="1" t="inlineStr">
@@ -48285,7 +48285,7 @@
       </c>
       <c r="D1496" s="1" t="inlineStr">
         <is>
-          <t>小孩；小不点</t>
+          <t>顽童；淘气鬼；（旧）棍棒</t>
         </is>
       </c>
       <c r="E1496" s="1" t="inlineStr">
@@ -48723,7 +48723,7 @@
       </c>
       <c r="B1510" s="1" t="inlineStr">
         <is>
-          <t>[t͡sɛʁʃlaɡən] 平板；以平板盖上〈v.〉</t>
+          <t>[t͡sɛʁʃlaɡən] 打碎；粉碎〈v.〉</t>
         </is>
       </c>
       <c r="C1510" s="1" t="inlineStr">
@@ -48733,7 +48733,7 @@
       </c>
       <c r="D1510" s="1" t="inlineStr">
         <is>
-          <t>平板；以平板盖上</t>
+          <t>打碎；粉碎</t>
         </is>
       </c>
       <c r="E1510" s="1" t="inlineStr">
@@ -48883,7 +48883,7 @@
       </c>
       <c r="B1515" s="1" t="inlineStr">
         <is>
-          <t>[ʃɪçtən] 成层；分层〈n.〉</t>
+          <t>[ʃɪçtən] schichten：堆叠；使成层〈v.〉〈n.〉</t>
         </is>
       </c>
       <c r="C1515" s="1" t="inlineStr">
@@ -48893,7 +48893,7 @@
       </c>
       <c r="D1515" s="1" t="inlineStr">
         <is>
-          <t>成层；分层</t>
+          <t>schichten：堆叠；使成层〈v.〉</t>
         </is>
       </c>
       <c r="E1515" s="1" t="inlineStr">
@@ -49011,7 +49011,7 @@
       </c>
       <c r="B1519" s="1" t="inlineStr">
         <is>
-          <t>[vaɪzɐ] 卡胡纳〈n.m.〉</t>
+          <t>[vaɪzɐ] 指针（智者应为 der Weise）〈n.m.〉</t>
         </is>
       </c>
       <c r="C1519" s="1" t="inlineStr">
@@ -49021,7 +49021,7 @@
       </c>
       <c r="D1519" s="1" t="inlineStr">
         <is>
-          <t>卡胡纳</t>
+          <t>指针（智者应为 der Weise）</t>
         </is>
       </c>
       <c r="E1519" s="1" t="inlineStr">
@@ -49107,7 +49107,7 @@
       </c>
       <c r="B1522" s="1" t="inlineStr">
         <is>
-          <t>[ʁyːʁənt] 激动地；刺激地；令人兴奋地〈adv.〉</t>
+          <t>[ʁyːʁənt] 感人的；动人的〈adv.〉</t>
         </is>
       </c>
       <c r="C1522" s="1" t="inlineStr">
@@ -49117,7 +49117,7 @@
       </c>
       <c r="D1522" s="1" t="inlineStr">
         <is>
-          <t>激动地；刺激地；令人兴奋地</t>
+          <t>感人的；动人的</t>
         </is>
       </c>
       <c r="E1522" s="1" t="inlineStr">
@@ -49203,7 +49203,7 @@
       </c>
       <c r="B1525" s="1" t="inlineStr">
         <is>
-          <t>[vɪʁbəl] 转环；旋转轴承〈n.m.〉</t>
+          <t>[vɪʁbəl] 漩涡；旋转；椎骨〈n.m.〉</t>
         </is>
       </c>
       <c r="C1525" s="1" t="inlineStr">
@@ -49213,7 +49213,7 @@
       </c>
       <c r="D1525" s="1" t="inlineStr">
         <is>
-          <t>转环；旋转轴承</t>
+          <t>漩涡；旋转；椎骨</t>
         </is>
       </c>
       <c r="E1525" s="1" t="inlineStr">
@@ -49395,17 +49395,17 @@
       </c>
       <c r="B1531" s="1" t="inlineStr">
         <is>
-          <t>[aːbʊ] 阿布扎比〈n.〉</t>
+          <t>[aːbu] 非标准德语词；Abu Dhabi 的简称通常写作 Abu Dhabi，无独立词条 „Abu“〈n.〉</t>
         </is>
       </c>
       <c r="C1531" s="1" t="inlineStr">
         <is>
-          <t>aːbʊ</t>
+          <t>aːbu</t>
         </is>
       </c>
       <c r="D1531" s="1" t="inlineStr">
         <is>
-          <t>阿布扎比</t>
+          <t>非标准德语词；Abu Dhabi 的简称通常写作 Abu Dhabi，无独立词条 „Abu“</t>
         </is>
       </c>
       <c r="E1531" s="1" t="inlineStr">
@@ -49459,12 +49459,12 @@
       </c>
       <c r="B1533" s="1" t="inlineStr">
         <is>
-          <t>[fasʊnk] 框；结构；体格；构成〈n.f.〉</t>
+          <t>[fasʊŋ] 框；结构；体格；构成〈n.f.〉</t>
         </is>
       </c>
       <c r="C1533" s="1" t="inlineStr">
         <is>
-          <t>fasʊnk</t>
+          <t>fasʊŋ</t>
         </is>
       </c>
       <c r="D1533" s="1" t="inlineStr">
@@ -49587,7 +49587,7 @@
       </c>
       <c r="B1537" s="1" t="inlineStr">
         <is>
-          <t>[vɔxənlank] 永久的；永恒的〈adv.〉</t>
+          <t>[vɔxənlank] 数周之久的；持续数周的〈adv.〉</t>
         </is>
       </c>
       <c r="C1537" s="1" t="inlineStr">
@@ -49597,7 +49597,7 @@
       </c>
       <c r="D1537" s="1" t="inlineStr">
         <is>
-          <t>永久的；永恒的</t>
+          <t>数周之久的；持续数周的</t>
         </is>
       </c>
       <c r="E1537" s="1" t="inlineStr">
@@ -49811,7 +49811,7 @@
       </c>
       <c r="B1544" s="1" t="inlineStr">
         <is>
-          <t>[fɛʁvəndʊnk] 利用〈n.f.〉</t>
+          <t>[fɛʁvəndʊnk] 使用；应用；用途〈n.f.〉</t>
         </is>
       </c>
       <c r="C1544" s="1" t="inlineStr">
@@ -49821,7 +49821,7 @@
       </c>
       <c r="D1544" s="1" t="inlineStr">
         <is>
-          <t>利用</t>
+          <t>使用；应用；用途</t>
         </is>
       </c>
       <c r="E1544" s="1" t="inlineStr">
@@ -49875,7 +49875,7 @@
       </c>
       <c r="B1546" s="1" t="inlineStr">
         <is>
-          <t>[alɡəmaɪn] 通常的；共同的；通俗的〈adj.〉</t>
+          <t>[alɡəmaɪn] 一般的；普遍的；公众的〈adj.〉〈adj.〉</t>
         </is>
       </c>
       <c r="C1546" s="1" t="inlineStr">
@@ -49885,7 +49885,7 @@
       </c>
       <c r="D1546" s="1" t="inlineStr">
         <is>
-          <t>通常的；共同的；通俗的</t>
+          <t>一般的；普遍的；公众的〈adj.〉</t>
         </is>
       </c>
       <c r="E1546" s="1" t="inlineStr">
@@ -49907,17 +49907,17 @@
       </c>
       <c r="B1547" s="1" t="inlineStr">
         <is>
-          <t>[blas] 吹；打击；殴打〈n.m.〉</t>
+          <t>[blaːs] 德语中无此独立名词，应为 Blase（气泡；水泡；膀胱）〈n.m.〉</t>
         </is>
       </c>
       <c r="C1547" s="1" t="inlineStr">
         <is>
-          <t>blas</t>
+          <t>blaːs</t>
         </is>
       </c>
       <c r="D1547" s="1" t="inlineStr">
         <is>
-          <t>吹；打击；殴打</t>
+          <t>德语中无此独立名词，应为 Blase（气泡；水泡；膀胱）</t>
         </is>
       </c>
       <c r="E1547" s="1" t="inlineStr">
@@ -50067,7 +50067,7 @@
       </c>
       <c r="B1552" s="1" t="inlineStr">
         <is>
-          <t>[ʊnfəʁzeːʁt] 未亵渎的；未受侵犯的；无污点的〈adv.〉</t>
+          <t>[ʊnfəʁzeːʁt] 完好无损的；安然无恙的〈adv.〉</t>
         </is>
       </c>
       <c r="C1552" s="1" t="inlineStr">
@@ -50077,7 +50077,7 @@
       </c>
       <c r="D1552" s="1" t="inlineStr">
         <is>
-          <t>未亵渎的；未受侵犯的；无污点的</t>
+          <t>完好无损的；安然无恙的</t>
         </is>
       </c>
       <c r="E1552" s="1" t="inlineStr">
@@ -50259,7 +50259,7 @@
       </c>
       <c r="B1558" s="1" t="inlineStr">
         <is>
-          <t>[t͡siːɡɔʏnɐ] 流浪〈n.m.〉</t>
+          <t>[t͡siːɡɔʏnɐ] 吉普赛人〈n.m.〉</t>
         </is>
       </c>
       <c r="C1558" s="1" t="inlineStr">
@@ -50269,7 +50269,7 @@
       </c>
       <c r="D1558" s="1" t="inlineStr">
         <is>
-          <t>流浪</t>
+          <t>吉普赛人</t>
         </is>
       </c>
       <c r="E1558" s="1" t="inlineStr">
@@ -50451,7 +50451,7 @@
       </c>
       <c r="B1564" s="1" t="inlineStr">
         <is>
-          <t>[ɛʁfɔʁdəʁliːç] 必需品；要素〈adj.〉</t>
+          <t>[ɛʁfɔʁdəʁliːç] 必需的；必要的；所需的〈adj.〉</t>
         </is>
       </c>
       <c r="C1564" s="1" t="inlineStr">
@@ -50461,7 +50461,7 @@
       </c>
       <c r="D1564" s="1" t="inlineStr">
         <is>
-          <t>必需品；要素</t>
+          <t>必需的；必要的；所需的</t>
         </is>
       </c>
       <c r="E1564" s="1" t="inlineStr">
@@ -50515,7 +50515,7 @@
       </c>
       <c r="B1566" s="1" t="inlineStr">
         <is>
-          <t>[zɛntɪməntaːl] 乡巴佬的；陈腐的〈adv.〉</t>
+          <t>[zɛntɪməntaːl] 感伤的；多愁善感的〈adv.〉</t>
         </is>
       </c>
       <c r="C1566" s="1" t="inlineStr">
@@ -50525,7 +50525,7 @@
       </c>
       <c r="D1566" s="1" t="inlineStr">
         <is>
-          <t>乡巴佬的；陈腐的</t>
+          <t>感伤的；多愁善感的</t>
         </is>
       </c>
       <c r="E1566" s="1" t="inlineStr">
@@ -50611,7 +50611,7 @@
       </c>
       <c r="B1569" s="1" t="inlineStr">
         <is>
-          <t>[iːdɪɔtɪʃ] 笨蛋；呆子〈adj.〉</t>
+          <t>[iːdɪɔtɪʃ] 愚蠢的；白痴般的〈adj.〉〈adj.〉</t>
         </is>
       </c>
       <c r="C1569" s="1" t="inlineStr">
@@ -50621,7 +50621,7 @@
       </c>
       <c r="D1569" s="1" t="inlineStr">
         <is>
-          <t>笨蛋；呆子</t>
+          <t>愚蠢的；白痴般的〈adj.〉</t>
         </is>
       </c>
       <c r="E1569" s="1" t="inlineStr">
@@ -50675,7 +50675,7 @@
       </c>
       <c r="B1571" s="1" t="inlineStr">
         <is>
-          <t>[zɔʏbɐn] 擦拭；用力打；凸轮；擦〈v.〉</t>
+          <t>[zɔʏbɐn] 清扫；清除；使清洁〈v.〉</t>
         </is>
       </c>
       <c r="C1571" s="1" t="inlineStr">
@@ -50685,7 +50685,7 @@
       </c>
       <c r="D1571" s="1" t="inlineStr">
         <is>
-          <t>擦拭；用力打；凸轮；擦</t>
+          <t>清扫；清除；使清洁</t>
         </is>
       </c>
       <c r="E1571" s="1" t="inlineStr">
@@ -50739,7 +50739,7 @@
       </c>
       <c r="B1573" s="1" t="inlineStr">
         <is>
-          <t>[aɪnbʁɪnɡən] 倾销；倾倒；倾泻；填埋〈n.〉</t>
+          <t>[aɪnbʁɪnɡən] 带来；贡献；提出〈n.〉</t>
         </is>
       </c>
       <c r="C1573" s="1" t="inlineStr">
@@ -50749,7 +50749,7 @@
       </c>
       <c r="D1573" s="1" t="inlineStr">
         <is>
-          <t>倾销；倾倒；倾泻；填埋</t>
+          <t>带来；贡献；提出</t>
         </is>
       </c>
       <c r="E1573" s="1" t="inlineStr">
@@ -50931,7 +50931,7 @@
       </c>
       <c r="B1579" s="1" t="inlineStr">
         <is>
-          <t>[hʊnɡɐn] 饥饿；饿死；绝食；饥锇〈n.〉</t>
+          <t>[hʊnɡɐn] 挨饿；饿死；绝食〈v.〉〈n.〉</t>
         </is>
       </c>
       <c r="C1579" s="1" t="inlineStr">
@@ -50941,7 +50941,7 @@
       </c>
       <c r="D1579" s="1" t="inlineStr">
         <is>
-          <t>饥饿；饿死；绝食；饥锇</t>
+          <t>挨饿；饿死；绝食〈v.〉</t>
         </is>
       </c>
       <c r="E1579" s="1" t="inlineStr">
@@ -51027,12 +51027,12 @@
       </c>
       <c r="B1582" s="1" t="inlineStr">
         <is>
-          <t>[beːdiːnʊnk] 操作；动作；手术〈n.f.〉</t>
+          <t>[beːdiːnʊŋ] 操作；动作；手术〈n.f.〉</t>
         </is>
       </c>
       <c r="C1582" s="1" t="inlineStr">
         <is>
-          <t>beːdiːnʊnk</t>
+          <t>beːdiːnʊŋ</t>
         </is>
       </c>
       <c r="D1582" s="1" t="inlineStr">
@@ -51091,7 +51091,7 @@
       </c>
       <c r="B1584" s="1" t="inlineStr">
         <is>
-          <t>[fɛʁiːɡəlt] 连结；连锁；相关〈adv.〉</t>
+          <t>[fɛʁiːɡəlt] 锁上的；闩住的〈adv.〉</t>
         </is>
       </c>
       <c r="C1584" s="1" t="inlineStr">
@@ -51101,7 +51101,7 @@
       </c>
       <c r="D1584" s="1" t="inlineStr">
         <is>
-          <t>连结；连锁；相关</t>
+          <t>锁上的；闩住的</t>
         </is>
       </c>
       <c r="E1584" s="1" t="inlineStr">
@@ -51123,7 +51123,7 @@
       </c>
       <c r="B1585" s="1" t="inlineStr">
         <is>
-          <t>[ʃpuːʁənzɪçəʁʊnk] 收集；采集；收藏品〈n.f.〉</t>
+          <t>[ʃpuːʁənzɪçəʁʊnk] 痕迹保全；取证〈n.f.〉</t>
         </is>
       </c>
       <c r="C1585" s="1" t="inlineStr">
@@ -51133,7 +51133,7 @@
       </c>
       <c r="D1585" s="1" t="inlineStr">
         <is>
-          <t>收集；采集；收藏品</t>
+          <t>痕迹保全；取证</t>
         </is>
       </c>
       <c r="E1585" s="1" t="inlineStr">
@@ -51347,7 +51347,7 @@
       </c>
       <c r="B1592" s="1" t="inlineStr">
         <is>
-          <t>[kɪpən] 交换；变换；代替；整流〈n.〉</t>
+          <t>[kɪpən] 名词 das Kippen 指烟头、烟蒂；倾斜、翻倒、下跌是动词 kippen 的释义〈n.〉</t>
         </is>
       </c>
       <c r="C1592" s="1" t="inlineStr">
@@ -51357,7 +51357,7 @@
       </c>
       <c r="D1592" s="1" t="inlineStr">
         <is>
-          <t>交换；变换；代替；整流</t>
+          <t>名词 das Kippen 指烟头、烟蒂；倾斜、翻倒、下跌是动词 kippen 的释义</t>
         </is>
       </c>
       <c r="E1592" s="1" t="inlineStr">
@@ -51379,7 +51379,7 @@
       </c>
       <c r="B1593" s="1" t="inlineStr">
         <is>
-          <t>[pflastɐ] 地方；地点；位置〈n.〉</t>
+          <t>[pflastɐ] 铺石路面；创可贴〈n.〉</t>
         </is>
       </c>
       <c r="C1593" s="1" t="inlineStr">
@@ -51389,7 +51389,7 @@
       </c>
       <c r="D1593" s="1" t="inlineStr">
         <is>
-          <t>地方；地点；位置</t>
+          <t>铺石路面；创可贴</t>
         </is>
       </c>
       <c r="E1593" s="1" t="inlineStr">
@@ -51443,7 +51443,7 @@
       </c>
       <c r="B1595" s="1" t="inlineStr">
         <is>
-          <t>[ampəl] 绞死；绞杀；悬挂；绞刑〈n.f.〉</t>
+          <t>[ampəl] 交通信号灯；红绿灯〈n.f.〉</t>
         </is>
       </c>
       <c r="C1595" s="1" t="inlineStr">
@@ -51453,7 +51453,7 @@
       </c>
       <c r="D1595" s="1" t="inlineStr">
         <is>
-          <t>绞死；绞杀；悬挂；绞刑</t>
+          <t>交通信号灯；红绿灯</t>
         </is>
       </c>
       <c r="E1595" s="1" t="inlineStr">
@@ -51763,7 +51763,7 @@
       </c>
       <c r="B1605" s="1" t="inlineStr">
         <is>
-          <t>[ʁʏk] 回程；退回；反向〈n.〉</t>
+          <t>[ʁʏk] 单独名词罕见，多作前缀表示“回、返”（如 Rückfahrt 回程）〈n.〉</t>
         </is>
       </c>
       <c r="C1605" s="1" t="inlineStr">
@@ -51773,7 +51773,7 @@
       </c>
       <c r="D1605" s="1" t="inlineStr">
         <is>
-          <t>回程；退回；反向</t>
+          <t>单独名词罕见，多作前缀表示“回、返”（如 Rückfahrt 回程）</t>
         </is>
       </c>
       <c r="E1605" s="1" t="inlineStr">
@@ -51891,7 +51891,7 @@
       </c>
       <c r="B1609" s="1" t="inlineStr">
         <is>
-          <t>[juːɡəndlɪçən] 稚气〈n.〉</t>
+          <t>[juːɡəndlɪçən] 青少年；年轻人〈n.〉</t>
         </is>
       </c>
       <c r="C1609" s="1" t="inlineStr">
@@ -51901,7 +51901,7 @@
       </c>
       <c r="D1609" s="1" t="inlineStr">
         <is>
-          <t>稚气</t>
+          <t>青少年；年轻人</t>
         </is>
       </c>
       <c r="E1609" s="1" t="inlineStr">
@@ -52179,12 +52179,12 @@
       </c>
       <c r="B1618" s="1" t="inlineStr">
         <is>
-          <t>[ɛndəʁʊnk] 变更；改动〈n.f.〉</t>
+          <t>[ɛndəʁʊŋ] 变更；改动〈n.f.〉</t>
         </is>
       </c>
       <c r="C1618" s="1" t="inlineStr">
         <is>
-          <t>ɛndəʁʊnk</t>
+          <t>ɛndəʁʊŋ</t>
         </is>
       </c>
       <c r="D1618" s="1" t="inlineStr">
@@ -52211,7 +52211,7 @@
       </c>
       <c r="B1619" s="1" t="inlineStr">
         <is>
-          <t>[blɪndɐ] 白化病者〈n.〉</t>
+          <t>[blɪndɐ] 盲人〈n.〉</t>
         </is>
       </c>
       <c r="C1619" s="1" t="inlineStr">
@@ -52221,7 +52221,7 @@
       </c>
       <c r="D1619" s="1" t="inlineStr">
         <is>
-          <t>白化病者</t>
+          <t>盲人</t>
         </is>
       </c>
       <c r="E1619" s="1" t="inlineStr">
@@ -52371,7 +52371,7 @@
       </c>
       <c r="B1624" s="1" t="inlineStr">
         <is>
-          <t>[ɡʁaʊənfɔl] 冷酷的；坚强的；残忍的〈adv.〉</t>
+          <t>[ɡʁaʊənfɔl] 可怕的；骇人的〈adj.〉〈adv.〉</t>
         </is>
       </c>
       <c r="C1624" s="1" t="inlineStr">
@@ -52381,7 +52381,7 @@
       </c>
       <c r="D1624" s="1" t="inlineStr">
         <is>
-          <t>冷酷的；坚强的；残忍的</t>
+          <t>可怕的；骇人的〈adj.〉</t>
         </is>
       </c>
       <c r="E1624" s="1" t="inlineStr">
@@ -52915,7 +52915,7 @@
       </c>
       <c r="B1641" s="1" t="inlineStr">
         <is>
-          <t>[anʃaɪn] 颜色；面色；颜料〈n.m.〉</t>
+          <t>[anʃaɪn] 外表；外观；表象〈n.m.〉</t>
         </is>
       </c>
       <c r="C1641" s="1" t="inlineStr">
@@ -52925,7 +52925,7 @@
       </c>
       <c r="D1641" s="1" t="inlineStr">
         <is>
-          <t>颜色；面色；颜料</t>
+          <t>外表；外观；表象</t>
         </is>
       </c>
       <c r="E1641" s="1" t="inlineStr">
@@ -53075,7 +53075,7 @@
       </c>
       <c r="B1646" s="1" t="inlineStr">
         <is>
-          <t>[anstʁənɡən] 紧张；拉紧；张力〈v.〉</t>
+          <t>[anstʁənɡən] 使劳累；使费力；努力〈v.〉</t>
         </is>
       </c>
       <c r="C1646" s="1" t="inlineStr">
@@ -53085,7 +53085,7 @@
       </c>
       <c r="D1646" s="1" t="inlineStr">
         <is>
-          <t>紧张；拉紧；张力</t>
+          <t>使劳累；使费力；努力</t>
         </is>
       </c>
       <c r="E1646" s="1" t="inlineStr">
@@ -53267,7 +53267,7 @@
       </c>
       <c r="B1652" s="1" t="inlineStr">
         <is>
-          <t>[vaːlkampf] 选举；当选；选择权〈n.m.〉</t>
+          <t>[vaːlkampf] 竞选；竞选活动〈n.m.〉</t>
         </is>
       </c>
       <c r="C1652" s="1" t="inlineStr">
@@ -53277,7 +53277,7 @@
       </c>
       <c r="D1652" s="1" t="inlineStr">
         <is>
-          <t>选举；当选；选择权</t>
+          <t>竞选；竞选活动</t>
         </is>
       </c>
       <c r="E1652" s="1" t="inlineStr">
@@ -53299,7 +53299,7 @@
       </c>
       <c r="B1653" s="1" t="inlineStr">
         <is>
-          <t>[laːɡɐn] 谎言；假象；位置；躺着〈v.〉</t>
+          <t>[laːɡɐn] 储存；存放；放置；宿营〈v.〉</t>
         </is>
       </c>
       <c r="C1653" s="1" t="inlineStr">
@@ -53309,7 +53309,7 @@
       </c>
       <c r="D1653" s="1" t="inlineStr">
         <is>
-          <t>谎言；假象；位置；躺着</t>
+          <t>储存；存放；放置；宿营</t>
         </is>
       </c>
       <c r="E1653" s="1" t="inlineStr">
@@ -53395,7 +53395,7 @@
       </c>
       <c r="B1656" s="1" t="inlineStr">
         <is>
-          <t>[bʁɛmzə] 刹车；阻碍；丛林〈n.f.〉</t>
+          <t>[bʁɛmzə] 刹车；制动器；虻〈n.f.〉</t>
         </is>
       </c>
       <c r="C1656" s="1" t="inlineStr">
@@ -53405,7 +53405,7 @@
       </c>
       <c r="D1656" s="1" t="inlineStr">
         <is>
-          <t>刹车；阻碍；丛林</t>
+          <t>刹车；制动器；虻</t>
         </is>
       </c>
       <c r="E1656" s="1" t="inlineStr">
@@ -53651,7 +53651,7 @@
       </c>
       <c r="B1664" s="1" t="inlineStr">
         <is>
-          <t>[hɪntəʁm] 旁敲侧击〈adv.〉</t>
+          <t>[hɪntəʁm] 在…后面（hinter dem 的缩写）〈adv.〉〈adv.〉</t>
         </is>
       </c>
       <c r="C1664" s="1" t="inlineStr">
@@ -53661,7 +53661,7 @@
       </c>
       <c r="D1664" s="1" t="inlineStr">
         <is>
-          <t>旁敲侧击</t>
+          <t>在…后面（hinter dem 的缩写）〈adv.〉</t>
         </is>
       </c>
       <c r="E1664" s="1" t="inlineStr">
@@ -53747,7 +53747,7 @@
       </c>
       <c r="B1667" s="1" t="inlineStr">
         <is>
-          <t>[aɪnɡəlasən] 沉没的〈adj.〉</t>
+          <t>[aɪnɡəlasən] 嵌入的；镶嵌的；凹陷的〈adj.〉</t>
         </is>
       </c>
       <c r="C1667" s="1" t="inlineStr">
@@ -53757,7 +53757,7 @@
       </c>
       <c r="D1667" s="1" t="inlineStr">
         <is>
-          <t>沉没的</t>
+          <t>嵌入的；镶嵌的；凹陷的</t>
         </is>
       </c>
       <c r="E1667" s="1" t="inlineStr">
@@ -53811,7 +53811,7 @@
       </c>
       <c r="B1669" s="1" t="inlineStr">
         <is>
-          <t>[bɔʁɡən] 他；男孩；男人；雄性动物〈n.〉</t>
+          <t>[bɔʁɡən] 借；借入；借给〈n.〉</t>
         </is>
       </c>
       <c r="C1669" s="1" t="inlineStr">
@@ -53821,7 +53821,7 @@
       </c>
       <c r="D1669" s="1" t="inlineStr">
         <is>
-          <t>他；男孩；男人；雄性动物</t>
+          <t>借；借入；借给</t>
         </is>
       </c>
       <c r="E1669" s="1" t="inlineStr">
@@ -53939,7 +53939,7 @@
       </c>
       <c r="B1673" s="1" t="inlineStr">
         <is>
-          <t>[vant͡sə] 错误；虫；病菌〈n.f.〉</t>
+          <t>[vant͡sə] 臭虫；窃听器〈n.f.〉</t>
         </is>
       </c>
       <c r="C1673" s="1" t="inlineStr">
@@ -53949,7 +53949,7 @@
       </c>
       <c r="D1673" s="1" t="inlineStr">
         <is>
-          <t>错误；虫；病菌</t>
+          <t>臭虫；窃听器</t>
         </is>
       </c>
       <c r="E1673" s="1" t="inlineStr">
@@ -54035,7 +54035,7 @@
       </c>
       <c r="B1676" s="1" t="inlineStr">
         <is>
-          <t>[mɪʃ] 混合者；混合器；搅拌机〈n.〉</t>
+          <t>[mɪʃ] Misch 不是独立名词；‘混合者；混合器；搅拌机’应为 Mischer〈n.m.〉〈n.〉</t>
         </is>
       </c>
       <c r="C1676" s="1" t="inlineStr">
@@ -54045,7 +54045,7 @@
       </c>
       <c r="D1676" s="1" t="inlineStr">
         <is>
-          <t>混合者；混合器；搅拌机</t>
+          <t>Misch 不是独立名词；‘混合者；混合器；搅拌机’应为 Mischer〈n.m.〉</t>
         </is>
       </c>
       <c r="E1676" s="1" t="inlineStr">
@@ -54131,7 +54131,7 @@
       </c>
       <c r="B1679" s="1" t="inlineStr">
         <is>
-          <t>[klaɪnəʁə] 行为不良；失职；毁约；怠工〈adv.〉</t>
+          <t>[klaɪnəʁə] 更小的；较小的〈adv.〉</t>
         </is>
       </c>
       <c r="C1679" s="1" t="inlineStr">
@@ -54141,7 +54141,7 @@
       </c>
       <c r="D1679" s="1" t="inlineStr">
         <is>
-          <t>行为不良；失职；毁约；怠工</t>
+          <t>更小的；较小的</t>
         </is>
       </c>
       <c r="E1679" s="1" t="inlineStr">
@@ -54739,7 +54739,7 @@
       </c>
       <c r="B1698" s="1" t="inlineStr">
         <is>
-          <t>[fɔləs] 非常热情地；非常有魄力地〈adv.〉</t>
+          <t>[fɔləs] 满的；充满的〈adv.〉</t>
         </is>
       </c>
       <c r="C1698" s="1" t="inlineStr">
@@ -54749,7 +54749,7 @@
       </c>
       <c r="D1698" s="1" t="inlineStr">
         <is>
-          <t>非常热情地；非常有魄力地</t>
+          <t>满的；充满的</t>
         </is>
       </c>
       <c r="E1698" s="1" t="inlineStr">
@@ -55539,7 +55539,7 @@
       </c>
       <c r="B1723" s="1" t="inlineStr">
         <is>
-          <t>[anʁʊfɐ] 访客；召集员〈n.m.〉</t>
+          <t>[anʁʊfɐ] 打电话者；来电者〈n.m.〉</t>
         </is>
       </c>
       <c r="C1723" s="1" t="inlineStr">
@@ -55549,7 +55549,7 @@
       </c>
       <c r="D1723" s="1" t="inlineStr">
         <is>
-          <t>访客；召集员</t>
+          <t>打电话者；来电者</t>
         </is>
       </c>
       <c r="E1723" s="1" t="inlineStr">
@@ -55667,7 +55667,7 @@
       </c>
       <c r="B1727" s="1" t="inlineStr">
         <is>
-          <t>[lɔsfaːʁən] 离开；死；畅销〈v.〉</t>
+          <t>[lɔsfaːʁən] 出发；动身；（乘车）启程〈v.〉</t>
         </is>
       </c>
       <c r="C1727" s="1" t="inlineStr">
@@ -55677,7 +55677,7 @@
       </c>
       <c r="D1727" s="1" t="inlineStr">
         <is>
-          <t>离开；死；畅销</t>
+          <t>出发；动身；（乘车）启程</t>
         </is>
       </c>
       <c r="E1727" s="1" t="inlineStr">
@@ -55731,7 +55731,7 @@
       </c>
       <c r="B1729" s="1" t="inlineStr">
         <is>
-          <t>[naːdəln] 针〈n.〉</t>
+          <t>[naːdəln] 针（Nadel 的复数）〈f.〉〈n.〉</t>
         </is>
       </c>
       <c r="C1729" s="1" t="inlineStr">
@@ -55741,7 +55741,7 @@
       </c>
       <c r="D1729" s="1" t="inlineStr">
         <is>
-          <t>针</t>
+          <t>针（Nadel 的复数）〈f.〉</t>
         </is>
       </c>
       <c r="E1729" s="1" t="inlineStr">
@@ -55891,7 +55891,7 @@
       </c>
       <c r="B1734" s="1" t="inlineStr">
         <is>
-          <t>[ʃpɪt͡snamə] 碧海蓝天〈n.〉</t>
+          <t>[ʃpɪt͡snamə] 绰号；昵称〈n.〉</t>
         </is>
       </c>
       <c r="C1734" s="1" t="inlineStr">
@@ -55901,7 +55901,7 @@
       </c>
       <c r="D1734" s="1" t="inlineStr">
         <is>
-          <t>碧海蓝天</t>
+          <t>绰号；昵称</t>
         </is>
       </c>
       <c r="E1734" s="1" t="inlineStr">
@@ -55987,7 +55987,7 @@
       </c>
       <c r="B1737" s="1" t="inlineStr">
         <is>
-          <t>[beːfasən] 盖子；封面；藉口；覆盖〈v.〉</t>
+          <t>[beːfasən] 从事；处理；研究〈v.〉</t>
         </is>
       </c>
       <c r="C1737" s="1" t="inlineStr">
@@ -55997,7 +55997,7 @@
       </c>
       <c r="D1737" s="1" t="inlineStr">
         <is>
-          <t>盖子；封面；藉口；覆盖</t>
+          <t>从事；处理；研究</t>
         </is>
       </c>
       <c r="E1737" s="1" t="inlineStr">
@@ -56147,7 +56147,7 @@
       </c>
       <c r="B1742" s="1" t="inlineStr">
         <is>
-          <t>[hœkstvaːʁʃaɪnliːç] 大半有希望赢的；多半有希望取胜的〈adj.〉</t>
+          <t>[hœkstvaːʁʃaɪnliːç] 极有可能的；非常可能的〈adj.〉〈adj.〉</t>
         </is>
       </c>
       <c r="C1742" s="1" t="inlineStr">
@@ -56157,7 +56157,7 @@
       </c>
       <c r="D1742" s="1" t="inlineStr">
         <is>
-          <t>大半有希望赢的；多半有希望取胜的</t>
+          <t>极有可能的；非常可能的〈adj.〉</t>
         </is>
       </c>
       <c r="E1742" s="1" t="inlineStr">
@@ -56243,7 +56243,7 @@
       </c>
       <c r="B1745" s="1" t="inlineStr">
         <is>
-          <t>[tʁuːə] 保险箱〈n.f.〉</t>
+          <t>[tʁuːə] （带盖的）大箱子；宝箱〈n.f.〉</t>
         </is>
       </c>
       <c r="C1745" s="1" t="inlineStr">
@@ -56253,7 +56253,7 @@
       </c>
       <c r="D1745" s="1" t="inlineStr">
         <is>
-          <t>保险箱</t>
+          <t>（带盖的）大箱子；宝箱</t>
         </is>
       </c>
       <c r="E1745" s="1" t="inlineStr">
@@ -56371,7 +56371,7 @@
       </c>
       <c r="B1749" s="1" t="inlineStr">
         <is>
-          <t>[abhəbən] 损失；遗失；失败〈n.〉</t>
+          <t>[abhəbən] 起飞；提款；举起〈n.〉</t>
         </is>
       </c>
       <c r="C1749" s="1" t="inlineStr">
@@ -56381,7 +56381,7 @@
       </c>
       <c r="D1749" s="1" t="inlineStr">
         <is>
-          <t>损失；遗失；失败</t>
+          <t>起飞；提款；举起</t>
         </is>
       </c>
       <c r="E1749" s="1" t="inlineStr">
@@ -56851,7 +56851,7 @@
       </c>
       <c r="B1764" s="1" t="inlineStr">
         <is>
-          <t>[viːɡən] 卷；滚动；名单〈n.〉</t>
+          <t>[viːɡən] 称重；摇晃〈n.〉</t>
         </is>
       </c>
       <c r="C1764" s="1" t="inlineStr">
@@ -56861,7 +56861,7 @@
       </c>
       <c r="D1764" s="1" t="inlineStr">
         <is>
-          <t>卷；滚动；名单</t>
+          <t>称重；摇晃</t>
         </is>
       </c>
       <c r="E1764" s="1" t="inlineStr">
@@ -57299,7 +57299,7 @@
       </c>
       <c r="B1778" s="1" t="inlineStr">
         <is>
-          <t>[aːlaʁmanlaɡə] 惊恐；警报〈n.f.〉</t>
+          <t>[aːlaʁmanlaɡə] 警报系统；报警装置〈n.f.〉</t>
         </is>
       </c>
       <c r="C1778" s="1" t="inlineStr">
@@ -57309,7 +57309,7 @@
       </c>
       <c r="D1778" s="1" t="inlineStr">
         <is>
-          <t>惊恐；警报</t>
+          <t>警报系统；报警装置</t>
         </is>
       </c>
       <c r="E1778" s="1" t="inlineStr">
@@ -57491,7 +57491,7 @@
       </c>
       <c r="B1784" s="1" t="inlineStr">
         <is>
-          <t>[ɪntəʁnə] 领导人会议〈adv.〉</t>
+          <t>[ɪntəʁnə] 内部的〈adj.〉〈adv.〉</t>
         </is>
       </c>
       <c r="C1784" s="1" t="inlineStr">
@@ -57501,7 +57501,7 @@
       </c>
       <c r="D1784" s="1" t="inlineStr">
         <is>
-          <t>领导人会议</t>
+          <t>内部的〈adj.〉</t>
         </is>
       </c>
       <c r="E1784" s="1" t="inlineStr">
@@ -57651,7 +57651,7 @@
       </c>
       <c r="B1789" s="1" t="inlineStr">
         <is>
-          <t>[ʊʁtaɪlsfəʁmœɡən] 胜任；职称；能力〈n.〉</t>
+          <t>[ʊʁtaɪlsfəʁmœɡən] 判断力；辨别力〈n.〉</t>
         </is>
       </c>
       <c r="C1789" s="1" t="inlineStr">
@@ -57661,7 +57661,7 @@
       </c>
       <c r="D1789" s="1" t="inlineStr">
         <is>
-          <t>胜任；职称；能力</t>
+          <t>判断力；辨别力</t>
         </is>
       </c>
       <c r="E1789" s="1" t="inlineStr">
@@ -57683,7 +57683,7 @@
       </c>
       <c r="B1790" s="1" t="inlineStr">
         <is>
-          <t>[t͡svɛkə] 角钉；曲头钉〈n.f.〉</t>
+          <t>[t͡svɛkə] 目的；宗旨〈n.m.〉（Zweck的复数）〈n.f.〉</t>
         </is>
       </c>
       <c r="C1790" s="1" t="inlineStr">
@@ -57693,7 +57693,7 @@
       </c>
       <c r="D1790" s="1" t="inlineStr">
         <is>
-          <t>角钉；曲头钉</t>
+          <t>目的；宗旨〈n.m.〉（Zweck的复数）</t>
         </is>
       </c>
       <c r="E1790" s="1" t="inlineStr">
@@ -58003,7 +58003,7 @@
       </c>
       <c r="B1800" s="1" t="inlineStr">
         <is>
-          <t>[tɪfanʏ] 丝纱罗〈n.〉</t>
+          <t>[tɪfanʏ] 蒂芙尼（人名；珠宝品牌）〈n.〉</t>
         </is>
       </c>
       <c r="C1800" s="1" t="inlineStr">
@@ -58013,7 +58013,7 @@
       </c>
       <c r="D1800" s="1" t="inlineStr">
         <is>
-          <t>丝纱罗</t>
+          <t>蒂芙尼（人名；珠宝品牌）</t>
         </is>
       </c>
       <c r="E1800" s="1" t="inlineStr">
@@ -58067,7 +58067,7 @@
       </c>
       <c r="B1802" s="1" t="inlineStr">
         <is>
-          <t>[fʁyːəʁə] 从前的；模型〈adv.〉</t>
+          <t>[fʁyːəʁə] 以前的；较早的；从前的〈adv.〉</t>
         </is>
       </c>
       <c r="C1802" s="1" t="inlineStr">
@@ -58077,7 +58077,7 @@
       </c>
       <c r="D1802" s="1" t="inlineStr">
         <is>
-          <t>从前的；模型</t>
+          <t>以前的；较早的；从前的</t>
         </is>
       </c>
       <c r="E1802" s="1" t="inlineStr">
@@ -58387,7 +58387,7 @@
       </c>
       <c r="B1812" s="1" t="inlineStr">
         <is>
-          <t>[t͡suːʁʏkfəʁfɔlɡən] 返回；退走；撤退〈v.〉</t>
+          <t>[t͡suːʁʏkfəʁfɔlɡən] 追溯；回溯〈v.〉</t>
         </is>
       </c>
       <c r="C1812" s="1" t="inlineStr">
@@ -58397,7 +58397,7 @@
       </c>
       <c r="D1812" s="1" t="inlineStr">
         <is>
-          <t>返回；退走；撤退</t>
+          <t>追溯；回溯</t>
         </is>
       </c>
       <c r="E1812" s="1" t="inlineStr">
@@ -58483,7 +58483,7 @@
       </c>
       <c r="B1815" s="1" t="inlineStr">
         <is>
-          <t>[ʃpaɪzən] 热身；重新煮热；变暖；温车〈n.〉</t>
+          <t>[ʃpaɪzən] 用餐；进食；食物；菜肴〈n.〉</t>
         </is>
       </c>
       <c r="C1815" s="1" t="inlineStr">
@@ -58493,7 +58493,7 @@
       </c>
       <c r="D1815" s="1" t="inlineStr">
         <is>
-          <t>热身；重新煮热；变暖；温车</t>
+          <t>用餐；进食；食物；菜肴</t>
         </is>
       </c>
       <c r="E1815" s="1" t="inlineStr">
@@ -58835,7 +58835,7 @@
       </c>
       <c r="B1826" s="1" t="inlineStr">
         <is>
-          <t>[fɔʁmɪtaːk] 早晨；早上；初期〈n.m.〉</t>
+          <t>[fɔʁmɪtaːk] 上午〈m.〉〈n.m.〉</t>
         </is>
       </c>
       <c r="C1826" s="1" t="inlineStr">
@@ -58845,7 +58845,7 @@
       </c>
       <c r="D1826" s="1" t="inlineStr">
         <is>
-          <t>早晨；早上；初期</t>
+          <t>上午〈m.〉</t>
         </is>
       </c>
       <c r="E1826" s="1" t="inlineStr">
@@ -58931,7 +58931,7 @@
       </c>
       <c r="B1829" s="1" t="inlineStr">
         <is>
-          <t>[kasiːʁən] 收集；聚集；集中〈v.〉</t>
+          <t>[kasiːʁən] 收取；收款；收进〈v.〉〈v.〉</t>
         </is>
       </c>
       <c r="C1829" s="1" t="inlineStr">
@@ -58941,7 +58941,7 @@
       </c>
       <c r="D1829" s="1" t="inlineStr">
         <is>
-          <t>收集；聚集；集中</t>
+          <t>收取；收款；收进〈v.〉</t>
         </is>
       </c>
       <c r="E1829" s="1" t="inlineStr">
@@ -58963,7 +58963,7 @@
       </c>
       <c r="B1830" s="1" t="inlineStr">
         <is>
-          <t>[biːnə] 蜜蜂；聚会〈n.f.〉</t>
+          <t>[biːnə] 蜜蜂〈n.f.〉</t>
         </is>
       </c>
       <c r="C1830" s="1" t="inlineStr">
@@ -58973,7 +58973,7 @@
       </c>
       <c r="D1830" s="1" t="inlineStr">
         <is>
-          <t>蜜蜂；聚会</t>
+          <t>蜜蜂</t>
         </is>
       </c>
       <c r="E1830" s="1" t="inlineStr">
@@ -58995,7 +58995,7 @@
       </c>
       <c r="B1831" s="1" t="inlineStr">
         <is>
-          <t>[toːtəs] 死海〈n.〉</t>
+          <t>[toːtəs] 死者；死物〈n.〉</t>
         </is>
       </c>
       <c r="C1831" s="1" t="inlineStr">
@@ -59005,7 +59005,7 @@
       </c>
       <c r="D1831" s="1" t="inlineStr">
         <is>
-          <t>死海</t>
+          <t>死者；死物</t>
         </is>
       </c>
       <c r="E1831" s="1" t="inlineStr">
@@ -59027,12 +59027,12 @@
       </c>
       <c r="B1832" s="1" t="inlineStr">
         <is>
-          <t>[ɡɛkvɛlt] 忧伤的；痛苦的；耙地；折磨〈adj.〉</t>
+          <t>[ɡəkvɛːlt] 忧伤的；痛苦的；耙地；折磨〈adj.〉</t>
         </is>
       </c>
       <c r="C1832" s="1" t="inlineStr">
         <is>
-          <t>ɡɛkvɛlt</t>
+          <t>ɡəkvɛːlt</t>
         </is>
       </c>
       <c r="D1832" s="1" t="inlineStr">
@@ -59507,7 +59507,7 @@
       </c>
       <c r="B1847" s="1" t="inlineStr">
         <is>
-          <t>[fɛʁmiːtən] 说谎〈n.〉</t>
+          <t>[fɛʁmiːtən] 出租〈n.〉</t>
         </is>
       </c>
       <c r="C1847" s="1" t="inlineStr">
@@ -59517,7 +59517,7 @@
       </c>
       <c r="D1847" s="1" t="inlineStr">
         <is>
-          <t>说谎</t>
+          <t>出租</t>
         </is>
       </c>
       <c r="E1847" s="1" t="inlineStr">
@@ -59827,17 +59827,17 @@
       </c>
       <c r="B1857" s="1" t="inlineStr">
         <is>
-          <t>[abɡank] 下马；卸除卷〈n.m.〉</t>
+          <t>[abɡaŋ] 离开；退出；下降；损耗〈n.m.〉</t>
         </is>
       </c>
       <c r="C1857" s="1" t="inlineStr">
         <is>
-          <t>abɡank</t>
+          <t>abɡaŋ</t>
         </is>
       </c>
       <c r="D1857" s="1" t="inlineStr">
         <is>
-          <t>下马；卸除卷</t>
+          <t>离开；退出；下降；损耗</t>
         </is>
       </c>
       <c r="E1857" s="1" t="inlineStr">
@@ -59955,7 +59955,7 @@
       </c>
       <c r="B1861" s="1" t="inlineStr">
         <is>
-          <t>[vaːʁhaftɪç] 说实话的；诚实的；老实的〈adj.〉</t>
+          <t>[vaːʁhaftɪç] 真实的；确实的（亦作副词：真的，的确）〈adj.〉</t>
         </is>
       </c>
       <c r="C1861" s="1" t="inlineStr">
@@ -59965,7 +59965,7 @@
       </c>
       <c r="D1861" s="1" t="inlineStr">
         <is>
-          <t>说实话的；诚实的；老实的</t>
+          <t>真实的；确实的（亦作副词：真的，的确）</t>
         </is>
       </c>
       <c r="E1861" s="1" t="inlineStr">
@@ -59987,7 +59987,7 @@
       </c>
       <c r="B1862" s="1" t="inlineStr">
         <is>
-          <t>[beːzəsənhaɪt] 拥有；占有；所有〈n.f.〉</t>
+          <t>[beːzəsənhaɪt] 着迷；痴迷；着魔；执念〈n.f.〉</t>
         </is>
       </c>
       <c r="C1862" s="1" t="inlineStr">
@@ -59997,7 +59997,7 @@
       </c>
       <c r="D1862" s="1" t="inlineStr">
         <is>
-          <t>拥有；占有；所有</t>
+          <t>着迷；痴迷；着魔；执念</t>
         </is>
       </c>
       <c r="E1862" s="1" t="inlineStr">
@@ -60115,7 +60115,7 @@
       </c>
       <c r="B1866" s="1" t="inlineStr">
         <is>
-          <t>[feːʁaɪn] 移动；手势；动作〈n.〉</t>
+          <t>[feːʁaɪn] 协会；俱乐部；社团〈n.〉</t>
         </is>
       </c>
       <c r="C1866" s="1" t="inlineStr">
@@ -60125,7 +60125,7 @@
       </c>
       <c r="D1866" s="1" t="inlineStr">
         <is>
-          <t>移动；手势；动作</t>
+          <t>协会；俱乐部；社团</t>
         </is>
       </c>
       <c r="E1866" s="1" t="inlineStr">
@@ -60339,12 +60339,12 @@
       </c>
       <c r="B1873" s="1" t="inlineStr">
         <is>
-          <t>[voːlstant] 丰富；充足；大量〈n.m.〉</t>
+          <t>[voːlʃtant] 丰富；充足；大量〈n.m.〉</t>
         </is>
       </c>
       <c r="C1873" s="1" t="inlineStr">
         <is>
-          <t>voːlstant</t>
+          <t>voːlʃtant</t>
         </is>
       </c>
       <c r="D1873" s="1" t="inlineStr">
@@ -60371,7 +60371,7 @@
       </c>
       <c r="B1874" s="1" t="inlineStr">
         <is>
-          <t>[pɔltɐn] 风狂吹；咆哮〈v.〉</t>
+          <t>[pɔltɐn] 发出轰隆声；喧闹；砰砰作响〈v.〉</t>
         </is>
       </c>
       <c r="C1874" s="1" t="inlineStr">
@@ -60381,7 +60381,7 @@
       </c>
       <c r="D1874" s="1" t="inlineStr">
         <is>
-          <t>风狂吹；咆哮</t>
+          <t>发出轰隆声；喧闹；砰砰作响</t>
         </is>
       </c>
       <c r="E1874" s="1" t="inlineStr">
@@ -60531,7 +60531,7 @@
       </c>
       <c r="B1879" s="1" t="inlineStr">
         <is>
-          <t>[aktʊələ] 辩论；讨论；争论〈n.〉</t>
+          <t>[aktʊələ] 时事；热点话题〈n.〉</t>
         </is>
       </c>
       <c r="C1879" s="1" t="inlineStr">
@@ -60541,7 +60541,7 @@
       </c>
       <c r="D1879" s="1" t="inlineStr">
         <is>
-          <t>辩论；讨论；争论</t>
+          <t>时事；热点话题</t>
         </is>
       </c>
       <c r="E1879" s="1" t="inlineStr">
@@ -60787,7 +60787,7 @@
       </c>
       <c r="B1887" s="1" t="inlineStr">
         <is>
-          <t>[kʁuːk] 广口瓶；震动〈n.m.〉</t>
+          <t>[kʁuːk] 罐；壶；带柄水罐〈n.m.〉</t>
         </is>
       </c>
       <c r="C1887" s="1" t="inlineStr">
@@ -60797,7 +60797,7 @@
       </c>
       <c r="D1887" s="1" t="inlineStr">
         <is>
-          <t>广口瓶；震动</t>
+          <t>罐；壶；带柄水罐</t>
         </is>
       </c>
       <c r="E1887" s="1" t="inlineStr">
@@ -60851,7 +60851,7 @@
       </c>
       <c r="B1889" s="1" t="inlineStr">
         <is>
-          <t>[ʃpʊʁlɔs] 全体的；总的〈adj.〉</t>
+          <t>[ʃpʊʁlɔs] 无痕迹的；无踪影的〈adj.〉</t>
         </is>
       </c>
       <c r="C1889" s="1" t="inlineStr">
@@ -60861,7 +60861,7 @@
       </c>
       <c r="D1889" s="1" t="inlineStr">
         <is>
-          <t>全体的；总的</t>
+          <t>无痕迹的；无踪影的</t>
         </is>
       </c>
       <c r="E1889" s="1" t="inlineStr">
@@ -60915,7 +60915,7 @@
       </c>
       <c r="B1891" s="1" t="inlineStr">
         <is>
-          <t>[ʃnɛləs] 快速的；紧紧地〈adv.〉</t>
+          <t>[ʃnɛləs] 快的；快速的〈adv.〉</t>
         </is>
       </c>
       <c r="C1891" s="1" t="inlineStr">
@@ -60925,7 +60925,7 @@
       </c>
       <c r="D1891" s="1" t="inlineStr">
         <is>
-          <t>快速的；紧紧地</t>
+          <t>快的；快速的</t>
         </is>
       </c>
       <c r="E1891" s="1" t="inlineStr">
@@ -61203,7 +61203,7 @@
       </c>
       <c r="B1900" s="1" t="inlineStr">
         <is>
-          <t>[mɪtəndʁiːn] 权利；右边；正义〈adv.〉</t>
+          <t>[mɪtəndʁiːn] 正当中；就在中间〈adv.〉</t>
         </is>
       </c>
       <c r="C1900" s="1" t="inlineStr">
@@ -61213,7 +61213,7 @@
       </c>
       <c r="D1900" s="1" t="inlineStr">
         <is>
-          <t>权利；右边；正义</t>
+          <t>正当中；就在中间</t>
         </is>
       </c>
       <c r="E1900" s="1" t="inlineStr">
@@ -61331,7 +61331,7 @@
       </c>
       <c r="B1904" s="1" t="inlineStr">
         <is>
-          <t>[buːk] 弓〈n.m.〉</t>
+          <t>[buːk] 船头；车头；（动物）肩部〈n.m.〉</t>
         </is>
       </c>
       <c r="C1904" s="1" t="inlineStr">
@@ -61341,7 +61341,7 @@
       </c>
       <c r="D1904" s="1" t="inlineStr">
         <is>
-          <t>弓</t>
+          <t>船头；车头；（动物）肩部</t>
         </is>
       </c>
       <c r="E1904" s="1" t="inlineStr">
@@ -61363,7 +61363,7 @@
       </c>
       <c r="B1905" s="1" t="inlineStr">
         <is>
-          <t>[ʃpeːt͡sɪalɪstən] 钥匙；键；解答〈n.〉</t>
+          <t>[ʃpeːt͡sɪalɪstən] Spezialist 专家〈n.m.〉（词条应为单数）〈n.〉</t>
         </is>
       </c>
       <c r="C1905" s="1" t="inlineStr">
@@ -61373,7 +61373,7 @@
       </c>
       <c r="D1905" s="1" t="inlineStr">
         <is>
-          <t>钥匙；键；解答</t>
+          <t>Spezialist 专家〈n.m.〉（词条应为单数）</t>
         </is>
       </c>
       <c r="E1905" s="1" t="inlineStr">
@@ -61459,7 +61459,7 @@
       </c>
       <c r="B1908" s="1" t="inlineStr">
         <is>
-          <t>[t͡suːtatən] 材料；作料〈n.〉</t>
+          <t>[t͡suːtatən] 配料；佐料〈n.f.〉（Zutat的复数）〈n.〉</t>
         </is>
       </c>
       <c r="C1908" s="1" t="inlineStr">
@@ -61469,7 +61469,7 @@
       </c>
       <c r="D1908" s="1" t="inlineStr">
         <is>
-          <t>材料；作料</t>
+          <t>配料；佐料〈n.f.〉（Zutat的复数）</t>
         </is>
       </c>
       <c r="E1908" s="1" t="inlineStr">
@@ -61491,7 +61491,7 @@
       </c>
       <c r="B1909" s="1" t="inlineStr">
         <is>
-          <t>[ʊnzɪçtbaʁə] 玻璃天花板；玻璃天花板封顶〈adv.〉</t>
+          <t>[ʊnzɪçtbaʁə] 看不见的；无形的〈adv.〉</t>
         </is>
       </c>
       <c r="C1909" s="1" t="inlineStr">
@@ -61501,7 +61501,7 @@
       </c>
       <c r="D1909" s="1" t="inlineStr">
         <is>
-          <t>玻璃天花板；玻璃天花板封顶</t>
+          <t>看不见的；无形的</t>
         </is>
       </c>
       <c r="E1909" s="1" t="inlineStr">
@@ -61523,7 +61523,7 @@
       </c>
       <c r="B1910" s="1" t="inlineStr">
         <is>
-          <t>[zamstaɡabənt] 星期六〈n.m.〉</t>
+          <t>[zamstaɡabənt] 星期六晚上〈n.m.〉</t>
         </is>
       </c>
       <c r="C1910" s="1" t="inlineStr">
@@ -61533,7 +61533,7 @@
       </c>
       <c r="D1910" s="1" t="inlineStr">
         <is>
-          <t>星期六</t>
+          <t>星期六晚上</t>
         </is>
       </c>
       <c r="E1910" s="1" t="inlineStr">
@@ -61587,7 +61587,7 @@
       </c>
       <c r="B1912" s="1" t="inlineStr">
         <is>
-          <t>[fɛʁvøːnt] 优美；美味；讲究〈adv.〉</t>
+          <t>[fɛʁvøːnt] 娇生惯养的；被宠坏的〈adv.〉</t>
         </is>
       </c>
       <c r="C1912" s="1" t="inlineStr">
@@ -61597,7 +61597,7 @@
       </c>
       <c r="D1912" s="1" t="inlineStr">
         <is>
-          <t>优美；美味；讲究</t>
+          <t>娇生惯养的；被宠坏的</t>
         </is>
       </c>
       <c r="E1912" s="1" t="inlineStr">
@@ -61875,7 +61875,7 @@
       </c>
       <c r="B1921" s="1" t="inlineStr">
         <is>
-          <t>[t͡sʏndɐ] 保险丝；导火线；熔化；融合〈n.m.〉</t>
+          <t>[t͡sʏndɐ] 雷管；引信；点火器〈n.m.〉</t>
         </is>
       </c>
       <c r="C1921" s="1" t="inlineStr">
@@ -61885,7 +61885,7 @@
       </c>
       <c r="D1921" s="1" t="inlineStr">
         <is>
-          <t>保险丝；导火线；熔化；融合</t>
+          <t>雷管；引信；点火器</t>
         </is>
       </c>
       <c r="E1921" s="1" t="inlineStr">
@@ -61939,7 +61939,7 @@
       </c>
       <c r="B1923" s="1" t="inlineStr">
         <is>
-          <t>[ʃneːvɪtçən] 雪；积雪；下雪〈n.〉</t>
+          <t>[ʃneːvɪtçən] 白雪公主〈n.〉</t>
         </is>
       </c>
       <c r="C1923" s="1" t="inlineStr">
@@ -61949,7 +61949,7 @@
       </c>
       <c r="D1923" s="1" t="inlineStr">
         <is>
-          <t>雪；积雪；下雪</t>
+          <t>白雪公主</t>
         </is>
       </c>
       <c r="E1923" s="1" t="inlineStr">
@@ -61971,7 +61971,7 @@
       </c>
       <c r="B1924" s="1" t="inlineStr">
         <is>
-          <t>[paːʁɪzɐ] 巴黎；重楼属〈n.〉</t>
+          <t>[paːʁɪzɐ] 巴黎人〈n.〉</t>
         </is>
       </c>
       <c r="C1924" s="1" t="inlineStr">
@@ -61981,7 +61981,7 @@
       </c>
       <c r="D1924" s="1" t="inlineStr">
         <is>
-          <t>巴黎；重楼属</t>
+          <t>巴黎人</t>
         </is>
       </c>
       <c r="E1924" s="1" t="inlineStr">
@@ -62419,7 +62419,7 @@
       </c>
       <c r="B1938" s="1" t="inlineStr">
         <is>
-          <t>[bɛtlɐ] 使成乞丐〈n.m.〉</t>
+          <t>[bɛtlɐ] 乞丐〈n.m.〉</t>
         </is>
       </c>
       <c r="C1938" s="1" t="inlineStr">
@@ -62429,7 +62429,7 @@
       </c>
       <c r="D1938" s="1" t="inlineStr">
         <is>
-          <t>使成乞丐</t>
+          <t>乞丐</t>
         </is>
       </c>
       <c r="E1938" s="1" t="inlineStr">
@@ -62515,7 +62515,7 @@
       </c>
       <c r="B1941" s="1" t="inlineStr">
         <is>
-          <t>[ʁeːt͡səpt͡sjoːn] 旅馆；客栈〈n.f.〉</t>
+          <t>[ʁeːt͡səpt͡sjoːn] 接待处；前台〈n.f.〉</t>
         </is>
       </c>
       <c r="C1941" s="1" t="inlineStr">
@@ -62525,7 +62525,7 @@
       </c>
       <c r="D1941" s="1" t="inlineStr">
         <is>
-          <t>旅馆；客栈</t>
+          <t>接待处；前台</t>
         </is>
       </c>
       <c r="E1941" s="1" t="inlineStr">
@@ -62643,12 +62643,12 @@
       </c>
       <c r="B1945" s="1" t="inlineStr">
         <is>
-          <t>[plaːnʊnk] 计划的制订；策划；设计〈n.f.〉</t>
+          <t>[plaːnʊŋ] 计划的制订；策划；设计〈n.f.〉</t>
         </is>
       </c>
       <c r="C1945" s="1" t="inlineStr">
         <is>
-          <t>plaːnʊnk</t>
+          <t>plaːnʊŋ</t>
         </is>
       </c>
       <c r="D1945" s="1" t="inlineStr">
@@ -62707,7 +62707,7 @@
       </c>
       <c r="B1947" s="1" t="inlineStr">
         <is>
-          <t>[poːpə] 祭司；牧师；神父〈n.m.〉</t>
+          <t>[poːpə] 东正教神父；教皇〈n.m.〉</t>
         </is>
       </c>
       <c r="C1947" s="1" t="inlineStr">
@@ -62717,7 +62717,7 @@
       </c>
       <c r="D1947" s="1" t="inlineStr">
         <is>
-          <t>祭司；牧师；神父</t>
+          <t>东正教神父；教皇</t>
         </is>
       </c>
       <c r="E1947" s="1" t="inlineStr">
@@ -62771,7 +62771,7 @@
       </c>
       <c r="B1949" s="1" t="inlineStr">
         <is>
-          <t>[tankən] 得到；获得；变成〈v.〉</t>
+          <t>[tankən] 加油；加注燃料；充电〈v.〉</t>
         </is>
       </c>
       <c r="C1949" s="1" t="inlineStr">
@@ -62781,7 +62781,7 @@
       </c>
       <c r="D1949" s="1" t="inlineStr">
         <is>
-          <t>得到；获得；变成</t>
+          <t>加油；加注燃料；充电</t>
         </is>
       </c>
       <c r="E1949" s="1" t="inlineStr">
@@ -62963,7 +62963,7 @@
       </c>
       <c r="B1955" s="1" t="inlineStr">
         <is>
-          <t>[ablaʊf] 周期；循环；自行车〈n.m.〉</t>
+          <t>[ablaʊf] 过程；流程〈n.m.〉</t>
         </is>
       </c>
       <c r="C1955" s="1" t="inlineStr">
@@ -62973,7 +62973,7 @@
       </c>
       <c r="D1955" s="1" t="inlineStr">
         <is>
-          <t>周期；循环；自行车</t>
+          <t>过程；流程</t>
         </is>
       </c>
       <c r="E1955" s="1" t="inlineStr">
@@ -63123,7 +63123,7 @@
       </c>
       <c r="B1960" s="1" t="inlineStr">
         <is>
-          <t>[fɛʁklaɪdʊnk] 集市上卖的礼物；减阻装置；整流罩〈n.f.〉</t>
+          <t>[fɛʁklaɪdʊnk] 伪装；化装；戏服〈n.f.〉</t>
         </is>
       </c>
       <c r="C1960" s="1" t="inlineStr">
@@ -63133,7 +63133,7 @@
       </c>
       <c r="D1960" s="1" t="inlineStr">
         <is>
-          <t>集市上卖的礼物；减阻装置；整流罩</t>
+          <t>伪装；化装；戏服</t>
         </is>
       </c>
       <c r="E1960" s="1" t="inlineStr">
@@ -63219,7 +63219,7 @@
       </c>
       <c r="B1963" s="1" t="inlineStr">
         <is>
-          <t>[bɛvaɪstʏk] 块；片；篇〈n.〉</t>
+          <t>[bɛvaɪstʏk] 证据；物证〈n.〉</t>
         </is>
       </c>
       <c r="C1963" s="1" t="inlineStr">
@@ -63229,7 +63229,7 @@
       </c>
       <c r="D1963" s="1" t="inlineStr">
         <is>
-          <t>块；片；篇</t>
+          <t>证据；物证</t>
         </is>
       </c>
       <c r="E1963" s="1" t="inlineStr">
@@ -63251,7 +63251,7 @@
       </c>
       <c r="B1964" s="1" t="inlineStr">
         <is>
-          <t>[pfɛfɐ] 胡椒粉；胡椒；辣椒〈n.m.〉</t>
+          <t>[pfɛfɐ] 胡椒；胡椒粉〈n.m.〉〈n.m.〉</t>
         </is>
       </c>
       <c r="C1964" s="1" t="inlineStr">
@@ -63261,7 +63261,7 @@
       </c>
       <c r="D1964" s="1" t="inlineStr">
         <is>
-          <t>胡椒粉；胡椒；辣椒</t>
+          <t>胡椒；胡椒粉〈n.m.〉</t>
         </is>
       </c>
       <c r="E1964" s="1" t="inlineStr">
@@ -63315,12 +63315,12 @@
       </c>
       <c r="B1966" s="1" t="inlineStr">
         <is>
-          <t>[pɪtsbʊʁɡh] 匹兹堡〈n.〉</t>
+          <t>[pɪtsbʊʁɡ] 匹兹堡〈n.〉</t>
         </is>
       </c>
       <c r="C1966" s="1" t="inlineStr">
         <is>
-          <t>pɪtsbʊʁɡh</t>
+          <t>pɪtsbʊʁɡ</t>
         </is>
       </c>
       <c r="D1966" s="1" t="inlineStr">
@@ -63347,7 +63347,7 @@
       </c>
       <c r="B1967" s="1" t="inlineStr">
         <is>
-          <t>[ʃtaːdɪuːm] 阶段；舞台；场所〈n.〉</t>
+          <t>[ʃtaːdɪuːm] 阶段；时期〈n.〉〈n.〉</t>
         </is>
       </c>
       <c r="C1967" s="1" t="inlineStr">
@@ -63357,7 +63357,7 @@
       </c>
       <c r="D1967" s="1" t="inlineStr">
         <is>
-          <t>阶段；舞台；场所</t>
+          <t>阶段；时期〈n.〉</t>
         </is>
       </c>
       <c r="E1967" s="1" t="inlineStr">
@@ -63507,7 +63507,7 @@
       </c>
       <c r="B1972" s="1" t="inlineStr">
         <is>
-          <t>[yːbəʁvɛltɪɡənt] 引起幻觉的；使兴奋的〈adv.〉</t>
+          <t>[yːbəʁvɛltɪɡənt] 压倒性的；势不可挡的〈adv.〉</t>
         </is>
       </c>
       <c r="C1972" s="1" t="inlineStr">
@@ -63517,7 +63517,7 @@
       </c>
       <c r="D1972" s="1" t="inlineStr">
         <is>
-          <t>引起幻觉的；使兴奋的</t>
+          <t>压倒性的；势不可挡的</t>
         </is>
       </c>
       <c r="E1972" s="1" t="inlineStr">
@@ -63539,7 +63539,7 @@
       </c>
       <c r="B1973" s="1" t="inlineStr">
         <is>
-          <t>[teːləfɔnt͡sələ] 电话〈n.f.〉</t>
+          <t>[teːləfɔnt͡sələ] 电话亭〈n.f.〉</t>
         </is>
       </c>
       <c r="C1973" s="1" t="inlineStr">
@@ -63549,7 +63549,7 @@
       </c>
       <c r="D1973" s="1" t="inlineStr">
         <is>
-          <t>电话</t>
+          <t>电话亭</t>
         </is>
       </c>
       <c r="E1973" s="1" t="inlineStr">
@@ -63763,7 +63763,7 @@
       </c>
       <c r="B1980" s="1" t="inlineStr">
         <is>
-          <t>[feːləndə] 皮肤发育不全〈adv.〉</t>
+          <t>[feːləndə] 缺失的；缺少的；缺席的〈adv.〉</t>
         </is>
       </c>
       <c r="C1980" s="1" t="inlineStr">
@@ -63773,7 +63773,7 @@
       </c>
       <c r="D1980" s="1" t="inlineStr">
         <is>
-          <t>皮肤发育不全</t>
+          <t>缺失的；缺少的；缺席的</t>
         </is>
       </c>
       <c r="E1980" s="1" t="inlineStr">
@@ -63923,7 +63923,7 @@
       </c>
       <c r="B1985" s="1" t="inlineStr">
         <is>
-          <t>[ʃnɛkən] 腹足类；蜗牛〈n.〉</t>
+          <t>[ʃnɛkən] 蜗牛（Schnecke 的复数）〈n.pl.〉〈n.〉</t>
         </is>
       </c>
       <c r="C1985" s="1" t="inlineStr">
@@ -63933,7 +63933,7 @@
       </c>
       <c r="D1985" s="1" t="inlineStr">
         <is>
-          <t>腹足类；蜗牛</t>
+          <t>蜗牛（Schnecke 的复数）〈n.pl.〉</t>
         </is>
       </c>
       <c r="E1985" s="1" t="inlineStr">
@@ -64083,7 +64083,7 @@
       </c>
       <c r="B1990" s="1" t="inlineStr">
         <is>
-          <t>[zoːlɪdə] 声音；语音；吵闹〈adv.〉</t>
+          <t>[zoːlɪdə] 坚固的；可靠的；稳当的〈adv.〉</t>
         </is>
       </c>
       <c r="C1990" s="1" t="inlineStr">
@@ -64093,7 +64093,7 @@
       </c>
       <c r="D1990" s="1" t="inlineStr">
         <is>
-          <t>声音；语音；吵闹</t>
+          <t>坚固的；可靠的；稳当的</t>
         </is>
       </c>
       <c r="E1990" s="1" t="inlineStr">
@@ -64307,17 +64307,17 @@
       </c>
       <c r="B1997" s="1" t="inlineStr">
         <is>
-          <t>[ʁeːlɪɡɪœzə] 盲从；偏见；偏执的行为〈adv.〉</t>
+          <t>[ʁeliɡjøːzə] 宗教的；虔诚的〈adv.〉</t>
         </is>
       </c>
       <c r="C1997" s="1" t="inlineStr">
         <is>
-          <t>ʁeːlɪɡɪœzə</t>
+          <t>ʁeliɡjøːzə</t>
         </is>
       </c>
       <c r="D1997" s="1" t="inlineStr">
         <is>
-          <t>盲从；偏见；偏执的行为</t>
+          <t>宗教的；虔诚的</t>
         </is>
       </c>
       <c r="E1997" s="1" t="inlineStr">
@@ -64371,7 +64371,7 @@
       </c>
       <c r="B1999" s="1" t="inlineStr">
         <is>
-          <t>[dɛpʁɪmiːʁənt] 强拍；下降；低沉〈adv.〉</t>
+          <t>[dɛpʁɪmiːʁənt] 令人沮丧的；使人抑郁的〈adv.〉</t>
         </is>
       </c>
       <c r="C1999" s="1" t="inlineStr">
@@ -64381,7 +64381,7 @@
       </c>
       <c r="D1999" s="1" t="inlineStr">
         <is>
-          <t>强拍；下降；低沉</t>
+          <t>令人沮丧的；使人抑郁的</t>
         </is>
       </c>
       <c r="E1999" s="1" t="inlineStr">
@@ -64595,7 +64595,7 @@
       </c>
       <c r="B2006" s="1" t="inlineStr">
         <is>
-          <t>[kʊʁt͡səs] 浸；降下；把伸入〈adv.〉</t>
+          <t>[kʊʁt͡səs] 短的〈adv.〉</t>
         </is>
       </c>
       <c r="C2006" s="1" t="inlineStr">
@@ -64605,7 +64605,7 @@
       </c>
       <c r="D2006" s="1" t="inlineStr">
         <is>
-          <t>浸；降下；把伸入</t>
+          <t>短的</t>
         </is>
       </c>
       <c r="E2006" s="1" t="inlineStr">
@@ -64659,7 +64659,7 @@
       </c>
       <c r="B2008" s="1" t="inlineStr">
         <is>
-          <t>[ɔksfɔʁt] 牛津阶〈n.〉</t>
+          <t>[ɔksfɔʁt] 牛津〈n.〉</t>
         </is>
       </c>
       <c r="C2008" s="1" t="inlineStr">
@@ -64669,7 +64669,7 @@
       </c>
       <c r="D2008" s="1" t="inlineStr">
         <is>
-          <t>牛津阶</t>
+          <t>牛津</t>
         </is>
       </c>
       <c r="E2008" s="1" t="inlineStr">
@@ -64723,7 +64723,7 @@
       </c>
       <c r="B2010" s="1" t="inlineStr">
         <is>
-          <t>[beːzət͡sʊnk] 充填物；填料；加填；填充〈n.f.〉</t>
+          <t>[beːzət͡sʊnk] 占领；占据；演员阵容；人员配备〈n.f.〉</t>
         </is>
       </c>
       <c r="C2010" s="1" t="inlineStr">
@@ -64733,7 +64733,7 @@
       </c>
       <c r="D2010" s="1" t="inlineStr">
         <is>
-          <t>充填物；填料；加填；填充</t>
+          <t>占领；占据；演员阵容；人员配备</t>
         </is>
       </c>
       <c r="E2010" s="1" t="inlineStr">
@@ -64819,7 +64819,7 @@
       </c>
       <c r="B2013" s="1" t="inlineStr">
         <is>
-          <t>[haʊpt] 飞行员；领航员；航船者〈n.〉</t>
+          <t>[haʊpt] 头；头部〈n.〉</t>
         </is>
       </c>
       <c r="C2013" s="1" t="inlineStr">
@@ -64829,7 +64829,7 @@
       </c>
       <c r="D2013" s="1" t="inlineStr">
         <is>
-          <t>飞行员；领航员；航船者</t>
+          <t>头；头部</t>
         </is>
       </c>
       <c r="E2013" s="1" t="inlineStr">
@@ -65171,7 +65171,7 @@
       </c>
       <c r="B2024" s="1" t="inlineStr">
         <is>
-          <t>[ɔʏlə] 猫头鹰；走私〈n.f.〉</t>
+          <t>[ɔʏlə] 猫头鹰；枭〈n.f.〉</t>
         </is>
       </c>
       <c r="C2024" s="1" t="inlineStr">
@@ -65181,7 +65181,7 @@
       </c>
       <c r="D2024" s="1" t="inlineStr">
         <is>
-          <t>猫头鹰；走私</t>
+          <t>猫头鹰；枭</t>
         </is>
       </c>
       <c r="E2024" s="1" t="inlineStr">
@@ -65427,7 +65427,7 @@
       </c>
       <c r="B2032" s="1" t="inlineStr">
         <is>
-          <t>[loːkalə] 延长；扩充；范围〈adv.〉</t>
+          <t>[loːkalə] 当地的；本地的；局部的〈adv.〉</t>
         </is>
       </c>
       <c r="C2032" s="1" t="inlineStr">
@@ -65437,7 +65437,7 @@
       </c>
       <c r="D2032" s="1" t="inlineStr">
         <is>
-          <t>延长；扩充；范围</t>
+          <t>当地的；本地的；局部的</t>
         </is>
       </c>
       <c r="E2032" s="1" t="inlineStr">
@@ -65683,7 +65683,7 @@
       </c>
       <c r="B2040" s="1" t="inlineStr">
         <is>
-          <t>[zɪçtkɔntakt] 视觉的；视力的；视觉性记忆优势者〈n.m.〉</t>
+          <t>[zɪçtkɔntakt] 目光接触；视线接触〈n.m.〉</t>
         </is>
       </c>
       <c r="C2040" s="1" t="inlineStr">
@@ -65693,7 +65693,7 @@
       </c>
       <c r="D2040" s="1" t="inlineStr">
         <is>
-          <t>视觉的；视力的；视觉性记忆优势者</t>
+          <t>目光接触；视线接触</t>
         </is>
       </c>
       <c r="E2040" s="1" t="inlineStr">
@@ -65875,12 +65875,12 @@
       </c>
       <c r="B2046" s="1" t="inlineStr">
         <is>
-          <t>[bɛvəʁbʊnk] 应用；申请；志愿书〈n.f.〉</t>
+          <t>[bɛvəʁbʊŋ] 应用；申请；志愿书〈n.f.〉</t>
         </is>
       </c>
       <c r="C2046" s="1" t="inlineStr">
         <is>
-          <t>bɛvəʁbʊnk</t>
+          <t>bɛvəʁbʊŋ</t>
         </is>
       </c>
       <c r="D2046" s="1" t="inlineStr">
@@ -66195,7 +66195,7 @@
       </c>
       <c r="B2056" s="1" t="inlineStr">
         <is>
-          <t>[aɪnɡəbaʊt] 综合的；完整的〈adv.〉</t>
+          <t>[aɪnɡəbaʊt] 内置的；嵌入的；固定的〈adv.〉</t>
         </is>
       </c>
       <c r="C2056" s="1" t="inlineStr">
@@ -66205,7 +66205,7 @@
       </c>
       <c r="D2056" s="1" t="inlineStr">
         <is>
-          <t>综合的；完整的</t>
+          <t>内置的；嵌入的；固定的</t>
         </is>
       </c>
       <c r="E2056" s="1" t="inlineStr">
@@ -66227,7 +66227,7 @@
       </c>
       <c r="B2057" s="1" t="inlineStr">
         <is>
-          <t>[ɔfənɐ] 壁炉〈adv.〉</t>
+          <t>[ɔfənɐ] 更开放的；更敞开的〈adv.〉</t>
         </is>
       </c>
       <c r="C2057" s="1" t="inlineStr">
@@ -66237,7 +66237,7 @@
       </c>
       <c r="D2057" s="1" t="inlineStr">
         <is>
-          <t>壁炉</t>
+          <t>更开放的；更敞开的</t>
         </is>
       </c>
       <c r="E2057" s="1" t="inlineStr">
@@ -66515,7 +66515,7 @@
       </c>
       <c r="B2066" s="1" t="inlineStr">
         <is>
-          <t>[anzaɡə] 声音；嗓音；嗓子〈n.f.〉</t>
+          <t>[anzaɡə] 通知；广播；宣告〈n.f.〉</t>
         </is>
       </c>
       <c r="C2066" s="1" t="inlineStr">
@@ -66525,7 +66525,7 @@
       </c>
       <c r="D2066" s="1" t="inlineStr">
         <is>
-          <t>声音；嗓音；嗓子</t>
+          <t>通知；广播；宣告</t>
         </is>
       </c>
       <c r="E2066" s="1" t="inlineStr">
@@ -66643,7 +66643,7 @@
       </c>
       <c r="B2070" s="1" t="inlineStr">
         <is>
-          <t>[fɔʁləzʊnk] 演讲；谴责；讲稿〈n.f.〉</t>
+          <t>[fɔʁləzʊnk] 讲课；讲座〈f.〉〈n.f.〉</t>
         </is>
       </c>
       <c r="C2070" s="1" t="inlineStr">
@@ -66653,7 +66653,7 @@
       </c>
       <c r="D2070" s="1" t="inlineStr">
         <is>
-          <t>演讲；谴责；讲稿</t>
+          <t>讲课；讲座〈f.〉</t>
         </is>
       </c>
       <c r="E2070" s="1" t="inlineStr">
@@ -66739,7 +66739,7 @@
       </c>
       <c r="B2073" s="1" t="inlineStr">
         <is>
-          <t>[lɛnkʁaːt] 掌舵；操纵；指导〈n.〉</t>
+          <t>[lɛnkʁaːt] 方向盘；转向盘〈n.〉</t>
         </is>
       </c>
       <c r="C2073" s="1" t="inlineStr">
@@ -66749,7 +66749,7 @@
       </c>
       <c r="D2073" s="1" t="inlineStr">
         <is>
-          <t>掌舵；操纵；指导</t>
+          <t>方向盘；转向盘</t>
         </is>
       </c>
       <c r="E2073" s="1" t="inlineStr">
@@ -66803,7 +66803,7 @@
       </c>
       <c r="B2075" s="1" t="inlineStr">
         <is>
-          <t>[ɡʁʏndɐ] 漂浮者；漂浮物〈n.m.〉</t>
+          <t>[ɡʁʏndɐ] 创始人；缔造者〈n.m.〉</t>
         </is>
       </c>
       <c r="C2075" s="1" t="inlineStr">
@@ -66813,7 +66813,7 @@
       </c>
       <c r="D2075" s="1" t="inlineStr">
         <is>
-          <t>漂浮者；漂浮物</t>
+          <t>创始人；缔造者</t>
         </is>
       </c>
       <c r="E2075" s="1" t="inlineStr">
@@ -66931,7 +66931,7 @@
       </c>
       <c r="B2079" s="1" t="inlineStr">
         <is>
-          <t>[ʃtɛlfəʁtʁətɐ] 秒；瞬间；第二名〈n.m.〉</t>
+          <t>[ʃtɛlfəʁtʁətɐ] 代理人；副手；代表〈n.m.〉</t>
         </is>
       </c>
       <c r="C2079" s="1" t="inlineStr">
@@ -66941,7 +66941,7 @@
       </c>
       <c r="D2079" s="1" t="inlineStr">
         <is>
-          <t>秒；瞬间；第二名</t>
+          <t>代理人；副手；代表</t>
         </is>
       </c>
       <c r="E2079" s="1" t="inlineStr">
@@ -67603,7 +67603,7 @@
       </c>
       <c r="B2100" s="1" t="inlineStr">
         <is>
-          <t>[fleːdəʁmaʊs] 蝙蝠；眨眼；成批〈n.f.〉</t>
+          <t>[fleːdəʁmaʊs] 蝙蝠〈n.f.〉</t>
         </is>
       </c>
       <c r="C2100" s="1" t="inlineStr">
@@ -67613,7 +67613,7 @@
       </c>
       <c r="D2100" s="1" t="inlineStr">
         <is>
-          <t>蝙蝠；眨眼；成批</t>
+          <t>蝙蝠</t>
         </is>
       </c>
       <c r="E2100" s="1" t="inlineStr">
@@ -67955,7 +67955,7 @@
       </c>
       <c r="B2111" s="1" t="inlineStr">
         <is>
-          <t>[aɪnʁaɪçən] 锉；琢磨；锉屑；编档〈n.〉</t>
+          <t>[aɪnʁaɪçən] 提交；递交；呈递〈n.〉</t>
         </is>
       </c>
       <c r="C2111" s="1" t="inlineStr">
@@ -67965,7 +67965,7 @@
       </c>
       <c r="D2111" s="1" t="inlineStr">
         <is>
-          <t>锉；琢磨；锉屑；编档</t>
+          <t>提交；递交；呈递</t>
         </is>
       </c>
       <c r="E2111" s="1" t="inlineStr">
@@ -68147,7 +68147,7 @@
       </c>
       <c r="B2117" s="1" t="inlineStr">
         <is>
-          <t>[pfanə] 勺子；以勺掬〈n.f.〉</t>
+          <t>[pfanə] 平底锅；锅〈n.f.〉</t>
         </is>
       </c>
       <c r="C2117" s="1" t="inlineStr">
@@ -68157,7 +68157,7 @@
       </c>
       <c r="D2117" s="1" t="inlineStr">
         <is>
-          <t>勺子；以勺掬</t>
+          <t>平底锅；锅</t>
         </is>
       </c>
       <c r="E2117" s="1" t="inlineStr">
@@ -68211,7 +68211,7 @@
       </c>
       <c r="B2119" s="1" t="inlineStr">
         <is>
-          <t>[fʁɔʏndlɪçkaɪt] 高兴；快活〈n.f.〉</t>
+          <t>[fʁɔʏndlɪçkaɪt] 友好；亲切；和蔼〈n.f.〉</t>
         </is>
       </c>
       <c r="C2119" s="1" t="inlineStr">
@@ -68221,7 +68221,7 @@
       </c>
       <c r="D2119" s="1" t="inlineStr">
         <is>
-          <t>高兴；快活</t>
+          <t>友好；亲切；和蔼</t>
         </is>
       </c>
       <c r="E2119" s="1" t="inlineStr">
@@ -68307,7 +68307,7 @@
       </c>
       <c r="B2122" s="1" t="inlineStr">
         <is>
-          <t>[uːnəʁhœʁt] 显著地；显眼地〈adv.〉</t>
+          <t>[uːnəʁhœʁt] 骇人听闻的；闻所未闻的；空前的〈adv.〉</t>
         </is>
       </c>
       <c r="C2122" s="1" t="inlineStr">
@@ -68317,7 +68317,7 @@
       </c>
       <c r="D2122" s="1" t="inlineStr">
         <is>
-          <t>显著地；显眼地</t>
+          <t>骇人听闻的；闻所未闻的；空前的</t>
         </is>
       </c>
       <c r="E2122" s="1" t="inlineStr">
@@ -68659,7 +68659,7 @@
       </c>
       <c r="B2133" s="1" t="inlineStr">
         <is>
-          <t>[ɡʁɛːbɐ] 挖掘者〈n.m.〉</t>
+          <t>[ɡʁɛːbɐ] 坟墓；墓穴〈n.m.〉</t>
         </is>
       </c>
       <c r="C2133" s="1" t="inlineStr">
@@ -68669,7 +68669,7 @@
       </c>
       <c r="D2133" s="1" t="inlineStr">
         <is>
-          <t>挖掘者</t>
+          <t>坟墓；墓穴</t>
         </is>
       </c>
       <c r="E2133" s="1" t="inlineStr">
@@ -68787,7 +68787,7 @@
       </c>
       <c r="B2137" s="1" t="inlineStr">
         <is>
-          <t>[bɛvɛltɪɡən] 主人；硕士；大师〈v.〉</t>
+          <t>[bɛvɛltɪɡən] 克服；战胜；处理好；应付〈v.〉</t>
         </is>
       </c>
       <c r="C2137" s="1" t="inlineStr">
@@ -68797,7 +68797,7 @@
       </c>
       <c r="D2137" s="1" t="inlineStr">
         <is>
-          <t>主人；硕士；大师</t>
+          <t>克服；战胜；处理好；应付</t>
         </is>
       </c>
       <c r="E2137" s="1" t="inlineStr">
@@ -69043,7 +69043,7 @@
       </c>
       <c r="B2145" s="1" t="inlineStr">
         <is>
-          <t>[ɪndɪana] 亚利桑那州〈n.〉</t>
+          <t>[ɪndɪana] 印第安纳州〈n.〉</t>
         </is>
       </c>
       <c r="C2145" s="1" t="inlineStr">
@@ -69053,7 +69053,7 @@
       </c>
       <c r="D2145" s="1" t="inlineStr">
         <is>
-          <t>亚利桑那州</t>
+          <t>印第安纳州</t>
         </is>
       </c>
       <c r="E2145" s="1" t="inlineStr">
@@ -69107,7 +69107,7 @@
       </c>
       <c r="B2147" s="1" t="inlineStr">
         <is>
-          <t>[vʏʁdɪɡən] 认为；相信〈v.〉</t>
+          <t>[vʏʁdɪɡən] 赞赏；尊重；评价〈v.〉</t>
         </is>
       </c>
       <c r="C2147" s="1" t="inlineStr">
@@ -69117,7 +69117,7 @@
       </c>
       <c r="D2147" s="1" t="inlineStr">
         <is>
-          <t>认为；相信</t>
+          <t>赞赏；尊重；评价</t>
         </is>
       </c>
       <c r="E2147" s="1" t="inlineStr">
@@ -69139,7 +69139,7 @@
       </c>
       <c r="B2148" s="1" t="inlineStr">
         <is>
-          <t>[fɔʁaːt] 补给；供给〈n.m.〉</t>
+          <t>[fɔʁaːt] 储备；库存；存货〈m.〉〈n.m.〉</t>
         </is>
       </c>
       <c r="C2148" s="1" t="inlineStr">
@@ -69149,7 +69149,7 @@
       </c>
       <c r="D2148" s="1" t="inlineStr">
         <is>
-          <t>补给；供给</t>
+          <t>储备；库存；存货〈m.〉</t>
         </is>
       </c>
       <c r="E2148" s="1" t="inlineStr">
@@ -69171,7 +69171,7 @@
       </c>
       <c r="B2149" s="1" t="inlineStr">
         <is>
-          <t>[tʁɔknən] 天气；气象〈v.〉</t>
+          <t>[tʁɔknən] （使）干燥；晾干；变干〈v.〉</t>
         </is>
       </c>
       <c r="C2149" s="1" t="inlineStr">
@@ -69181,7 +69181,7 @@
       </c>
       <c r="D2149" s="1" t="inlineStr">
         <is>
-          <t>天气；气象</t>
+          <t>（使）干燥；晾干；变干</t>
         </is>
       </c>
       <c r="E2149" s="1" t="inlineStr">
@@ -69555,7 +69555,7 @@
       </c>
       <c r="B2161" s="1" t="inlineStr">
         <is>
-          <t>[bluːtɪɡə] 暴力的；猛烈的；激烈的〈adv.〉</t>
+          <t>[bluːtɪɡə] blutig 的变格形式，非独立词条〈adv.〉</t>
         </is>
       </c>
       <c r="C2161" s="1" t="inlineStr">
@@ -69565,7 +69565,7 @@
       </c>
       <c r="D2161" s="1" t="inlineStr">
         <is>
-          <t>暴力的；猛烈的；激烈的</t>
+          <t>blutig 的变格形式，非独立词条</t>
         </is>
       </c>
       <c r="E2161" s="1" t="inlineStr">
@@ -69811,7 +69811,7 @@
       </c>
       <c r="B2169" s="1" t="inlineStr">
         <is>
-          <t>[liːbənsvʏʁdɪç] 讨好地；奉承地〈adv.〉</t>
+          <t>[liːbənsvʏʁdɪç] 亲切的；和蔼可亲的；可爱的〈adv.〉</t>
         </is>
       </c>
       <c r="C2169" s="1" t="inlineStr">
@@ -69821,7 +69821,7 @@
       </c>
       <c r="D2169" s="1" t="inlineStr">
         <is>
-          <t>讨好地；奉承地</t>
+          <t>亲切的；和蔼可亲的；可爱的</t>
         </is>
       </c>
       <c r="E2169" s="1" t="inlineStr">
@@ -69907,7 +69907,7 @@
       </c>
       <c r="B2172" s="1" t="inlineStr">
         <is>
-          <t>[beːzɔʁɡnɪs] 领悟力；忧虑感〈n.f.〉</t>
+          <t>[beːzɔʁɡnɪs] 忧虑；担心；不安〈n.f.〉</t>
         </is>
       </c>
       <c r="C2172" s="1" t="inlineStr">
@@ -69917,7 +69917,7 @@
       </c>
       <c r="D2172" s="1" t="inlineStr">
         <is>
-          <t>领悟力；忧虑感</t>
+          <t>忧虑；担心；不安</t>
         </is>
       </c>
       <c r="E2172" s="1" t="inlineStr">
@@ -70099,7 +70099,7 @@
       </c>
       <c r="B2178" s="1" t="inlineStr">
         <is>
-          <t>[t͡suːʁʏkfaːʁən] 驾车；快车道；推进力〈v.〉</t>
+          <t>[t͡suːʁʏkfaːʁən] 驶回；返回〈v.〉</t>
         </is>
       </c>
       <c r="C2178" s="1" t="inlineStr">
@@ -70109,7 +70109,7 @@
       </c>
       <c r="D2178" s="1" t="inlineStr">
         <is>
-          <t>驾车；快车道；推进力</t>
+          <t>驶回；返回</t>
         </is>
       </c>
       <c r="E2178" s="1" t="inlineStr">
@@ -70163,7 +70163,7 @@
       </c>
       <c r="B2180" s="1" t="inlineStr">
         <is>
-          <t>[beːzət͡sən] 针〈n.〉</t>
+          <t>[beːzət͡sən] 占领；占据；占用〈n.〉</t>
         </is>
       </c>
       <c r="C2180" s="1" t="inlineStr">
@@ -70173,7 +70173,7 @@
       </c>
       <c r="D2180" s="1" t="inlineStr">
         <is>
-          <t>针</t>
+          <t>占领；占据；占用</t>
         </is>
       </c>
       <c r="E2180" s="1" t="inlineStr">
@@ -70387,7 +70387,7 @@
       </c>
       <c r="B2187" s="1" t="inlineStr">
         <is>
-          <t>[fɔʁɡətɔʏʃt] 假；赝品；骗子〈adv.〉</t>
+          <t>[fɔʁɡətɔʏʃt] 假装的；伪装的〈adv.〉</t>
         </is>
       </c>
       <c r="C2187" s="1" t="inlineStr">
@@ -70397,7 +70397,7 @@
       </c>
       <c r="D2187" s="1" t="inlineStr">
         <is>
-          <t>假；赝品；骗子</t>
+          <t>假装的；伪装的</t>
         </is>
       </c>
       <c r="E2187" s="1" t="inlineStr">
@@ -70419,7 +70419,7 @@
       </c>
       <c r="B2188" s="1" t="inlineStr">
         <is>
-          <t>[zaːtəliːt] 陪静脉；陪病部〈n.m.〉</t>
+          <t>[zaːtəliːt] 卫星；人造卫星；附庸国〈n.m.〉</t>
         </is>
       </c>
       <c r="C2188" s="1" t="inlineStr">
@@ -70429,7 +70429,7 @@
       </c>
       <c r="D2188" s="1" t="inlineStr">
         <is>
-          <t>陪静脉；陪病部</t>
+          <t>卫星；人造卫星；附庸国</t>
         </is>
       </c>
       <c r="E2188" s="1" t="inlineStr">
@@ -70451,7 +70451,7 @@
       </c>
       <c r="B2189" s="1" t="inlineStr">
         <is>
-          <t>[ʃiːfɡeːən] 逆火；回火〈v.〉</t>
+          <t>[ʃiːfɡeːən] 出错；失败；出岔子〈v.〉</t>
         </is>
       </c>
       <c r="C2189" s="1" t="inlineStr">
@@ -70461,7 +70461,7 @@
       </c>
       <c r="D2189" s="1" t="inlineStr">
         <is>
-          <t>逆火；回火</t>
+          <t>出错；失败；出岔子</t>
         </is>
       </c>
       <c r="E2189" s="1" t="inlineStr">
@@ -70483,7 +70483,7 @@
       </c>
       <c r="B2190" s="1" t="inlineStr">
         <is>
-          <t>[tɛːtɔviːʁʊnk] 归营号；连续有节奏的敲击；文身〈n.f.〉</t>
+          <t>[tɛːtɔviːʁʊnk] 文身；刺青〈n.f.〉</t>
         </is>
       </c>
       <c r="C2190" s="1" t="inlineStr">
@@ -70493,7 +70493,7 @@
       </c>
       <c r="D2190" s="1" t="inlineStr">
         <is>
-          <t>归营号；连续有节奏的敲击；文身</t>
+          <t>文身；刺青</t>
         </is>
       </c>
       <c r="E2190" s="1" t="inlineStr">
@@ -70739,7 +70739,7 @@
       </c>
       <c r="B2198" s="1" t="inlineStr">
         <is>
-          <t>[ɔfənbaʁʊnk] 外观；显然；明白〈n.f.〉</t>
+          <t>[ɔfənbaʁʊnk] 启示；揭示；天启〈n.f.〉</t>
         </is>
       </c>
       <c r="C2198" s="1" t="inlineStr">
@@ -70749,7 +70749,7 @@
       </c>
       <c r="D2198" s="1" t="inlineStr">
         <is>
-          <t>外观；显然；明白</t>
+          <t>启示；揭示；天启</t>
         </is>
       </c>
       <c r="E2198" s="1" t="inlineStr">
@@ -71059,7 +71059,7 @@
       </c>
       <c r="B2208" s="1" t="inlineStr">
         <is>
-          <t>[bakbɔʁt] 港口；埠；舱门〈n.〉</t>
+          <t>[bakbɔʁt] 左舷〈n.〉</t>
         </is>
       </c>
       <c r="C2208" s="1" t="inlineStr">
@@ -71069,7 +71069,7 @@
       </c>
       <c r="D2208" s="1" t="inlineStr">
         <is>
-          <t>港口；埠；舱门</t>
+          <t>左舷</t>
         </is>
       </c>
       <c r="E2208" s="1" t="inlineStr">
@@ -71091,7 +71091,7 @@
       </c>
       <c r="B2209" s="1" t="inlineStr">
         <is>
-          <t>[bʊənɔs] 布宜诺斯艾利斯〈n.〉</t>
+          <t>[bʊənɔs] 无独立词条，仅见于 Buenos Aires（布宜诺斯艾利斯）〈n.〉</t>
         </is>
       </c>
       <c r="C2209" s="1" t="inlineStr">
@@ -71101,7 +71101,7 @@
       </c>
       <c r="D2209" s="1" t="inlineStr">
         <is>
-          <t>布宜诺斯艾利斯</t>
+          <t>无独立词条，仅见于 Buenos Aires（布宜诺斯艾利斯）</t>
         </is>
       </c>
       <c r="E2209" s="1" t="inlineStr">
@@ -71283,7 +71283,7 @@
       </c>
       <c r="B2215" s="1" t="inlineStr">
         <is>
-          <t>[kaːn] 光；光亮；灯〈n.m.〉</t>
+          <t>[kaːn] 小船；平底船；驳船〈n.m.〉</t>
         </is>
       </c>
       <c r="C2215" s="1" t="inlineStr">
@@ -71293,7 +71293,7 @@
       </c>
       <c r="D2215" s="1" t="inlineStr">
         <is>
-          <t>光；光亮；灯</t>
+          <t>小船；平底船；驳船</t>
         </is>
       </c>
       <c r="E2215" s="1" t="inlineStr">
@@ -71347,7 +71347,7 @@
       </c>
       <c r="B2217" s="1" t="inlineStr">
         <is>
-          <t>[kʁaftfəlt] 领域；田地；场地〈n.〉</t>
+          <t>[kʁaftfəlt] 力场〈n.〉</t>
         </is>
       </c>
       <c r="C2217" s="1" t="inlineStr">
@@ -71357,7 +71357,7 @@
       </c>
       <c r="D2217" s="1" t="inlineStr">
         <is>
-          <t>领域；田地；场地</t>
+          <t>力场</t>
         </is>
       </c>
       <c r="E2217" s="1" t="inlineStr">
@@ -71443,7 +71443,7 @@
       </c>
       <c r="B2220" s="1" t="inlineStr">
         <is>
-          <t>[ʃtʁoːmaʊsfal] 力；体力；力量〈n.m.〉</t>
+          <t>[ʃtʁoːmaʊsfal] 停电；断电〈n.m.〉</t>
         </is>
       </c>
       <c r="C2220" s="1" t="inlineStr">
@@ -71453,7 +71453,7 @@
       </c>
       <c r="D2220" s="1" t="inlineStr">
         <is>
-          <t>力；体力；力量</t>
+          <t>停电；断电</t>
         </is>
       </c>
       <c r="E2220" s="1" t="inlineStr">
@@ -71539,7 +71539,7 @@
       </c>
       <c r="B2223" s="1" t="inlineStr">
         <is>
-          <t>[fɛʁzənkən] 甲板排水孔；泄水口〈v.〉</t>
+          <t>[fɛʁzənkən] 使下沉；淹没〈v.〉</t>
         </is>
       </c>
       <c r="C2223" s="1" t="inlineStr">
@@ -71549,7 +71549,7 @@
       </c>
       <c r="D2223" s="1" t="inlineStr">
         <is>
-          <t>甲板排水孔；泄水口</t>
+          <t>使下沉；淹没</t>
         </is>
       </c>
       <c r="E2223" s="1" t="inlineStr">
@@ -71795,7 +71795,7 @@
       </c>
       <c r="B2231" s="1" t="inlineStr">
         <is>
-          <t>[aɪnɡətʁaɡən] 持会员证的；彻底的；真正的〈v.〉</t>
+          <t>[aɪnɡətʁaɡən] 已登记的；注册的；记录在案的〈v.〉</t>
         </is>
       </c>
       <c r="C2231" s="1" t="inlineStr">
@@ -71805,7 +71805,7 @@
       </c>
       <c r="D2231" s="1" t="inlineStr">
         <is>
-          <t>持会员证的；彻底的；真正的</t>
+          <t>已登记的；注册的；记录在案的</t>
         </is>
       </c>
       <c r="E2231" s="1" t="inlineStr">
@@ -71987,7 +71987,7 @@
       </c>
       <c r="B2237" s="1" t="inlineStr">
         <is>
-          <t>[ɡeːt͡siːlt] 目标\目的〈adj.〉</t>
+          <t>[ɡeːt͡siːlt] 有针对性的；蓄意的〈adj.〉〈adj.〉</t>
         </is>
       </c>
       <c r="C2237" s="1" t="inlineStr">
@@ -71997,7 +71997,7 @@
       </c>
       <c r="D2237" s="1" t="inlineStr">
         <is>
-          <t>目标\目的</t>
+          <t>有针对性的；蓄意的〈adj.〉</t>
         </is>
       </c>
       <c r="E2237" s="1" t="inlineStr">
@@ -72275,7 +72275,7 @@
       </c>
       <c r="B2246" s="1" t="inlineStr">
         <is>
-          <t>[uːnənt͡ʃiːdən] 带子；线；鞋带〈n.〉</t>
+          <t>[uːnənt͡ʃiːdən] 平局；不分胜负；未决〈n.〉</t>
         </is>
       </c>
       <c r="C2246" s="1" t="inlineStr">
@@ -72285,7 +72285,7 @@
       </c>
       <c r="D2246" s="1" t="inlineStr">
         <is>
-          <t>带子；线；鞋带</t>
+          <t>平局；不分胜负；未决</t>
         </is>
       </c>
       <c r="E2246" s="1" t="inlineStr">
@@ -72307,7 +72307,7 @@
       </c>
       <c r="B2247" s="1" t="inlineStr">
         <is>
-          <t>[aʊsfəʁkaʊft] 卖完；出卖；背叛〈adv.〉</t>
+          <t>[aʊsfəʁkaʊft] 售罄的；卖完的〈adv.〉</t>
         </is>
       </c>
       <c r="C2247" s="1" t="inlineStr">
@@ -72317,7 +72317,7 @@
       </c>
       <c r="D2247" s="1" t="inlineStr">
         <is>
-          <t>卖完；出卖；背叛</t>
+          <t>售罄的；卖完的</t>
         </is>
       </c>
       <c r="E2247" s="1" t="inlineStr">
@@ -72499,7 +72499,7 @@
       </c>
       <c r="B2253" s="1" t="inlineStr">
         <is>
-          <t>[teːləfɔnbuːx] 电话〈n.〉</t>
+          <t>[teːləfɔnbuːx] 电话簿；电话号码簿〈n.〉</t>
         </is>
       </c>
       <c r="C2253" s="1" t="inlineStr">
@@ -72509,7 +72509,7 @@
       </c>
       <c r="D2253" s="1" t="inlineStr">
         <is>
-          <t>电话</t>
+          <t>电话簿；电话号码簿</t>
         </is>
       </c>
       <c r="E2253" s="1" t="inlineStr">
@@ -73011,7 +73011,7 @@
       </c>
       <c r="B2269" s="1" t="inlineStr">
         <is>
-          <t>[aɪnlaɪtən] 倾销；倾倒；倾泻；填埋〈n.〉</t>
+          <t>[aɪnlaɪtən] 开始；着手；引导〈n.〉</t>
         </is>
       </c>
       <c r="C2269" s="1" t="inlineStr">
@@ -73021,7 +73021,7 @@
       </c>
       <c r="D2269" s="1" t="inlineStr">
         <is>
-          <t>倾销；倾倒；倾泻；填埋</t>
+          <t>开始；着手；引导</t>
         </is>
       </c>
       <c r="E2269" s="1" t="inlineStr">
@@ -73107,7 +73107,7 @@
       </c>
       <c r="B2272" s="1" t="inlineStr">
         <is>
-          <t>[feːʁaɪnbaʁən] 使固定；修理；准备〈v.〉</t>
+          <t>[feːʁaɪnbaʁən] 约定；商定；达成协议〈v.〉</t>
         </is>
       </c>
       <c r="C2272" s="1" t="inlineStr">
@@ -73117,7 +73117,7 @@
       </c>
       <c r="D2272" s="1" t="inlineStr">
         <is>
-          <t>使固定；修理；准备</t>
+          <t>约定；商定；达成协议</t>
         </is>
       </c>
       <c r="E2272" s="1" t="inlineStr">
@@ -73171,7 +73171,7 @@
       </c>
       <c r="B2274" s="1" t="inlineStr">
         <is>
-          <t>[dʊʁçdaxt] 想法；思想；思维〈adj.〉</t>
+          <t>[dʊʁçdaxt] 深思熟虑的；经过周密考虑的〈adj.〉</t>
         </is>
       </c>
       <c r="C2274" s="1" t="inlineStr">
@@ -73181,7 +73181,7 @@
       </c>
       <c r="D2274" s="1" t="inlineStr">
         <is>
-          <t>想法；思想；思维</t>
+          <t>深思熟虑的；经过周密考虑的</t>
         </is>
       </c>
       <c r="E2274" s="1" t="inlineStr">
@@ -73395,7 +73395,7 @@
       </c>
       <c r="B2281" s="1" t="inlineStr">
         <is>
-          <t>[aʊsɡəbʊxt] 记载入册的；登记了的〈adv.〉</t>
+          <t>[aʊsɡəbʊxt] 订满的；客满的〈adv.〉</t>
         </is>
       </c>
       <c r="C2281" s="1" t="inlineStr">
@@ -73405,7 +73405,7 @@
       </c>
       <c r="D2281" s="1" t="inlineStr">
         <is>
-          <t>记载入册的；登记了的</t>
+          <t>订满的；客满的</t>
         </is>
       </c>
       <c r="E2281" s="1" t="inlineStr">
@@ -73619,7 +73619,7 @@
       </c>
       <c r="B2288" s="1" t="inlineStr">
         <is>
-          <t>[kɔʁʊpt] 弯曲的〈adv.〉</t>
+          <t>[kɔʁʊpt] 腐败的；贪污的〈adv.〉</t>
         </is>
       </c>
       <c r="C2288" s="1" t="inlineStr">
@@ -73629,7 +73629,7 @@
       </c>
       <c r="D2288" s="1" t="inlineStr">
         <is>
-          <t>弯曲的</t>
+          <t>腐败的；贪污的</t>
         </is>
       </c>
       <c r="E2288" s="1" t="inlineStr">
@@ -73715,12 +73715,12 @@
       </c>
       <c r="B2291" s="1" t="inlineStr">
         <is>
-          <t>[neːfada] 内华达〈n.〉</t>
+          <t>[neːvada] 内华达〈n.〉</t>
         </is>
       </c>
       <c r="C2291" s="1" t="inlineStr">
         <is>
-          <t>neːfada</t>
+          <t>neːvada</t>
         </is>
       </c>
       <c r="D2291" s="1" t="inlineStr">
@@ -73907,7 +73907,7 @@
       </c>
       <c r="B2297" s="1" t="inlineStr">
         <is>
-          <t>[bʏʁdə] 猴子；猿〈n.f.〉</t>
+          <t>[bʏʁdə] 负担；重担〈n.f.〉</t>
         </is>
       </c>
       <c r="C2297" s="1" t="inlineStr">
@@ -73917,7 +73917,7 @@
       </c>
       <c r="D2297" s="1" t="inlineStr">
         <is>
-          <t>猴子；猿</t>
+          <t>负担；重担</t>
         </is>
       </c>
       <c r="E2297" s="1" t="inlineStr">
@@ -74195,7 +74195,7 @@
       </c>
       <c r="B2306" s="1" t="inlineStr">
         <is>
-          <t>[tʁɛpənhaʊs] 楼梯；梯子〈n.〉</t>
+          <t>[tʁɛpənhaʊs] 楼梯间；楼梯井〈n.〉</t>
         </is>
       </c>
       <c r="C2306" s="1" t="inlineStr">
@@ -74205,7 +74205,7 @@
       </c>
       <c r="D2306" s="1" t="inlineStr">
         <is>
-          <t>楼梯；梯子</t>
+          <t>楼梯间；楼梯井</t>
         </is>
       </c>
       <c r="E2306" s="1" t="inlineStr">
@@ -74227,7 +74227,7 @@
       </c>
       <c r="B2307" s="1" t="inlineStr">
         <is>
-          <t>[noːtiːʁən] 注意；布告；通知〈v.〉</t>
+          <t>[noːtiːʁən] 记下；记录；写下〈v.〉</t>
         </is>
       </c>
       <c r="C2307" s="1" t="inlineStr">
@@ -74237,7 +74237,7 @@
       </c>
       <c r="D2307" s="1" t="inlineStr">
         <is>
-          <t>注意；布告；通知</t>
+          <t>记下；记录；写下</t>
         </is>
       </c>
       <c r="E2307" s="1" t="inlineStr">
@@ -74259,7 +74259,7 @@
       </c>
       <c r="B2308" s="1" t="inlineStr">
         <is>
-          <t>[ɛʁvɪdɐn] 回来；返回；来回票〈v.〉</t>
+          <t>[ɛʁvɪdɐn] 回答；答复；回应〈v.〉</t>
         </is>
       </c>
       <c r="C2308" s="1" t="inlineStr">
@@ -74269,7 +74269,7 @@
       </c>
       <c r="D2308" s="1" t="inlineStr">
         <is>
-          <t>回来；返回；来回票</t>
+          <t>回答；答复；回应</t>
         </is>
       </c>
       <c r="E2308" s="1" t="inlineStr">
@@ -74323,7 +74323,7 @@
       </c>
       <c r="B2310" s="1" t="inlineStr">
         <is>
-          <t>[loːkalɪziːʁən] 极小之物；针尖；立锥之地〈v.〉</t>
+          <t>[loːkalɪziːʁən] 定位；确定…的位置；使局部化〈v.〉</t>
         </is>
       </c>
       <c r="C2310" s="1" t="inlineStr">
@@ -74333,7 +74333,7 @@
       </c>
       <c r="D2310" s="1" t="inlineStr">
         <is>
-          <t>极小之物；针尖；立锥之地</t>
+          <t>定位；确定…的位置；使局部化</t>
         </is>
       </c>
       <c r="E2310" s="1" t="inlineStr">
@@ -74387,7 +74387,7 @@
       </c>
       <c r="B2312" s="1" t="inlineStr">
         <is>
-          <t>[hœkstɐ] 紧急状况〈adv.〉</t>
+          <t>[hœkstɐ] 最高的〈adj.〉〈adv.〉</t>
         </is>
       </c>
       <c r="C2312" s="1" t="inlineStr">
@@ -74397,7 +74397,7 @@
       </c>
       <c r="D2312" s="1" t="inlineStr">
         <is>
-          <t>紧急状况</t>
+          <t>最高的〈adj.〉</t>
         </is>
       </c>
       <c r="E2312" s="1" t="inlineStr">
@@ -74867,7 +74867,7 @@
       </c>
       <c r="B2327" s="1" t="inlineStr">
         <is>
-          <t>[tʁaːp] 策马小跑〈n.m.〉</t>
+          <t>[tʁaːp] 小跑；（马的）快步〈n.m.〉</t>
         </is>
       </c>
       <c r="C2327" s="1" t="inlineStr">
@@ -74877,7 +74877,7 @@
       </c>
       <c r="D2327" s="1" t="inlineStr">
         <is>
-          <t>策马小跑</t>
+          <t>小跑；（马的）快步</t>
         </is>
       </c>
       <c r="E2327" s="1" t="inlineStr">
@@ -74899,17 +74899,17 @@
       </c>
       <c r="B2328" s="1" t="inlineStr">
         <is>
-          <t>[ɡʁɛaːt] 大堡礁〈n.〉</t>
+          <t>[ɡʁeːt] 非德语词条；德语中无此词（大堡礁为 das Great Barrier Reef）〈n.〉</t>
         </is>
       </c>
       <c r="C2328" s="1" t="inlineStr">
         <is>
-          <t>ɡʁɛaːt</t>
+          <t>ɡʁeːt</t>
         </is>
       </c>
       <c r="D2328" s="1" t="inlineStr">
         <is>
-          <t>大堡礁</t>
+          <t>非德语词条；德语中无此词（大堡礁为 das Great Barrier Reef）</t>
         </is>
       </c>
       <c r="E2328" s="1" t="inlineStr">
@@ -75027,7 +75027,7 @@
       </c>
       <c r="B2332" s="1" t="inlineStr">
         <is>
-          <t>[ʃɛnkəl] 武器；军事行动；军械〈n.〉</t>
+          <t>[ʃɛnkəl] 大腿；（圆规的）脚；（三角形的）腰〈n.〉</t>
         </is>
       </c>
       <c r="C2332" s="1" t="inlineStr">
@@ -75037,7 +75037,7 @@
       </c>
       <c r="D2332" s="1" t="inlineStr">
         <is>
-          <t>武器；军事行动；军械</t>
+          <t>大腿；（圆规的）脚；（三角形的）腰</t>
         </is>
       </c>
       <c r="E2332" s="1" t="inlineStr">
@@ -75731,7 +75731,7 @@
       </c>
       <c r="B2354" s="1" t="inlineStr">
         <is>
-          <t>[tʁɔʏɐ] 伙伴；插袋〈adv.〉</t>
+          <t>[tʁɔʏɐ] 忠实的；忠诚的；忠心的〈adv.〉</t>
         </is>
       </c>
       <c r="C2354" s="1" t="inlineStr">
@@ -75741,7 +75741,7 @@
       </c>
       <c r="D2354" s="1" t="inlineStr">
         <is>
-          <t>伙伴；插袋</t>
+          <t>忠实的；忠诚的；忠心的</t>
         </is>
       </c>
       <c r="E2354" s="1" t="inlineStr">
@@ -75795,7 +75795,7 @@
       </c>
       <c r="B2356" s="1" t="inlineStr">
         <is>
-          <t>[ʃpʁaxlɔs] 不会说话的；哑的；说不出话的〈adj.〉</t>
+          <t>[ʃpʁaxlɔs] 说不出话的；无言的；惊呆的〈adj.〉〈adj.〉</t>
         </is>
       </c>
       <c r="C2356" s="1" t="inlineStr">
@@ -75805,7 +75805,7 @@
       </c>
       <c r="D2356" s="1" t="inlineStr">
         <is>
-          <t>不会说话的；哑的；说不出话的</t>
+          <t>说不出话的；无言的；惊呆的〈adj.〉</t>
         </is>
       </c>
       <c r="E2356" s="1" t="inlineStr">
@@ -75859,7 +75859,7 @@
       </c>
       <c r="B2358" s="1" t="inlineStr">
         <is>
-          <t>[loːɡɪʃə] 推断；推理；结论〈adv.〉</t>
+          <t>[loːɡɪʃə] 逻辑的；合乎逻辑的〈adv.〉</t>
         </is>
       </c>
       <c r="C2358" s="1" t="inlineStr">
@@ -75869,7 +75869,7 @@
       </c>
       <c r="D2358" s="1" t="inlineStr">
         <is>
-          <t>推断；推理；结论</t>
+          <t>逻辑的；合乎逻辑的</t>
         </is>
       </c>
       <c r="E2358" s="1" t="inlineStr">
@@ -75923,7 +75923,7 @@
       </c>
       <c r="B2360" s="1" t="inlineStr">
         <is>
-          <t>[bɪɔlɔɡiː] 生物学；生物〈n.f.〉</t>
+          <t>[bɪɔlɔɡiː] 生物学〈n.f.〉〈n.f.〉</t>
         </is>
       </c>
       <c r="C2360" s="1" t="inlineStr">
@@ -75933,7 +75933,7 @@
       </c>
       <c r="D2360" s="1" t="inlineStr">
         <is>
-          <t>生物学；生物</t>
+          <t>生物学〈n.f.〉</t>
         </is>
       </c>
       <c r="E2360" s="1" t="inlineStr">
@@ -75987,12 +75987,12 @@
       </c>
       <c r="B2362" s="1" t="inlineStr">
         <is>
-          <t>[bɛɡʁʏsʊnk] 欢迎；迎接；乐于接受〈n.f.〉</t>
+          <t>[bɛɡʁʏsʊŋ] 欢迎；迎接；乐于接受〈n.f.〉</t>
         </is>
       </c>
       <c r="C2362" s="1" t="inlineStr">
         <is>
-          <t>bɛɡʁʏsʊnk</t>
+          <t>bɛɡʁʏsʊŋ</t>
         </is>
       </c>
       <c r="D2362" s="1" t="inlineStr">
@@ -76083,7 +76083,7 @@
       </c>
       <c r="B2365" s="1" t="inlineStr">
         <is>
-          <t>[ʊnɡəfɛːʁliːç] 保险箱；可靠的〈adj.〉</t>
+          <t>[ʊnɡəfɛːʁliːç] 无危险的；无害的〈adj.〉</t>
         </is>
       </c>
       <c r="C2365" s="1" t="inlineStr">
@@ -76093,7 +76093,7 @@
       </c>
       <c r="D2365" s="1" t="inlineStr">
         <is>
-          <t>保险箱；可靠的</t>
+          <t>无危险的；无害的</t>
         </is>
       </c>
       <c r="E2365" s="1" t="inlineStr">
@@ -76243,7 +76243,7 @@
       </c>
       <c r="B2370" s="1" t="inlineStr">
         <is>
-          <t>[poːlɪt͡saɪaʁbaɪt] 警察；警察当局〈n.f.〉</t>
+          <t>[poːlɪt͡saɪaʁbaɪt] 警务工作；侦查工作〈n.f.〉</t>
         </is>
       </c>
       <c r="C2370" s="1" t="inlineStr">
@@ -76253,7 +76253,7 @@
       </c>
       <c r="D2370" s="1" t="inlineStr">
         <is>
-          <t>警察；警察当局</t>
+          <t>警务工作；侦查工作</t>
         </is>
       </c>
       <c r="E2370" s="1" t="inlineStr">
@@ -76467,7 +76467,7 @@
       </c>
       <c r="B2377" s="1" t="inlineStr">
         <is>
-          <t>[beːtɔʏbən] 使聋；变聋〈v.〉</t>
+          <t>[beːtɔʏbən] 使麻木；使昏迷；麻醉〈v.〉</t>
         </is>
       </c>
       <c r="C2377" s="1" t="inlineStr">
@@ -76477,7 +76477,7 @@
       </c>
       <c r="D2377" s="1" t="inlineStr">
         <is>
-          <t>使聋；变聋</t>
+          <t>使麻木；使昏迷；麻醉</t>
         </is>
       </c>
       <c r="E2377" s="1" t="inlineStr">
@@ -76531,7 +76531,7 @@
       </c>
       <c r="B2379" s="1" t="inlineStr">
         <is>
-          <t>[antɪkɐ] 指关节骨；骨〈adv.〉</t>
+          <t>[antɪkɐ] 古代的；古董的〈adv.〉</t>
         </is>
       </c>
       <c r="C2379" s="1" t="inlineStr">
@@ -76541,7 +76541,7 @@
       </c>
       <c r="D2379" s="1" t="inlineStr">
         <is>
-          <t>指关节骨；骨</t>
+          <t>古代的；古董的</t>
         </is>
       </c>
       <c r="E2379" s="1" t="inlineStr">
@@ -76563,7 +76563,7 @@
       </c>
       <c r="B2380" s="1" t="inlineStr">
         <is>
-          <t>[mɪkʁɔvələ] 微波〈n.f.〉</t>
+          <t>[mɪkʁɔvələ] 微波；微波炉〈n.f.〉</t>
         </is>
       </c>
       <c r="C2380" s="1" t="inlineStr">
@@ -76573,7 +76573,7 @@
       </c>
       <c r="D2380" s="1" t="inlineStr">
         <is>
-          <t>微波</t>
+          <t>微波；微波炉</t>
         </is>
       </c>
       <c r="E2380" s="1" t="inlineStr">
@@ -76659,7 +76659,7 @@
       </c>
       <c r="B2383" s="1" t="inlineStr">
         <is>
-          <t>[aʊzʏbən] 强烈呼吁〈n.〉</t>
+          <t>[aʊzʏbən] 行使；施加；从事〈n.〉</t>
         </is>
       </c>
       <c r="C2383" s="1" t="inlineStr">
@@ -76669,7 +76669,7 @@
       </c>
       <c r="D2383" s="1" t="inlineStr">
         <is>
-          <t>强烈呼吁</t>
+          <t>行使；施加；从事</t>
         </is>
       </c>
       <c r="E2383" s="1" t="inlineStr">
@@ -76755,7 +76755,7 @@
       </c>
       <c r="B2386" s="1" t="inlineStr">
         <is>
-          <t>[ʃaʊspiːl] 引人羡慕的东西；景象；眼镜〈n.〉</t>
+          <t>[ʃaʊspiːl] 戏剧；话剧；景象；场面〈n.〉</t>
         </is>
       </c>
       <c r="C2386" s="1" t="inlineStr">
@@ -76765,7 +76765,7 @@
       </c>
       <c r="D2386" s="1" t="inlineStr">
         <is>
-          <t>引人羡慕的东西；景象；眼镜</t>
+          <t>戏剧；话剧；景象；场面</t>
         </is>
       </c>
       <c r="E2386" s="1" t="inlineStr">
@@ -76851,7 +76851,7 @@
       </c>
       <c r="B2389" s="1" t="inlineStr">
         <is>
-          <t>[blaɪstɪft] 铅笔；色笔；眉笔〈n.m.〉</t>
+          <t>[blaɪstɪft] 铅笔〈n.m.〉〈n.m.〉</t>
         </is>
       </c>
       <c r="C2389" s="1" t="inlineStr">
@@ -76861,7 +76861,7 @@
       </c>
       <c r="D2389" s="1" t="inlineStr">
         <is>
-          <t>铅笔；色笔；眉笔</t>
+          <t>铅笔〈n.m.〉</t>
         </is>
       </c>
       <c r="E2389" s="1" t="inlineStr">
@@ -77011,7 +77011,7 @@
       </c>
       <c r="B2394" s="1" t="inlineStr">
         <is>
-          <t>[ɡɛbʁant] 因祸得福〈adj.〉</t>
+          <t>[ɡɛbʁant] brennen 的过去分词；烧过的；烤制的〈adj.（分词）〉〈adj.〉</t>
         </is>
       </c>
       <c r="C2394" s="1" t="inlineStr">
@@ -77021,7 +77021,7 @@
       </c>
       <c r="D2394" s="1" t="inlineStr">
         <is>
-          <t>因祸得福</t>
+          <t>brennen 的过去分词；烧过的；烤制的〈adj.（分词）〉</t>
         </is>
       </c>
       <c r="E2394" s="1" t="inlineStr">
@@ -77171,12 +77171,12 @@
       </c>
       <c r="B2399" s="1" t="inlineStr">
         <is>
-          <t>[pʊt͡st͡slə] 拼图〈n.〉</t>
+          <t>[pʊt͡slə] 拼图〈n.〉</t>
         </is>
       </c>
       <c r="C2399" s="1" t="inlineStr">
         <is>
-          <t>pʊt͡st͡slə</t>
+          <t>pʊt͡slə</t>
         </is>
       </c>
       <c r="D2399" s="1" t="inlineStr">
